--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mots" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liens" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Référence" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +29,33 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16809,7 +16835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.796875" customWidth="1" min="1" max="2"/>
@@ -16824,6 +16850,36 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>mot_2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mot_3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mot_4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mot_5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>mot_6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mot_7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mot_8</t>
         </is>
       </c>
     </row>
@@ -17856,4 +17912,7505 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I206"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>📋 Validation des liens</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Total erreurs (✗) :</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>COUNTIF(B7:I206,"✗*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Légende : ✓ = trouvé dans la feuille Mots,  ✗ = introuvable (faute de frappe ou mot absent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Liens ligne</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>mot_1</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>mot_2</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>mot_3</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>mot_4</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>mot_5</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>mot_6</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>mot_7</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>mot_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>IF(Liens!A2="","",IF(COUNTIF(Mots!B:B,Liens!A2)&gt;0,"✓ "&amp;Liens!A2,"✗ "&amp;Liens!A2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>IF(Liens!B2="","",IF(COUNTIF(Mots!B:B,Liens!B2)&gt;0,"✓ "&amp;Liens!B2,"✗ "&amp;Liens!B2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IF(Liens!C2="","",IF(COUNTIF(Mots!B:B,Liens!C2)&gt;0,"✓ "&amp;Liens!C2,"✗ "&amp;Liens!C2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IF(Liens!D2="","",IF(COUNTIF(Mots!B:B,Liens!D2)&gt;0,"✓ "&amp;Liens!D2,"✗ "&amp;Liens!D2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IF(Liens!E2="","",IF(COUNTIF(Mots!B:B,Liens!E2)&gt;0,"✓ "&amp;Liens!E2,"✗ "&amp;Liens!E2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(Liens!F2="","",IF(COUNTIF(Mots!B:B,Liens!F2)&gt;0,"✓ "&amp;Liens!F2,"✗ "&amp;Liens!F2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IF(Liens!G2="","",IF(COUNTIF(Mots!B:B,Liens!G2)&gt;0,"✓ "&amp;Liens!G2,"✗ "&amp;Liens!G2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(Liens!H2="","",IF(COUNTIF(Mots!B:B,Liens!H2)&gt;0,"✓ "&amp;Liens!H2,"✗ "&amp;Liens!H2&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <f>IF(Liens!A3="","",IF(COUNTIF(Mots!B:B,Liens!A3)&gt;0,"✓ "&amp;Liens!A3,"✗ "&amp;Liens!A3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IF(Liens!B3="","",IF(COUNTIF(Mots!B:B,Liens!B3)&gt;0,"✓ "&amp;Liens!B3,"✗ "&amp;Liens!B3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF(Liens!C3="","",IF(COUNTIF(Mots!B:B,Liens!C3)&gt;0,"✓ "&amp;Liens!C3,"✗ "&amp;Liens!C3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IF(Liens!D3="","",IF(COUNTIF(Mots!B:B,Liens!D3)&gt;0,"✓ "&amp;Liens!D3,"✗ "&amp;Liens!D3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IF(Liens!E3="","",IF(COUNTIF(Mots!B:B,Liens!E3)&gt;0,"✓ "&amp;Liens!E3,"✗ "&amp;Liens!E3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(Liens!F3="","",IF(COUNTIF(Mots!B:B,Liens!F3)&gt;0,"✓ "&amp;Liens!F3,"✗ "&amp;Liens!F3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IF(Liens!G3="","",IF(COUNTIF(Mots!B:B,Liens!G3)&gt;0,"✓ "&amp;Liens!G3,"✗ "&amp;Liens!G3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(Liens!H3="","",IF(COUNTIF(Mots!B:B,Liens!H3)&gt;0,"✓ "&amp;Liens!H3,"✗ "&amp;Liens!H3&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <f>IF(Liens!A4="","",IF(COUNTIF(Mots!B:B,Liens!A4)&gt;0,"✓ "&amp;Liens!A4,"✗ "&amp;Liens!A4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF(Liens!B4="","",IF(COUNTIF(Mots!B:B,Liens!B4)&gt;0,"✓ "&amp;Liens!B4,"✗ "&amp;Liens!B4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF(Liens!C4="","",IF(COUNTIF(Mots!B:B,Liens!C4)&gt;0,"✓ "&amp;Liens!C4,"✗ "&amp;Liens!C4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>IF(Liens!D4="","",IF(COUNTIF(Mots!B:B,Liens!D4)&gt;0,"✓ "&amp;Liens!D4,"✗ "&amp;Liens!D4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>IF(Liens!E4="","",IF(COUNTIF(Mots!B:B,Liens!E4)&gt;0,"✓ "&amp;Liens!E4,"✗ "&amp;Liens!E4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(Liens!F4="","",IF(COUNTIF(Mots!B:B,Liens!F4)&gt;0,"✓ "&amp;Liens!F4,"✗ "&amp;Liens!F4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IF(Liens!G4="","",IF(COUNTIF(Mots!B:B,Liens!G4)&gt;0,"✓ "&amp;Liens!G4,"✗ "&amp;Liens!G4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(Liens!H4="","",IF(COUNTIF(Mots!B:B,Liens!H4)&gt;0,"✓ "&amp;Liens!H4,"✗ "&amp;Liens!H4&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <f>IF(Liens!A5="","",IF(COUNTIF(Mots!B:B,Liens!A5)&gt;0,"✓ "&amp;Liens!A5,"✗ "&amp;Liens!A5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>IF(Liens!B5="","",IF(COUNTIF(Mots!B:B,Liens!B5)&gt;0,"✓ "&amp;Liens!B5,"✗ "&amp;Liens!B5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IF(Liens!C5="","",IF(COUNTIF(Mots!B:B,Liens!C5)&gt;0,"✓ "&amp;Liens!C5,"✗ "&amp;Liens!C5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>IF(Liens!D5="","",IF(COUNTIF(Mots!B:B,Liens!D5)&gt;0,"✓ "&amp;Liens!D5,"✗ "&amp;Liens!D5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>IF(Liens!E5="","",IF(COUNTIF(Mots!B:B,Liens!E5)&gt;0,"✓ "&amp;Liens!E5,"✗ "&amp;Liens!E5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF(Liens!F5="","",IF(COUNTIF(Mots!B:B,Liens!F5)&gt;0,"✓ "&amp;Liens!F5,"✗ "&amp;Liens!F5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>IF(Liens!G5="","",IF(COUNTIF(Mots!B:B,Liens!G5)&gt;0,"✓ "&amp;Liens!G5,"✗ "&amp;Liens!G5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(Liens!H5="","",IF(COUNTIF(Mots!B:B,Liens!H5)&gt;0,"✓ "&amp;Liens!H5,"✗ "&amp;Liens!H5&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <f>IF(Liens!A6="","",IF(COUNTIF(Mots!B:B,Liens!A6)&gt;0,"✓ "&amp;Liens!A6,"✗ "&amp;Liens!A6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>IF(Liens!B6="","",IF(COUNTIF(Mots!B:B,Liens!B6)&gt;0,"✓ "&amp;Liens!B6,"✗ "&amp;Liens!B6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IF(Liens!C6="","",IF(COUNTIF(Mots!B:B,Liens!C6)&gt;0,"✓ "&amp;Liens!C6,"✗ "&amp;Liens!C6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>IF(Liens!D6="","",IF(COUNTIF(Mots!B:B,Liens!D6)&gt;0,"✓ "&amp;Liens!D6,"✗ "&amp;Liens!D6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IF(Liens!E6="","",IF(COUNTIF(Mots!B:B,Liens!E6)&gt;0,"✓ "&amp;Liens!E6,"✗ "&amp;Liens!E6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(Liens!F6="","",IF(COUNTIF(Mots!B:B,Liens!F6)&gt;0,"✓ "&amp;Liens!F6,"✗ "&amp;Liens!F6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>IF(Liens!G6="","",IF(COUNTIF(Mots!B:B,Liens!G6)&gt;0,"✓ "&amp;Liens!G6,"✗ "&amp;Liens!G6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(Liens!H6="","",IF(COUNTIF(Mots!B:B,Liens!H6)&gt;0,"✓ "&amp;Liens!H6,"✗ "&amp;Liens!H6&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <f>IF(Liens!A7="","",IF(COUNTIF(Mots!B:B,Liens!A7)&gt;0,"✓ "&amp;Liens!A7,"✗ "&amp;Liens!A7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>IF(Liens!B7="","",IF(COUNTIF(Mots!B:B,Liens!B7)&gt;0,"✓ "&amp;Liens!B7,"✗ "&amp;Liens!B7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IF(Liens!C7="","",IF(COUNTIF(Mots!B:B,Liens!C7)&gt;0,"✓ "&amp;Liens!C7,"✗ "&amp;Liens!C7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IF(Liens!D7="","",IF(COUNTIF(Mots!B:B,Liens!D7)&gt;0,"✓ "&amp;Liens!D7,"✗ "&amp;Liens!D7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IF(Liens!E7="","",IF(COUNTIF(Mots!B:B,Liens!E7)&gt;0,"✓ "&amp;Liens!E7,"✗ "&amp;Liens!E7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF(Liens!F7="","",IF(COUNTIF(Mots!B:B,Liens!F7)&gt;0,"✓ "&amp;Liens!F7,"✗ "&amp;Liens!F7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IF(Liens!G7="","",IF(COUNTIF(Mots!B:B,Liens!G7)&gt;0,"✓ "&amp;Liens!G7,"✗ "&amp;Liens!G7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(Liens!H7="","",IF(COUNTIF(Mots!B:B,Liens!H7)&gt;0,"✓ "&amp;Liens!H7,"✗ "&amp;Liens!H7&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <f>IF(Liens!A8="","",IF(COUNTIF(Mots!B:B,Liens!A8)&gt;0,"✓ "&amp;Liens!A8,"✗ "&amp;Liens!A8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>IF(Liens!B8="","",IF(COUNTIF(Mots!B:B,Liens!B8)&gt;0,"✓ "&amp;Liens!B8,"✗ "&amp;Liens!B8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IF(Liens!C8="","",IF(COUNTIF(Mots!B:B,Liens!C8)&gt;0,"✓ "&amp;Liens!C8,"✗ "&amp;Liens!C8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IF(Liens!D8="","",IF(COUNTIF(Mots!B:B,Liens!D8)&gt;0,"✓ "&amp;Liens!D8,"✗ "&amp;Liens!D8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>IF(Liens!E8="","",IF(COUNTIF(Mots!B:B,Liens!E8)&gt;0,"✓ "&amp;Liens!E8,"✗ "&amp;Liens!E8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(Liens!F8="","",IF(COUNTIF(Mots!B:B,Liens!F8)&gt;0,"✓ "&amp;Liens!F8,"✗ "&amp;Liens!F8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IF(Liens!G8="","",IF(COUNTIF(Mots!B:B,Liens!G8)&gt;0,"✓ "&amp;Liens!G8,"✗ "&amp;Liens!G8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(Liens!H8="","",IF(COUNTIF(Mots!B:B,Liens!H8)&gt;0,"✓ "&amp;Liens!H8,"✗ "&amp;Liens!H8&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <f>IF(Liens!A9="","",IF(COUNTIF(Mots!B:B,Liens!A9)&gt;0,"✓ "&amp;Liens!A9,"✗ "&amp;Liens!A9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IF(Liens!B9="","",IF(COUNTIF(Mots!B:B,Liens!B9)&gt;0,"✓ "&amp;Liens!B9,"✗ "&amp;Liens!B9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(Liens!C9="","",IF(COUNTIF(Mots!B:B,Liens!C9)&gt;0,"✓ "&amp;Liens!C9,"✗ "&amp;Liens!C9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>IF(Liens!D9="","",IF(COUNTIF(Mots!B:B,Liens!D9)&gt;0,"✓ "&amp;Liens!D9,"✗ "&amp;Liens!D9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>IF(Liens!E9="","",IF(COUNTIF(Mots!B:B,Liens!E9)&gt;0,"✓ "&amp;Liens!E9,"✗ "&amp;Liens!E9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(Liens!F9="","",IF(COUNTIF(Mots!B:B,Liens!F9)&gt;0,"✓ "&amp;Liens!F9,"✗ "&amp;Liens!F9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>IF(Liens!G9="","",IF(COUNTIF(Mots!B:B,Liens!G9)&gt;0,"✓ "&amp;Liens!G9,"✗ "&amp;Liens!G9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(Liens!H9="","",IF(COUNTIF(Mots!B:B,Liens!H9)&gt;0,"✓ "&amp;Liens!H9,"✗ "&amp;Liens!H9&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <f>IF(Liens!A10="","",IF(COUNTIF(Mots!B:B,Liens!A10)&gt;0,"✓ "&amp;Liens!A10,"✗ "&amp;Liens!A10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>IF(Liens!B10="","",IF(COUNTIF(Mots!B:B,Liens!B10)&gt;0,"✓ "&amp;Liens!B10,"✗ "&amp;Liens!B10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(Liens!C10="","",IF(COUNTIF(Mots!B:B,Liens!C10)&gt;0,"✓ "&amp;Liens!C10,"✗ "&amp;Liens!C10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(Liens!D10="","",IF(COUNTIF(Mots!B:B,Liens!D10)&gt;0,"✓ "&amp;Liens!D10,"✗ "&amp;Liens!D10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IF(Liens!E10="","",IF(COUNTIF(Mots!B:B,Liens!E10)&gt;0,"✓ "&amp;Liens!E10,"✗ "&amp;Liens!E10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(Liens!F10="","",IF(COUNTIF(Mots!B:B,Liens!F10)&gt;0,"✓ "&amp;Liens!F10,"✗ "&amp;Liens!F10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IF(Liens!G10="","",IF(COUNTIF(Mots!B:B,Liens!G10)&gt;0,"✓ "&amp;Liens!G10,"✗ "&amp;Liens!G10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(Liens!H10="","",IF(COUNTIF(Mots!B:B,Liens!H10)&gt;0,"✓ "&amp;Liens!H10,"✗ "&amp;Liens!H10&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <f>IF(Liens!A11="","",IF(COUNTIF(Mots!B:B,Liens!A11)&gt;0,"✓ "&amp;Liens!A11,"✗ "&amp;Liens!A11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>IF(Liens!B11="","",IF(COUNTIF(Mots!B:B,Liens!B11)&gt;0,"✓ "&amp;Liens!B11,"✗ "&amp;Liens!B11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IF(Liens!C11="","",IF(COUNTIF(Mots!B:B,Liens!C11)&gt;0,"✓ "&amp;Liens!C11,"✗ "&amp;Liens!C11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IF(Liens!D11="","",IF(COUNTIF(Mots!B:B,Liens!D11)&gt;0,"✓ "&amp;Liens!D11,"✗ "&amp;Liens!D11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>IF(Liens!E11="","",IF(COUNTIF(Mots!B:B,Liens!E11)&gt;0,"✓ "&amp;Liens!E11,"✗ "&amp;Liens!E11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF(Liens!F11="","",IF(COUNTIF(Mots!B:B,Liens!F11)&gt;0,"✓ "&amp;Liens!F11,"✗ "&amp;Liens!F11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IF(Liens!G11="","",IF(COUNTIF(Mots!B:B,Liens!G11)&gt;0,"✓ "&amp;Liens!G11,"✗ "&amp;Liens!G11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(Liens!H11="","",IF(COUNTIF(Mots!B:B,Liens!H11)&gt;0,"✓ "&amp;Liens!H11,"✗ "&amp;Liens!H11&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <f>IF(Liens!A12="","",IF(COUNTIF(Mots!B:B,Liens!A12)&gt;0,"✓ "&amp;Liens!A12,"✗ "&amp;Liens!A12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>IF(Liens!B12="","",IF(COUNTIF(Mots!B:B,Liens!B12)&gt;0,"✓ "&amp;Liens!B12,"✗ "&amp;Liens!B12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>IF(Liens!C12="","",IF(COUNTIF(Mots!B:B,Liens!C12)&gt;0,"✓ "&amp;Liens!C12,"✗ "&amp;Liens!C12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>IF(Liens!D12="","",IF(COUNTIF(Mots!B:B,Liens!D12)&gt;0,"✓ "&amp;Liens!D12,"✗ "&amp;Liens!D12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>IF(Liens!E12="","",IF(COUNTIF(Mots!B:B,Liens!E12)&gt;0,"✓ "&amp;Liens!E12,"✗ "&amp;Liens!E12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF(Liens!F12="","",IF(COUNTIF(Mots!B:B,Liens!F12)&gt;0,"✓ "&amp;Liens!F12,"✗ "&amp;Liens!F12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>IF(Liens!G12="","",IF(COUNTIF(Mots!B:B,Liens!G12)&gt;0,"✓ "&amp;Liens!G12,"✗ "&amp;Liens!G12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(Liens!H12="","",IF(COUNTIF(Mots!B:B,Liens!H12)&gt;0,"✓ "&amp;Liens!H12,"✗ "&amp;Liens!H12&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <f>IF(Liens!A13="","",IF(COUNTIF(Mots!B:B,Liens!A13)&gt;0,"✓ "&amp;Liens!A13,"✗ "&amp;Liens!A13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF(Liens!B13="","",IF(COUNTIF(Mots!B:B,Liens!B13)&gt;0,"✓ "&amp;Liens!B13,"✗ "&amp;Liens!B13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IF(Liens!C13="","",IF(COUNTIF(Mots!B:B,Liens!C13)&gt;0,"✓ "&amp;Liens!C13,"✗ "&amp;Liens!C13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>IF(Liens!D13="","",IF(COUNTIF(Mots!B:B,Liens!D13)&gt;0,"✓ "&amp;Liens!D13,"✗ "&amp;Liens!D13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>IF(Liens!E13="","",IF(COUNTIF(Mots!B:B,Liens!E13)&gt;0,"✓ "&amp;Liens!E13,"✗ "&amp;Liens!E13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(Liens!F13="","",IF(COUNTIF(Mots!B:B,Liens!F13)&gt;0,"✓ "&amp;Liens!F13,"✗ "&amp;Liens!F13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>IF(Liens!G13="","",IF(COUNTIF(Mots!B:B,Liens!G13)&gt;0,"✓ "&amp;Liens!G13,"✗ "&amp;Liens!G13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(Liens!H13="","",IF(COUNTIF(Mots!B:B,Liens!H13)&gt;0,"✓ "&amp;Liens!H13,"✗ "&amp;Liens!H13&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <f>IF(Liens!A14="","",IF(COUNTIF(Mots!B:B,Liens!A14)&gt;0,"✓ "&amp;Liens!A14,"✗ "&amp;Liens!A14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(Liens!B14="","",IF(COUNTIF(Mots!B:B,Liens!B14)&gt;0,"✓ "&amp;Liens!B14,"✗ "&amp;Liens!B14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>IF(Liens!C14="","",IF(COUNTIF(Mots!B:B,Liens!C14)&gt;0,"✓ "&amp;Liens!C14,"✗ "&amp;Liens!C14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>IF(Liens!D14="","",IF(COUNTIF(Mots!B:B,Liens!D14)&gt;0,"✓ "&amp;Liens!D14,"✗ "&amp;Liens!D14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>IF(Liens!E14="","",IF(COUNTIF(Mots!B:B,Liens!E14)&gt;0,"✓ "&amp;Liens!E14,"✗ "&amp;Liens!E14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF(Liens!F14="","",IF(COUNTIF(Mots!B:B,Liens!F14)&gt;0,"✓ "&amp;Liens!F14,"✗ "&amp;Liens!F14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>IF(Liens!G14="","",IF(COUNTIF(Mots!B:B,Liens!G14)&gt;0,"✓ "&amp;Liens!G14,"✗ "&amp;Liens!G14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(Liens!H14="","",IF(COUNTIF(Mots!B:B,Liens!H14)&gt;0,"✓ "&amp;Liens!H14,"✗ "&amp;Liens!H14&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <f>IF(Liens!A15="","",IF(COUNTIF(Mots!B:B,Liens!A15)&gt;0,"✓ "&amp;Liens!A15,"✗ "&amp;Liens!A15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>IF(Liens!B15="","",IF(COUNTIF(Mots!B:B,Liens!B15)&gt;0,"✓ "&amp;Liens!B15,"✗ "&amp;Liens!B15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>IF(Liens!C15="","",IF(COUNTIF(Mots!B:B,Liens!C15)&gt;0,"✓ "&amp;Liens!C15,"✗ "&amp;Liens!C15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>IF(Liens!D15="","",IF(COUNTIF(Mots!B:B,Liens!D15)&gt;0,"✓ "&amp;Liens!D15,"✗ "&amp;Liens!D15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>IF(Liens!E15="","",IF(COUNTIF(Mots!B:B,Liens!E15)&gt;0,"✓ "&amp;Liens!E15,"✗ "&amp;Liens!E15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(Liens!F15="","",IF(COUNTIF(Mots!B:B,Liens!F15)&gt;0,"✓ "&amp;Liens!F15,"✗ "&amp;Liens!F15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>IF(Liens!G15="","",IF(COUNTIF(Mots!B:B,Liens!G15)&gt;0,"✓ "&amp;Liens!G15,"✗ "&amp;Liens!G15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(Liens!H15="","",IF(COUNTIF(Mots!B:B,Liens!H15)&gt;0,"✓ "&amp;Liens!H15,"✗ "&amp;Liens!H15&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <f>IF(Liens!A16="","",IF(COUNTIF(Mots!B:B,Liens!A16)&gt;0,"✓ "&amp;Liens!A16,"✗ "&amp;Liens!A16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>IF(Liens!B16="","",IF(COUNTIF(Mots!B:B,Liens!B16)&gt;0,"✓ "&amp;Liens!B16,"✗ "&amp;Liens!B16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>IF(Liens!C16="","",IF(COUNTIF(Mots!B:B,Liens!C16)&gt;0,"✓ "&amp;Liens!C16,"✗ "&amp;Liens!C16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>IF(Liens!D16="","",IF(COUNTIF(Mots!B:B,Liens!D16)&gt;0,"✓ "&amp;Liens!D16,"✗ "&amp;Liens!D16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>IF(Liens!E16="","",IF(COUNTIF(Mots!B:B,Liens!E16)&gt;0,"✓ "&amp;Liens!E16,"✗ "&amp;Liens!E16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF(Liens!F16="","",IF(COUNTIF(Mots!B:B,Liens!F16)&gt;0,"✓ "&amp;Liens!F16,"✗ "&amp;Liens!F16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>IF(Liens!G16="","",IF(COUNTIF(Mots!B:B,Liens!G16)&gt;0,"✓ "&amp;Liens!G16,"✗ "&amp;Liens!G16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(Liens!H16="","",IF(COUNTIF(Mots!B:B,Liens!H16)&gt;0,"✓ "&amp;Liens!H16,"✗ "&amp;Liens!H16&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22">
+        <f>IF(Liens!A17="","",IF(COUNTIF(Mots!B:B,Liens!A17)&gt;0,"✓ "&amp;Liens!A17,"✗ "&amp;Liens!A17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>IF(Liens!B17="","",IF(COUNTIF(Mots!B:B,Liens!B17)&gt;0,"✓ "&amp;Liens!B17,"✗ "&amp;Liens!B17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>IF(Liens!C17="","",IF(COUNTIF(Mots!B:B,Liens!C17)&gt;0,"✓ "&amp;Liens!C17,"✗ "&amp;Liens!C17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>IF(Liens!D17="","",IF(COUNTIF(Mots!B:B,Liens!D17)&gt;0,"✓ "&amp;Liens!D17,"✗ "&amp;Liens!D17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>IF(Liens!E17="","",IF(COUNTIF(Mots!B:B,Liens!E17)&gt;0,"✓ "&amp;Liens!E17,"✗ "&amp;Liens!E17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(Liens!F17="","",IF(COUNTIF(Mots!B:B,Liens!F17)&gt;0,"✓ "&amp;Liens!F17,"✗ "&amp;Liens!F17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>IF(Liens!G17="","",IF(COUNTIF(Mots!B:B,Liens!G17)&gt;0,"✓ "&amp;Liens!G17,"✗ "&amp;Liens!G17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(Liens!H17="","",IF(COUNTIF(Mots!B:B,Liens!H17)&gt;0,"✓ "&amp;Liens!H17,"✗ "&amp;Liens!H17&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <f>IF(Liens!A18="","",IF(COUNTIF(Mots!B:B,Liens!A18)&gt;0,"✓ "&amp;Liens!A18,"✗ "&amp;Liens!A18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>IF(Liens!B18="","",IF(COUNTIF(Mots!B:B,Liens!B18)&gt;0,"✓ "&amp;Liens!B18,"✗ "&amp;Liens!B18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>IF(Liens!C18="","",IF(COUNTIF(Mots!B:B,Liens!C18)&gt;0,"✓ "&amp;Liens!C18,"✗ "&amp;Liens!C18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>IF(Liens!D18="","",IF(COUNTIF(Mots!B:B,Liens!D18)&gt;0,"✓ "&amp;Liens!D18,"✗ "&amp;Liens!D18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>IF(Liens!E18="","",IF(COUNTIF(Mots!B:B,Liens!E18)&gt;0,"✓ "&amp;Liens!E18,"✗ "&amp;Liens!E18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF(Liens!F18="","",IF(COUNTIF(Mots!B:B,Liens!F18)&gt;0,"✓ "&amp;Liens!F18,"✗ "&amp;Liens!F18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IF(Liens!G18="","",IF(COUNTIF(Mots!B:B,Liens!G18)&gt;0,"✓ "&amp;Liens!G18,"✗ "&amp;Liens!G18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(Liens!H18="","",IF(COUNTIF(Mots!B:B,Liens!H18)&gt;0,"✓ "&amp;Liens!H18,"✗ "&amp;Liens!H18&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <f>IF(Liens!A19="","",IF(COUNTIF(Mots!B:B,Liens!A19)&gt;0,"✓ "&amp;Liens!A19,"✗ "&amp;Liens!A19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IF(Liens!B19="","",IF(COUNTIF(Mots!B:B,Liens!B19)&gt;0,"✓ "&amp;Liens!B19,"✗ "&amp;Liens!B19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>IF(Liens!C19="","",IF(COUNTIF(Mots!B:B,Liens!C19)&gt;0,"✓ "&amp;Liens!C19,"✗ "&amp;Liens!C19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>IF(Liens!D19="","",IF(COUNTIF(Mots!B:B,Liens!D19)&gt;0,"✓ "&amp;Liens!D19,"✗ "&amp;Liens!D19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>IF(Liens!E19="","",IF(COUNTIF(Mots!B:B,Liens!E19)&gt;0,"✓ "&amp;Liens!E19,"✗ "&amp;Liens!E19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(Liens!F19="","",IF(COUNTIF(Mots!B:B,Liens!F19)&gt;0,"✓ "&amp;Liens!F19,"✗ "&amp;Liens!F19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IF(Liens!G19="","",IF(COUNTIF(Mots!B:B,Liens!G19)&gt;0,"✓ "&amp;Liens!G19,"✗ "&amp;Liens!G19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(Liens!H19="","",IF(COUNTIF(Mots!B:B,Liens!H19)&gt;0,"✓ "&amp;Liens!H19,"✗ "&amp;Liens!H19&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25">
+        <f>IF(Liens!A20="","",IF(COUNTIF(Mots!B:B,Liens!A20)&gt;0,"✓ "&amp;Liens!A20,"✗ "&amp;Liens!A20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>IF(Liens!B20="","",IF(COUNTIF(Mots!B:B,Liens!B20)&gt;0,"✓ "&amp;Liens!B20,"✗ "&amp;Liens!B20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>IF(Liens!C20="","",IF(COUNTIF(Mots!B:B,Liens!C20)&gt;0,"✓ "&amp;Liens!C20,"✗ "&amp;Liens!C20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>IF(Liens!D20="","",IF(COUNTIF(Mots!B:B,Liens!D20)&gt;0,"✓ "&amp;Liens!D20,"✗ "&amp;Liens!D20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>IF(Liens!E20="","",IF(COUNTIF(Mots!B:B,Liens!E20)&gt;0,"✓ "&amp;Liens!E20,"✗ "&amp;Liens!E20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(Liens!F20="","",IF(COUNTIF(Mots!B:B,Liens!F20)&gt;0,"✓ "&amp;Liens!F20,"✗ "&amp;Liens!F20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>IF(Liens!G20="","",IF(COUNTIF(Mots!B:B,Liens!G20)&gt;0,"✓ "&amp;Liens!G20,"✗ "&amp;Liens!G20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(Liens!H20="","",IF(COUNTIF(Mots!B:B,Liens!H20)&gt;0,"✓ "&amp;Liens!H20,"✗ "&amp;Liens!H20&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <f>IF(Liens!A21="","",IF(COUNTIF(Mots!B:B,Liens!A21)&gt;0,"✓ "&amp;Liens!A21,"✗ "&amp;Liens!A21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>IF(Liens!B21="","",IF(COUNTIF(Mots!B:B,Liens!B21)&gt;0,"✓ "&amp;Liens!B21,"✗ "&amp;Liens!B21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>IF(Liens!C21="","",IF(COUNTIF(Mots!B:B,Liens!C21)&gt;0,"✓ "&amp;Liens!C21,"✗ "&amp;Liens!C21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>IF(Liens!D21="","",IF(COUNTIF(Mots!B:B,Liens!D21)&gt;0,"✓ "&amp;Liens!D21,"✗ "&amp;Liens!D21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>IF(Liens!E21="","",IF(COUNTIF(Mots!B:B,Liens!E21)&gt;0,"✓ "&amp;Liens!E21,"✗ "&amp;Liens!E21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF(Liens!F21="","",IF(COUNTIF(Mots!B:B,Liens!F21)&gt;0,"✓ "&amp;Liens!F21,"✗ "&amp;Liens!F21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>IF(Liens!G21="","",IF(COUNTIF(Mots!B:B,Liens!G21)&gt;0,"✓ "&amp;Liens!G21,"✗ "&amp;Liens!G21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(Liens!H21="","",IF(COUNTIF(Mots!B:B,Liens!H21)&gt;0,"✓ "&amp;Liens!H21,"✗ "&amp;Liens!H21&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27">
+        <f>IF(Liens!A22="","",IF(COUNTIF(Mots!B:B,Liens!A22)&gt;0,"✓ "&amp;Liens!A22,"✗ "&amp;Liens!A22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>IF(Liens!B22="","",IF(COUNTIF(Mots!B:B,Liens!B22)&gt;0,"✓ "&amp;Liens!B22,"✗ "&amp;Liens!B22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>IF(Liens!C22="","",IF(COUNTIF(Mots!B:B,Liens!C22)&gt;0,"✓ "&amp;Liens!C22,"✗ "&amp;Liens!C22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>IF(Liens!D22="","",IF(COUNTIF(Mots!B:B,Liens!D22)&gt;0,"✓ "&amp;Liens!D22,"✗ "&amp;Liens!D22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F27">
+        <f>IF(Liens!E22="","",IF(COUNTIF(Mots!B:B,Liens!E22)&gt;0,"✓ "&amp;Liens!E22,"✗ "&amp;Liens!E22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF(Liens!F22="","",IF(COUNTIF(Mots!B:B,Liens!F22)&gt;0,"✓ "&amp;Liens!F22,"✗ "&amp;Liens!F22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>IF(Liens!G22="","",IF(COUNTIF(Mots!B:B,Liens!G22)&gt;0,"✓ "&amp;Liens!G22,"✗ "&amp;Liens!G22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(Liens!H22="","",IF(COUNTIF(Mots!B:B,Liens!H22)&gt;0,"✓ "&amp;Liens!H22,"✗ "&amp;Liens!H22&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28">
+        <f>IF(Liens!A23="","",IF(COUNTIF(Mots!B:B,Liens!A23)&gt;0,"✓ "&amp;Liens!A23,"✗ "&amp;Liens!A23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>IF(Liens!B23="","",IF(COUNTIF(Mots!B:B,Liens!B23)&gt;0,"✓ "&amp;Liens!B23,"✗ "&amp;Liens!B23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>IF(Liens!C23="","",IF(COUNTIF(Mots!B:B,Liens!C23)&gt;0,"✓ "&amp;Liens!C23,"✗ "&amp;Liens!C23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>IF(Liens!D23="","",IF(COUNTIF(Mots!B:B,Liens!D23)&gt;0,"✓ "&amp;Liens!D23,"✗ "&amp;Liens!D23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F28">
+        <f>IF(Liens!E23="","",IF(COUNTIF(Mots!B:B,Liens!E23)&gt;0,"✓ "&amp;Liens!E23,"✗ "&amp;Liens!E23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF(Liens!F23="","",IF(COUNTIF(Mots!B:B,Liens!F23)&gt;0,"✓ "&amp;Liens!F23,"✗ "&amp;Liens!F23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>IF(Liens!G23="","",IF(COUNTIF(Mots!B:B,Liens!G23)&gt;0,"✓ "&amp;Liens!G23,"✗ "&amp;Liens!G23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(Liens!H23="","",IF(COUNTIF(Mots!B:B,Liens!H23)&gt;0,"✓ "&amp;Liens!H23,"✗ "&amp;Liens!H23&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <f>IF(Liens!A24="","",IF(COUNTIF(Mots!B:B,Liens!A24)&gt;0,"✓ "&amp;Liens!A24,"✗ "&amp;Liens!A24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>IF(Liens!B24="","",IF(COUNTIF(Mots!B:B,Liens!B24)&gt;0,"✓ "&amp;Liens!B24,"✗ "&amp;Liens!B24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>IF(Liens!C24="","",IF(COUNTIF(Mots!B:B,Liens!C24)&gt;0,"✓ "&amp;Liens!C24,"✗ "&amp;Liens!C24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E29">
+        <f>IF(Liens!D24="","",IF(COUNTIF(Mots!B:B,Liens!D24)&gt;0,"✓ "&amp;Liens!D24,"✗ "&amp;Liens!D24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F29">
+        <f>IF(Liens!E24="","",IF(COUNTIF(Mots!B:B,Liens!E24)&gt;0,"✓ "&amp;Liens!E24,"✗ "&amp;Liens!E24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF(Liens!F24="","",IF(COUNTIF(Mots!B:B,Liens!F24)&gt;0,"✓ "&amp;Liens!F24,"✗ "&amp;Liens!F24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>IF(Liens!G24="","",IF(COUNTIF(Mots!B:B,Liens!G24)&gt;0,"✓ "&amp;Liens!G24,"✗ "&amp;Liens!G24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(Liens!H24="","",IF(COUNTIF(Mots!B:B,Liens!H24)&gt;0,"✓ "&amp;Liens!H24,"✗ "&amp;Liens!H24&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30">
+        <f>IF(Liens!A25="","",IF(COUNTIF(Mots!B:B,Liens!A25)&gt;0,"✓ "&amp;Liens!A25,"✗ "&amp;Liens!A25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>IF(Liens!B25="","",IF(COUNTIF(Mots!B:B,Liens!B25)&gt;0,"✓ "&amp;Liens!B25,"✗ "&amp;Liens!B25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>IF(Liens!C25="","",IF(COUNTIF(Mots!B:B,Liens!C25)&gt;0,"✓ "&amp;Liens!C25,"✗ "&amp;Liens!C25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>IF(Liens!D25="","",IF(COUNTIF(Mots!B:B,Liens!D25)&gt;0,"✓ "&amp;Liens!D25,"✗ "&amp;Liens!D25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F30">
+        <f>IF(Liens!E25="","",IF(COUNTIF(Mots!B:B,Liens!E25)&gt;0,"✓ "&amp;Liens!E25,"✗ "&amp;Liens!E25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF(Liens!F25="","",IF(COUNTIF(Mots!B:B,Liens!F25)&gt;0,"✓ "&amp;Liens!F25,"✗ "&amp;Liens!F25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>IF(Liens!G25="","",IF(COUNTIF(Mots!B:B,Liens!G25)&gt;0,"✓ "&amp;Liens!G25,"✗ "&amp;Liens!G25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(Liens!H25="","",IF(COUNTIF(Mots!B:B,Liens!H25)&gt;0,"✓ "&amp;Liens!H25,"✗ "&amp;Liens!H25&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <f>IF(Liens!A26="","",IF(COUNTIF(Mots!B:B,Liens!A26)&gt;0,"✓ "&amp;Liens!A26,"✗ "&amp;Liens!A26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>IF(Liens!B26="","",IF(COUNTIF(Mots!B:B,Liens!B26)&gt;0,"✓ "&amp;Liens!B26,"✗ "&amp;Liens!B26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>IF(Liens!C26="","",IF(COUNTIF(Mots!B:B,Liens!C26)&gt;0,"✓ "&amp;Liens!C26,"✗ "&amp;Liens!C26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>IF(Liens!D26="","",IF(COUNTIF(Mots!B:B,Liens!D26)&gt;0,"✓ "&amp;Liens!D26,"✗ "&amp;Liens!D26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F31">
+        <f>IF(Liens!E26="","",IF(COUNTIF(Mots!B:B,Liens!E26)&gt;0,"✓ "&amp;Liens!E26,"✗ "&amp;Liens!E26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>IF(Liens!F26="","",IF(COUNTIF(Mots!B:B,Liens!F26)&gt;0,"✓ "&amp;Liens!F26,"✗ "&amp;Liens!F26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>IF(Liens!G26="","",IF(COUNTIF(Mots!B:B,Liens!G26)&gt;0,"✓ "&amp;Liens!G26,"✗ "&amp;Liens!G26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>IF(Liens!H26="","",IF(COUNTIF(Mots!B:B,Liens!H26)&gt;0,"✓ "&amp;Liens!H26,"✗ "&amp;Liens!H26&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32">
+        <f>IF(Liens!A27="","",IF(COUNTIF(Mots!B:B,Liens!A27)&gt;0,"✓ "&amp;Liens!A27,"✗ "&amp;Liens!A27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>IF(Liens!B27="","",IF(COUNTIF(Mots!B:B,Liens!B27)&gt;0,"✓ "&amp;Liens!B27,"✗ "&amp;Liens!B27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>IF(Liens!C27="","",IF(COUNTIF(Mots!B:B,Liens!C27)&gt;0,"✓ "&amp;Liens!C27,"✗ "&amp;Liens!C27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>IF(Liens!D27="","",IF(COUNTIF(Mots!B:B,Liens!D27)&gt;0,"✓ "&amp;Liens!D27,"✗ "&amp;Liens!D27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>IF(Liens!E27="","",IF(COUNTIF(Mots!B:B,Liens!E27)&gt;0,"✓ "&amp;Liens!E27,"✗ "&amp;Liens!E27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF(Liens!F27="","",IF(COUNTIF(Mots!B:B,Liens!F27)&gt;0,"✓ "&amp;Liens!F27,"✗ "&amp;Liens!F27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>IF(Liens!G27="","",IF(COUNTIF(Mots!B:B,Liens!G27)&gt;0,"✓ "&amp;Liens!G27,"✗ "&amp;Liens!G27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>IF(Liens!H27="","",IF(COUNTIF(Mots!B:B,Liens!H27)&gt;0,"✓ "&amp;Liens!H27,"✗ "&amp;Liens!H27&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33">
+        <f>IF(Liens!A28="","",IF(COUNTIF(Mots!B:B,Liens!A28)&gt;0,"✓ "&amp;Liens!A28,"✗ "&amp;Liens!A28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>IF(Liens!B28="","",IF(COUNTIF(Mots!B:B,Liens!B28)&gt;0,"✓ "&amp;Liens!B28,"✗ "&amp;Liens!B28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>IF(Liens!C28="","",IF(COUNTIF(Mots!B:B,Liens!C28)&gt;0,"✓ "&amp;Liens!C28,"✗ "&amp;Liens!C28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>IF(Liens!D28="","",IF(COUNTIF(Mots!B:B,Liens!D28)&gt;0,"✓ "&amp;Liens!D28,"✗ "&amp;Liens!D28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>IF(Liens!E28="","",IF(COUNTIF(Mots!B:B,Liens!E28)&gt;0,"✓ "&amp;Liens!E28,"✗ "&amp;Liens!E28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF(Liens!F28="","",IF(COUNTIF(Mots!B:B,Liens!F28)&gt;0,"✓ "&amp;Liens!F28,"✗ "&amp;Liens!F28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>IF(Liens!G28="","",IF(COUNTIF(Mots!B:B,Liens!G28)&gt;0,"✓ "&amp;Liens!G28,"✗ "&amp;Liens!G28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>IF(Liens!H28="","",IF(COUNTIF(Mots!B:B,Liens!H28)&gt;0,"✓ "&amp;Liens!H28,"✗ "&amp;Liens!H28&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34">
+        <f>IF(Liens!A29="","",IF(COUNTIF(Mots!B:B,Liens!A29)&gt;0,"✓ "&amp;Liens!A29,"✗ "&amp;Liens!A29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>IF(Liens!B29="","",IF(COUNTIF(Mots!B:B,Liens!B29)&gt;0,"✓ "&amp;Liens!B29,"✗ "&amp;Liens!B29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>IF(Liens!C29="","",IF(COUNTIF(Mots!B:B,Liens!C29)&gt;0,"✓ "&amp;Liens!C29,"✗ "&amp;Liens!C29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>IF(Liens!D29="","",IF(COUNTIF(Mots!B:B,Liens!D29)&gt;0,"✓ "&amp;Liens!D29,"✗ "&amp;Liens!D29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>IF(Liens!E29="","",IF(COUNTIF(Mots!B:B,Liens!E29)&gt;0,"✓ "&amp;Liens!E29,"✗ "&amp;Liens!E29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF(Liens!F29="","",IF(COUNTIF(Mots!B:B,Liens!F29)&gt;0,"✓ "&amp;Liens!F29,"✗ "&amp;Liens!F29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>IF(Liens!G29="","",IF(COUNTIF(Mots!B:B,Liens!G29)&gt;0,"✓ "&amp;Liens!G29,"✗ "&amp;Liens!G29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>IF(Liens!H29="","",IF(COUNTIF(Mots!B:B,Liens!H29)&gt;0,"✓ "&amp;Liens!H29,"✗ "&amp;Liens!H29&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35">
+        <f>IF(Liens!A30="","",IF(COUNTIF(Mots!B:B,Liens!A30)&gt;0,"✓ "&amp;Liens!A30,"✗ "&amp;Liens!A30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>IF(Liens!B30="","",IF(COUNTIF(Mots!B:B,Liens!B30)&gt;0,"✓ "&amp;Liens!B30,"✗ "&amp;Liens!B30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>IF(Liens!C30="","",IF(COUNTIF(Mots!B:B,Liens!C30)&gt;0,"✓ "&amp;Liens!C30,"✗ "&amp;Liens!C30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>IF(Liens!D30="","",IF(COUNTIF(Mots!B:B,Liens!D30)&gt;0,"✓ "&amp;Liens!D30,"✗ "&amp;Liens!D30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>IF(Liens!E30="","",IF(COUNTIF(Mots!B:B,Liens!E30)&gt;0,"✓ "&amp;Liens!E30,"✗ "&amp;Liens!E30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IF(Liens!F30="","",IF(COUNTIF(Mots!B:B,Liens!F30)&gt;0,"✓ "&amp;Liens!F30,"✗ "&amp;Liens!F30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>IF(Liens!G30="","",IF(COUNTIF(Mots!B:B,Liens!G30)&gt;0,"✓ "&amp;Liens!G30,"✗ "&amp;Liens!G30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>IF(Liens!H30="","",IF(COUNTIF(Mots!B:B,Liens!H30)&gt;0,"✓ "&amp;Liens!H30,"✗ "&amp;Liens!H30&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36">
+        <f>IF(Liens!A31="","",IF(COUNTIF(Mots!B:B,Liens!A31)&gt;0,"✓ "&amp;Liens!A31,"✗ "&amp;Liens!A31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>IF(Liens!B31="","",IF(COUNTIF(Mots!B:B,Liens!B31)&gt;0,"✓ "&amp;Liens!B31,"✗ "&amp;Liens!B31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D36">
+        <f>IF(Liens!C31="","",IF(COUNTIF(Mots!B:B,Liens!C31)&gt;0,"✓ "&amp;Liens!C31,"✗ "&amp;Liens!C31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>IF(Liens!D31="","",IF(COUNTIF(Mots!B:B,Liens!D31)&gt;0,"✓ "&amp;Liens!D31,"✗ "&amp;Liens!D31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>IF(Liens!E31="","",IF(COUNTIF(Mots!B:B,Liens!E31)&gt;0,"✓ "&amp;Liens!E31,"✗ "&amp;Liens!E31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>IF(Liens!F31="","",IF(COUNTIF(Mots!B:B,Liens!F31)&gt;0,"✓ "&amp;Liens!F31,"✗ "&amp;Liens!F31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>IF(Liens!G31="","",IF(COUNTIF(Mots!B:B,Liens!G31)&gt;0,"✓ "&amp;Liens!G31,"✗ "&amp;Liens!G31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>IF(Liens!H31="","",IF(COUNTIF(Mots!B:B,Liens!H31)&gt;0,"✓ "&amp;Liens!H31,"✗ "&amp;Liens!H31&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37">
+        <f>IF(Liens!A32="","",IF(COUNTIF(Mots!B:B,Liens!A32)&gt;0,"✓ "&amp;Liens!A32,"✗ "&amp;Liens!A32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>IF(Liens!B32="","",IF(COUNTIF(Mots!B:B,Liens!B32)&gt;0,"✓ "&amp;Liens!B32,"✗ "&amp;Liens!B32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>IF(Liens!C32="","",IF(COUNTIF(Mots!B:B,Liens!C32)&gt;0,"✓ "&amp;Liens!C32,"✗ "&amp;Liens!C32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>IF(Liens!D32="","",IF(COUNTIF(Mots!B:B,Liens!D32)&gt;0,"✓ "&amp;Liens!D32,"✗ "&amp;Liens!D32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>IF(Liens!E32="","",IF(COUNTIF(Mots!B:B,Liens!E32)&gt;0,"✓ "&amp;Liens!E32,"✗ "&amp;Liens!E32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>IF(Liens!F32="","",IF(COUNTIF(Mots!B:B,Liens!F32)&gt;0,"✓ "&amp;Liens!F32,"✗ "&amp;Liens!F32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(Liens!G32="","",IF(COUNTIF(Mots!B:B,Liens!G32)&gt;0,"✓ "&amp;Liens!G32,"✗ "&amp;Liens!G32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>IF(Liens!H32="","",IF(COUNTIF(Mots!B:B,Liens!H32)&gt;0,"✓ "&amp;Liens!H32,"✗ "&amp;Liens!H32&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38">
+        <f>IF(Liens!A33="","",IF(COUNTIF(Mots!B:B,Liens!A33)&gt;0,"✓ "&amp;Liens!A33,"✗ "&amp;Liens!A33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C38">
+        <f>IF(Liens!B33="","",IF(COUNTIF(Mots!B:B,Liens!B33)&gt;0,"✓ "&amp;Liens!B33,"✗ "&amp;Liens!B33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D38">
+        <f>IF(Liens!C33="","",IF(COUNTIF(Mots!B:B,Liens!C33)&gt;0,"✓ "&amp;Liens!C33,"✗ "&amp;Liens!C33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>IF(Liens!D33="","",IF(COUNTIF(Mots!B:B,Liens!D33)&gt;0,"✓ "&amp;Liens!D33,"✗ "&amp;Liens!D33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>IF(Liens!E33="","",IF(COUNTIF(Mots!B:B,Liens!E33)&gt;0,"✓ "&amp;Liens!E33,"✗ "&amp;Liens!E33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>IF(Liens!F33="","",IF(COUNTIF(Mots!B:B,Liens!F33)&gt;0,"✓ "&amp;Liens!F33,"✗ "&amp;Liens!F33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>IF(Liens!G33="","",IF(COUNTIF(Mots!B:B,Liens!G33)&gt;0,"✓ "&amp;Liens!G33,"✗ "&amp;Liens!G33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>IF(Liens!H33="","",IF(COUNTIF(Mots!B:B,Liens!H33)&gt;0,"✓ "&amp;Liens!H33,"✗ "&amp;Liens!H33&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39">
+        <f>IF(Liens!A34="","",IF(COUNTIF(Mots!B:B,Liens!A34)&gt;0,"✓ "&amp;Liens!A34,"✗ "&amp;Liens!A34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C39">
+        <f>IF(Liens!B34="","",IF(COUNTIF(Mots!B:B,Liens!B34)&gt;0,"✓ "&amp;Liens!B34,"✗ "&amp;Liens!B34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D39">
+        <f>IF(Liens!C34="","",IF(COUNTIF(Mots!B:B,Liens!C34)&gt;0,"✓ "&amp;Liens!C34,"✗ "&amp;Liens!C34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E39">
+        <f>IF(Liens!D34="","",IF(COUNTIF(Mots!B:B,Liens!D34)&gt;0,"✓ "&amp;Liens!D34,"✗ "&amp;Liens!D34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>IF(Liens!E34="","",IF(COUNTIF(Mots!B:B,Liens!E34)&gt;0,"✓ "&amp;Liens!E34,"✗ "&amp;Liens!E34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>IF(Liens!F34="","",IF(COUNTIF(Mots!B:B,Liens!F34)&gt;0,"✓ "&amp;Liens!F34,"✗ "&amp;Liens!F34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>IF(Liens!G34="","",IF(COUNTIF(Mots!B:B,Liens!G34)&gt;0,"✓ "&amp;Liens!G34,"✗ "&amp;Liens!G34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>IF(Liens!H34="","",IF(COUNTIF(Mots!B:B,Liens!H34)&gt;0,"✓ "&amp;Liens!H34,"✗ "&amp;Liens!H34&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40">
+        <f>IF(Liens!A35="","",IF(COUNTIF(Mots!B:B,Liens!A35)&gt;0,"✓ "&amp;Liens!A35,"✗ "&amp;Liens!A35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>IF(Liens!B35="","",IF(COUNTIF(Mots!B:B,Liens!B35)&gt;0,"✓ "&amp;Liens!B35,"✗ "&amp;Liens!B35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D40">
+        <f>IF(Liens!C35="","",IF(COUNTIF(Mots!B:B,Liens!C35)&gt;0,"✓ "&amp;Liens!C35,"✗ "&amp;Liens!C35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>IF(Liens!D35="","",IF(COUNTIF(Mots!B:B,Liens!D35)&gt;0,"✓ "&amp;Liens!D35,"✗ "&amp;Liens!D35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>IF(Liens!E35="","",IF(COUNTIF(Mots!B:B,Liens!E35)&gt;0,"✓ "&amp;Liens!E35,"✗ "&amp;Liens!E35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IF(Liens!F35="","",IF(COUNTIF(Mots!B:B,Liens!F35)&gt;0,"✓ "&amp;Liens!F35,"✗ "&amp;Liens!F35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>IF(Liens!G35="","",IF(COUNTIF(Mots!B:B,Liens!G35)&gt;0,"✓ "&amp;Liens!G35,"✗ "&amp;Liens!G35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>IF(Liens!H35="","",IF(COUNTIF(Mots!B:B,Liens!H35)&gt;0,"✓ "&amp;Liens!H35,"✗ "&amp;Liens!H35&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41">
+        <f>IF(Liens!A36="","",IF(COUNTIF(Mots!B:B,Liens!A36)&gt;0,"✓ "&amp;Liens!A36,"✗ "&amp;Liens!A36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>IF(Liens!B36="","",IF(COUNTIF(Mots!B:B,Liens!B36)&gt;0,"✓ "&amp;Liens!B36,"✗ "&amp;Liens!B36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D41">
+        <f>IF(Liens!C36="","",IF(COUNTIF(Mots!B:B,Liens!C36)&gt;0,"✓ "&amp;Liens!C36,"✗ "&amp;Liens!C36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>IF(Liens!D36="","",IF(COUNTIF(Mots!B:B,Liens!D36)&gt;0,"✓ "&amp;Liens!D36,"✗ "&amp;Liens!D36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>IF(Liens!E36="","",IF(COUNTIF(Mots!B:B,Liens!E36)&gt;0,"✓ "&amp;Liens!E36,"✗ "&amp;Liens!E36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>IF(Liens!F36="","",IF(COUNTIF(Mots!B:B,Liens!F36)&gt;0,"✓ "&amp;Liens!F36,"✗ "&amp;Liens!F36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>IF(Liens!G36="","",IF(COUNTIF(Mots!B:B,Liens!G36)&gt;0,"✓ "&amp;Liens!G36,"✗ "&amp;Liens!G36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>IF(Liens!H36="","",IF(COUNTIF(Mots!B:B,Liens!H36)&gt;0,"✓ "&amp;Liens!H36,"✗ "&amp;Liens!H36&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42">
+        <f>IF(Liens!A37="","",IF(COUNTIF(Mots!B:B,Liens!A37)&gt;0,"✓ "&amp;Liens!A37,"✗ "&amp;Liens!A37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C42">
+        <f>IF(Liens!B37="","",IF(COUNTIF(Mots!B:B,Liens!B37)&gt;0,"✓ "&amp;Liens!B37,"✗ "&amp;Liens!B37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D42">
+        <f>IF(Liens!C37="","",IF(COUNTIF(Mots!B:B,Liens!C37)&gt;0,"✓ "&amp;Liens!C37,"✗ "&amp;Liens!C37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>IF(Liens!D37="","",IF(COUNTIF(Mots!B:B,Liens!D37)&gt;0,"✓ "&amp;Liens!D37,"✗ "&amp;Liens!D37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>IF(Liens!E37="","",IF(COUNTIF(Mots!B:B,Liens!E37)&gt;0,"✓ "&amp;Liens!E37,"✗ "&amp;Liens!E37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IF(Liens!F37="","",IF(COUNTIF(Mots!B:B,Liens!F37)&gt;0,"✓ "&amp;Liens!F37,"✗ "&amp;Liens!F37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>IF(Liens!G37="","",IF(COUNTIF(Mots!B:B,Liens!G37)&gt;0,"✓ "&amp;Liens!G37,"✗ "&amp;Liens!G37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I42">
+        <f>IF(Liens!H37="","",IF(COUNTIF(Mots!B:B,Liens!H37)&gt;0,"✓ "&amp;Liens!H37,"✗ "&amp;Liens!H37&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43">
+        <f>IF(Liens!A38="","",IF(COUNTIF(Mots!B:B,Liens!A38)&gt;0,"✓ "&amp;Liens!A38,"✗ "&amp;Liens!A38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C43">
+        <f>IF(Liens!B38="","",IF(COUNTIF(Mots!B:B,Liens!B38)&gt;0,"✓ "&amp;Liens!B38,"✗ "&amp;Liens!B38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D43">
+        <f>IF(Liens!C38="","",IF(COUNTIF(Mots!B:B,Liens!C38)&gt;0,"✓ "&amp;Liens!C38,"✗ "&amp;Liens!C38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E43">
+        <f>IF(Liens!D38="","",IF(COUNTIF(Mots!B:B,Liens!D38)&gt;0,"✓ "&amp;Liens!D38,"✗ "&amp;Liens!D38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F43">
+        <f>IF(Liens!E38="","",IF(COUNTIF(Mots!B:B,Liens!E38)&gt;0,"✓ "&amp;Liens!E38,"✗ "&amp;Liens!E38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>IF(Liens!F38="","",IF(COUNTIF(Mots!B:B,Liens!F38)&gt;0,"✓ "&amp;Liens!F38,"✗ "&amp;Liens!F38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>IF(Liens!G38="","",IF(COUNTIF(Mots!B:B,Liens!G38)&gt;0,"✓ "&amp;Liens!G38,"✗ "&amp;Liens!G38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I43">
+        <f>IF(Liens!H38="","",IF(COUNTIF(Mots!B:B,Liens!H38)&gt;0,"✓ "&amp;Liens!H38,"✗ "&amp;Liens!H38&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44">
+        <f>IF(Liens!A39="","",IF(COUNTIF(Mots!B:B,Liens!A39)&gt;0,"✓ "&amp;Liens!A39,"✗ "&amp;Liens!A39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C44">
+        <f>IF(Liens!B39="","",IF(COUNTIF(Mots!B:B,Liens!B39)&gt;0,"✓ "&amp;Liens!B39,"✗ "&amp;Liens!B39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D44">
+        <f>IF(Liens!C39="","",IF(COUNTIF(Mots!B:B,Liens!C39)&gt;0,"✓ "&amp;Liens!C39,"✗ "&amp;Liens!C39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E44">
+        <f>IF(Liens!D39="","",IF(COUNTIF(Mots!B:B,Liens!D39)&gt;0,"✓ "&amp;Liens!D39,"✗ "&amp;Liens!D39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F44">
+        <f>IF(Liens!E39="","",IF(COUNTIF(Mots!B:B,Liens!E39)&gt;0,"✓ "&amp;Liens!E39,"✗ "&amp;Liens!E39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>IF(Liens!F39="","",IF(COUNTIF(Mots!B:B,Liens!F39)&gt;0,"✓ "&amp;Liens!F39,"✗ "&amp;Liens!F39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H44">
+        <f>IF(Liens!G39="","",IF(COUNTIF(Mots!B:B,Liens!G39)&gt;0,"✓ "&amp;Liens!G39,"✗ "&amp;Liens!G39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I44">
+        <f>IF(Liens!H39="","",IF(COUNTIF(Mots!B:B,Liens!H39)&gt;0,"✓ "&amp;Liens!H39,"✗ "&amp;Liens!H39&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45">
+        <f>IF(Liens!A40="","",IF(COUNTIF(Mots!B:B,Liens!A40)&gt;0,"✓ "&amp;Liens!A40,"✗ "&amp;Liens!A40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C45">
+        <f>IF(Liens!B40="","",IF(COUNTIF(Mots!B:B,Liens!B40)&gt;0,"✓ "&amp;Liens!B40,"✗ "&amp;Liens!B40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>IF(Liens!C40="","",IF(COUNTIF(Mots!B:B,Liens!C40)&gt;0,"✓ "&amp;Liens!C40,"✗ "&amp;Liens!C40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E45">
+        <f>IF(Liens!D40="","",IF(COUNTIF(Mots!B:B,Liens!D40)&gt;0,"✓ "&amp;Liens!D40,"✗ "&amp;Liens!D40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F45">
+        <f>IF(Liens!E40="","",IF(COUNTIF(Mots!B:B,Liens!E40)&gt;0,"✓ "&amp;Liens!E40,"✗ "&amp;Liens!E40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>IF(Liens!F40="","",IF(COUNTIF(Mots!B:B,Liens!F40)&gt;0,"✓ "&amp;Liens!F40,"✗ "&amp;Liens!F40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(Liens!G40="","",IF(COUNTIF(Mots!B:B,Liens!G40)&gt;0,"✓ "&amp;Liens!G40,"✗ "&amp;Liens!G40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I45">
+        <f>IF(Liens!H40="","",IF(COUNTIF(Mots!B:B,Liens!H40)&gt;0,"✓ "&amp;Liens!H40,"✗ "&amp;Liens!H40&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46">
+        <f>IF(Liens!A41="","",IF(COUNTIF(Mots!B:B,Liens!A41)&gt;0,"✓ "&amp;Liens!A41,"✗ "&amp;Liens!A41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>IF(Liens!B41="","",IF(COUNTIF(Mots!B:B,Liens!B41)&gt;0,"✓ "&amp;Liens!B41,"✗ "&amp;Liens!B41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>IF(Liens!C41="","",IF(COUNTIF(Mots!B:B,Liens!C41)&gt;0,"✓ "&amp;Liens!C41,"✗ "&amp;Liens!C41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>IF(Liens!D41="","",IF(COUNTIF(Mots!B:B,Liens!D41)&gt;0,"✓ "&amp;Liens!D41,"✗ "&amp;Liens!D41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>IF(Liens!E41="","",IF(COUNTIF(Mots!B:B,Liens!E41)&gt;0,"✓ "&amp;Liens!E41,"✗ "&amp;Liens!E41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>IF(Liens!F41="","",IF(COUNTIF(Mots!B:B,Liens!F41)&gt;0,"✓ "&amp;Liens!F41,"✗ "&amp;Liens!F41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H46">
+        <f>IF(Liens!G41="","",IF(COUNTIF(Mots!B:B,Liens!G41)&gt;0,"✓ "&amp;Liens!G41,"✗ "&amp;Liens!G41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I46">
+        <f>IF(Liens!H41="","",IF(COUNTIF(Mots!B:B,Liens!H41)&gt;0,"✓ "&amp;Liens!H41,"✗ "&amp;Liens!H41&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47">
+        <f>IF(Liens!A42="","",IF(COUNTIF(Mots!B:B,Liens!A42)&gt;0,"✓ "&amp;Liens!A42,"✗ "&amp;Liens!A42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>IF(Liens!B42="","",IF(COUNTIF(Mots!B:B,Liens!B42)&gt;0,"✓ "&amp;Liens!B42,"✗ "&amp;Liens!B42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>IF(Liens!C42="","",IF(COUNTIF(Mots!B:B,Liens!C42)&gt;0,"✓ "&amp;Liens!C42,"✗ "&amp;Liens!C42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>IF(Liens!D42="","",IF(COUNTIF(Mots!B:B,Liens!D42)&gt;0,"✓ "&amp;Liens!D42,"✗ "&amp;Liens!D42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>IF(Liens!E42="","",IF(COUNTIF(Mots!B:B,Liens!E42)&gt;0,"✓ "&amp;Liens!E42,"✗ "&amp;Liens!E42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>IF(Liens!F42="","",IF(COUNTIF(Mots!B:B,Liens!F42)&gt;0,"✓ "&amp;Liens!F42,"✗ "&amp;Liens!F42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>IF(Liens!G42="","",IF(COUNTIF(Mots!B:B,Liens!G42)&gt;0,"✓ "&amp;Liens!G42,"✗ "&amp;Liens!G42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I47">
+        <f>IF(Liens!H42="","",IF(COUNTIF(Mots!B:B,Liens!H42)&gt;0,"✓ "&amp;Liens!H42,"✗ "&amp;Liens!H42&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48">
+        <f>IF(Liens!A43="","",IF(COUNTIF(Mots!B:B,Liens!A43)&gt;0,"✓ "&amp;Liens!A43,"✗ "&amp;Liens!A43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C48">
+        <f>IF(Liens!B43="","",IF(COUNTIF(Mots!B:B,Liens!B43)&gt;0,"✓ "&amp;Liens!B43,"✗ "&amp;Liens!B43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>IF(Liens!C43="","",IF(COUNTIF(Mots!B:B,Liens!C43)&gt;0,"✓ "&amp;Liens!C43,"✗ "&amp;Liens!C43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>IF(Liens!D43="","",IF(COUNTIF(Mots!B:B,Liens!D43)&gt;0,"✓ "&amp;Liens!D43,"✗ "&amp;Liens!D43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>IF(Liens!E43="","",IF(COUNTIF(Mots!B:B,Liens!E43)&gt;0,"✓ "&amp;Liens!E43,"✗ "&amp;Liens!E43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>IF(Liens!F43="","",IF(COUNTIF(Mots!B:B,Liens!F43)&gt;0,"✓ "&amp;Liens!F43,"✗ "&amp;Liens!F43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H48">
+        <f>IF(Liens!G43="","",IF(COUNTIF(Mots!B:B,Liens!G43)&gt;0,"✓ "&amp;Liens!G43,"✗ "&amp;Liens!G43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I48">
+        <f>IF(Liens!H43="","",IF(COUNTIF(Mots!B:B,Liens!H43)&gt;0,"✓ "&amp;Liens!H43,"✗ "&amp;Liens!H43&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49">
+        <f>IF(Liens!A44="","",IF(COUNTIF(Mots!B:B,Liens!A44)&gt;0,"✓ "&amp;Liens!A44,"✗ "&amp;Liens!A44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C49">
+        <f>IF(Liens!B44="","",IF(COUNTIF(Mots!B:B,Liens!B44)&gt;0,"✓ "&amp;Liens!B44,"✗ "&amp;Liens!B44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>IF(Liens!C44="","",IF(COUNTIF(Mots!B:B,Liens!C44)&gt;0,"✓ "&amp;Liens!C44,"✗ "&amp;Liens!C44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>IF(Liens!D44="","",IF(COUNTIF(Mots!B:B,Liens!D44)&gt;0,"✓ "&amp;Liens!D44,"✗ "&amp;Liens!D44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>IF(Liens!E44="","",IF(COUNTIF(Mots!B:B,Liens!E44)&gt;0,"✓ "&amp;Liens!E44,"✗ "&amp;Liens!E44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>IF(Liens!F44="","",IF(COUNTIF(Mots!B:B,Liens!F44)&gt;0,"✓ "&amp;Liens!F44,"✗ "&amp;Liens!F44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>IF(Liens!G44="","",IF(COUNTIF(Mots!B:B,Liens!G44)&gt;0,"✓ "&amp;Liens!G44,"✗ "&amp;Liens!G44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I49">
+        <f>IF(Liens!H44="","",IF(COUNTIF(Mots!B:B,Liens!H44)&gt;0,"✓ "&amp;Liens!H44,"✗ "&amp;Liens!H44&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50">
+        <f>IF(Liens!A45="","",IF(COUNTIF(Mots!B:B,Liens!A45)&gt;0,"✓ "&amp;Liens!A45,"✗ "&amp;Liens!A45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C50">
+        <f>IF(Liens!B45="","",IF(COUNTIF(Mots!B:B,Liens!B45)&gt;0,"✓ "&amp;Liens!B45,"✗ "&amp;Liens!B45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D50">
+        <f>IF(Liens!C45="","",IF(COUNTIF(Mots!B:B,Liens!C45)&gt;0,"✓ "&amp;Liens!C45,"✗ "&amp;Liens!C45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>IF(Liens!D45="","",IF(COUNTIF(Mots!B:B,Liens!D45)&gt;0,"✓ "&amp;Liens!D45,"✗ "&amp;Liens!D45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F50">
+        <f>IF(Liens!E45="","",IF(COUNTIF(Mots!B:B,Liens!E45)&gt;0,"✓ "&amp;Liens!E45,"✗ "&amp;Liens!E45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>IF(Liens!F45="","",IF(COUNTIF(Mots!B:B,Liens!F45)&gt;0,"✓ "&amp;Liens!F45,"✗ "&amp;Liens!F45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H50">
+        <f>IF(Liens!G45="","",IF(COUNTIF(Mots!B:B,Liens!G45)&gt;0,"✓ "&amp;Liens!G45,"✗ "&amp;Liens!G45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I50">
+        <f>IF(Liens!H45="","",IF(COUNTIF(Mots!B:B,Liens!H45)&gt;0,"✓ "&amp;Liens!H45,"✗ "&amp;Liens!H45&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51">
+        <f>IF(Liens!A46="","",IF(COUNTIF(Mots!B:B,Liens!A46)&gt;0,"✓ "&amp;Liens!A46,"✗ "&amp;Liens!A46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C51">
+        <f>IF(Liens!B46="","",IF(COUNTIF(Mots!B:B,Liens!B46)&gt;0,"✓ "&amp;Liens!B46,"✗ "&amp;Liens!B46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D51">
+        <f>IF(Liens!C46="","",IF(COUNTIF(Mots!B:B,Liens!C46)&gt;0,"✓ "&amp;Liens!C46,"✗ "&amp;Liens!C46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E51">
+        <f>IF(Liens!D46="","",IF(COUNTIF(Mots!B:B,Liens!D46)&gt;0,"✓ "&amp;Liens!D46,"✗ "&amp;Liens!D46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F51">
+        <f>IF(Liens!E46="","",IF(COUNTIF(Mots!B:B,Liens!E46)&gt;0,"✓ "&amp;Liens!E46,"✗ "&amp;Liens!E46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>IF(Liens!F46="","",IF(COUNTIF(Mots!B:B,Liens!F46)&gt;0,"✓ "&amp;Liens!F46,"✗ "&amp;Liens!F46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H51">
+        <f>IF(Liens!G46="","",IF(COUNTIF(Mots!B:B,Liens!G46)&gt;0,"✓ "&amp;Liens!G46,"✗ "&amp;Liens!G46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I51">
+        <f>IF(Liens!H46="","",IF(COUNTIF(Mots!B:B,Liens!H46)&gt;0,"✓ "&amp;Liens!H46,"✗ "&amp;Liens!H46&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52">
+        <f>IF(Liens!A47="","",IF(COUNTIF(Mots!B:B,Liens!A47)&gt;0,"✓ "&amp;Liens!A47,"✗ "&amp;Liens!A47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>IF(Liens!B47="","",IF(COUNTIF(Mots!B:B,Liens!B47)&gt;0,"✓ "&amp;Liens!B47,"✗ "&amp;Liens!B47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D52">
+        <f>IF(Liens!C47="","",IF(COUNTIF(Mots!B:B,Liens!C47)&gt;0,"✓ "&amp;Liens!C47,"✗ "&amp;Liens!C47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>IF(Liens!D47="","",IF(COUNTIF(Mots!B:B,Liens!D47)&gt;0,"✓ "&amp;Liens!D47,"✗ "&amp;Liens!D47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>IF(Liens!E47="","",IF(COUNTIF(Mots!B:B,Liens!E47)&gt;0,"✓ "&amp;Liens!E47,"✗ "&amp;Liens!E47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>IF(Liens!F47="","",IF(COUNTIF(Mots!B:B,Liens!F47)&gt;0,"✓ "&amp;Liens!F47,"✗ "&amp;Liens!F47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H52">
+        <f>IF(Liens!G47="","",IF(COUNTIF(Mots!B:B,Liens!G47)&gt;0,"✓ "&amp;Liens!G47,"✗ "&amp;Liens!G47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I52">
+        <f>IF(Liens!H47="","",IF(COUNTIF(Mots!B:B,Liens!H47)&gt;0,"✓ "&amp;Liens!H47,"✗ "&amp;Liens!H47&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53">
+        <f>IF(Liens!A48="","",IF(COUNTIF(Mots!B:B,Liens!A48)&gt;0,"✓ "&amp;Liens!A48,"✗ "&amp;Liens!A48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>IF(Liens!B48="","",IF(COUNTIF(Mots!B:B,Liens!B48)&gt;0,"✓ "&amp;Liens!B48,"✗ "&amp;Liens!B48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>IF(Liens!C48="","",IF(COUNTIF(Mots!B:B,Liens!C48)&gt;0,"✓ "&amp;Liens!C48,"✗ "&amp;Liens!C48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>IF(Liens!D48="","",IF(COUNTIF(Mots!B:B,Liens!D48)&gt;0,"✓ "&amp;Liens!D48,"✗ "&amp;Liens!D48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>IF(Liens!E48="","",IF(COUNTIF(Mots!B:B,Liens!E48)&gt;0,"✓ "&amp;Liens!E48,"✗ "&amp;Liens!E48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>IF(Liens!F48="","",IF(COUNTIF(Mots!B:B,Liens!F48)&gt;0,"✓ "&amp;Liens!F48,"✗ "&amp;Liens!F48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H53">
+        <f>IF(Liens!G48="","",IF(COUNTIF(Mots!B:B,Liens!G48)&gt;0,"✓ "&amp;Liens!G48,"✗ "&amp;Liens!G48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I53">
+        <f>IF(Liens!H48="","",IF(COUNTIF(Mots!B:B,Liens!H48)&gt;0,"✓ "&amp;Liens!H48,"✗ "&amp;Liens!H48&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54">
+        <f>IF(Liens!A49="","",IF(COUNTIF(Mots!B:B,Liens!A49)&gt;0,"✓ "&amp;Liens!A49,"✗ "&amp;Liens!A49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>IF(Liens!B49="","",IF(COUNTIF(Mots!B:B,Liens!B49)&gt;0,"✓ "&amp;Liens!B49,"✗ "&amp;Liens!B49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>IF(Liens!C49="","",IF(COUNTIF(Mots!B:B,Liens!C49)&gt;0,"✓ "&amp;Liens!C49,"✗ "&amp;Liens!C49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>IF(Liens!D49="","",IF(COUNTIF(Mots!B:B,Liens!D49)&gt;0,"✓ "&amp;Liens!D49,"✗ "&amp;Liens!D49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>IF(Liens!E49="","",IF(COUNTIF(Mots!B:B,Liens!E49)&gt;0,"✓ "&amp;Liens!E49,"✗ "&amp;Liens!E49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>IF(Liens!F49="","",IF(COUNTIF(Mots!B:B,Liens!F49)&gt;0,"✓ "&amp;Liens!F49,"✗ "&amp;Liens!F49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>IF(Liens!G49="","",IF(COUNTIF(Mots!B:B,Liens!G49)&gt;0,"✓ "&amp;Liens!G49,"✗ "&amp;Liens!G49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>IF(Liens!H49="","",IF(COUNTIF(Mots!B:B,Liens!H49)&gt;0,"✓ "&amp;Liens!H49,"✗ "&amp;Liens!H49&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <f>IF(Liens!A50="","",IF(COUNTIF(Mots!B:B,Liens!A50)&gt;0,"✓ "&amp;Liens!A50,"✗ "&amp;Liens!A50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>IF(Liens!B50="","",IF(COUNTIF(Mots!B:B,Liens!B50)&gt;0,"✓ "&amp;Liens!B50,"✗ "&amp;Liens!B50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>IF(Liens!C50="","",IF(COUNTIF(Mots!B:B,Liens!C50)&gt;0,"✓ "&amp;Liens!C50,"✗ "&amp;Liens!C50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>IF(Liens!D50="","",IF(COUNTIF(Mots!B:B,Liens!D50)&gt;0,"✓ "&amp;Liens!D50,"✗ "&amp;Liens!D50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>IF(Liens!E50="","",IF(COUNTIF(Mots!B:B,Liens!E50)&gt;0,"✓ "&amp;Liens!E50,"✗ "&amp;Liens!E50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>IF(Liens!F50="","",IF(COUNTIF(Mots!B:B,Liens!F50)&gt;0,"✓ "&amp;Liens!F50,"✗ "&amp;Liens!F50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H55">
+        <f>IF(Liens!G50="","",IF(COUNTIF(Mots!B:B,Liens!G50)&gt;0,"✓ "&amp;Liens!G50,"✗ "&amp;Liens!G50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I55">
+        <f>IF(Liens!H50="","",IF(COUNTIF(Mots!B:B,Liens!H50)&gt;0,"✓ "&amp;Liens!H50,"✗ "&amp;Liens!H50&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56">
+        <f>IF(Liens!A51="","",IF(COUNTIF(Mots!B:B,Liens!A51)&gt;0,"✓ "&amp;Liens!A51,"✗ "&amp;Liens!A51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>IF(Liens!B51="","",IF(COUNTIF(Mots!B:B,Liens!B51)&gt;0,"✓ "&amp;Liens!B51,"✗ "&amp;Liens!B51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>IF(Liens!C51="","",IF(COUNTIF(Mots!B:B,Liens!C51)&gt;0,"✓ "&amp;Liens!C51,"✗ "&amp;Liens!C51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>IF(Liens!D51="","",IF(COUNTIF(Mots!B:B,Liens!D51)&gt;0,"✓ "&amp;Liens!D51,"✗ "&amp;Liens!D51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>IF(Liens!E51="","",IF(COUNTIF(Mots!B:B,Liens!E51)&gt;0,"✓ "&amp;Liens!E51,"✗ "&amp;Liens!E51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>IF(Liens!F51="","",IF(COUNTIF(Mots!B:B,Liens!F51)&gt;0,"✓ "&amp;Liens!F51,"✗ "&amp;Liens!F51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>IF(Liens!G51="","",IF(COUNTIF(Mots!B:B,Liens!G51)&gt;0,"✓ "&amp;Liens!G51,"✗ "&amp;Liens!G51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>IF(Liens!H51="","",IF(COUNTIF(Mots!B:B,Liens!H51)&gt;0,"✓ "&amp;Liens!H51,"✗ "&amp;Liens!H51&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57">
+        <f>IF(Liens!A52="","",IF(COUNTIF(Mots!B:B,Liens!A52)&gt;0,"✓ "&amp;Liens!A52,"✗ "&amp;Liens!A52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>IF(Liens!B52="","",IF(COUNTIF(Mots!B:B,Liens!B52)&gt;0,"✓ "&amp;Liens!B52,"✗ "&amp;Liens!B52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF(Liens!C52="","",IF(COUNTIF(Mots!B:B,Liens!C52)&gt;0,"✓ "&amp;Liens!C52,"✗ "&amp;Liens!C52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF(Liens!D52="","",IF(COUNTIF(Mots!B:B,Liens!D52)&gt;0,"✓ "&amp;Liens!D52,"✗ "&amp;Liens!D52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF(Liens!E52="","",IF(COUNTIF(Mots!B:B,Liens!E52)&gt;0,"✓ "&amp;Liens!E52,"✗ "&amp;Liens!E52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IF(Liens!F52="","",IF(COUNTIF(Mots!B:B,Liens!F52)&gt;0,"✓ "&amp;Liens!F52,"✗ "&amp;Liens!F52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>IF(Liens!G52="","",IF(COUNTIF(Mots!B:B,Liens!G52)&gt;0,"✓ "&amp;Liens!G52,"✗ "&amp;Liens!G52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>IF(Liens!H52="","",IF(COUNTIF(Mots!B:B,Liens!H52)&gt;0,"✓ "&amp;Liens!H52,"✗ "&amp;Liens!H52&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58">
+        <f>IF(Liens!A53="","",IF(COUNTIF(Mots!B:B,Liens!A53)&gt;0,"✓ "&amp;Liens!A53,"✗ "&amp;Liens!A53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>IF(Liens!B53="","",IF(COUNTIF(Mots!B:B,Liens!B53)&gt;0,"✓ "&amp;Liens!B53,"✗ "&amp;Liens!B53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IF(Liens!C53="","",IF(COUNTIF(Mots!B:B,Liens!C53)&gt;0,"✓ "&amp;Liens!C53,"✗ "&amp;Liens!C53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IF(Liens!D53="","",IF(COUNTIF(Mots!B:B,Liens!D53)&gt;0,"✓ "&amp;Liens!D53,"✗ "&amp;Liens!D53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF(Liens!E53="","",IF(COUNTIF(Mots!B:B,Liens!E53)&gt;0,"✓ "&amp;Liens!E53,"✗ "&amp;Liens!E53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>IF(Liens!F53="","",IF(COUNTIF(Mots!B:B,Liens!F53)&gt;0,"✓ "&amp;Liens!F53,"✗ "&amp;Liens!F53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>IF(Liens!G53="","",IF(COUNTIF(Mots!B:B,Liens!G53)&gt;0,"✓ "&amp;Liens!G53,"✗ "&amp;Liens!G53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>IF(Liens!H53="","",IF(COUNTIF(Mots!B:B,Liens!H53)&gt;0,"✓ "&amp;Liens!H53,"✗ "&amp;Liens!H53&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59">
+        <f>IF(Liens!A54="","",IF(COUNTIF(Mots!B:B,Liens!A54)&gt;0,"✓ "&amp;Liens!A54,"✗ "&amp;Liens!A54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>IF(Liens!B54="","",IF(COUNTIF(Mots!B:B,Liens!B54)&gt;0,"✓ "&amp;Liens!B54,"✗ "&amp;Liens!B54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>IF(Liens!C54="","",IF(COUNTIF(Mots!B:B,Liens!C54)&gt;0,"✓ "&amp;Liens!C54,"✗ "&amp;Liens!C54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>IF(Liens!D54="","",IF(COUNTIF(Mots!B:B,Liens!D54)&gt;0,"✓ "&amp;Liens!D54,"✗ "&amp;Liens!D54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IF(Liens!E54="","",IF(COUNTIF(Mots!B:B,Liens!E54)&gt;0,"✓ "&amp;Liens!E54,"✗ "&amp;Liens!E54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IF(Liens!F54="","",IF(COUNTIF(Mots!B:B,Liens!F54)&gt;0,"✓ "&amp;Liens!F54,"✗ "&amp;Liens!F54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>IF(Liens!G54="","",IF(COUNTIF(Mots!B:B,Liens!G54)&gt;0,"✓ "&amp;Liens!G54,"✗ "&amp;Liens!G54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>IF(Liens!H54="","",IF(COUNTIF(Mots!B:B,Liens!H54)&gt;0,"✓ "&amp;Liens!H54,"✗ "&amp;Liens!H54&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60">
+        <f>IF(Liens!A55="","",IF(COUNTIF(Mots!B:B,Liens!A55)&gt;0,"✓ "&amp;Liens!A55,"✗ "&amp;Liens!A55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>IF(Liens!B55="","",IF(COUNTIF(Mots!B:B,Liens!B55)&gt;0,"✓ "&amp;Liens!B55,"✗ "&amp;Liens!B55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>IF(Liens!C55="","",IF(COUNTIF(Mots!B:B,Liens!C55)&gt;0,"✓ "&amp;Liens!C55,"✗ "&amp;Liens!C55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>IF(Liens!D55="","",IF(COUNTIF(Mots!B:B,Liens!D55)&gt;0,"✓ "&amp;Liens!D55,"✗ "&amp;Liens!D55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>IF(Liens!E55="","",IF(COUNTIF(Mots!B:B,Liens!E55)&gt;0,"✓ "&amp;Liens!E55,"✗ "&amp;Liens!E55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>IF(Liens!F55="","",IF(COUNTIF(Mots!B:B,Liens!F55)&gt;0,"✓ "&amp;Liens!F55,"✗ "&amp;Liens!F55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>IF(Liens!G55="","",IF(COUNTIF(Mots!B:B,Liens!G55)&gt;0,"✓ "&amp;Liens!G55,"✗ "&amp;Liens!G55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>IF(Liens!H55="","",IF(COUNTIF(Mots!B:B,Liens!H55)&gt;0,"✓ "&amp;Liens!H55,"✗ "&amp;Liens!H55&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61">
+        <f>IF(Liens!A56="","",IF(COUNTIF(Mots!B:B,Liens!A56)&gt;0,"✓ "&amp;Liens!A56,"✗ "&amp;Liens!A56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>IF(Liens!B56="","",IF(COUNTIF(Mots!B:B,Liens!B56)&gt;0,"✓ "&amp;Liens!B56,"✗ "&amp;Liens!B56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>IF(Liens!C56="","",IF(COUNTIF(Mots!B:B,Liens!C56)&gt;0,"✓ "&amp;Liens!C56,"✗ "&amp;Liens!C56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>IF(Liens!D56="","",IF(COUNTIF(Mots!B:B,Liens!D56)&gt;0,"✓ "&amp;Liens!D56,"✗ "&amp;Liens!D56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IF(Liens!E56="","",IF(COUNTIF(Mots!B:B,Liens!E56)&gt;0,"✓ "&amp;Liens!E56,"✗ "&amp;Liens!E56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IF(Liens!F56="","",IF(COUNTIF(Mots!B:B,Liens!F56)&gt;0,"✓ "&amp;Liens!F56,"✗ "&amp;Liens!F56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>IF(Liens!G56="","",IF(COUNTIF(Mots!B:B,Liens!G56)&gt;0,"✓ "&amp;Liens!G56,"✗ "&amp;Liens!G56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IF(Liens!H56="","",IF(COUNTIF(Mots!B:B,Liens!H56)&gt;0,"✓ "&amp;Liens!H56,"✗ "&amp;Liens!H56&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62">
+        <f>IF(Liens!A57="","",IF(COUNTIF(Mots!B:B,Liens!A57)&gt;0,"✓ "&amp;Liens!A57,"✗ "&amp;Liens!A57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>IF(Liens!B57="","",IF(COUNTIF(Mots!B:B,Liens!B57)&gt;0,"✓ "&amp;Liens!B57,"✗ "&amp;Liens!B57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>IF(Liens!C57="","",IF(COUNTIF(Mots!B:B,Liens!C57)&gt;0,"✓ "&amp;Liens!C57,"✗ "&amp;Liens!C57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>IF(Liens!D57="","",IF(COUNTIF(Mots!B:B,Liens!D57)&gt;0,"✓ "&amp;Liens!D57,"✗ "&amp;Liens!D57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>IF(Liens!E57="","",IF(COUNTIF(Mots!B:B,Liens!E57)&gt;0,"✓ "&amp;Liens!E57,"✗ "&amp;Liens!E57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>IF(Liens!F57="","",IF(COUNTIF(Mots!B:B,Liens!F57)&gt;0,"✓ "&amp;Liens!F57,"✗ "&amp;Liens!F57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H62">
+        <f>IF(Liens!G57="","",IF(COUNTIF(Mots!B:B,Liens!G57)&gt;0,"✓ "&amp;Liens!G57,"✗ "&amp;Liens!G57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I62">
+        <f>IF(Liens!H57="","",IF(COUNTIF(Mots!B:B,Liens!H57)&gt;0,"✓ "&amp;Liens!H57,"✗ "&amp;Liens!H57&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63">
+        <f>IF(Liens!A58="","",IF(COUNTIF(Mots!B:B,Liens!A58)&gt;0,"✓ "&amp;Liens!A58,"✗ "&amp;Liens!A58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>IF(Liens!B58="","",IF(COUNTIF(Mots!B:B,Liens!B58)&gt;0,"✓ "&amp;Liens!B58,"✗ "&amp;Liens!B58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>IF(Liens!C58="","",IF(COUNTIF(Mots!B:B,Liens!C58)&gt;0,"✓ "&amp;Liens!C58,"✗ "&amp;Liens!C58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>IF(Liens!D58="","",IF(COUNTIF(Mots!B:B,Liens!D58)&gt;0,"✓ "&amp;Liens!D58,"✗ "&amp;Liens!D58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>IF(Liens!E58="","",IF(COUNTIF(Mots!B:B,Liens!E58)&gt;0,"✓ "&amp;Liens!E58,"✗ "&amp;Liens!E58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>IF(Liens!F58="","",IF(COUNTIF(Mots!B:B,Liens!F58)&gt;0,"✓ "&amp;Liens!F58,"✗ "&amp;Liens!F58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>IF(Liens!G58="","",IF(COUNTIF(Mots!B:B,Liens!G58)&gt;0,"✓ "&amp;Liens!G58,"✗ "&amp;Liens!G58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>IF(Liens!H58="","",IF(COUNTIF(Mots!B:B,Liens!H58)&gt;0,"✓ "&amp;Liens!H58,"✗ "&amp;Liens!H58&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64">
+        <f>IF(Liens!A59="","",IF(COUNTIF(Mots!B:B,Liens!A59)&gt;0,"✓ "&amp;Liens!A59,"✗ "&amp;Liens!A59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>IF(Liens!B59="","",IF(COUNTIF(Mots!B:B,Liens!B59)&gt;0,"✓ "&amp;Liens!B59,"✗ "&amp;Liens!B59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>IF(Liens!C59="","",IF(COUNTIF(Mots!B:B,Liens!C59)&gt;0,"✓ "&amp;Liens!C59,"✗ "&amp;Liens!C59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>IF(Liens!D59="","",IF(COUNTIF(Mots!B:B,Liens!D59)&gt;0,"✓ "&amp;Liens!D59,"✗ "&amp;Liens!D59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>IF(Liens!E59="","",IF(COUNTIF(Mots!B:B,Liens!E59)&gt;0,"✓ "&amp;Liens!E59,"✗ "&amp;Liens!E59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>IF(Liens!F59="","",IF(COUNTIF(Mots!B:B,Liens!F59)&gt;0,"✓ "&amp;Liens!F59,"✗ "&amp;Liens!F59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>IF(Liens!G59="","",IF(COUNTIF(Mots!B:B,Liens!G59)&gt;0,"✓ "&amp;Liens!G59,"✗ "&amp;Liens!G59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>IF(Liens!H59="","",IF(COUNTIF(Mots!B:B,Liens!H59)&gt;0,"✓ "&amp;Liens!H59,"✗ "&amp;Liens!H59&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65">
+        <f>IF(Liens!A60="","",IF(COUNTIF(Mots!B:B,Liens!A60)&gt;0,"✓ "&amp;Liens!A60,"✗ "&amp;Liens!A60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>IF(Liens!B60="","",IF(COUNTIF(Mots!B:B,Liens!B60)&gt;0,"✓ "&amp;Liens!B60,"✗ "&amp;Liens!B60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>IF(Liens!C60="","",IF(COUNTIF(Mots!B:B,Liens!C60)&gt;0,"✓ "&amp;Liens!C60,"✗ "&amp;Liens!C60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>IF(Liens!D60="","",IF(COUNTIF(Mots!B:B,Liens!D60)&gt;0,"✓ "&amp;Liens!D60,"✗ "&amp;Liens!D60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>IF(Liens!E60="","",IF(COUNTIF(Mots!B:B,Liens!E60)&gt;0,"✓ "&amp;Liens!E60,"✗ "&amp;Liens!E60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>IF(Liens!F60="","",IF(COUNTIF(Mots!B:B,Liens!F60)&gt;0,"✓ "&amp;Liens!F60,"✗ "&amp;Liens!F60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>IF(Liens!G60="","",IF(COUNTIF(Mots!B:B,Liens!G60)&gt;0,"✓ "&amp;Liens!G60,"✗ "&amp;Liens!G60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>IF(Liens!H60="","",IF(COUNTIF(Mots!B:B,Liens!H60)&gt;0,"✓ "&amp;Liens!H60,"✗ "&amp;Liens!H60&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66">
+        <f>IF(Liens!A61="","",IF(COUNTIF(Mots!B:B,Liens!A61)&gt;0,"✓ "&amp;Liens!A61,"✗ "&amp;Liens!A61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>IF(Liens!B61="","",IF(COUNTIF(Mots!B:B,Liens!B61)&gt;0,"✓ "&amp;Liens!B61,"✗ "&amp;Liens!B61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>IF(Liens!C61="","",IF(COUNTIF(Mots!B:B,Liens!C61)&gt;0,"✓ "&amp;Liens!C61,"✗ "&amp;Liens!C61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>IF(Liens!D61="","",IF(COUNTIF(Mots!B:B,Liens!D61)&gt;0,"✓ "&amp;Liens!D61,"✗ "&amp;Liens!D61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>IF(Liens!E61="","",IF(COUNTIF(Mots!B:B,Liens!E61)&gt;0,"✓ "&amp;Liens!E61,"✗ "&amp;Liens!E61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>IF(Liens!F61="","",IF(COUNTIF(Mots!B:B,Liens!F61)&gt;0,"✓ "&amp;Liens!F61,"✗ "&amp;Liens!F61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H66">
+        <f>IF(Liens!G61="","",IF(COUNTIF(Mots!B:B,Liens!G61)&gt;0,"✓ "&amp;Liens!G61,"✗ "&amp;Liens!G61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I66">
+        <f>IF(Liens!H61="","",IF(COUNTIF(Mots!B:B,Liens!H61)&gt;0,"✓ "&amp;Liens!H61,"✗ "&amp;Liens!H61&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67">
+        <f>IF(Liens!A62="","",IF(COUNTIF(Mots!B:B,Liens!A62)&gt;0,"✓ "&amp;Liens!A62,"✗ "&amp;Liens!A62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>IF(Liens!B62="","",IF(COUNTIF(Mots!B:B,Liens!B62)&gt;0,"✓ "&amp;Liens!B62,"✗ "&amp;Liens!B62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>IF(Liens!C62="","",IF(COUNTIF(Mots!B:B,Liens!C62)&gt;0,"✓ "&amp;Liens!C62,"✗ "&amp;Liens!C62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>IF(Liens!D62="","",IF(COUNTIF(Mots!B:B,Liens!D62)&gt;0,"✓ "&amp;Liens!D62,"✗ "&amp;Liens!D62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>IF(Liens!E62="","",IF(COUNTIF(Mots!B:B,Liens!E62)&gt;0,"✓ "&amp;Liens!E62,"✗ "&amp;Liens!E62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>IF(Liens!F62="","",IF(COUNTIF(Mots!B:B,Liens!F62)&gt;0,"✓ "&amp;Liens!F62,"✗ "&amp;Liens!F62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>IF(Liens!G62="","",IF(COUNTIF(Mots!B:B,Liens!G62)&gt;0,"✓ "&amp;Liens!G62,"✗ "&amp;Liens!G62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>IF(Liens!H62="","",IF(COUNTIF(Mots!B:B,Liens!H62)&gt;0,"✓ "&amp;Liens!H62,"✗ "&amp;Liens!H62&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68">
+        <f>IF(Liens!A63="","",IF(COUNTIF(Mots!B:B,Liens!A63)&gt;0,"✓ "&amp;Liens!A63,"✗ "&amp;Liens!A63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>IF(Liens!B63="","",IF(COUNTIF(Mots!B:B,Liens!B63)&gt;0,"✓ "&amp;Liens!B63,"✗ "&amp;Liens!B63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>IF(Liens!C63="","",IF(COUNTIF(Mots!B:B,Liens!C63)&gt;0,"✓ "&amp;Liens!C63,"✗ "&amp;Liens!C63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>IF(Liens!D63="","",IF(COUNTIF(Mots!B:B,Liens!D63)&gt;0,"✓ "&amp;Liens!D63,"✗ "&amp;Liens!D63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>IF(Liens!E63="","",IF(COUNTIF(Mots!B:B,Liens!E63)&gt;0,"✓ "&amp;Liens!E63,"✗ "&amp;Liens!E63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>IF(Liens!F63="","",IF(COUNTIF(Mots!B:B,Liens!F63)&gt;0,"✓ "&amp;Liens!F63,"✗ "&amp;Liens!F63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H68">
+        <f>IF(Liens!G63="","",IF(COUNTIF(Mots!B:B,Liens!G63)&gt;0,"✓ "&amp;Liens!G63,"✗ "&amp;Liens!G63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>IF(Liens!H63="","",IF(COUNTIF(Mots!B:B,Liens!H63)&gt;0,"✓ "&amp;Liens!H63,"✗ "&amp;Liens!H63&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69">
+        <f>IF(Liens!A64="","",IF(COUNTIF(Mots!B:B,Liens!A64)&gt;0,"✓ "&amp;Liens!A64,"✗ "&amp;Liens!A64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>IF(Liens!B64="","",IF(COUNTIF(Mots!B:B,Liens!B64)&gt;0,"✓ "&amp;Liens!B64,"✗ "&amp;Liens!B64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>IF(Liens!C64="","",IF(COUNTIF(Mots!B:B,Liens!C64)&gt;0,"✓ "&amp;Liens!C64,"✗ "&amp;Liens!C64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>IF(Liens!D64="","",IF(COUNTIF(Mots!B:B,Liens!D64)&gt;0,"✓ "&amp;Liens!D64,"✗ "&amp;Liens!D64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>IF(Liens!E64="","",IF(COUNTIF(Mots!B:B,Liens!E64)&gt;0,"✓ "&amp;Liens!E64,"✗ "&amp;Liens!E64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>IF(Liens!F64="","",IF(COUNTIF(Mots!B:B,Liens!F64)&gt;0,"✓ "&amp;Liens!F64,"✗ "&amp;Liens!F64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H69">
+        <f>IF(Liens!G64="","",IF(COUNTIF(Mots!B:B,Liens!G64)&gt;0,"✓ "&amp;Liens!G64,"✗ "&amp;Liens!G64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>IF(Liens!H64="","",IF(COUNTIF(Mots!B:B,Liens!H64)&gt;0,"✓ "&amp;Liens!H64,"✗ "&amp;Liens!H64&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70">
+        <f>IF(Liens!A65="","",IF(COUNTIF(Mots!B:B,Liens!A65)&gt;0,"✓ "&amp;Liens!A65,"✗ "&amp;Liens!A65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>IF(Liens!B65="","",IF(COUNTIF(Mots!B:B,Liens!B65)&gt;0,"✓ "&amp;Liens!B65,"✗ "&amp;Liens!B65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>IF(Liens!C65="","",IF(COUNTIF(Mots!B:B,Liens!C65)&gt;0,"✓ "&amp;Liens!C65,"✗ "&amp;Liens!C65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>IF(Liens!D65="","",IF(COUNTIF(Mots!B:B,Liens!D65)&gt;0,"✓ "&amp;Liens!D65,"✗ "&amp;Liens!D65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>IF(Liens!E65="","",IF(COUNTIF(Mots!B:B,Liens!E65)&gt;0,"✓ "&amp;Liens!E65,"✗ "&amp;Liens!E65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>IF(Liens!F65="","",IF(COUNTIF(Mots!B:B,Liens!F65)&gt;0,"✓ "&amp;Liens!F65,"✗ "&amp;Liens!F65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H70">
+        <f>IF(Liens!G65="","",IF(COUNTIF(Mots!B:B,Liens!G65)&gt;0,"✓ "&amp;Liens!G65,"✗ "&amp;Liens!G65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>IF(Liens!H65="","",IF(COUNTIF(Mots!B:B,Liens!H65)&gt;0,"✓ "&amp;Liens!H65,"✗ "&amp;Liens!H65&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71">
+        <f>IF(Liens!A66="","",IF(COUNTIF(Mots!B:B,Liens!A66)&gt;0,"✓ "&amp;Liens!A66,"✗ "&amp;Liens!A66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C71">
+        <f>IF(Liens!B66="","",IF(COUNTIF(Mots!B:B,Liens!B66)&gt;0,"✓ "&amp;Liens!B66,"✗ "&amp;Liens!B66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D71">
+        <f>IF(Liens!C66="","",IF(COUNTIF(Mots!B:B,Liens!C66)&gt;0,"✓ "&amp;Liens!C66,"✗ "&amp;Liens!C66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E71">
+        <f>IF(Liens!D66="","",IF(COUNTIF(Mots!B:B,Liens!D66)&gt;0,"✓ "&amp;Liens!D66,"✗ "&amp;Liens!D66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F71">
+        <f>IF(Liens!E66="","",IF(COUNTIF(Mots!B:B,Liens!E66)&gt;0,"✓ "&amp;Liens!E66,"✗ "&amp;Liens!E66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>IF(Liens!F66="","",IF(COUNTIF(Mots!B:B,Liens!F66)&gt;0,"✓ "&amp;Liens!F66,"✗ "&amp;Liens!F66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H71">
+        <f>IF(Liens!G66="","",IF(COUNTIF(Mots!B:B,Liens!G66)&gt;0,"✓ "&amp;Liens!G66,"✗ "&amp;Liens!G66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I71">
+        <f>IF(Liens!H66="","",IF(COUNTIF(Mots!B:B,Liens!H66)&gt;0,"✓ "&amp;Liens!H66,"✗ "&amp;Liens!H66&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72">
+        <f>IF(Liens!A67="","",IF(COUNTIF(Mots!B:B,Liens!A67)&gt;0,"✓ "&amp;Liens!A67,"✗ "&amp;Liens!A67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C72">
+        <f>IF(Liens!B67="","",IF(COUNTIF(Mots!B:B,Liens!B67)&gt;0,"✓ "&amp;Liens!B67,"✗ "&amp;Liens!B67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>IF(Liens!C67="","",IF(COUNTIF(Mots!B:B,Liens!C67)&gt;0,"✓ "&amp;Liens!C67,"✗ "&amp;Liens!C67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>IF(Liens!D67="","",IF(COUNTIF(Mots!B:B,Liens!D67)&gt;0,"✓ "&amp;Liens!D67,"✗ "&amp;Liens!D67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>IF(Liens!E67="","",IF(COUNTIF(Mots!B:B,Liens!E67)&gt;0,"✓ "&amp;Liens!E67,"✗ "&amp;Liens!E67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>IF(Liens!F67="","",IF(COUNTIF(Mots!B:B,Liens!F67)&gt;0,"✓ "&amp;Liens!F67,"✗ "&amp;Liens!F67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H72">
+        <f>IF(Liens!G67="","",IF(COUNTIF(Mots!B:B,Liens!G67)&gt;0,"✓ "&amp;Liens!G67,"✗ "&amp;Liens!G67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>IF(Liens!H67="","",IF(COUNTIF(Mots!B:B,Liens!H67)&gt;0,"✓ "&amp;Liens!H67,"✗ "&amp;Liens!H67&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73">
+        <f>IF(Liens!A68="","",IF(COUNTIF(Mots!B:B,Liens!A68)&gt;0,"✓ "&amp;Liens!A68,"✗ "&amp;Liens!A68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>IF(Liens!B68="","",IF(COUNTIF(Mots!B:B,Liens!B68)&gt;0,"✓ "&amp;Liens!B68,"✗ "&amp;Liens!B68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>IF(Liens!C68="","",IF(COUNTIF(Mots!B:B,Liens!C68)&gt;0,"✓ "&amp;Liens!C68,"✗ "&amp;Liens!C68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>IF(Liens!D68="","",IF(COUNTIF(Mots!B:B,Liens!D68)&gt;0,"✓ "&amp;Liens!D68,"✗ "&amp;Liens!D68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>IF(Liens!E68="","",IF(COUNTIF(Mots!B:B,Liens!E68)&gt;0,"✓ "&amp;Liens!E68,"✗ "&amp;Liens!E68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>IF(Liens!F68="","",IF(COUNTIF(Mots!B:B,Liens!F68)&gt;0,"✓ "&amp;Liens!F68,"✗ "&amp;Liens!F68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H73">
+        <f>IF(Liens!G68="","",IF(COUNTIF(Mots!B:B,Liens!G68)&gt;0,"✓ "&amp;Liens!G68,"✗ "&amp;Liens!G68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>IF(Liens!H68="","",IF(COUNTIF(Mots!B:B,Liens!H68)&gt;0,"✓ "&amp;Liens!H68,"✗ "&amp;Liens!H68&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74">
+        <f>IF(Liens!A69="","",IF(COUNTIF(Mots!B:B,Liens!A69)&gt;0,"✓ "&amp;Liens!A69,"✗ "&amp;Liens!A69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C74">
+        <f>IF(Liens!B69="","",IF(COUNTIF(Mots!B:B,Liens!B69)&gt;0,"✓ "&amp;Liens!B69,"✗ "&amp;Liens!B69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D74">
+        <f>IF(Liens!C69="","",IF(COUNTIF(Mots!B:B,Liens!C69)&gt;0,"✓ "&amp;Liens!C69,"✗ "&amp;Liens!C69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E74">
+        <f>IF(Liens!D69="","",IF(COUNTIF(Mots!B:B,Liens!D69)&gt;0,"✓ "&amp;Liens!D69,"✗ "&amp;Liens!D69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F74">
+        <f>IF(Liens!E69="","",IF(COUNTIF(Mots!B:B,Liens!E69)&gt;0,"✓ "&amp;Liens!E69,"✗ "&amp;Liens!E69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>IF(Liens!F69="","",IF(COUNTIF(Mots!B:B,Liens!F69)&gt;0,"✓ "&amp;Liens!F69,"✗ "&amp;Liens!F69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H74">
+        <f>IF(Liens!G69="","",IF(COUNTIF(Mots!B:B,Liens!G69)&gt;0,"✓ "&amp;Liens!G69,"✗ "&amp;Liens!G69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I74">
+        <f>IF(Liens!H69="","",IF(COUNTIF(Mots!B:B,Liens!H69)&gt;0,"✓ "&amp;Liens!H69,"✗ "&amp;Liens!H69&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75">
+        <f>IF(Liens!A70="","",IF(COUNTIF(Mots!B:B,Liens!A70)&gt;0,"✓ "&amp;Liens!A70,"✗ "&amp;Liens!A70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C75">
+        <f>IF(Liens!B70="","",IF(COUNTIF(Mots!B:B,Liens!B70)&gt;0,"✓ "&amp;Liens!B70,"✗ "&amp;Liens!B70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D75">
+        <f>IF(Liens!C70="","",IF(COUNTIF(Mots!B:B,Liens!C70)&gt;0,"✓ "&amp;Liens!C70,"✗ "&amp;Liens!C70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E75">
+        <f>IF(Liens!D70="","",IF(COUNTIF(Mots!B:B,Liens!D70)&gt;0,"✓ "&amp;Liens!D70,"✗ "&amp;Liens!D70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F75">
+        <f>IF(Liens!E70="","",IF(COUNTIF(Mots!B:B,Liens!E70)&gt;0,"✓ "&amp;Liens!E70,"✗ "&amp;Liens!E70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>IF(Liens!F70="","",IF(COUNTIF(Mots!B:B,Liens!F70)&gt;0,"✓ "&amp;Liens!F70,"✗ "&amp;Liens!F70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H75">
+        <f>IF(Liens!G70="","",IF(COUNTIF(Mots!B:B,Liens!G70)&gt;0,"✓ "&amp;Liens!G70,"✗ "&amp;Liens!G70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I75">
+        <f>IF(Liens!H70="","",IF(COUNTIF(Mots!B:B,Liens!H70)&gt;0,"✓ "&amp;Liens!H70,"✗ "&amp;Liens!H70&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76">
+        <f>IF(Liens!A71="","",IF(COUNTIF(Mots!B:B,Liens!A71)&gt;0,"✓ "&amp;Liens!A71,"✗ "&amp;Liens!A71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>IF(Liens!B71="","",IF(COUNTIF(Mots!B:B,Liens!B71)&gt;0,"✓ "&amp;Liens!B71,"✗ "&amp;Liens!B71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>IF(Liens!C71="","",IF(COUNTIF(Mots!B:B,Liens!C71)&gt;0,"✓ "&amp;Liens!C71,"✗ "&amp;Liens!C71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>IF(Liens!D71="","",IF(COUNTIF(Mots!B:B,Liens!D71)&gt;0,"✓ "&amp;Liens!D71,"✗ "&amp;Liens!D71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>IF(Liens!E71="","",IF(COUNTIF(Mots!B:B,Liens!E71)&gt;0,"✓ "&amp;Liens!E71,"✗ "&amp;Liens!E71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>IF(Liens!F71="","",IF(COUNTIF(Mots!B:B,Liens!F71)&gt;0,"✓ "&amp;Liens!F71,"✗ "&amp;Liens!F71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>IF(Liens!G71="","",IF(COUNTIF(Mots!B:B,Liens!G71)&gt;0,"✓ "&amp;Liens!G71,"✗ "&amp;Liens!G71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>IF(Liens!H71="","",IF(COUNTIF(Mots!B:B,Liens!H71)&gt;0,"✓ "&amp;Liens!H71,"✗ "&amp;Liens!H71&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77">
+        <f>IF(Liens!A72="","",IF(COUNTIF(Mots!B:B,Liens!A72)&gt;0,"✓ "&amp;Liens!A72,"✗ "&amp;Liens!A72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>IF(Liens!B72="","",IF(COUNTIF(Mots!B:B,Liens!B72)&gt;0,"✓ "&amp;Liens!B72,"✗ "&amp;Liens!B72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>IF(Liens!C72="","",IF(COUNTIF(Mots!B:B,Liens!C72)&gt;0,"✓ "&amp;Liens!C72,"✗ "&amp;Liens!C72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>IF(Liens!D72="","",IF(COUNTIF(Mots!B:B,Liens!D72)&gt;0,"✓ "&amp;Liens!D72,"✗ "&amp;Liens!D72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>IF(Liens!E72="","",IF(COUNTIF(Mots!B:B,Liens!E72)&gt;0,"✓ "&amp;Liens!E72,"✗ "&amp;Liens!E72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>IF(Liens!F72="","",IF(COUNTIF(Mots!B:B,Liens!F72)&gt;0,"✓ "&amp;Liens!F72,"✗ "&amp;Liens!F72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H77">
+        <f>IF(Liens!G72="","",IF(COUNTIF(Mots!B:B,Liens!G72)&gt;0,"✓ "&amp;Liens!G72,"✗ "&amp;Liens!G72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>IF(Liens!H72="","",IF(COUNTIF(Mots!B:B,Liens!H72)&gt;0,"✓ "&amp;Liens!H72,"✗ "&amp;Liens!H72&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78">
+        <f>IF(Liens!A73="","",IF(COUNTIF(Mots!B:B,Liens!A73)&gt;0,"✓ "&amp;Liens!A73,"✗ "&amp;Liens!A73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>IF(Liens!B73="","",IF(COUNTIF(Mots!B:B,Liens!B73)&gt;0,"✓ "&amp;Liens!B73,"✗ "&amp;Liens!B73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>IF(Liens!C73="","",IF(COUNTIF(Mots!B:B,Liens!C73)&gt;0,"✓ "&amp;Liens!C73,"✗ "&amp;Liens!C73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>IF(Liens!D73="","",IF(COUNTIF(Mots!B:B,Liens!D73)&gt;0,"✓ "&amp;Liens!D73,"✗ "&amp;Liens!D73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>IF(Liens!E73="","",IF(COUNTIF(Mots!B:B,Liens!E73)&gt;0,"✓ "&amp;Liens!E73,"✗ "&amp;Liens!E73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>IF(Liens!F73="","",IF(COUNTIF(Mots!B:B,Liens!F73)&gt;0,"✓ "&amp;Liens!F73,"✗ "&amp;Liens!F73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>IF(Liens!G73="","",IF(COUNTIF(Mots!B:B,Liens!G73)&gt;0,"✓ "&amp;Liens!G73,"✗ "&amp;Liens!G73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>IF(Liens!H73="","",IF(COUNTIF(Mots!B:B,Liens!H73)&gt;0,"✓ "&amp;Liens!H73,"✗ "&amp;Liens!H73&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79">
+        <f>IF(Liens!A74="","",IF(COUNTIF(Mots!B:B,Liens!A74)&gt;0,"✓ "&amp;Liens!A74,"✗ "&amp;Liens!A74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>IF(Liens!B74="","",IF(COUNTIF(Mots!B:B,Liens!B74)&gt;0,"✓ "&amp;Liens!B74,"✗ "&amp;Liens!B74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>IF(Liens!C74="","",IF(COUNTIF(Mots!B:B,Liens!C74)&gt;0,"✓ "&amp;Liens!C74,"✗ "&amp;Liens!C74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E79">
+        <f>IF(Liens!D74="","",IF(COUNTIF(Mots!B:B,Liens!D74)&gt;0,"✓ "&amp;Liens!D74,"✗ "&amp;Liens!D74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F79">
+        <f>IF(Liens!E74="","",IF(COUNTIF(Mots!B:B,Liens!E74)&gt;0,"✓ "&amp;Liens!E74,"✗ "&amp;Liens!E74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>IF(Liens!F74="","",IF(COUNTIF(Mots!B:B,Liens!F74)&gt;0,"✓ "&amp;Liens!F74,"✗ "&amp;Liens!F74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H79">
+        <f>IF(Liens!G74="","",IF(COUNTIF(Mots!B:B,Liens!G74)&gt;0,"✓ "&amp;Liens!G74,"✗ "&amp;Liens!G74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I79">
+        <f>IF(Liens!H74="","",IF(COUNTIF(Mots!B:B,Liens!H74)&gt;0,"✓ "&amp;Liens!H74,"✗ "&amp;Liens!H74&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80">
+        <f>IF(Liens!A75="","",IF(COUNTIF(Mots!B:B,Liens!A75)&gt;0,"✓ "&amp;Liens!A75,"✗ "&amp;Liens!A75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>IF(Liens!B75="","",IF(COUNTIF(Mots!B:B,Liens!B75)&gt;0,"✓ "&amp;Liens!B75,"✗ "&amp;Liens!B75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>IF(Liens!C75="","",IF(COUNTIF(Mots!B:B,Liens!C75)&gt;0,"✓ "&amp;Liens!C75,"✗ "&amp;Liens!C75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>IF(Liens!D75="","",IF(COUNTIF(Mots!B:B,Liens!D75)&gt;0,"✓ "&amp;Liens!D75,"✗ "&amp;Liens!D75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>IF(Liens!E75="","",IF(COUNTIF(Mots!B:B,Liens!E75)&gt;0,"✓ "&amp;Liens!E75,"✗ "&amp;Liens!E75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>IF(Liens!F75="","",IF(COUNTIF(Mots!B:B,Liens!F75)&gt;0,"✓ "&amp;Liens!F75,"✗ "&amp;Liens!F75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>IF(Liens!G75="","",IF(COUNTIF(Mots!B:B,Liens!G75)&gt;0,"✓ "&amp;Liens!G75,"✗ "&amp;Liens!G75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>IF(Liens!H75="","",IF(COUNTIF(Mots!B:B,Liens!H75)&gt;0,"✓ "&amp;Liens!H75,"✗ "&amp;Liens!H75&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81">
+        <f>IF(Liens!A76="","",IF(COUNTIF(Mots!B:B,Liens!A76)&gt;0,"✓ "&amp;Liens!A76,"✗ "&amp;Liens!A76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>IF(Liens!B76="","",IF(COUNTIF(Mots!B:B,Liens!B76)&gt;0,"✓ "&amp;Liens!B76,"✗ "&amp;Liens!B76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>IF(Liens!C76="","",IF(COUNTIF(Mots!B:B,Liens!C76)&gt;0,"✓ "&amp;Liens!C76,"✗ "&amp;Liens!C76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>IF(Liens!D76="","",IF(COUNTIF(Mots!B:B,Liens!D76)&gt;0,"✓ "&amp;Liens!D76,"✗ "&amp;Liens!D76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>IF(Liens!E76="","",IF(COUNTIF(Mots!B:B,Liens!E76)&gt;0,"✓ "&amp;Liens!E76,"✗ "&amp;Liens!E76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>IF(Liens!F76="","",IF(COUNTIF(Mots!B:B,Liens!F76)&gt;0,"✓ "&amp;Liens!F76,"✗ "&amp;Liens!F76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H81">
+        <f>IF(Liens!G76="","",IF(COUNTIF(Mots!B:B,Liens!G76)&gt;0,"✓ "&amp;Liens!G76,"✗ "&amp;Liens!G76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>IF(Liens!H76="","",IF(COUNTIF(Mots!B:B,Liens!H76)&gt;0,"✓ "&amp;Liens!H76,"✗ "&amp;Liens!H76&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82">
+        <f>IF(Liens!A77="","",IF(COUNTIF(Mots!B:B,Liens!A77)&gt;0,"✓ "&amp;Liens!A77,"✗ "&amp;Liens!A77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>IF(Liens!B77="","",IF(COUNTIF(Mots!B:B,Liens!B77)&gt;0,"✓ "&amp;Liens!B77,"✗ "&amp;Liens!B77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>IF(Liens!C77="","",IF(COUNTIF(Mots!B:B,Liens!C77)&gt;0,"✓ "&amp;Liens!C77,"✗ "&amp;Liens!C77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>IF(Liens!D77="","",IF(COUNTIF(Mots!B:B,Liens!D77)&gt;0,"✓ "&amp;Liens!D77,"✗ "&amp;Liens!D77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>IF(Liens!E77="","",IF(COUNTIF(Mots!B:B,Liens!E77)&gt;0,"✓ "&amp;Liens!E77,"✗ "&amp;Liens!E77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>IF(Liens!F77="","",IF(COUNTIF(Mots!B:B,Liens!F77)&gt;0,"✓ "&amp;Liens!F77,"✗ "&amp;Liens!F77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H82">
+        <f>IF(Liens!G77="","",IF(COUNTIF(Mots!B:B,Liens!G77)&gt;0,"✓ "&amp;Liens!G77,"✗ "&amp;Liens!G77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>IF(Liens!H77="","",IF(COUNTIF(Mots!B:B,Liens!H77)&gt;0,"✓ "&amp;Liens!H77,"✗ "&amp;Liens!H77&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83">
+        <f>IF(Liens!A78="","",IF(COUNTIF(Mots!B:B,Liens!A78)&gt;0,"✓ "&amp;Liens!A78,"✗ "&amp;Liens!A78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>IF(Liens!B78="","",IF(COUNTIF(Mots!B:B,Liens!B78)&gt;0,"✓ "&amp;Liens!B78,"✗ "&amp;Liens!B78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D83">
+        <f>IF(Liens!C78="","",IF(COUNTIF(Mots!B:B,Liens!C78)&gt;0,"✓ "&amp;Liens!C78,"✗ "&amp;Liens!C78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E83">
+        <f>IF(Liens!D78="","",IF(COUNTIF(Mots!B:B,Liens!D78)&gt;0,"✓ "&amp;Liens!D78,"✗ "&amp;Liens!D78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F83">
+        <f>IF(Liens!E78="","",IF(COUNTIF(Mots!B:B,Liens!E78)&gt;0,"✓ "&amp;Liens!E78,"✗ "&amp;Liens!E78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G83">
+        <f>IF(Liens!F78="","",IF(COUNTIF(Mots!B:B,Liens!F78)&gt;0,"✓ "&amp;Liens!F78,"✗ "&amp;Liens!F78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H83">
+        <f>IF(Liens!G78="","",IF(COUNTIF(Mots!B:B,Liens!G78)&gt;0,"✓ "&amp;Liens!G78,"✗ "&amp;Liens!G78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I83">
+        <f>IF(Liens!H78="","",IF(COUNTIF(Mots!B:B,Liens!H78)&gt;0,"✓ "&amp;Liens!H78,"✗ "&amp;Liens!H78&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84">
+        <f>IF(Liens!A79="","",IF(COUNTIF(Mots!B:B,Liens!A79)&gt;0,"✓ "&amp;Liens!A79,"✗ "&amp;Liens!A79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>IF(Liens!B79="","",IF(COUNTIF(Mots!B:B,Liens!B79)&gt;0,"✓ "&amp;Liens!B79,"✗ "&amp;Liens!B79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D84">
+        <f>IF(Liens!C79="","",IF(COUNTIF(Mots!B:B,Liens!C79)&gt;0,"✓ "&amp;Liens!C79,"✗ "&amp;Liens!C79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E84">
+        <f>IF(Liens!D79="","",IF(COUNTIF(Mots!B:B,Liens!D79)&gt;0,"✓ "&amp;Liens!D79,"✗ "&amp;Liens!D79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F84">
+        <f>IF(Liens!E79="","",IF(COUNTIF(Mots!B:B,Liens!E79)&gt;0,"✓ "&amp;Liens!E79,"✗ "&amp;Liens!E79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G84">
+        <f>IF(Liens!F79="","",IF(COUNTIF(Mots!B:B,Liens!F79)&gt;0,"✓ "&amp;Liens!F79,"✗ "&amp;Liens!F79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H84">
+        <f>IF(Liens!G79="","",IF(COUNTIF(Mots!B:B,Liens!G79)&gt;0,"✓ "&amp;Liens!G79,"✗ "&amp;Liens!G79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I84">
+        <f>IF(Liens!H79="","",IF(COUNTIF(Mots!B:B,Liens!H79)&gt;0,"✓ "&amp;Liens!H79,"✗ "&amp;Liens!H79&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85">
+        <f>IF(Liens!A80="","",IF(COUNTIF(Mots!B:B,Liens!A80)&gt;0,"✓ "&amp;Liens!A80,"✗ "&amp;Liens!A80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>IF(Liens!B80="","",IF(COUNTIF(Mots!B:B,Liens!B80)&gt;0,"✓ "&amp;Liens!B80,"✗ "&amp;Liens!B80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>IF(Liens!C80="","",IF(COUNTIF(Mots!B:B,Liens!C80)&gt;0,"✓ "&amp;Liens!C80,"✗ "&amp;Liens!C80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>IF(Liens!D80="","",IF(COUNTIF(Mots!B:B,Liens!D80)&gt;0,"✓ "&amp;Liens!D80,"✗ "&amp;Liens!D80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>IF(Liens!E80="","",IF(COUNTIF(Mots!B:B,Liens!E80)&gt;0,"✓ "&amp;Liens!E80,"✗ "&amp;Liens!E80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>IF(Liens!F80="","",IF(COUNTIF(Mots!B:B,Liens!F80)&gt;0,"✓ "&amp;Liens!F80,"✗ "&amp;Liens!F80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H85">
+        <f>IF(Liens!G80="","",IF(COUNTIF(Mots!B:B,Liens!G80)&gt;0,"✓ "&amp;Liens!G80,"✗ "&amp;Liens!G80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>IF(Liens!H80="","",IF(COUNTIF(Mots!B:B,Liens!H80)&gt;0,"✓ "&amp;Liens!H80,"✗ "&amp;Liens!H80&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86">
+        <f>IF(Liens!A81="","",IF(COUNTIF(Mots!B:B,Liens!A81)&gt;0,"✓ "&amp;Liens!A81,"✗ "&amp;Liens!A81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C86">
+        <f>IF(Liens!B81="","",IF(COUNTIF(Mots!B:B,Liens!B81)&gt;0,"✓ "&amp;Liens!B81,"✗ "&amp;Liens!B81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D86">
+        <f>IF(Liens!C81="","",IF(COUNTIF(Mots!B:B,Liens!C81)&gt;0,"✓ "&amp;Liens!C81,"✗ "&amp;Liens!C81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E86">
+        <f>IF(Liens!D81="","",IF(COUNTIF(Mots!B:B,Liens!D81)&gt;0,"✓ "&amp;Liens!D81,"✗ "&amp;Liens!D81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F86">
+        <f>IF(Liens!E81="","",IF(COUNTIF(Mots!B:B,Liens!E81)&gt;0,"✓ "&amp;Liens!E81,"✗ "&amp;Liens!E81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G86">
+        <f>IF(Liens!F81="","",IF(COUNTIF(Mots!B:B,Liens!F81)&gt;0,"✓ "&amp;Liens!F81,"✗ "&amp;Liens!F81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H86">
+        <f>IF(Liens!G81="","",IF(COUNTIF(Mots!B:B,Liens!G81)&gt;0,"✓ "&amp;Liens!G81,"✗ "&amp;Liens!G81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I86">
+        <f>IF(Liens!H81="","",IF(COUNTIF(Mots!B:B,Liens!H81)&gt;0,"✓ "&amp;Liens!H81,"✗ "&amp;Liens!H81&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87">
+        <f>IF(Liens!A82="","",IF(COUNTIF(Mots!B:B,Liens!A82)&gt;0,"✓ "&amp;Liens!A82,"✗ "&amp;Liens!A82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C87">
+        <f>IF(Liens!B82="","",IF(COUNTIF(Mots!B:B,Liens!B82)&gt;0,"✓ "&amp;Liens!B82,"✗ "&amp;Liens!B82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D87">
+        <f>IF(Liens!C82="","",IF(COUNTIF(Mots!B:B,Liens!C82)&gt;0,"✓ "&amp;Liens!C82,"✗ "&amp;Liens!C82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E87">
+        <f>IF(Liens!D82="","",IF(COUNTIF(Mots!B:B,Liens!D82)&gt;0,"✓ "&amp;Liens!D82,"✗ "&amp;Liens!D82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F87">
+        <f>IF(Liens!E82="","",IF(COUNTIF(Mots!B:B,Liens!E82)&gt;0,"✓ "&amp;Liens!E82,"✗ "&amp;Liens!E82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G87">
+        <f>IF(Liens!F82="","",IF(COUNTIF(Mots!B:B,Liens!F82)&gt;0,"✓ "&amp;Liens!F82,"✗ "&amp;Liens!F82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H87">
+        <f>IF(Liens!G82="","",IF(COUNTIF(Mots!B:B,Liens!G82)&gt;0,"✓ "&amp;Liens!G82,"✗ "&amp;Liens!G82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I87">
+        <f>IF(Liens!H82="","",IF(COUNTIF(Mots!B:B,Liens!H82)&gt;0,"✓ "&amp;Liens!H82,"✗ "&amp;Liens!H82&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88">
+        <f>IF(Liens!A83="","",IF(COUNTIF(Mots!B:B,Liens!A83)&gt;0,"✓ "&amp;Liens!A83,"✗ "&amp;Liens!A83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C88">
+        <f>IF(Liens!B83="","",IF(COUNTIF(Mots!B:B,Liens!B83)&gt;0,"✓ "&amp;Liens!B83,"✗ "&amp;Liens!B83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D88">
+        <f>IF(Liens!C83="","",IF(COUNTIF(Mots!B:B,Liens!C83)&gt;0,"✓ "&amp;Liens!C83,"✗ "&amp;Liens!C83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E88">
+        <f>IF(Liens!D83="","",IF(COUNTIF(Mots!B:B,Liens!D83)&gt;0,"✓ "&amp;Liens!D83,"✗ "&amp;Liens!D83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F88">
+        <f>IF(Liens!E83="","",IF(COUNTIF(Mots!B:B,Liens!E83)&gt;0,"✓ "&amp;Liens!E83,"✗ "&amp;Liens!E83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G88">
+        <f>IF(Liens!F83="","",IF(COUNTIF(Mots!B:B,Liens!F83)&gt;0,"✓ "&amp;Liens!F83,"✗ "&amp;Liens!F83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H88">
+        <f>IF(Liens!G83="","",IF(COUNTIF(Mots!B:B,Liens!G83)&gt;0,"✓ "&amp;Liens!G83,"✗ "&amp;Liens!G83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I88">
+        <f>IF(Liens!H83="","",IF(COUNTIF(Mots!B:B,Liens!H83)&gt;0,"✓ "&amp;Liens!H83,"✗ "&amp;Liens!H83&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89">
+        <f>IF(Liens!A84="","",IF(COUNTIF(Mots!B:B,Liens!A84)&gt;0,"✓ "&amp;Liens!A84,"✗ "&amp;Liens!A84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C89">
+        <f>IF(Liens!B84="","",IF(COUNTIF(Mots!B:B,Liens!B84)&gt;0,"✓ "&amp;Liens!B84,"✗ "&amp;Liens!B84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D89">
+        <f>IF(Liens!C84="","",IF(COUNTIF(Mots!B:B,Liens!C84)&gt;0,"✓ "&amp;Liens!C84,"✗ "&amp;Liens!C84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E89">
+        <f>IF(Liens!D84="","",IF(COUNTIF(Mots!B:B,Liens!D84)&gt;0,"✓ "&amp;Liens!D84,"✗ "&amp;Liens!D84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F89">
+        <f>IF(Liens!E84="","",IF(COUNTIF(Mots!B:B,Liens!E84)&gt;0,"✓ "&amp;Liens!E84,"✗ "&amp;Liens!E84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G89">
+        <f>IF(Liens!F84="","",IF(COUNTIF(Mots!B:B,Liens!F84)&gt;0,"✓ "&amp;Liens!F84,"✗ "&amp;Liens!F84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H89">
+        <f>IF(Liens!G84="","",IF(COUNTIF(Mots!B:B,Liens!G84)&gt;0,"✓ "&amp;Liens!G84,"✗ "&amp;Liens!G84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I89">
+        <f>IF(Liens!H84="","",IF(COUNTIF(Mots!B:B,Liens!H84)&gt;0,"✓ "&amp;Liens!H84,"✗ "&amp;Liens!H84&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90">
+        <f>IF(Liens!A85="","",IF(COUNTIF(Mots!B:B,Liens!A85)&gt;0,"✓ "&amp;Liens!A85,"✗ "&amp;Liens!A85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C90">
+        <f>IF(Liens!B85="","",IF(COUNTIF(Mots!B:B,Liens!B85)&gt;0,"✓ "&amp;Liens!B85,"✗ "&amp;Liens!B85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D90">
+        <f>IF(Liens!C85="","",IF(COUNTIF(Mots!B:B,Liens!C85)&gt;0,"✓ "&amp;Liens!C85,"✗ "&amp;Liens!C85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E90">
+        <f>IF(Liens!D85="","",IF(COUNTIF(Mots!B:B,Liens!D85)&gt;0,"✓ "&amp;Liens!D85,"✗ "&amp;Liens!D85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F90">
+        <f>IF(Liens!E85="","",IF(COUNTIF(Mots!B:B,Liens!E85)&gt;0,"✓ "&amp;Liens!E85,"✗ "&amp;Liens!E85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G90">
+        <f>IF(Liens!F85="","",IF(COUNTIF(Mots!B:B,Liens!F85)&gt;0,"✓ "&amp;Liens!F85,"✗ "&amp;Liens!F85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H90">
+        <f>IF(Liens!G85="","",IF(COUNTIF(Mots!B:B,Liens!G85)&gt;0,"✓ "&amp;Liens!G85,"✗ "&amp;Liens!G85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I90">
+        <f>IF(Liens!H85="","",IF(COUNTIF(Mots!B:B,Liens!H85)&gt;0,"✓ "&amp;Liens!H85,"✗ "&amp;Liens!H85&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91">
+        <f>IF(Liens!A86="","",IF(COUNTIF(Mots!B:B,Liens!A86)&gt;0,"✓ "&amp;Liens!A86,"✗ "&amp;Liens!A86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C91">
+        <f>IF(Liens!B86="","",IF(COUNTIF(Mots!B:B,Liens!B86)&gt;0,"✓ "&amp;Liens!B86,"✗ "&amp;Liens!B86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D91">
+        <f>IF(Liens!C86="","",IF(COUNTIF(Mots!B:B,Liens!C86)&gt;0,"✓ "&amp;Liens!C86,"✗ "&amp;Liens!C86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E91">
+        <f>IF(Liens!D86="","",IF(COUNTIF(Mots!B:B,Liens!D86)&gt;0,"✓ "&amp;Liens!D86,"✗ "&amp;Liens!D86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F91">
+        <f>IF(Liens!E86="","",IF(COUNTIF(Mots!B:B,Liens!E86)&gt;0,"✓ "&amp;Liens!E86,"✗ "&amp;Liens!E86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G91">
+        <f>IF(Liens!F86="","",IF(COUNTIF(Mots!B:B,Liens!F86)&gt;0,"✓ "&amp;Liens!F86,"✗ "&amp;Liens!F86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H91">
+        <f>IF(Liens!G86="","",IF(COUNTIF(Mots!B:B,Liens!G86)&gt;0,"✓ "&amp;Liens!G86,"✗ "&amp;Liens!G86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I91">
+        <f>IF(Liens!H86="","",IF(COUNTIF(Mots!B:B,Liens!H86)&gt;0,"✓ "&amp;Liens!H86,"✗ "&amp;Liens!H86&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92">
+        <f>IF(Liens!A87="","",IF(COUNTIF(Mots!B:B,Liens!A87)&gt;0,"✓ "&amp;Liens!A87,"✗ "&amp;Liens!A87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>IF(Liens!B87="","",IF(COUNTIF(Mots!B:B,Liens!B87)&gt;0,"✓ "&amp;Liens!B87,"✗ "&amp;Liens!B87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>IF(Liens!C87="","",IF(COUNTIF(Mots!B:B,Liens!C87)&gt;0,"✓ "&amp;Liens!C87,"✗ "&amp;Liens!C87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>IF(Liens!D87="","",IF(COUNTIF(Mots!B:B,Liens!D87)&gt;0,"✓ "&amp;Liens!D87,"✗ "&amp;Liens!D87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>IF(Liens!E87="","",IF(COUNTIF(Mots!B:B,Liens!E87)&gt;0,"✓ "&amp;Liens!E87,"✗ "&amp;Liens!E87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G92">
+        <f>IF(Liens!F87="","",IF(COUNTIF(Mots!B:B,Liens!F87)&gt;0,"✓ "&amp;Liens!F87,"✗ "&amp;Liens!F87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H92">
+        <f>IF(Liens!G87="","",IF(COUNTIF(Mots!B:B,Liens!G87)&gt;0,"✓ "&amp;Liens!G87,"✗ "&amp;Liens!G87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I92">
+        <f>IF(Liens!H87="","",IF(COUNTIF(Mots!B:B,Liens!H87)&gt;0,"✓ "&amp;Liens!H87,"✗ "&amp;Liens!H87&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93">
+        <f>IF(Liens!A88="","",IF(COUNTIF(Mots!B:B,Liens!A88)&gt;0,"✓ "&amp;Liens!A88,"✗ "&amp;Liens!A88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C93">
+        <f>IF(Liens!B88="","",IF(COUNTIF(Mots!B:B,Liens!B88)&gt;0,"✓ "&amp;Liens!B88,"✗ "&amp;Liens!B88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>IF(Liens!C88="","",IF(COUNTIF(Mots!B:B,Liens!C88)&gt;0,"✓ "&amp;Liens!C88,"✗ "&amp;Liens!C88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E93">
+        <f>IF(Liens!D88="","",IF(COUNTIF(Mots!B:B,Liens!D88)&gt;0,"✓ "&amp;Liens!D88,"✗ "&amp;Liens!D88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F93">
+        <f>IF(Liens!E88="","",IF(COUNTIF(Mots!B:B,Liens!E88)&gt;0,"✓ "&amp;Liens!E88,"✗ "&amp;Liens!E88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G93">
+        <f>IF(Liens!F88="","",IF(COUNTIF(Mots!B:B,Liens!F88)&gt;0,"✓ "&amp;Liens!F88,"✗ "&amp;Liens!F88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H93">
+        <f>IF(Liens!G88="","",IF(COUNTIF(Mots!B:B,Liens!G88)&gt;0,"✓ "&amp;Liens!G88,"✗ "&amp;Liens!G88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I93">
+        <f>IF(Liens!H88="","",IF(COUNTIF(Mots!B:B,Liens!H88)&gt;0,"✓ "&amp;Liens!H88,"✗ "&amp;Liens!H88&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94">
+        <f>IF(Liens!A89="","",IF(COUNTIF(Mots!B:B,Liens!A89)&gt;0,"✓ "&amp;Liens!A89,"✗ "&amp;Liens!A89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>IF(Liens!B89="","",IF(COUNTIF(Mots!B:B,Liens!B89)&gt;0,"✓ "&amp;Liens!B89,"✗ "&amp;Liens!B89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D94">
+        <f>IF(Liens!C89="","",IF(COUNTIF(Mots!B:B,Liens!C89)&gt;0,"✓ "&amp;Liens!C89,"✗ "&amp;Liens!C89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E94">
+        <f>IF(Liens!D89="","",IF(COUNTIF(Mots!B:B,Liens!D89)&gt;0,"✓ "&amp;Liens!D89,"✗ "&amp;Liens!D89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F94">
+        <f>IF(Liens!E89="","",IF(COUNTIF(Mots!B:B,Liens!E89)&gt;0,"✓ "&amp;Liens!E89,"✗ "&amp;Liens!E89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G94">
+        <f>IF(Liens!F89="","",IF(COUNTIF(Mots!B:B,Liens!F89)&gt;0,"✓ "&amp;Liens!F89,"✗ "&amp;Liens!F89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H94">
+        <f>IF(Liens!G89="","",IF(COUNTIF(Mots!B:B,Liens!G89)&gt;0,"✓ "&amp;Liens!G89,"✗ "&amp;Liens!G89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I94">
+        <f>IF(Liens!H89="","",IF(COUNTIF(Mots!B:B,Liens!H89)&gt;0,"✓ "&amp;Liens!H89,"✗ "&amp;Liens!H89&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95">
+        <f>IF(Liens!A90="","",IF(COUNTIF(Mots!B:B,Liens!A90)&gt;0,"✓ "&amp;Liens!A90,"✗ "&amp;Liens!A90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C95">
+        <f>IF(Liens!B90="","",IF(COUNTIF(Mots!B:B,Liens!B90)&gt;0,"✓ "&amp;Liens!B90,"✗ "&amp;Liens!B90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D95">
+        <f>IF(Liens!C90="","",IF(COUNTIF(Mots!B:B,Liens!C90)&gt;0,"✓ "&amp;Liens!C90,"✗ "&amp;Liens!C90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E95">
+        <f>IF(Liens!D90="","",IF(COUNTIF(Mots!B:B,Liens!D90)&gt;0,"✓ "&amp;Liens!D90,"✗ "&amp;Liens!D90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F95">
+        <f>IF(Liens!E90="","",IF(COUNTIF(Mots!B:B,Liens!E90)&gt;0,"✓ "&amp;Liens!E90,"✗ "&amp;Liens!E90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G95">
+        <f>IF(Liens!F90="","",IF(COUNTIF(Mots!B:B,Liens!F90)&gt;0,"✓ "&amp;Liens!F90,"✗ "&amp;Liens!F90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H95">
+        <f>IF(Liens!G90="","",IF(COUNTIF(Mots!B:B,Liens!G90)&gt;0,"✓ "&amp;Liens!G90,"✗ "&amp;Liens!G90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I95">
+        <f>IF(Liens!H90="","",IF(COUNTIF(Mots!B:B,Liens!H90)&gt;0,"✓ "&amp;Liens!H90,"✗ "&amp;Liens!H90&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96">
+        <f>IF(Liens!A91="","",IF(COUNTIF(Mots!B:B,Liens!A91)&gt;0,"✓ "&amp;Liens!A91,"✗ "&amp;Liens!A91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>IF(Liens!B91="","",IF(COUNTIF(Mots!B:B,Liens!B91)&gt;0,"✓ "&amp;Liens!B91,"✗ "&amp;Liens!B91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>IF(Liens!C91="","",IF(COUNTIF(Mots!B:B,Liens!C91)&gt;0,"✓ "&amp;Liens!C91,"✗ "&amp;Liens!C91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>IF(Liens!D91="","",IF(COUNTIF(Mots!B:B,Liens!D91)&gt;0,"✓ "&amp;Liens!D91,"✗ "&amp;Liens!D91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>IF(Liens!E91="","",IF(COUNTIF(Mots!B:B,Liens!E91)&gt;0,"✓ "&amp;Liens!E91,"✗ "&amp;Liens!E91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G96">
+        <f>IF(Liens!F91="","",IF(COUNTIF(Mots!B:B,Liens!F91)&gt;0,"✓ "&amp;Liens!F91,"✗ "&amp;Liens!F91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H96">
+        <f>IF(Liens!G91="","",IF(COUNTIF(Mots!B:B,Liens!G91)&gt;0,"✓ "&amp;Liens!G91,"✗ "&amp;Liens!G91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I96">
+        <f>IF(Liens!H91="","",IF(COUNTIF(Mots!B:B,Liens!H91)&gt;0,"✓ "&amp;Liens!H91,"✗ "&amp;Liens!H91&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97">
+        <f>IF(Liens!A92="","",IF(COUNTIF(Mots!B:B,Liens!A92)&gt;0,"✓ "&amp;Liens!A92,"✗ "&amp;Liens!A92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C97">
+        <f>IF(Liens!B92="","",IF(COUNTIF(Mots!B:B,Liens!B92)&gt;0,"✓ "&amp;Liens!B92,"✗ "&amp;Liens!B92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D97">
+        <f>IF(Liens!C92="","",IF(COUNTIF(Mots!B:B,Liens!C92)&gt;0,"✓ "&amp;Liens!C92,"✗ "&amp;Liens!C92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E97">
+        <f>IF(Liens!D92="","",IF(COUNTIF(Mots!B:B,Liens!D92)&gt;0,"✓ "&amp;Liens!D92,"✗ "&amp;Liens!D92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F97">
+        <f>IF(Liens!E92="","",IF(COUNTIF(Mots!B:B,Liens!E92)&gt;0,"✓ "&amp;Liens!E92,"✗ "&amp;Liens!E92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G97">
+        <f>IF(Liens!F92="","",IF(COUNTIF(Mots!B:B,Liens!F92)&gt;0,"✓ "&amp;Liens!F92,"✗ "&amp;Liens!F92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H97">
+        <f>IF(Liens!G92="","",IF(COUNTIF(Mots!B:B,Liens!G92)&gt;0,"✓ "&amp;Liens!G92,"✗ "&amp;Liens!G92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I97">
+        <f>IF(Liens!H92="","",IF(COUNTIF(Mots!B:B,Liens!H92)&gt;0,"✓ "&amp;Liens!H92,"✗ "&amp;Liens!H92&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98">
+        <f>IF(Liens!A93="","",IF(COUNTIF(Mots!B:B,Liens!A93)&gt;0,"✓ "&amp;Liens!A93,"✗ "&amp;Liens!A93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>IF(Liens!B93="","",IF(COUNTIF(Mots!B:B,Liens!B93)&gt;0,"✓ "&amp;Liens!B93,"✗ "&amp;Liens!B93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>IF(Liens!C93="","",IF(COUNTIF(Mots!B:B,Liens!C93)&gt;0,"✓ "&amp;Liens!C93,"✗ "&amp;Liens!C93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>IF(Liens!D93="","",IF(COUNTIF(Mots!B:B,Liens!D93)&gt;0,"✓ "&amp;Liens!D93,"✗ "&amp;Liens!D93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF(Liens!E93="","",IF(COUNTIF(Mots!B:B,Liens!E93)&gt;0,"✓ "&amp;Liens!E93,"✗ "&amp;Liens!E93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G98">
+        <f>IF(Liens!F93="","",IF(COUNTIF(Mots!B:B,Liens!F93)&gt;0,"✓ "&amp;Liens!F93,"✗ "&amp;Liens!F93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H98">
+        <f>IF(Liens!G93="","",IF(COUNTIF(Mots!B:B,Liens!G93)&gt;0,"✓ "&amp;Liens!G93,"✗ "&amp;Liens!G93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I98">
+        <f>IF(Liens!H93="","",IF(COUNTIF(Mots!B:B,Liens!H93)&gt;0,"✓ "&amp;Liens!H93,"✗ "&amp;Liens!H93&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99">
+        <f>IF(Liens!A94="","",IF(COUNTIF(Mots!B:B,Liens!A94)&gt;0,"✓ "&amp;Liens!A94,"✗ "&amp;Liens!A94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>IF(Liens!B94="","",IF(COUNTIF(Mots!B:B,Liens!B94)&gt;0,"✓ "&amp;Liens!B94,"✗ "&amp;Liens!B94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>IF(Liens!C94="","",IF(COUNTIF(Mots!B:B,Liens!C94)&gt;0,"✓ "&amp;Liens!C94,"✗ "&amp;Liens!C94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E99">
+        <f>IF(Liens!D94="","",IF(COUNTIF(Mots!B:B,Liens!D94)&gt;0,"✓ "&amp;Liens!D94,"✗ "&amp;Liens!D94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>IF(Liens!E94="","",IF(COUNTIF(Mots!B:B,Liens!E94)&gt;0,"✓ "&amp;Liens!E94,"✗ "&amp;Liens!E94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G99">
+        <f>IF(Liens!F94="","",IF(COUNTIF(Mots!B:B,Liens!F94)&gt;0,"✓ "&amp;Liens!F94,"✗ "&amp;Liens!F94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H99">
+        <f>IF(Liens!G94="","",IF(COUNTIF(Mots!B:B,Liens!G94)&gt;0,"✓ "&amp;Liens!G94,"✗ "&amp;Liens!G94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I99">
+        <f>IF(Liens!H94="","",IF(COUNTIF(Mots!B:B,Liens!H94)&gt;0,"✓ "&amp;Liens!H94,"✗ "&amp;Liens!H94&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100">
+        <f>IF(Liens!A95="","",IF(COUNTIF(Mots!B:B,Liens!A95)&gt;0,"✓ "&amp;Liens!A95,"✗ "&amp;Liens!A95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>IF(Liens!B95="","",IF(COUNTIF(Mots!B:B,Liens!B95)&gt;0,"✓ "&amp;Liens!B95,"✗ "&amp;Liens!B95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>IF(Liens!C95="","",IF(COUNTIF(Mots!B:B,Liens!C95)&gt;0,"✓ "&amp;Liens!C95,"✗ "&amp;Liens!C95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>IF(Liens!D95="","",IF(COUNTIF(Mots!B:B,Liens!D95)&gt;0,"✓ "&amp;Liens!D95,"✗ "&amp;Liens!D95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>IF(Liens!E95="","",IF(COUNTIF(Mots!B:B,Liens!E95)&gt;0,"✓ "&amp;Liens!E95,"✗ "&amp;Liens!E95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G100">
+        <f>IF(Liens!F95="","",IF(COUNTIF(Mots!B:B,Liens!F95)&gt;0,"✓ "&amp;Liens!F95,"✗ "&amp;Liens!F95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H100">
+        <f>IF(Liens!G95="","",IF(COUNTIF(Mots!B:B,Liens!G95)&gt;0,"✓ "&amp;Liens!G95,"✗ "&amp;Liens!G95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I100">
+        <f>IF(Liens!H95="","",IF(COUNTIF(Mots!B:B,Liens!H95)&gt;0,"✓ "&amp;Liens!H95,"✗ "&amp;Liens!H95&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101">
+        <f>IF(Liens!A96="","",IF(COUNTIF(Mots!B:B,Liens!A96)&gt;0,"✓ "&amp;Liens!A96,"✗ "&amp;Liens!A96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>IF(Liens!B96="","",IF(COUNTIF(Mots!B:B,Liens!B96)&gt;0,"✓ "&amp;Liens!B96,"✗ "&amp;Liens!B96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>IF(Liens!C96="","",IF(COUNTIF(Mots!B:B,Liens!C96)&gt;0,"✓ "&amp;Liens!C96,"✗ "&amp;Liens!C96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>IF(Liens!D96="","",IF(COUNTIF(Mots!B:B,Liens!D96)&gt;0,"✓ "&amp;Liens!D96,"✗ "&amp;Liens!D96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF(Liens!E96="","",IF(COUNTIF(Mots!B:B,Liens!E96)&gt;0,"✓ "&amp;Liens!E96,"✗ "&amp;Liens!E96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G101">
+        <f>IF(Liens!F96="","",IF(COUNTIF(Mots!B:B,Liens!F96)&gt;0,"✓ "&amp;Liens!F96,"✗ "&amp;Liens!F96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H101">
+        <f>IF(Liens!G96="","",IF(COUNTIF(Mots!B:B,Liens!G96)&gt;0,"✓ "&amp;Liens!G96,"✗ "&amp;Liens!G96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I101">
+        <f>IF(Liens!H96="","",IF(COUNTIF(Mots!B:B,Liens!H96)&gt;0,"✓ "&amp;Liens!H96,"✗ "&amp;Liens!H96&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102">
+        <f>IF(Liens!A97="","",IF(COUNTIF(Mots!B:B,Liens!A97)&gt;0,"✓ "&amp;Liens!A97,"✗ "&amp;Liens!A97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C102">
+        <f>IF(Liens!B97="","",IF(COUNTIF(Mots!B:B,Liens!B97)&gt;0,"✓ "&amp;Liens!B97,"✗ "&amp;Liens!B97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D102">
+        <f>IF(Liens!C97="","",IF(COUNTIF(Mots!B:B,Liens!C97)&gt;0,"✓ "&amp;Liens!C97,"✗ "&amp;Liens!C97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E102">
+        <f>IF(Liens!D97="","",IF(COUNTIF(Mots!B:B,Liens!D97)&gt;0,"✓ "&amp;Liens!D97,"✗ "&amp;Liens!D97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F102">
+        <f>IF(Liens!E97="","",IF(COUNTIF(Mots!B:B,Liens!E97)&gt;0,"✓ "&amp;Liens!E97,"✗ "&amp;Liens!E97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G102">
+        <f>IF(Liens!F97="","",IF(COUNTIF(Mots!B:B,Liens!F97)&gt;0,"✓ "&amp;Liens!F97,"✗ "&amp;Liens!F97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H102">
+        <f>IF(Liens!G97="","",IF(COUNTIF(Mots!B:B,Liens!G97)&gt;0,"✓ "&amp;Liens!G97,"✗ "&amp;Liens!G97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I102">
+        <f>IF(Liens!H97="","",IF(COUNTIF(Mots!B:B,Liens!H97)&gt;0,"✓ "&amp;Liens!H97,"✗ "&amp;Liens!H97&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103">
+        <f>IF(Liens!A98="","",IF(COUNTIF(Mots!B:B,Liens!A98)&gt;0,"✓ "&amp;Liens!A98,"✗ "&amp;Liens!A98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C103">
+        <f>IF(Liens!B98="","",IF(COUNTIF(Mots!B:B,Liens!B98)&gt;0,"✓ "&amp;Liens!B98,"✗ "&amp;Liens!B98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D103">
+        <f>IF(Liens!C98="","",IF(COUNTIF(Mots!B:B,Liens!C98)&gt;0,"✓ "&amp;Liens!C98,"✗ "&amp;Liens!C98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E103">
+        <f>IF(Liens!D98="","",IF(COUNTIF(Mots!B:B,Liens!D98)&gt;0,"✓ "&amp;Liens!D98,"✗ "&amp;Liens!D98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F103">
+        <f>IF(Liens!E98="","",IF(COUNTIF(Mots!B:B,Liens!E98)&gt;0,"✓ "&amp;Liens!E98,"✗ "&amp;Liens!E98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G103">
+        <f>IF(Liens!F98="","",IF(COUNTIF(Mots!B:B,Liens!F98)&gt;0,"✓ "&amp;Liens!F98,"✗ "&amp;Liens!F98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H103">
+        <f>IF(Liens!G98="","",IF(COUNTIF(Mots!B:B,Liens!G98)&gt;0,"✓ "&amp;Liens!G98,"✗ "&amp;Liens!G98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I103">
+        <f>IF(Liens!H98="","",IF(COUNTIF(Mots!B:B,Liens!H98)&gt;0,"✓ "&amp;Liens!H98,"✗ "&amp;Liens!H98&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104">
+        <f>IF(Liens!A99="","",IF(COUNTIF(Mots!B:B,Liens!A99)&gt;0,"✓ "&amp;Liens!A99,"✗ "&amp;Liens!A99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>IF(Liens!B99="","",IF(COUNTIF(Mots!B:B,Liens!B99)&gt;0,"✓ "&amp;Liens!B99,"✗ "&amp;Liens!B99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D104">
+        <f>IF(Liens!C99="","",IF(COUNTIF(Mots!B:B,Liens!C99)&gt;0,"✓ "&amp;Liens!C99,"✗ "&amp;Liens!C99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E104">
+        <f>IF(Liens!D99="","",IF(COUNTIF(Mots!B:B,Liens!D99)&gt;0,"✓ "&amp;Liens!D99,"✗ "&amp;Liens!D99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F104">
+        <f>IF(Liens!E99="","",IF(COUNTIF(Mots!B:B,Liens!E99)&gt;0,"✓ "&amp;Liens!E99,"✗ "&amp;Liens!E99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G104">
+        <f>IF(Liens!F99="","",IF(COUNTIF(Mots!B:B,Liens!F99)&gt;0,"✓ "&amp;Liens!F99,"✗ "&amp;Liens!F99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H104">
+        <f>IF(Liens!G99="","",IF(COUNTIF(Mots!B:B,Liens!G99)&gt;0,"✓ "&amp;Liens!G99,"✗ "&amp;Liens!G99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I104">
+        <f>IF(Liens!H99="","",IF(COUNTIF(Mots!B:B,Liens!H99)&gt;0,"✓ "&amp;Liens!H99,"✗ "&amp;Liens!H99&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105">
+        <f>IF(Liens!A100="","",IF(COUNTIF(Mots!B:B,Liens!A100)&gt;0,"✓ "&amp;Liens!A100,"✗ "&amp;Liens!A100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C105">
+        <f>IF(Liens!B100="","",IF(COUNTIF(Mots!B:B,Liens!B100)&gt;0,"✓ "&amp;Liens!B100,"✗ "&amp;Liens!B100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D105">
+        <f>IF(Liens!C100="","",IF(COUNTIF(Mots!B:B,Liens!C100)&gt;0,"✓ "&amp;Liens!C100,"✗ "&amp;Liens!C100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E105">
+        <f>IF(Liens!D100="","",IF(COUNTIF(Mots!B:B,Liens!D100)&gt;0,"✓ "&amp;Liens!D100,"✗ "&amp;Liens!D100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F105">
+        <f>IF(Liens!E100="","",IF(COUNTIF(Mots!B:B,Liens!E100)&gt;0,"✓ "&amp;Liens!E100,"✗ "&amp;Liens!E100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G105">
+        <f>IF(Liens!F100="","",IF(COUNTIF(Mots!B:B,Liens!F100)&gt;0,"✓ "&amp;Liens!F100,"✗ "&amp;Liens!F100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H105">
+        <f>IF(Liens!G100="","",IF(COUNTIF(Mots!B:B,Liens!G100)&gt;0,"✓ "&amp;Liens!G100,"✗ "&amp;Liens!G100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I105">
+        <f>IF(Liens!H100="","",IF(COUNTIF(Mots!B:B,Liens!H100)&gt;0,"✓ "&amp;Liens!H100,"✗ "&amp;Liens!H100&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106">
+        <f>IF(Liens!A101="","",IF(COUNTIF(Mots!B:B,Liens!A101)&gt;0,"✓ "&amp;Liens!A101,"✗ "&amp;Liens!A101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(Liens!B101="","",IF(COUNTIF(Mots!B:B,Liens!B101)&gt;0,"✓ "&amp;Liens!B101,"✗ "&amp;Liens!B101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(Liens!C101="","",IF(COUNTIF(Mots!B:B,Liens!C101)&gt;0,"✓ "&amp;Liens!C101,"✗ "&amp;Liens!C101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(Liens!D101="","",IF(COUNTIF(Mots!B:B,Liens!D101)&gt;0,"✓ "&amp;Liens!D101,"✗ "&amp;Liens!D101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(Liens!E101="","",IF(COUNTIF(Mots!B:B,Liens!E101)&gt;0,"✓ "&amp;Liens!E101,"✗ "&amp;Liens!E101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G106">
+        <f>IF(Liens!F101="","",IF(COUNTIF(Mots!B:B,Liens!F101)&gt;0,"✓ "&amp;Liens!F101,"✗ "&amp;Liens!F101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H106">
+        <f>IF(Liens!G101="","",IF(COUNTIF(Mots!B:B,Liens!G101)&gt;0,"✓ "&amp;Liens!G101,"✗ "&amp;Liens!G101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I106">
+        <f>IF(Liens!H101="","",IF(COUNTIF(Mots!B:B,Liens!H101)&gt;0,"✓ "&amp;Liens!H101,"✗ "&amp;Liens!H101&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107">
+        <f>IF(Liens!A102="","",IF(COUNTIF(Mots!B:B,Liens!A102)&gt;0,"✓ "&amp;Liens!A102,"✗ "&amp;Liens!A102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C107">
+        <f>IF(Liens!B102="","",IF(COUNTIF(Mots!B:B,Liens!B102)&gt;0,"✓ "&amp;Liens!B102,"✗ "&amp;Liens!B102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D107">
+        <f>IF(Liens!C102="","",IF(COUNTIF(Mots!B:B,Liens!C102)&gt;0,"✓ "&amp;Liens!C102,"✗ "&amp;Liens!C102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E107">
+        <f>IF(Liens!D102="","",IF(COUNTIF(Mots!B:B,Liens!D102)&gt;0,"✓ "&amp;Liens!D102,"✗ "&amp;Liens!D102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F107">
+        <f>IF(Liens!E102="","",IF(COUNTIF(Mots!B:B,Liens!E102)&gt;0,"✓ "&amp;Liens!E102,"✗ "&amp;Liens!E102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G107">
+        <f>IF(Liens!F102="","",IF(COUNTIF(Mots!B:B,Liens!F102)&gt;0,"✓ "&amp;Liens!F102,"✗ "&amp;Liens!F102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H107">
+        <f>IF(Liens!G102="","",IF(COUNTIF(Mots!B:B,Liens!G102)&gt;0,"✓ "&amp;Liens!G102,"✗ "&amp;Liens!G102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I107">
+        <f>IF(Liens!H102="","",IF(COUNTIF(Mots!B:B,Liens!H102)&gt;0,"✓ "&amp;Liens!H102,"✗ "&amp;Liens!H102&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108">
+        <f>IF(Liens!A103="","",IF(COUNTIF(Mots!B:B,Liens!A103)&gt;0,"✓ "&amp;Liens!A103,"✗ "&amp;Liens!A103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C108">
+        <f>IF(Liens!B103="","",IF(COUNTIF(Mots!B:B,Liens!B103)&gt;0,"✓ "&amp;Liens!B103,"✗ "&amp;Liens!B103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D108">
+        <f>IF(Liens!C103="","",IF(COUNTIF(Mots!B:B,Liens!C103)&gt;0,"✓ "&amp;Liens!C103,"✗ "&amp;Liens!C103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E108">
+        <f>IF(Liens!D103="","",IF(COUNTIF(Mots!B:B,Liens!D103)&gt;0,"✓ "&amp;Liens!D103,"✗ "&amp;Liens!D103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F108">
+        <f>IF(Liens!E103="","",IF(COUNTIF(Mots!B:B,Liens!E103)&gt;0,"✓ "&amp;Liens!E103,"✗ "&amp;Liens!E103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G108">
+        <f>IF(Liens!F103="","",IF(COUNTIF(Mots!B:B,Liens!F103)&gt;0,"✓ "&amp;Liens!F103,"✗ "&amp;Liens!F103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H108">
+        <f>IF(Liens!G103="","",IF(COUNTIF(Mots!B:B,Liens!G103)&gt;0,"✓ "&amp;Liens!G103,"✗ "&amp;Liens!G103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I108">
+        <f>IF(Liens!H103="","",IF(COUNTIF(Mots!B:B,Liens!H103)&gt;0,"✓ "&amp;Liens!H103,"✗ "&amp;Liens!H103&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109">
+        <f>IF(Liens!A104="","",IF(COUNTIF(Mots!B:B,Liens!A104)&gt;0,"✓ "&amp;Liens!A104,"✗ "&amp;Liens!A104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C109">
+        <f>IF(Liens!B104="","",IF(COUNTIF(Mots!B:B,Liens!B104)&gt;0,"✓ "&amp;Liens!B104,"✗ "&amp;Liens!B104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D109">
+        <f>IF(Liens!C104="","",IF(COUNTIF(Mots!B:B,Liens!C104)&gt;0,"✓ "&amp;Liens!C104,"✗ "&amp;Liens!C104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E109">
+        <f>IF(Liens!D104="","",IF(COUNTIF(Mots!B:B,Liens!D104)&gt;0,"✓ "&amp;Liens!D104,"✗ "&amp;Liens!D104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F109">
+        <f>IF(Liens!E104="","",IF(COUNTIF(Mots!B:B,Liens!E104)&gt;0,"✓ "&amp;Liens!E104,"✗ "&amp;Liens!E104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G109">
+        <f>IF(Liens!F104="","",IF(COUNTIF(Mots!B:B,Liens!F104)&gt;0,"✓ "&amp;Liens!F104,"✗ "&amp;Liens!F104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H109">
+        <f>IF(Liens!G104="","",IF(COUNTIF(Mots!B:B,Liens!G104)&gt;0,"✓ "&amp;Liens!G104,"✗ "&amp;Liens!G104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I109">
+        <f>IF(Liens!H104="","",IF(COUNTIF(Mots!B:B,Liens!H104)&gt;0,"✓ "&amp;Liens!H104,"✗ "&amp;Liens!H104&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110">
+        <f>IF(Liens!A105="","",IF(COUNTIF(Mots!B:B,Liens!A105)&gt;0,"✓ "&amp;Liens!A105,"✗ "&amp;Liens!A105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C110">
+        <f>IF(Liens!B105="","",IF(COUNTIF(Mots!B:B,Liens!B105)&gt;0,"✓ "&amp;Liens!B105,"✗ "&amp;Liens!B105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D110">
+        <f>IF(Liens!C105="","",IF(COUNTIF(Mots!B:B,Liens!C105)&gt;0,"✓ "&amp;Liens!C105,"✗ "&amp;Liens!C105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E110">
+        <f>IF(Liens!D105="","",IF(COUNTIF(Mots!B:B,Liens!D105)&gt;0,"✓ "&amp;Liens!D105,"✗ "&amp;Liens!D105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F110">
+        <f>IF(Liens!E105="","",IF(COUNTIF(Mots!B:B,Liens!E105)&gt;0,"✓ "&amp;Liens!E105,"✗ "&amp;Liens!E105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G110">
+        <f>IF(Liens!F105="","",IF(COUNTIF(Mots!B:B,Liens!F105)&gt;0,"✓ "&amp;Liens!F105,"✗ "&amp;Liens!F105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H110">
+        <f>IF(Liens!G105="","",IF(COUNTIF(Mots!B:B,Liens!G105)&gt;0,"✓ "&amp;Liens!G105,"✗ "&amp;Liens!G105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I110">
+        <f>IF(Liens!H105="","",IF(COUNTIF(Mots!B:B,Liens!H105)&gt;0,"✓ "&amp;Liens!H105,"✗ "&amp;Liens!H105&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111">
+        <f>IF(Liens!A106="","",IF(COUNTIF(Mots!B:B,Liens!A106)&gt;0,"✓ "&amp;Liens!A106,"✗ "&amp;Liens!A106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C111">
+        <f>IF(Liens!B106="","",IF(COUNTIF(Mots!B:B,Liens!B106)&gt;0,"✓ "&amp;Liens!B106,"✗ "&amp;Liens!B106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D111">
+        <f>IF(Liens!C106="","",IF(COUNTIF(Mots!B:B,Liens!C106)&gt;0,"✓ "&amp;Liens!C106,"✗ "&amp;Liens!C106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E111">
+        <f>IF(Liens!D106="","",IF(COUNTIF(Mots!B:B,Liens!D106)&gt;0,"✓ "&amp;Liens!D106,"✗ "&amp;Liens!D106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F111">
+        <f>IF(Liens!E106="","",IF(COUNTIF(Mots!B:B,Liens!E106)&gt;0,"✓ "&amp;Liens!E106,"✗ "&amp;Liens!E106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G111">
+        <f>IF(Liens!F106="","",IF(COUNTIF(Mots!B:B,Liens!F106)&gt;0,"✓ "&amp;Liens!F106,"✗ "&amp;Liens!F106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H111">
+        <f>IF(Liens!G106="","",IF(COUNTIF(Mots!B:B,Liens!G106)&gt;0,"✓ "&amp;Liens!G106,"✗ "&amp;Liens!G106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I111">
+        <f>IF(Liens!H106="","",IF(COUNTIF(Mots!B:B,Liens!H106)&gt;0,"✓ "&amp;Liens!H106,"✗ "&amp;Liens!H106&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112">
+        <f>IF(Liens!A107="","",IF(COUNTIF(Mots!B:B,Liens!A107)&gt;0,"✓ "&amp;Liens!A107,"✗ "&amp;Liens!A107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C112">
+        <f>IF(Liens!B107="","",IF(COUNTIF(Mots!B:B,Liens!B107)&gt;0,"✓ "&amp;Liens!B107,"✗ "&amp;Liens!B107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D112">
+        <f>IF(Liens!C107="","",IF(COUNTIF(Mots!B:B,Liens!C107)&gt;0,"✓ "&amp;Liens!C107,"✗ "&amp;Liens!C107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E112">
+        <f>IF(Liens!D107="","",IF(COUNTIF(Mots!B:B,Liens!D107)&gt;0,"✓ "&amp;Liens!D107,"✗ "&amp;Liens!D107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F112">
+        <f>IF(Liens!E107="","",IF(COUNTIF(Mots!B:B,Liens!E107)&gt;0,"✓ "&amp;Liens!E107,"✗ "&amp;Liens!E107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G112">
+        <f>IF(Liens!F107="","",IF(COUNTIF(Mots!B:B,Liens!F107)&gt;0,"✓ "&amp;Liens!F107,"✗ "&amp;Liens!F107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H112">
+        <f>IF(Liens!G107="","",IF(COUNTIF(Mots!B:B,Liens!G107)&gt;0,"✓ "&amp;Liens!G107,"✗ "&amp;Liens!G107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I112">
+        <f>IF(Liens!H107="","",IF(COUNTIF(Mots!B:B,Liens!H107)&gt;0,"✓ "&amp;Liens!H107,"✗ "&amp;Liens!H107&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113">
+        <f>IF(Liens!A108="","",IF(COUNTIF(Mots!B:B,Liens!A108)&gt;0,"✓ "&amp;Liens!A108,"✗ "&amp;Liens!A108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C113">
+        <f>IF(Liens!B108="","",IF(COUNTIF(Mots!B:B,Liens!B108)&gt;0,"✓ "&amp;Liens!B108,"✗ "&amp;Liens!B108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D113">
+        <f>IF(Liens!C108="","",IF(COUNTIF(Mots!B:B,Liens!C108)&gt;0,"✓ "&amp;Liens!C108,"✗ "&amp;Liens!C108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E113">
+        <f>IF(Liens!D108="","",IF(COUNTIF(Mots!B:B,Liens!D108)&gt;0,"✓ "&amp;Liens!D108,"✗ "&amp;Liens!D108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F113">
+        <f>IF(Liens!E108="","",IF(COUNTIF(Mots!B:B,Liens!E108)&gt;0,"✓ "&amp;Liens!E108,"✗ "&amp;Liens!E108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G113">
+        <f>IF(Liens!F108="","",IF(COUNTIF(Mots!B:B,Liens!F108)&gt;0,"✓ "&amp;Liens!F108,"✗ "&amp;Liens!F108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H113">
+        <f>IF(Liens!G108="","",IF(COUNTIF(Mots!B:B,Liens!G108)&gt;0,"✓ "&amp;Liens!G108,"✗ "&amp;Liens!G108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I113">
+        <f>IF(Liens!H108="","",IF(COUNTIF(Mots!B:B,Liens!H108)&gt;0,"✓ "&amp;Liens!H108,"✗ "&amp;Liens!H108&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114">
+        <f>IF(Liens!A109="","",IF(COUNTIF(Mots!B:B,Liens!A109)&gt;0,"✓ "&amp;Liens!A109,"✗ "&amp;Liens!A109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C114">
+        <f>IF(Liens!B109="","",IF(COUNTIF(Mots!B:B,Liens!B109)&gt;0,"✓ "&amp;Liens!B109,"✗ "&amp;Liens!B109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D114">
+        <f>IF(Liens!C109="","",IF(COUNTIF(Mots!B:B,Liens!C109)&gt;0,"✓ "&amp;Liens!C109,"✗ "&amp;Liens!C109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E114">
+        <f>IF(Liens!D109="","",IF(COUNTIF(Mots!B:B,Liens!D109)&gt;0,"✓ "&amp;Liens!D109,"✗ "&amp;Liens!D109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F114">
+        <f>IF(Liens!E109="","",IF(COUNTIF(Mots!B:B,Liens!E109)&gt;0,"✓ "&amp;Liens!E109,"✗ "&amp;Liens!E109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G114">
+        <f>IF(Liens!F109="","",IF(COUNTIF(Mots!B:B,Liens!F109)&gt;0,"✓ "&amp;Liens!F109,"✗ "&amp;Liens!F109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H114">
+        <f>IF(Liens!G109="","",IF(COUNTIF(Mots!B:B,Liens!G109)&gt;0,"✓ "&amp;Liens!G109,"✗ "&amp;Liens!G109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I114">
+        <f>IF(Liens!H109="","",IF(COUNTIF(Mots!B:B,Liens!H109)&gt;0,"✓ "&amp;Liens!H109,"✗ "&amp;Liens!H109&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115">
+        <f>IF(Liens!A110="","",IF(COUNTIF(Mots!B:B,Liens!A110)&gt;0,"✓ "&amp;Liens!A110,"✗ "&amp;Liens!A110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C115">
+        <f>IF(Liens!B110="","",IF(COUNTIF(Mots!B:B,Liens!B110)&gt;0,"✓ "&amp;Liens!B110,"✗ "&amp;Liens!B110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D115">
+        <f>IF(Liens!C110="","",IF(COUNTIF(Mots!B:B,Liens!C110)&gt;0,"✓ "&amp;Liens!C110,"✗ "&amp;Liens!C110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E115">
+        <f>IF(Liens!D110="","",IF(COUNTIF(Mots!B:B,Liens!D110)&gt;0,"✓ "&amp;Liens!D110,"✗ "&amp;Liens!D110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F115">
+        <f>IF(Liens!E110="","",IF(COUNTIF(Mots!B:B,Liens!E110)&gt;0,"✓ "&amp;Liens!E110,"✗ "&amp;Liens!E110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G115">
+        <f>IF(Liens!F110="","",IF(COUNTIF(Mots!B:B,Liens!F110)&gt;0,"✓ "&amp;Liens!F110,"✗ "&amp;Liens!F110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H115">
+        <f>IF(Liens!G110="","",IF(COUNTIF(Mots!B:B,Liens!G110)&gt;0,"✓ "&amp;Liens!G110,"✗ "&amp;Liens!G110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I115">
+        <f>IF(Liens!H110="","",IF(COUNTIF(Mots!B:B,Liens!H110)&gt;0,"✓ "&amp;Liens!H110,"✗ "&amp;Liens!H110&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116">
+        <f>IF(Liens!A111="","",IF(COUNTIF(Mots!B:B,Liens!A111)&gt;0,"✓ "&amp;Liens!A111,"✗ "&amp;Liens!A111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C116">
+        <f>IF(Liens!B111="","",IF(COUNTIF(Mots!B:B,Liens!B111)&gt;0,"✓ "&amp;Liens!B111,"✗ "&amp;Liens!B111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D116">
+        <f>IF(Liens!C111="","",IF(COUNTIF(Mots!B:B,Liens!C111)&gt;0,"✓ "&amp;Liens!C111,"✗ "&amp;Liens!C111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E116">
+        <f>IF(Liens!D111="","",IF(COUNTIF(Mots!B:B,Liens!D111)&gt;0,"✓ "&amp;Liens!D111,"✗ "&amp;Liens!D111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F116">
+        <f>IF(Liens!E111="","",IF(COUNTIF(Mots!B:B,Liens!E111)&gt;0,"✓ "&amp;Liens!E111,"✗ "&amp;Liens!E111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G116">
+        <f>IF(Liens!F111="","",IF(COUNTIF(Mots!B:B,Liens!F111)&gt;0,"✓ "&amp;Liens!F111,"✗ "&amp;Liens!F111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H116">
+        <f>IF(Liens!G111="","",IF(COUNTIF(Mots!B:B,Liens!G111)&gt;0,"✓ "&amp;Liens!G111,"✗ "&amp;Liens!G111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I116">
+        <f>IF(Liens!H111="","",IF(COUNTIF(Mots!B:B,Liens!H111)&gt;0,"✓ "&amp;Liens!H111,"✗ "&amp;Liens!H111&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117">
+        <f>IF(Liens!A112="","",IF(COUNTIF(Mots!B:B,Liens!A112)&gt;0,"✓ "&amp;Liens!A112,"✗ "&amp;Liens!A112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C117">
+        <f>IF(Liens!B112="","",IF(COUNTIF(Mots!B:B,Liens!B112)&gt;0,"✓ "&amp;Liens!B112,"✗ "&amp;Liens!B112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D117">
+        <f>IF(Liens!C112="","",IF(COUNTIF(Mots!B:B,Liens!C112)&gt;0,"✓ "&amp;Liens!C112,"✗ "&amp;Liens!C112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E117">
+        <f>IF(Liens!D112="","",IF(COUNTIF(Mots!B:B,Liens!D112)&gt;0,"✓ "&amp;Liens!D112,"✗ "&amp;Liens!D112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F117">
+        <f>IF(Liens!E112="","",IF(COUNTIF(Mots!B:B,Liens!E112)&gt;0,"✓ "&amp;Liens!E112,"✗ "&amp;Liens!E112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G117">
+        <f>IF(Liens!F112="","",IF(COUNTIF(Mots!B:B,Liens!F112)&gt;0,"✓ "&amp;Liens!F112,"✗ "&amp;Liens!F112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H117">
+        <f>IF(Liens!G112="","",IF(COUNTIF(Mots!B:B,Liens!G112)&gt;0,"✓ "&amp;Liens!G112,"✗ "&amp;Liens!G112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I117">
+        <f>IF(Liens!H112="","",IF(COUNTIF(Mots!B:B,Liens!H112)&gt;0,"✓ "&amp;Liens!H112,"✗ "&amp;Liens!H112&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118">
+        <f>IF(Liens!A113="","",IF(COUNTIF(Mots!B:B,Liens!A113)&gt;0,"✓ "&amp;Liens!A113,"✗ "&amp;Liens!A113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C118">
+        <f>IF(Liens!B113="","",IF(COUNTIF(Mots!B:B,Liens!B113)&gt;0,"✓ "&amp;Liens!B113,"✗ "&amp;Liens!B113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D118">
+        <f>IF(Liens!C113="","",IF(COUNTIF(Mots!B:B,Liens!C113)&gt;0,"✓ "&amp;Liens!C113,"✗ "&amp;Liens!C113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E118">
+        <f>IF(Liens!D113="","",IF(COUNTIF(Mots!B:B,Liens!D113)&gt;0,"✓ "&amp;Liens!D113,"✗ "&amp;Liens!D113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F118">
+        <f>IF(Liens!E113="","",IF(COUNTIF(Mots!B:B,Liens!E113)&gt;0,"✓ "&amp;Liens!E113,"✗ "&amp;Liens!E113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G118">
+        <f>IF(Liens!F113="","",IF(COUNTIF(Mots!B:B,Liens!F113)&gt;0,"✓ "&amp;Liens!F113,"✗ "&amp;Liens!F113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H118">
+        <f>IF(Liens!G113="","",IF(COUNTIF(Mots!B:B,Liens!G113)&gt;0,"✓ "&amp;Liens!G113,"✗ "&amp;Liens!G113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I118">
+        <f>IF(Liens!H113="","",IF(COUNTIF(Mots!B:B,Liens!H113)&gt;0,"✓ "&amp;Liens!H113,"✗ "&amp;Liens!H113&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119">
+        <f>IF(Liens!A114="","",IF(COUNTIF(Mots!B:B,Liens!A114)&gt;0,"✓ "&amp;Liens!A114,"✗ "&amp;Liens!A114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C119">
+        <f>IF(Liens!B114="","",IF(COUNTIF(Mots!B:B,Liens!B114)&gt;0,"✓ "&amp;Liens!B114,"✗ "&amp;Liens!B114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D119">
+        <f>IF(Liens!C114="","",IF(COUNTIF(Mots!B:B,Liens!C114)&gt;0,"✓ "&amp;Liens!C114,"✗ "&amp;Liens!C114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E119">
+        <f>IF(Liens!D114="","",IF(COUNTIF(Mots!B:B,Liens!D114)&gt;0,"✓ "&amp;Liens!D114,"✗ "&amp;Liens!D114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F119">
+        <f>IF(Liens!E114="","",IF(COUNTIF(Mots!B:B,Liens!E114)&gt;0,"✓ "&amp;Liens!E114,"✗ "&amp;Liens!E114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G119">
+        <f>IF(Liens!F114="","",IF(COUNTIF(Mots!B:B,Liens!F114)&gt;0,"✓ "&amp;Liens!F114,"✗ "&amp;Liens!F114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H119">
+        <f>IF(Liens!G114="","",IF(COUNTIF(Mots!B:B,Liens!G114)&gt;0,"✓ "&amp;Liens!G114,"✗ "&amp;Liens!G114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I119">
+        <f>IF(Liens!H114="","",IF(COUNTIF(Mots!B:B,Liens!H114)&gt;0,"✓ "&amp;Liens!H114,"✗ "&amp;Liens!H114&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120">
+        <f>IF(Liens!A115="","",IF(COUNTIF(Mots!B:B,Liens!A115)&gt;0,"✓ "&amp;Liens!A115,"✗ "&amp;Liens!A115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C120">
+        <f>IF(Liens!B115="","",IF(COUNTIF(Mots!B:B,Liens!B115)&gt;0,"✓ "&amp;Liens!B115,"✗ "&amp;Liens!B115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D120">
+        <f>IF(Liens!C115="","",IF(COUNTIF(Mots!B:B,Liens!C115)&gt;0,"✓ "&amp;Liens!C115,"✗ "&amp;Liens!C115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E120">
+        <f>IF(Liens!D115="","",IF(COUNTIF(Mots!B:B,Liens!D115)&gt;0,"✓ "&amp;Liens!D115,"✗ "&amp;Liens!D115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F120">
+        <f>IF(Liens!E115="","",IF(COUNTIF(Mots!B:B,Liens!E115)&gt;0,"✓ "&amp;Liens!E115,"✗ "&amp;Liens!E115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G120">
+        <f>IF(Liens!F115="","",IF(COUNTIF(Mots!B:B,Liens!F115)&gt;0,"✓ "&amp;Liens!F115,"✗ "&amp;Liens!F115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H120">
+        <f>IF(Liens!G115="","",IF(COUNTIF(Mots!B:B,Liens!G115)&gt;0,"✓ "&amp;Liens!G115,"✗ "&amp;Liens!G115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I120">
+        <f>IF(Liens!H115="","",IF(COUNTIF(Mots!B:B,Liens!H115)&gt;0,"✓ "&amp;Liens!H115,"✗ "&amp;Liens!H115&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121">
+        <f>IF(Liens!A116="","",IF(COUNTIF(Mots!B:B,Liens!A116)&gt;0,"✓ "&amp;Liens!A116,"✗ "&amp;Liens!A116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C121">
+        <f>IF(Liens!B116="","",IF(COUNTIF(Mots!B:B,Liens!B116)&gt;0,"✓ "&amp;Liens!B116,"✗ "&amp;Liens!B116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D121">
+        <f>IF(Liens!C116="","",IF(COUNTIF(Mots!B:B,Liens!C116)&gt;0,"✓ "&amp;Liens!C116,"✗ "&amp;Liens!C116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E121">
+        <f>IF(Liens!D116="","",IF(COUNTIF(Mots!B:B,Liens!D116)&gt;0,"✓ "&amp;Liens!D116,"✗ "&amp;Liens!D116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F121">
+        <f>IF(Liens!E116="","",IF(COUNTIF(Mots!B:B,Liens!E116)&gt;0,"✓ "&amp;Liens!E116,"✗ "&amp;Liens!E116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G121">
+        <f>IF(Liens!F116="","",IF(COUNTIF(Mots!B:B,Liens!F116)&gt;0,"✓ "&amp;Liens!F116,"✗ "&amp;Liens!F116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H121">
+        <f>IF(Liens!G116="","",IF(COUNTIF(Mots!B:B,Liens!G116)&gt;0,"✓ "&amp;Liens!G116,"✗ "&amp;Liens!G116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I121">
+        <f>IF(Liens!H116="","",IF(COUNTIF(Mots!B:B,Liens!H116)&gt;0,"✓ "&amp;Liens!H116,"✗ "&amp;Liens!H116&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122">
+        <f>IF(Liens!A117="","",IF(COUNTIF(Mots!B:B,Liens!A117)&gt;0,"✓ "&amp;Liens!A117,"✗ "&amp;Liens!A117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C122">
+        <f>IF(Liens!B117="","",IF(COUNTIF(Mots!B:B,Liens!B117)&gt;0,"✓ "&amp;Liens!B117,"✗ "&amp;Liens!B117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D122">
+        <f>IF(Liens!C117="","",IF(COUNTIF(Mots!B:B,Liens!C117)&gt;0,"✓ "&amp;Liens!C117,"✗ "&amp;Liens!C117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E122">
+        <f>IF(Liens!D117="","",IF(COUNTIF(Mots!B:B,Liens!D117)&gt;0,"✓ "&amp;Liens!D117,"✗ "&amp;Liens!D117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F122">
+        <f>IF(Liens!E117="","",IF(COUNTIF(Mots!B:B,Liens!E117)&gt;0,"✓ "&amp;Liens!E117,"✗ "&amp;Liens!E117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G122">
+        <f>IF(Liens!F117="","",IF(COUNTIF(Mots!B:B,Liens!F117)&gt;0,"✓ "&amp;Liens!F117,"✗ "&amp;Liens!F117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H122">
+        <f>IF(Liens!G117="","",IF(COUNTIF(Mots!B:B,Liens!G117)&gt;0,"✓ "&amp;Liens!G117,"✗ "&amp;Liens!G117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I122">
+        <f>IF(Liens!H117="","",IF(COUNTIF(Mots!B:B,Liens!H117)&gt;0,"✓ "&amp;Liens!H117,"✗ "&amp;Liens!H117&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123">
+        <f>IF(Liens!A118="","",IF(COUNTIF(Mots!B:B,Liens!A118)&gt;0,"✓ "&amp;Liens!A118,"✗ "&amp;Liens!A118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C123">
+        <f>IF(Liens!B118="","",IF(COUNTIF(Mots!B:B,Liens!B118)&gt;0,"✓ "&amp;Liens!B118,"✗ "&amp;Liens!B118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D123">
+        <f>IF(Liens!C118="","",IF(COUNTIF(Mots!B:B,Liens!C118)&gt;0,"✓ "&amp;Liens!C118,"✗ "&amp;Liens!C118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E123">
+        <f>IF(Liens!D118="","",IF(COUNTIF(Mots!B:B,Liens!D118)&gt;0,"✓ "&amp;Liens!D118,"✗ "&amp;Liens!D118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F123">
+        <f>IF(Liens!E118="","",IF(COUNTIF(Mots!B:B,Liens!E118)&gt;0,"✓ "&amp;Liens!E118,"✗ "&amp;Liens!E118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G123">
+        <f>IF(Liens!F118="","",IF(COUNTIF(Mots!B:B,Liens!F118)&gt;0,"✓ "&amp;Liens!F118,"✗ "&amp;Liens!F118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H123">
+        <f>IF(Liens!G118="","",IF(COUNTIF(Mots!B:B,Liens!G118)&gt;0,"✓ "&amp;Liens!G118,"✗ "&amp;Liens!G118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I123">
+        <f>IF(Liens!H118="","",IF(COUNTIF(Mots!B:B,Liens!H118)&gt;0,"✓ "&amp;Liens!H118,"✗ "&amp;Liens!H118&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124">
+        <f>IF(Liens!A119="","",IF(COUNTIF(Mots!B:B,Liens!A119)&gt;0,"✓ "&amp;Liens!A119,"✗ "&amp;Liens!A119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C124">
+        <f>IF(Liens!B119="","",IF(COUNTIF(Mots!B:B,Liens!B119)&gt;0,"✓ "&amp;Liens!B119,"✗ "&amp;Liens!B119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D124">
+        <f>IF(Liens!C119="","",IF(COUNTIF(Mots!B:B,Liens!C119)&gt;0,"✓ "&amp;Liens!C119,"✗ "&amp;Liens!C119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E124">
+        <f>IF(Liens!D119="","",IF(COUNTIF(Mots!B:B,Liens!D119)&gt;0,"✓ "&amp;Liens!D119,"✗ "&amp;Liens!D119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F124">
+        <f>IF(Liens!E119="","",IF(COUNTIF(Mots!B:B,Liens!E119)&gt;0,"✓ "&amp;Liens!E119,"✗ "&amp;Liens!E119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G124">
+        <f>IF(Liens!F119="","",IF(COUNTIF(Mots!B:B,Liens!F119)&gt;0,"✓ "&amp;Liens!F119,"✗ "&amp;Liens!F119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H124">
+        <f>IF(Liens!G119="","",IF(COUNTIF(Mots!B:B,Liens!G119)&gt;0,"✓ "&amp;Liens!G119,"✗ "&amp;Liens!G119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I124">
+        <f>IF(Liens!H119="","",IF(COUNTIF(Mots!B:B,Liens!H119)&gt;0,"✓ "&amp;Liens!H119,"✗ "&amp;Liens!H119&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125">
+        <f>IF(Liens!A120="","",IF(COUNTIF(Mots!B:B,Liens!A120)&gt;0,"✓ "&amp;Liens!A120,"✗ "&amp;Liens!A120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C125">
+        <f>IF(Liens!B120="","",IF(COUNTIF(Mots!B:B,Liens!B120)&gt;0,"✓ "&amp;Liens!B120,"✗ "&amp;Liens!B120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D125">
+        <f>IF(Liens!C120="","",IF(COUNTIF(Mots!B:B,Liens!C120)&gt;0,"✓ "&amp;Liens!C120,"✗ "&amp;Liens!C120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E125">
+        <f>IF(Liens!D120="","",IF(COUNTIF(Mots!B:B,Liens!D120)&gt;0,"✓ "&amp;Liens!D120,"✗ "&amp;Liens!D120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F125">
+        <f>IF(Liens!E120="","",IF(COUNTIF(Mots!B:B,Liens!E120)&gt;0,"✓ "&amp;Liens!E120,"✗ "&amp;Liens!E120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G125">
+        <f>IF(Liens!F120="","",IF(COUNTIF(Mots!B:B,Liens!F120)&gt;0,"✓ "&amp;Liens!F120,"✗ "&amp;Liens!F120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H125">
+        <f>IF(Liens!G120="","",IF(COUNTIF(Mots!B:B,Liens!G120)&gt;0,"✓ "&amp;Liens!G120,"✗ "&amp;Liens!G120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I125">
+        <f>IF(Liens!H120="","",IF(COUNTIF(Mots!B:B,Liens!H120)&gt;0,"✓ "&amp;Liens!H120,"✗ "&amp;Liens!H120&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126">
+        <f>IF(Liens!A121="","",IF(COUNTIF(Mots!B:B,Liens!A121)&gt;0,"✓ "&amp;Liens!A121,"✗ "&amp;Liens!A121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C126">
+        <f>IF(Liens!B121="","",IF(COUNTIF(Mots!B:B,Liens!B121)&gt;0,"✓ "&amp;Liens!B121,"✗ "&amp;Liens!B121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D126">
+        <f>IF(Liens!C121="","",IF(COUNTIF(Mots!B:B,Liens!C121)&gt;0,"✓ "&amp;Liens!C121,"✗ "&amp;Liens!C121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E126">
+        <f>IF(Liens!D121="","",IF(COUNTIF(Mots!B:B,Liens!D121)&gt;0,"✓ "&amp;Liens!D121,"✗ "&amp;Liens!D121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F126">
+        <f>IF(Liens!E121="","",IF(COUNTIF(Mots!B:B,Liens!E121)&gt;0,"✓ "&amp;Liens!E121,"✗ "&amp;Liens!E121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G126">
+        <f>IF(Liens!F121="","",IF(COUNTIF(Mots!B:B,Liens!F121)&gt;0,"✓ "&amp;Liens!F121,"✗ "&amp;Liens!F121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H126">
+        <f>IF(Liens!G121="","",IF(COUNTIF(Mots!B:B,Liens!G121)&gt;0,"✓ "&amp;Liens!G121,"✗ "&amp;Liens!G121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I126">
+        <f>IF(Liens!H121="","",IF(COUNTIF(Mots!B:B,Liens!H121)&gt;0,"✓ "&amp;Liens!H121,"✗ "&amp;Liens!H121&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127">
+        <f>IF(Liens!A122="","",IF(COUNTIF(Mots!B:B,Liens!A122)&gt;0,"✓ "&amp;Liens!A122,"✗ "&amp;Liens!A122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C127">
+        <f>IF(Liens!B122="","",IF(COUNTIF(Mots!B:B,Liens!B122)&gt;0,"✓ "&amp;Liens!B122,"✗ "&amp;Liens!B122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D127">
+        <f>IF(Liens!C122="","",IF(COUNTIF(Mots!B:B,Liens!C122)&gt;0,"✓ "&amp;Liens!C122,"✗ "&amp;Liens!C122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>IF(Liens!D122="","",IF(COUNTIF(Mots!B:B,Liens!D122)&gt;0,"✓ "&amp;Liens!D122,"✗ "&amp;Liens!D122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F127">
+        <f>IF(Liens!E122="","",IF(COUNTIF(Mots!B:B,Liens!E122)&gt;0,"✓ "&amp;Liens!E122,"✗ "&amp;Liens!E122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>IF(Liens!F122="","",IF(COUNTIF(Mots!B:B,Liens!F122)&gt;0,"✓ "&amp;Liens!F122,"✗ "&amp;Liens!F122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H127">
+        <f>IF(Liens!G122="","",IF(COUNTIF(Mots!B:B,Liens!G122)&gt;0,"✓ "&amp;Liens!G122,"✗ "&amp;Liens!G122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>IF(Liens!H122="","",IF(COUNTIF(Mots!B:B,Liens!H122)&gt;0,"✓ "&amp;Liens!H122,"✗ "&amp;Liens!H122&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128">
+        <f>IF(Liens!A123="","",IF(COUNTIF(Mots!B:B,Liens!A123)&gt;0,"✓ "&amp;Liens!A123,"✗ "&amp;Liens!A123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C128">
+        <f>IF(Liens!B123="","",IF(COUNTIF(Mots!B:B,Liens!B123)&gt;0,"✓ "&amp;Liens!B123,"✗ "&amp;Liens!B123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D128">
+        <f>IF(Liens!C123="","",IF(COUNTIF(Mots!B:B,Liens!C123)&gt;0,"✓ "&amp;Liens!C123,"✗ "&amp;Liens!C123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E128">
+        <f>IF(Liens!D123="","",IF(COUNTIF(Mots!B:B,Liens!D123)&gt;0,"✓ "&amp;Liens!D123,"✗ "&amp;Liens!D123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F128">
+        <f>IF(Liens!E123="","",IF(COUNTIF(Mots!B:B,Liens!E123)&gt;0,"✓ "&amp;Liens!E123,"✗ "&amp;Liens!E123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G128">
+        <f>IF(Liens!F123="","",IF(COUNTIF(Mots!B:B,Liens!F123)&gt;0,"✓ "&amp;Liens!F123,"✗ "&amp;Liens!F123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H128">
+        <f>IF(Liens!G123="","",IF(COUNTIF(Mots!B:B,Liens!G123)&gt;0,"✓ "&amp;Liens!G123,"✗ "&amp;Liens!G123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I128">
+        <f>IF(Liens!H123="","",IF(COUNTIF(Mots!B:B,Liens!H123)&gt;0,"✓ "&amp;Liens!H123,"✗ "&amp;Liens!H123&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129">
+        <f>IF(Liens!A124="","",IF(COUNTIF(Mots!B:B,Liens!A124)&gt;0,"✓ "&amp;Liens!A124,"✗ "&amp;Liens!A124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C129">
+        <f>IF(Liens!B124="","",IF(COUNTIF(Mots!B:B,Liens!B124)&gt;0,"✓ "&amp;Liens!B124,"✗ "&amp;Liens!B124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D129">
+        <f>IF(Liens!C124="","",IF(COUNTIF(Mots!B:B,Liens!C124)&gt;0,"✓ "&amp;Liens!C124,"✗ "&amp;Liens!C124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E129">
+        <f>IF(Liens!D124="","",IF(COUNTIF(Mots!B:B,Liens!D124)&gt;0,"✓ "&amp;Liens!D124,"✗ "&amp;Liens!D124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F129">
+        <f>IF(Liens!E124="","",IF(COUNTIF(Mots!B:B,Liens!E124)&gt;0,"✓ "&amp;Liens!E124,"✗ "&amp;Liens!E124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G129">
+        <f>IF(Liens!F124="","",IF(COUNTIF(Mots!B:B,Liens!F124)&gt;0,"✓ "&amp;Liens!F124,"✗ "&amp;Liens!F124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H129">
+        <f>IF(Liens!G124="","",IF(COUNTIF(Mots!B:B,Liens!G124)&gt;0,"✓ "&amp;Liens!G124,"✗ "&amp;Liens!G124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I129">
+        <f>IF(Liens!H124="","",IF(COUNTIF(Mots!B:B,Liens!H124)&gt;0,"✓ "&amp;Liens!H124,"✗ "&amp;Liens!H124&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130">
+        <f>IF(Liens!A125="","",IF(COUNTIF(Mots!B:B,Liens!A125)&gt;0,"✓ "&amp;Liens!A125,"✗ "&amp;Liens!A125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C130">
+        <f>IF(Liens!B125="","",IF(COUNTIF(Mots!B:B,Liens!B125)&gt;0,"✓ "&amp;Liens!B125,"✗ "&amp;Liens!B125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D130">
+        <f>IF(Liens!C125="","",IF(COUNTIF(Mots!B:B,Liens!C125)&gt;0,"✓ "&amp;Liens!C125,"✗ "&amp;Liens!C125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E130">
+        <f>IF(Liens!D125="","",IF(COUNTIF(Mots!B:B,Liens!D125)&gt;0,"✓ "&amp;Liens!D125,"✗ "&amp;Liens!D125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F130">
+        <f>IF(Liens!E125="","",IF(COUNTIF(Mots!B:B,Liens!E125)&gt;0,"✓ "&amp;Liens!E125,"✗ "&amp;Liens!E125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G130">
+        <f>IF(Liens!F125="","",IF(COUNTIF(Mots!B:B,Liens!F125)&gt;0,"✓ "&amp;Liens!F125,"✗ "&amp;Liens!F125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H130">
+        <f>IF(Liens!G125="","",IF(COUNTIF(Mots!B:B,Liens!G125)&gt;0,"✓ "&amp;Liens!G125,"✗ "&amp;Liens!G125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I130">
+        <f>IF(Liens!H125="","",IF(COUNTIF(Mots!B:B,Liens!H125)&gt;0,"✓ "&amp;Liens!H125,"✗ "&amp;Liens!H125&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131">
+        <f>IF(Liens!A126="","",IF(COUNTIF(Mots!B:B,Liens!A126)&gt;0,"✓ "&amp;Liens!A126,"✗ "&amp;Liens!A126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C131">
+        <f>IF(Liens!B126="","",IF(COUNTIF(Mots!B:B,Liens!B126)&gt;0,"✓ "&amp;Liens!B126,"✗ "&amp;Liens!B126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D131">
+        <f>IF(Liens!C126="","",IF(COUNTIF(Mots!B:B,Liens!C126)&gt;0,"✓ "&amp;Liens!C126,"✗ "&amp;Liens!C126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>IF(Liens!D126="","",IF(COUNTIF(Mots!B:B,Liens!D126)&gt;0,"✓ "&amp;Liens!D126,"✗ "&amp;Liens!D126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F131">
+        <f>IF(Liens!E126="","",IF(COUNTIF(Mots!B:B,Liens!E126)&gt;0,"✓ "&amp;Liens!E126,"✗ "&amp;Liens!E126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G131">
+        <f>IF(Liens!F126="","",IF(COUNTIF(Mots!B:B,Liens!F126)&gt;0,"✓ "&amp;Liens!F126,"✗ "&amp;Liens!F126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H131">
+        <f>IF(Liens!G126="","",IF(COUNTIF(Mots!B:B,Liens!G126)&gt;0,"✓ "&amp;Liens!G126,"✗ "&amp;Liens!G126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I131">
+        <f>IF(Liens!H126="","",IF(COUNTIF(Mots!B:B,Liens!H126)&gt;0,"✓ "&amp;Liens!H126,"✗ "&amp;Liens!H126&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132">
+        <f>IF(Liens!A127="","",IF(COUNTIF(Mots!B:B,Liens!A127)&gt;0,"✓ "&amp;Liens!A127,"✗ "&amp;Liens!A127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C132">
+        <f>IF(Liens!B127="","",IF(COUNTIF(Mots!B:B,Liens!B127)&gt;0,"✓ "&amp;Liens!B127,"✗ "&amp;Liens!B127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D132">
+        <f>IF(Liens!C127="","",IF(COUNTIF(Mots!B:B,Liens!C127)&gt;0,"✓ "&amp;Liens!C127,"✗ "&amp;Liens!C127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E132">
+        <f>IF(Liens!D127="","",IF(COUNTIF(Mots!B:B,Liens!D127)&gt;0,"✓ "&amp;Liens!D127,"✗ "&amp;Liens!D127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F132">
+        <f>IF(Liens!E127="","",IF(COUNTIF(Mots!B:B,Liens!E127)&gt;0,"✓ "&amp;Liens!E127,"✗ "&amp;Liens!E127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G132">
+        <f>IF(Liens!F127="","",IF(COUNTIF(Mots!B:B,Liens!F127)&gt;0,"✓ "&amp;Liens!F127,"✗ "&amp;Liens!F127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H132">
+        <f>IF(Liens!G127="","",IF(COUNTIF(Mots!B:B,Liens!G127)&gt;0,"✓ "&amp;Liens!G127,"✗ "&amp;Liens!G127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I132">
+        <f>IF(Liens!H127="","",IF(COUNTIF(Mots!B:B,Liens!H127)&gt;0,"✓ "&amp;Liens!H127,"✗ "&amp;Liens!H127&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133">
+        <f>IF(Liens!A128="","",IF(COUNTIF(Mots!B:B,Liens!A128)&gt;0,"✓ "&amp;Liens!A128,"✗ "&amp;Liens!A128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C133">
+        <f>IF(Liens!B128="","",IF(COUNTIF(Mots!B:B,Liens!B128)&gt;0,"✓ "&amp;Liens!B128,"✗ "&amp;Liens!B128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D133">
+        <f>IF(Liens!C128="","",IF(COUNTIF(Mots!B:B,Liens!C128)&gt;0,"✓ "&amp;Liens!C128,"✗ "&amp;Liens!C128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E133">
+        <f>IF(Liens!D128="","",IF(COUNTIF(Mots!B:B,Liens!D128)&gt;0,"✓ "&amp;Liens!D128,"✗ "&amp;Liens!D128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F133">
+        <f>IF(Liens!E128="","",IF(COUNTIF(Mots!B:B,Liens!E128)&gt;0,"✓ "&amp;Liens!E128,"✗ "&amp;Liens!E128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G133">
+        <f>IF(Liens!F128="","",IF(COUNTIF(Mots!B:B,Liens!F128)&gt;0,"✓ "&amp;Liens!F128,"✗ "&amp;Liens!F128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H133">
+        <f>IF(Liens!G128="","",IF(COUNTIF(Mots!B:B,Liens!G128)&gt;0,"✓ "&amp;Liens!G128,"✗ "&amp;Liens!G128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I133">
+        <f>IF(Liens!H128="","",IF(COUNTIF(Mots!B:B,Liens!H128)&gt;0,"✓ "&amp;Liens!H128,"✗ "&amp;Liens!H128&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134">
+        <f>IF(Liens!A129="","",IF(COUNTIF(Mots!B:B,Liens!A129)&gt;0,"✓ "&amp;Liens!A129,"✗ "&amp;Liens!A129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C134">
+        <f>IF(Liens!B129="","",IF(COUNTIF(Mots!B:B,Liens!B129)&gt;0,"✓ "&amp;Liens!B129,"✗ "&amp;Liens!B129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D134">
+        <f>IF(Liens!C129="","",IF(COUNTIF(Mots!B:B,Liens!C129)&gt;0,"✓ "&amp;Liens!C129,"✗ "&amp;Liens!C129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E134">
+        <f>IF(Liens!D129="","",IF(COUNTIF(Mots!B:B,Liens!D129)&gt;0,"✓ "&amp;Liens!D129,"✗ "&amp;Liens!D129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F134">
+        <f>IF(Liens!E129="","",IF(COUNTIF(Mots!B:B,Liens!E129)&gt;0,"✓ "&amp;Liens!E129,"✗ "&amp;Liens!E129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G134">
+        <f>IF(Liens!F129="","",IF(COUNTIF(Mots!B:B,Liens!F129)&gt;0,"✓ "&amp;Liens!F129,"✗ "&amp;Liens!F129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H134">
+        <f>IF(Liens!G129="","",IF(COUNTIF(Mots!B:B,Liens!G129)&gt;0,"✓ "&amp;Liens!G129,"✗ "&amp;Liens!G129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I134">
+        <f>IF(Liens!H129="","",IF(COUNTIF(Mots!B:B,Liens!H129)&gt;0,"✓ "&amp;Liens!H129,"✗ "&amp;Liens!H129&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135">
+        <f>IF(Liens!A130="","",IF(COUNTIF(Mots!B:B,Liens!A130)&gt;0,"✓ "&amp;Liens!A130,"✗ "&amp;Liens!A130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C135">
+        <f>IF(Liens!B130="","",IF(COUNTIF(Mots!B:B,Liens!B130)&gt;0,"✓ "&amp;Liens!B130,"✗ "&amp;Liens!B130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D135">
+        <f>IF(Liens!C130="","",IF(COUNTIF(Mots!B:B,Liens!C130)&gt;0,"✓ "&amp;Liens!C130,"✗ "&amp;Liens!C130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E135">
+        <f>IF(Liens!D130="","",IF(COUNTIF(Mots!B:B,Liens!D130)&gt;0,"✓ "&amp;Liens!D130,"✗ "&amp;Liens!D130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F135">
+        <f>IF(Liens!E130="","",IF(COUNTIF(Mots!B:B,Liens!E130)&gt;0,"✓ "&amp;Liens!E130,"✗ "&amp;Liens!E130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G135">
+        <f>IF(Liens!F130="","",IF(COUNTIF(Mots!B:B,Liens!F130)&gt;0,"✓ "&amp;Liens!F130,"✗ "&amp;Liens!F130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H135">
+        <f>IF(Liens!G130="","",IF(COUNTIF(Mots!B:B,Liens!G130)&gt;0,"✓ "&amp;Liens!G130,"✗ "&amp;Liens!G130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I135">
+        <f>IF(Liens!H130="","",IF(COUNTIF(Mots!B:B,Liens!H130)&gt;0,"✓ "&amp;Liens!H130,"✗ "&amp;Liens!H130&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136">
+        <f>IF(Liens!A131="","",IF(COUNTIF(Mots!B:B,Liens!A131)&gt;0,"✓ "&amp;Liens!A131,"✗ "&amp;Liens!A131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C136">
+        <f>IF(Liens!B131="","",IF(COUNTIF(Mots!B:B,Liens!B131)&gt;0,"✓ "&amp;Liens!B131,"✗ "&amp;Liens!B131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D136">
+        <f>IF(Liens!C131="","",IF(COUNTIF(Mots!B:B,Liens!C131)&gt;0,"✓ "&amp;Liens!C131,"✗ "&amp;Liens!C131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E136">
+        <f>IF(Liens!D131="","",IF(COUNTIF(Mots!B:B,Liens!D131)&gt;0,"✓ "&amp;Liens!D131,"✗ "&amp;Liens!D131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F136">
+        <f>IF(Liens!E131="","",IF(COUNTIF(Mots!B:B,Liens!E131)&gt;0,"✓ "&amp;Liens!E131,"✗ "&amp;Liens!E131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G136">
+        <f>IF(Liens!F131="","",IF(COUNTIF(Mots!B:B,Liens!F131)&gt;0,"✓ "&amp;Liens!F131,"✗ "&amp;Liens!F131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H136">
+        <f>IF(Liens!G131="","",IF(COUNTIF(Mots!B:B,Liens!G131)&gt;0,"✓ "&amp;Liens!G131,"✗ "&amp;Liens!G131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I136">
+        <f>IF(Liens!H131="","",IF(COUNTIF(Mots!B:B,Liens!H131)&gt;0,"✓ "&amp;Liens!H131,"✗ "&amp;Liens!H131&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137">
+        <f>IF(Liens!A132="","",IF(COUNTIF(Mots!B:B,Liens!A132)&gt;0,"✓ "&amp;Liens!A132,"✗ "&amp;Liens!A132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C137">
+        <f>IF(Liens!B132="","",IF(COUNTIF(Mots!B:B,Liens!B132)&gt;0,"✓ "&amp;Liens!B132,"✗ "&amp;Liens!B132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D137">
+        <f>IF(Liens!C132="","",IF(COUNTIF(Mots!B:B,Liens!C132)&gt;0,"✓ "&amp;Liens!C132,"✗ "&amp;Liens!C132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E137">
+        <f>IF(Liens!D132="","",IF(COUNTIF(Mots!B:B,Liens!D132)&gt;0,"✓ "&amp;Liens!D132,"✗ "&amp;Liens!D132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F137">
+        <f>IF(Liens!E132="","",IF(COUNTIF(Mots!B:B,Liens!E132)&gt;0,"✓ "&amp;Liens!E132,"✗ "&amp;Liens!E132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G137">
+        <f>IF(Liens!F132="","",IF(COUNTIF(Mots!B:B,Liens!F132)&gt;0,"✓ "&amp;Liens!F132,"✗ "&amp;Liens!F132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H137">
+        <f>IF(Liens!G132="","",IF(COUNTIF(Mots!B:B,Liens!G132)&gt;0,"✓ "&amp;Liens!G132,"✗ "&amp;Liens!G132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I137">
+        <f>IF(Liens!H132="","",IF(COUNTIF(Mots!B:B,Liens!H132)&gt;0,"✓ "&amp;Liens!H132,"✗ "&amp;Liens!H132&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138">
+        <f>IF(Liens!A133="","",IF(COUNTIF(Mots!B:B,Liens!A133)&gt;0,"✓ "&amp;Liens!A133,"✗ "&amp;Liens!A133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C138">
+        <f>IF(Liens!B133="","",IF(COUNTIF(Mots!B:B,Liens!B133)&gt;0,"✓ "&amp;Liens!B133,"✗ "&amp;Liens!B133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D138">
+        <f>IF(Liens!C133="","",IF(COUNTIF(Mots!B:B,Liens!C133)&gt;0,"✓ "&amp;Liens!C133,"✗ "&amp;Liens!C133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E138">
+        <f>IF(Liens!D133="","",IF(COUNTIF(Mots!B:B,Liens!D133)&gt;0,"✓ "&amp;Liens!D133,"✗ "&amp;Liens!D133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F138">
+        <f>IF(Liens!E133="","",IF(COUNTIF(Mots!B:B,Liens!E133)&gt;0,"✓ "&amp;Liens!E133,"✗ "&amp;Liens!E133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G138">
+        <f>IF(Liens!F133="","",IF(COUNTIF(Mots!B:B,Liens!F133)&gt;0,"✓ "&amp;Liens!F133,"✗ "&amp;Liens!F133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H138">
+        <f>IF(Liens!G133="","",IF(COUNTIF(Mots!B:B,Liens!G133)&gt;0,"✓ "&amp;Liens!G133,"✗ "&amp;Liens!G133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I138">
+        <f>IF(Liens!H133="","",IF(COUNTIF(Mots!B:B,Liens!H133)&gt;0,"✓ "&amp;Liens!H133,"✗ "&amp;Liens!H133&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139">
+        <f>IF(Liens!A134="","",IF(COUNTIF(Mots!B:B,Liens!A134)&gt;0,"✓ "&amp;Liens!A134,"✗ "&amp;Liens!A134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C139">
+        <f>IF(Liens!B134="","",IF(COUNTIF(Mots!B:B,Liens!B134)&gt;0,"✓ "&amp;Liens!B134,"✗ "&amp;Liens!B134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D139">
+        <f>IF(Liens!C134="","",IF(COUNTIF(Mots!B:B,Liens!C134)&gt;0,"✓ "&amp;Liens!C134,"✗ "&amp;Liens!C134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E139">
+        <f>IF(Liens!D134="","",IF(COUNTIF(Mots!B:B,Liens!D134)&gt;0,"✓ "&amp;Liens!D134,"✗ "&amp;Liens!D134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F139">
+        <f>IF(Liens!E134="","",IF(COUNTIF(Mots!B:B,Liens!E134)&gt;0,"✓ "&amp;Liens!E134,"✗ "&amp;Liens!E134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G139">
+        <f>IF(Liens!F134="","",IF(COUNTIF(Mots!B:B,Liens!F134)&gt;0,"✓ "&amp;Liens!F134,"✗ "&amp;Liens!F134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H139">
+        <f>IF(Liens!G134="","",IF(COUNTIF(Mots!B:B,Liens!G134)&gt;0,"✓ "&amp;Liens!G134,"✗ "&amp;Liens!G134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I139">
+        <f>IF(Liens!H134="","",IF(COUNTIF(Mots!B:B,Liens!H134)&gt;0,"✓ "&amp;Liens!H134,"✗ "&amp;Liens!H134&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140">
+        <f>IF(Liens!A135="","",IF(COUNTIF(Mots!B:B,Liens!A135)&gt;0,"✓ "&amp;Liens!A135,"✗ "&amp;Liens!A135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C140">
+        <f>IF(Liens!B135="","",IF(COUNTIF(Mots!B:B,Liens!B135)&gt;0,"✓ "&amp;Liens!B135,"✗ "&amp;Liens!B135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D140">
+        <f>IF(Liens!C135="","",IF(COUNTIF(Mots!B:B,Liens!C135)&gt;0,"✓ "&amp;Liens!C135,"✗ "&amp;Liens!C135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E140">
+        <f>IF(Liens!D135="","",IF(COUNTIF(Mots!B:B,Liens!D135)&gt;0,"✓ "&amp;Liens!D135,"✗ "&amp;Liens!D135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F140">
+        <f>IF(Liens!E135="","",IF(COUNTIF(Mots!B:B,Liens!E135)&gt;0,"✓ "&amp;Liens!E135,"✗ "&amp;Liens!E135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G140">
+        <f>IF(Liens!F135="","",IF(COUNTIF(Mots!B:B,Liens!F135)&gt;0,"✓ "&amp;Liens!F135,"✗ "&amp;Liens!F135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H140">
+        <f>IF(Liens!G135="","",IF(COUNTIF(Mots!B:B,Liens!G135)&gt;0,"✓ "&amp;Liens!G135,"✗ "&amp;Liens!G135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I140">
+        <f>IF(Liens!H135="","",IF(COUNTIF(Mots!B:B,Liens!H135)&gt;0,"✓ "&amp;Liens!H135,"✗ "&amp;Liens!H135&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141">
+        <f>IF(Liens!A136="","",IF(COUNTIF(Mots!B:B,Liens!A136)&gt;0,"✓ "&amp;Liens!A136,"✗ "&amp;Liens!A136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C141">
+        <f>IF(Liens!B136="","",IF(COUNTIF(Mots!B:B,Liens!B136)&gt;0,"✓ "&amp;Liens!B136,"✗ "&amp;Liens!B136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D141">
+        <f>IF(Liens!C136="","",IF(COUNTIF(Mots!B:B,Liens!C136)&gt;0,"✓ "&amp;Liens!C136,"✗ "&amp;Liens!C136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E141">
+        <f>IF(Liens!D136="","",IF(COUNTIF(Mots!B:B,Liens!D136)&gt;0,"✓ "&amp;Liens!D136,"✗ "&amp;Liens!D136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F141">
+        <f>IF(Liens!E136="","",IF(COUNTIF(Mots!B:B,Liens!E136)&gt;0,"✓ "&amp;Liens!E136,"✗ "&amp;Liens!E136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G141">
+        <f>IF(Liens!F136="","",IF(COUNTIF(Mots!B:B,Liens!F136)&gt;0,"✓ "&amp;Liens!F136,"✗ "&amp;Liens!F136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H141">
+        <f>IF(Liens!G136="","",IF(COUNTIF(Mots!B:B,Liens!G136)&gt;0,"✓ "&amp;Liens!G136,"✗ "&amp;Liens!G136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I141">
+        <f>IF(Liens!H136="","",IF(COUNTIF(Mots!B:B,Liens!H136)&gt;0,"✓ "&amp;Liens!H136,"✗ "&amp;Liens!H136&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142">
+        <f>IF(Liens!A137="","",IF(COUNTIF(Mots!B:B,Liens!A137)&gt;0,"✓ "&amp;Liens!A137,"✗ "&amp;Liens!A137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C142">
+        <f>IF(Liens!B137="","",IF(COUNTIF(Mots!B:B,Liens!B137)&gt;0,"✓ "&amp;Liens!B137,"✗ "&amp;Liens!B137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D142">
+        <f>IF(Liens!C137="","",IF(COUNTIF(Mots!B:B,Liens!C137)&gt;0,"✓ "&amp;Liens!C137,"✗ "&amp;Liens!C137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E142">
+        <f>IF(Liens!D137="","",IF(COUNTIF(Mots!B:B,Liens!D137)&gt;0,"✓ "&amp;Liens!D137,"✗ "&amp;Liens!D137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F142">
+        <f>IF(Liens!E137="","",IF(COUNTIF(Mots!B:B,Liens!E137)&gt;0,"✓ "&amp;Liens!E137,"✗ "&amp;Liens!E137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G142">
+        <f>IF(Liens!F137="","",IF(COUNTIF(Mots!B:B,Liens!F137)&gt;0,"✓ "&amp;Liens!F137,"✗ "&amp;Liens!F137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H142">
+        <f>IF(Liens!G137="","",IF(COUNTIF(Mots!B:B,Liens!G137)&gt;0,"✓ "&amp;Liens!G137,"✗ "&amp;Liens!G137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I142">
+        <f>IF(Liens!H137="","",IF(COUNTIF(Mots!B:B,Liens!H137)&gt;0,"✓ "&amp;Liens!H137,"✗ "&amp;Liens!H137&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143">
+        <f>IF(Liens!A138="","",IF(COUNTIF(Mots!B:B,Liens!A138)&gt;0,"✓ "&amp;Liens!A138,"✗ "&amp;Liens!A138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C143">
+        <f>IF(Liens!B138="","",IF(COUNTIF(Mots!B:B,Liens!B138)&gt;0,"✓ "&amp;Liens!B138,"✗ "&amp;Liens!B138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D143">
+        <f>IF(Liens!C138="","",IF(COUNTIF(Mots!B:B,Liens!C138)&gt;0,"✓ "&amp;Liens!C138,"✗ "&amp;Liens!C138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E143">
+        <f>IF(Liens!D138="","",IF(COUNTIF(Mots!B:B,Liens!D138)&gt;0,"✓ "&amp;Liens!D138,"✗ "&amp;Liens!D138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F143">
+        <f>IF(Liens!E138="","",IF(COUNTIF(Mots!B:B,Liens!E138)&gt;0,"✓ "&amp;Liens!E138,"✗ "&amp;Liens!E138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G143">
+        <f>IF(Liens!F138="","",IF(COUNTIF(Mots!B:B,Liens!F138)&gt;0,"✓ "&amp;Liens!F138,"✗ "&amp;Liens!F138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H143">
+        <f>IF(Liens!G138="","",IF(COUNTIF(Mots!B:B,Liens!G138)&gt;0,"✓ "&amp;Liens!G138,"✗ "&amp;Liens!G138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I143">
+        <f>IF(Liens!H138="","",IF(COUNTIF(Mots!B:B,Liens!H138)&gt;0,"✓ "&amp;Liens!H138,"✗ "&amp;Liens!H138&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144">
+        <f>IF(Liens!A139="","",IF(COUNTIF(Mots!B:B,Liens!A139)&gt;0,"✓ "&amp;Liens!A139,"✗ "&amp;Liens!A139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C144">
+        <f>IF(Liens!B139="","",IF(COUNTIF(Mots!B:B,Liens!B139)&gt;0,"✓ "&amp;Liens!B139,"✗ "&amp;Liens!B139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D144">
+        <f>IF(Liens!C139="","",IF(COUNTIF(Mots!B:B,Liens!C139)&gt;0,"✓ "&amp;Liens!C139,"✗ "&amp;Liens!C139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E144">
+        <f>IF(Liens!D139="","",IF(COUNTIF(Mots!B:B,Liens!D139)&gt;0,"✓ "&amp;Liens!D139,"✗ "&amp;Liens!D139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F144">
+        <f>IF(Liens!E139="","",IF(COUNTIF(Mots!B:B,Liens!E139)&gt;0,"✓ "&amp;Liens!E139,"✗ "&amp;Liens!E139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G144">
+        <f>IF(Liens!F139="","",IF(COUNTIF(Mots!B:B,Liens!F139)&gt;0,"✓ "&amp;Liens!F139,"✗ "&amp;Liens!F139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H144">
+        <f>IF(Liens!G139="","",IF(COUNTIF(Mots!B:B,Liens!G139)&gt;0,"✓ "&amp;Liens!G139,"✗ "&amp;Liens!G139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I144">
+        <f>IF(Liens!H139="","",IF(COUNTIF(Mots!B:B,Liens!H139)&gt;0,"✓ "&amp;Liens!H139,"✗ "&amp;Liens!H139&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145">
+        <f>IF(Liens!A140="","",IF(COUNTIF(Mots!B:B,Liens!A140)&gt;0,"✓ "&amp;Liens!A140,"✗ "&amp;Liens!A140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C145">
+        <f>IF(Liens!B140="","",IF(COUNTIF(Mots!B:B,Liens!B140)&gt;0,"✓ "&amp;Liens!B140,"✗ "&amp;Liens!B140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D145">
+        <f>IF(Liens!C140="","",IF(COUNTIF(Mots!B:B,Liens!C140)&gt;0,"✓ "&amp;Liens!C140,"✗ "&amp;Liens!C140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E145">
+        <f>IF(Liens!D140="","",IF(COUNTIF(Mots!B:B,Liens!D140)&gt;0,"✓ "&amp;Liens!D140,"✗ "&amp;Liens!D140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F145">
+        <f>IF(Liens!E140="","",IF(COUNTIF(Mots!B:B,Liens!E140)&gt;0,"✓ "&amp;Liens!E140,"✗ "&amp;Liens!E140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G145">
+        <f>IF(Liens!F140="","",IF(COUNTIF(Mots!B:B,Liens!F140)&gt;0,"✓ "&amp;Liens!F140,"✗ "&amp;Liens!F140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H145">
+        <f>IF(Liens!G140="","",IF(COUNTIF(Mots!B:B,Liens!G140)&gt;0,"✓ "&amp;Liens!G140,"✗ "&amp;Liens!G140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I145">
+        <f>IF(Liens!H140="","",IF(COUNTIF(Mots!B:B,Liens!H140)&gt;0,"✓ "&amp;Liens!H140,"✗ "&amp;Liens!H140&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146">
+        <f>IF(Liens!A141="","",IF(COUNTIF(Mots!B:B,Liens!A141)&gt;0,"✓ "&amp;Liens!A141,"✗ "&amp;Liens!A141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C146">
+        <f>IF(Liens!B141="","",IF(COUNTIF(Mots!B:B,Liens!B141)&gt;0,"✓ "&amp;Liens!B141,"✗ "&amp;Liens!B141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D146">
+        <f>IF(Liens!C141="","",IF(COUNTIF(Mots!B:B,Liens!C141)&gt;0,"✓ "&amp;Liens!C141,"✗ "&amp;Liens!C141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E146">
+        <f>IF(Liens!D141="","",IF(COUNTIF(Mots!B:B,Liens!D141)&gt;0,"✓ "&amp;Liens!D141,"✗ "&amp;Liens!D141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F146">
+        <f>IF(Liens!E141="","",IF(COUNTIF(Mots!B:B,Liens!E141)&gt;0,"✓ "&amp;Liens!E141,"✗ "&amp;Liens!E141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G146">
+        <f>IF(Liens!F141="","",IF(COUNTIF(Mots!B:B,Liens!F141)&gt;0,"✓ "&amp;Liens!F141,"✗ "&amp;Liens!F141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H146">
+        <f>IF(Liens!G141="","",IF(COUNTIF(Mots!B:B,Liens!G141)&gt;0,"✓ "&amp;Liens!G141,"✗ "&amp;Liens!G141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I146">
+        <f>IF(Liens!H141="","",IF(COUNTIF(Mots!B:B,Liens!H141)&gt;0,"✓ "&amp;Liens!H141,"✗ "&amp;Liens!H141&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147">
+        <f>IF(Liens!A142="","",IF(COUNTIF(Mots!B:B,Liens!A142)&gt;0,"✓ "&amp;Liens!A142,"✗ "&amp;Liens!A142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C147">
+        <f>IF(Liens!B142="","",IF(COUNTIF(Mots!B:B,Liens!B142)&gt;0,"✓ "&amp;Liens!B142,"✗ "&amp;Liens!B142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D147">
+        <f>IF(Liens!C142="","",IF(COUNTIF(Mots!B:B,Liens!C142)&gt;0,"✓ "&amp;Liens!C142,"✗ "&amp;Liens!C142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E147">
+        <f>IF(Liens!D142="","",IF(COUNTIF(Mots!B:B,Liens!D142)&gt;0,"✓ "&amp;Liens!D142,"✗ "&amp;Liens!D142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F147">
+        <f>IF(Liens!E142="","",IF(COUNTIF(Mots!B:B,Liens!E142)&gt;0,"✓ "&amp;Liens!E142,"✗ "&amp;Liens!E142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G147">
+        <f>IF(Liens!F142="","",IF(COUNTIF(Mots!B:B,Liens!F142)&gt;0,"✓ "&amp;Liens!F142,"✗ "&amp;Liens!F142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H147">
+        <f>IF(Liens!G142="","",IF(COUNTIF(Mots!B:B,Liens!G142)&gt;0,"✓ "&amp;Liens!G142,"✗ "&amp;Liens!G142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I147">
+        <f>IF(Liens!H142="","",IF(COUNTIF(Mots!B:B,Liens!H142)&gt;0,"✓ "&amp;Liens!H142,"✗ "&amp;Liens!H142&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148">
+        <f>IF(Liens!A143="","",IF(COUNTIF(Mots!B:B,Liens!A143)&gt;0,"✓ "&amp;Liens!A143,"✗ "&amp;Liens!A143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C148">
+        <f>IF(Liens!B143="","",IF(COUNTIF(Mots!B:B,Liens!B143)&gt;0,"✓ "&amp;Liens!B143,"✗ "&amp;Liens!B143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D148">
+        <f>IF(Liens!C143="","",IF(COUNTIF(Mots!B:B,Liens!C143)&gt;0,"✓ "&amp;Liens!C143,"✗ "&amp;Liens!C143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E148">
+        <f>IF(Liens!D143="","",IF(COUNTIF(Mots!B:B,Liens!D143)&gt;0,"✓ "&amp;Liens!D143,"✗ "&amp;Liens!D143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F148">
+        <f>IF(Liens!E143="","",IF(COUNTIF(Mots!B:B,Liens!E143)&gt;0,"✓ "&amp;Liens!E143,"✗ "&amp;Liens!E143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G148">
+        <f>IF(Liens!F143="","",IF(COUNTIF(Mots!B:B,Liens!F143)&gt;0,"✓ "&amp;Liens!F143,"✗ "&amp;Liens!F143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H148">
+        <f>IF(Liens!G143="","",IF(COUNTIF(Mots!B:B,Liens!G143)&gt;0,"✓ "&amp;Liens!G143,"✗ "&amp;Liens!G143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I148">
+        <f>IF(Liens!H143="","",IF(COUNTIF(Mots!B:B,Liens!H143)&gt;0,"✓ "&amp;Liens!H143,"✗ "&amp;Liens!H143&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149">
+        <f>IF(Liens!A144="","",IF(COUNTIF(Mots!B:B,Liens!A144)&gt;0,"✓ "&amp;Liens!A144,"✗ "&amp;Liens!A144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C149">
+        <f>IF(Liens!B144="","",IF(COUNTIF(Mots!B:B,Liens!B144)&gt;0,"✓ "&amp;Liens!B144,"✗ "&amp;Liens!B144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D149">
+        <f>IF(Liens!C144="","",IF(COUNTIF(Mots!B:B,Liens!C144)&gt;0,"✓ "&amp;Liens!C144,"✗ "&amp;Liens!C144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E149">
+        <f>IF(Liens!D144="","",IF(COUNTIF(Mots!B:B,Liens!D144)&gt;0,"✓ "&amp;Liens!D144,"✗ "&amp;Liens!D144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F149">
+        <f>IF(Liens!E144="","",IF(COUNTIF(Mots!B:B,Liens!E144)&gt;0,"✓ "&amp;Liens!E144,"✗ "&amp;Liens!E144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G149">
+        <f>IF(Liens!F144="","",IF(COUNTIF(Mots!B:B,Liens!F144)&gt;0,"✓ "&amp;Liens!F144,"✗ "&amp;Liens!F144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H149">
+        <f>IF(Liens!G144="","",IF(COUNTIF(Mots!B:B,Liens!G144)&gt;0,"✓ "&amp;Liens!G144,"✗ "&amp;Liens!G144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I149">
+        <f>IF(Liens!H144="","",IF(COUNTIF(Mots!B:B,Liens!H144)&gt;0,"✓ "&amp;Liens!H144,"✗ "&amp;Liens!H144&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150">
+        <f>IF(Liens!A145="","",IF(COUNTIF(Mots!B:B,Liens!A145)&gt;0,"✓ "&amp;Liens!A145,"✗ "&amp;Liens!A145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C150">
+        <f>IF(Liens!B145="","",IF(COUNTIF(Mots!B:B,Liens!B145)&gt;0,"✓ "&amp;Liens!B145,"✗ "&amp;Liens!B145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D150">
+        <f>IF(Liens!C145="","",IF(COUNTIF(Mots!B:B,Liens!C145)&gt;0,"✓ "&amp;Liens!C145,"✗ "&amp;Liens!C145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E150">
+        <f>IF(Liens!D145="","",IF(COUNTIF(Mots!B:B,Liens!D145)&gt;0,"✓ "&amp;Liens!D145,"✗ "&amp;Liens!D145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F150">
+        <f>IF(Liens!E145="","",IF(COUNTIF(Mots!B:B,Liens!E145)&gt;0,"✓ "&amp;Liens!E145,"✗ "&amp;Liens!E145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G150">
+        <f>IF(Liens!F145="","",IF(COUNTIF(Mots!B:B,Liens!F145)&gt;0,"✓ "&amp;Liens!F145,"✗ "&amp;Liens!F145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H150">
+        <f>IF(Liens!G145="","",IF(COUNTIF(Mots!B:B,Liens!G145)&gt;0,"✓ "&amp;Liens!G145,"✗ "&amp;Liens!G145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I150">
+        <f>IF(Liens!H145="","",IF(COUNTIF(Mots!B:B,Liens!H145)&gt;0,"✓ "&amp;Liens!H145,"✗ "&amp;Liens!H145&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151">
+        <f>IF(Liens!A146="","",IF(COUNTIF(Mots!B:B,Liens!A146)&gt;0,"✓ "&amp;Liens!A146,"✗ "&amp;Liens!A146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C151">
+        <f>IF(Liens!B146="","",IF(COUNTIF(Mots!B:B,Liens!B146)&gt;0,"✓ "&amp;Liens!B146,"✗ "&amp;Liens!B146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D151">
+        <f>IF(Liens!C146="","",IF(COUNTIF(Mots!B:B,Liens!C146)&gt;0,"✓ "&amp;Liens!C146,"✗ "&amp;Liens!C146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E151">
+        <f>IF(Liens!D146="","",IF(COUNTIF(Mots!B:B,Liens!D146)&gt;0,"✓ "&amp;Liens!D146,"✗ "&amp;Liens!D146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F151">
+        <f>IF(Liens!E146="","",IF(COUNTIF(Mots!B:B,Liens!E146)&gt;0,"✓ "&amp;Liens!E146,"✗ "&amp;Liens!E146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G151">
+        <f>IF(Liens!F146="","",IF(COUNTIF(Mots!B:B,Liens!F146)&gt;0,"✓ "&amp;Liens!F146,"✗ "&amp;Liens!F146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H151">
+        <f>IF(Liens!G146="","",IF(COUNTIF(Mots!B:B,Liens!G146)&gt;0,"✓ "&amp;Liens!G146,"✗ "&amp;Liens!G146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I151">
+        <f>IF(Liens!H146="","",IF(COUNTIF(Mots!B:B,Liens!H146)&gt;0,"✓ "&amp;Liens!H146,"✗ "&amp;Liens!H146&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152">
+        <f>IF(Liens!A147="","",IF(COUNTIF(Mots!B:B,Liens!A147)&gt;0,"✓ "&amp;Liens!A147,"✗ "&amp;Liens!A147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C152">
+        <f>IF(Liens!B147="","",IF(COUNTIF(Mots!B:B,Liens!B147)&gt;0,"✓ "&amp;Liens!B147,"✗ "&amp;Liens!B147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D152">
+        <f>IF(Liens!C147="","",IF(COUNTIF(Mots!B:B,Liens!C147)&gt;0,"✓ "&amp;Liens!C147,"✗ "&amp;Liens!C147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E152">
+        <f>IF(Liens!D147="","",IF(COUNTIF(Mots!B:B,Liens!D147)&gt;0,"✓ "&amp;Liens!D147,"✗ "&amp;Liens!D147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F152">
+        <f>IF(Liens!E147="","",IF(COUNTIF(Mots!B:B,Liens!E147)&gt;0,"✓ "&amp;Liens!E147,"✗ "&amp;Liens!E147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G152">
+        <f>IF(Liens!F147="","",IF(COUNTIF(Mots!B:B,Liens!F147)&gt;0,"✓ "&amp;Liens!F147,"✗ "&amp;Liens!F147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H152">
+        <f>IF(Liens!G147="","",IF(COUNTIF(Mots!B:B,Liens!G147)&gt;0,"✓ "&amp;Liens!G147,"✗ "&amp;Liens!G147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I152">
+        <f>IF(Liens!H147="","",IF(COUNTIF(Mots!B:B,Liens!H147)&gt;0,"✓ "&amp;Liens!H147,"✗ "&amp;Liens!H147&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153">
+        <f>IF(Liens!A148="","",IF(COUNTIF(Mots!B:B,Liens!A148)&gt;0,"✓ "&amp;Liens!A148,"✗ "&amp;Liens!A148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C153">
+        <f>IF(Liens!B148="","",IF(COUNTIF(Mots!B:B,Liens!B148)&gt;0,"✓ "&amp;Liens!B148,"✗ "&amp;Liens!B148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D153">
+        <f>IF(Liens!C148="","",IF(COUNTIF(Mots!B:B,Liens!C148)&gt;0,"✓ "&amp;Liens!C148,"✗ "&amp;Liens!C148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E153">
+        <f>IF(Liens!D148="","",IF(COUNTIF(Mots!B:B,Liens!D148)&gt;0,"✓ "&amp;Liens!D148,"✗ "&amp;Liens!D148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F153">
+        <f>IF(Liens!E148="","",IF(COUNTIF(Mots!B:B,Liens!E148)&gt;0,"✓ "&amp;Liens!E148,"✗ "&amp;Liens!E148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G153">
+        <f>IF(Liens!F148="","",IF(COUNTIF(Mots!B:B,Liens!F148)&gt;0,"✓ "&amp;Liens!F148,"✗ "&amp;Liens!F148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H153">
+        <f>IF(Liens!G148="","",IF(COUNTIF(Mots!B:B,Liens!G148)&gt;0,"✓ "&amp;Liens!G148,"✗ "&amp;Liens!G148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I153">
+        <f>IF(Liens!H148="","",IF(COUNTIF(Mots!B:B,Liens!H148)&gt;0,"✓ "&amp;Liens!H148,"✗ "&amp;Liens!H148&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154">
+        <f>IF(Liens!A149="","",IF(COUNTIF(Mots!B:B,Liens!A149)&gt;0,"✓ "&amp;Liens!A149,"✗ "&amp;Liens!A149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C154">
+        <f>IF(Liens!B149="","",IF(COUNTIF(Mots!B:B,Liens!B149)&gt;0,"✓ "&amp;Liens!B149,"✗ "&amp;Liens!B149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D154">
+        <f>IF(Liens!C149="","",IF(COUNTIF(Mots!B:B,Liens!C149)&gt;0,"✓ "&amp;Liens!C149,"✗ "&amp;Liens!C149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E154">
+        <f>IF(Liens!D149="","",IF(COUNTIF(Mots!B:B,Liens!D149)&gt;0,"✓ "&amp;Liens!D149,"✗ "&amp;Liens!D149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F154">
+        <f>IF(Liens!E149="","",IF(COUNTIF(Mots!B:B,Liens!E149)&gt;0,"✓ "&amp;Liens!E149,"✗ "&amp;Liens!E149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G154">
+        <f>IF(Liens!F149="","",IF(COUNTIF(Mots!B:B,Liens!F149)&gt;0,"✓ "&amp;Liens!F149,"✗ "&amp;Liens!F149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H154">
+        <f>IF(Liens!G149="","",IF(COUNTIF(Mots!B:B,Liens!G149)&gt;0,"✓ "&amp;Liens!G149,"✗ "&amp;Liens!G149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I154">
+        <f>IF(Liens!H149="","",IF(COUNTIF(Mots!B:B,Liens!H149)&gt;0,"✓ "&amp;Liens!H149,"✗ "&amp;Liens!H149&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155">
+        <f>IF(Liens!A150="","",IF(COUNTIF(Mots!B:B,Liens!A150)&gt;0,"✓ "&amp;Liens!A150,"✗ "&amp;Liens!A150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C155">
+        <f>IF(Liens!B150="","",IF(COUNTIF(Mots!B:B,Liens!B150)&gt;0,"✓ "&amp;Liens!B150,"✗ "&amp;Liens!B150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D155">
+        <f>IF(Liens!C150="","",IF(COUNTIF(Mots!B:B,Liens!C150)&gt;0,"✓ "&amp;Liens!C150,"✗ "&amp;Liens!C150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E155">
+        <f>IF(Liens!D150="","",IF(COUNTIF(Mots!B:B,Liens!D150)&gt;0,"✓ "&amp;Liens!D150,"✗ "&amp;Liens!D150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F155">
+        <f>IF(Liens!E150="","",IF(COUNTIF(Mots!B:B,Liens!E150)&gt;0,"✓ "&amp;Liens!E150,"✗ "&amp;Liens!E150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G155">
+        <f>IF(Liens!F150="","",IF(COUNTIF(Mots!B:B,Liens!F150)&gt;0,"✓ "&amp;Liens!F150,"✗ "&amp;Liens!F150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H155">
+        <f>IF(Liens!G150="","",IF(COUNTIF(Mots!B:B,Liens!G150)&gt;0,"✓ "&amp;Liens!G150,"✗ "&amp;Liens!G150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I155">
+        <f>IF(Liens!H150="","",IF(COUNTIF(Mots!B:B,Liens!H150)&gt;0,"✓ "&amp;Liens!H150,"✗ "&amp;Liens!H150&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156">
+        <f>IF(Liens!A151="","",IF(COUNTIF(Mots!B:B,Liens!A151)&gt;0,"✓ "&amp;Liens!A151,"✗ "&amp;Liens!A151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C156">
+        <f>IF(Liens!B151="","",IF(COUNTIF(Mots!B:B,Liens!B151)&gt;0,"✓ "&amp;Liens!B151,"✗ "&amp;Liens!B151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D156">
+        <f>IF(Liens!C151="","",IF(COUNTIF(Mots!B:B,Liens!C151)&gt;0,"✓ "&amp;Liens!C151,"✗ "&amp;Liens!C151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E156">
+        <f>IF(Liens!D151="","",IF(COUNTIF(Mots!B:B,Liens!D151)&gt;0,"✓ "&amp;Liens!D151,"✗ "&amp;Liens!D151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F156">
+        <f>IF(Liens!E151="","",IF(COUNTIF(Mots!B:B,Liens!E151)&gt;0,"✓ "&amp;Liens!E151,"✗ "&amp;Liens!E151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G156">
+        <f>IF(Liens!F151="","",IF(COUNTIF(Mots!B:B,Liens!F151)&gt;0,"✓ "&amp;Liens!F151,"✗ "&amp;Liens!F151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H156">
+        <f>IF(Liens!G151="","",IF(COUNTIF(Mots!B:B,Liens!G151)&gt;0,"✓ "&amp;Liens!G151,"✗ "&amp;Liens!G151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I156">
+        <f>IF(Liens!H151="","",IF(COUNTIF(Mots!B:B,Liens!H151)&gt;0,"✓ "&amp;Liens!H151,"✗ "&amp;Liens!H151&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157">
+        <f>IF(Liens!A152="","",IF(COUNTIF(Mots!B:B,Liens!A152)&gt;0,"✓ "&amp;Liens!A152,"✗ "&amp;Liens!A152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C157">
+        <f>IF(Liens!B152="","",IF(COUNTIF(Mots!B:B,Liens!B152)&gt;0,"✓ "&amp;Liens!B152,"✗ "&amp;Liens!B152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D157">
+        <f>IF(Liens!C152="","",IF(COUNTIF(Mots!B:B,Liens!C152)&gt;0,"✓ "&amp;Liens!C152,"✗ "&amp;Liens!C152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E157">
+        <f>IF(Liens!D152="","",IF(COUNTIF(Mots!B:B,Liens!D152)&gt;0,"✓ "&amp;Liens!D152,"✗ "&amp;Liens!D152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F157">
+        <f>IF(Liens!E152="","",IF(COUNTIF(Mots!B:B,Liens!E152)&gt;0,"✓ "&amp;Liens!E152,"✗ "&amp;Liens!E152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G157">
+        <f>IF(Liens!F152="","",IF(COUNTIF(Mots!B:B,Liens!F152)&gt;0,"✓ "&amp;Liens!F152,"✗ "&amp;Liens!F152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H157">
+        <f>IF(Liens!G152="","",IF(COUNTIF(Mots!B:B,Liens!G152)&gt;0,"✓ "&amp;Liens!G152,"✗ "&amp;Liens!G152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I157">
+        <f>IF(Liens!H152="","",IF(COUNTIF(Mots!B:B,Liens!H152)&gt;0,"✓ "&amp;Liens!H152,"✗ "&amp;Liens!H152&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158">
+        <f>IF(Liens!A153="","",IF(COUNTIF(Mots!B:B,Liens!A153)&gt;0,"✓ "&amp;Liens!A153,"✗ "&amp;Liens!A153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C158">
+        <f>IF(Liens!B153="","",IF(COUNTIF(Mots!B:B,Liens!B153)&gt;0,"✓ "&amp;Liens!B153,"✗ "&amp;Liens!B153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D158">
+        <f>IF(Liens!C153="","",IF(COUNTIF(Mots!B:B,Liens!C153)&gt;0,"✓ "&amp;Liens!C153,"✗ "&amp;Liens!C153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E158">
+        <f>IF(Liens!D153="","",IF(COUNTIF(Mots!B:B,Liens!D153)&gt;0,"✓ "&amp;Liens!D153,"✗ "&amp;Liens!D153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F158">
+        <f>IF(Liens!E153="","",IF(COUNTIF(Mots!B:B,Liens!E153)&gt;0,"✓ "&amp;Liens!E153,"✗ "&amp;Liens!E153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G158">
+        <f>IF(Liens!F153="","",IF(COUNTIF(Mots!B:B,Liens!F153)&gt;0,"✓ "&amp;Liens!F153,"✗ "&amp;Liens!F153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H158">
+        <f>IF(Liens!G153="","",IF(COUNTIF(Mots!B:B,Liens!G153)&gt;0,"✓ "&amp;Liens!G153,"✗ "&amp;Liens!G153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I158">
+        <f>IF(Liens!H153="","",IF(COUNTIF(Mots!B:B,Liens!H153)&gt;0,"✓ "&amp;Liens!H153,"✗ "&amp;Liens!H153&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159">
+        <f>IF(Liens!A154="","",IF(COUNTIF(Mots!B:B,Liens!A154)&gt;0,"✓ "&amp;Liens!A154,"✗ "&amp;Liens!A154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C159">
+        <f>IF(Liens!B154="","",IF(COUNTIF(Mots!B:B,Liens!B154)&gt;0,"✓ "&amp;Liens!B154,"✗ "&amp;Liens!B154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D159">
+        <f>IF(Liens!C154="","",IF(COUNTIF(Mots!B:B,Liens!C154)&gt;0,"✓ "&amp;Liens!C154,"✗ "&amp;Liens!C154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E159">
+        <f>IF(Liens!D154="","",IF(COUNTIF(Mots!B:B,Liens!D154)&gt;0,"✓ "&amp;Liens!D154,"✗ "&amp;Liens!D154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F159">
+        <f>IF(Liens!E154="","",IF(COUNTIF(Mots!B:B,Liens!E154)&gt;0,"✓ "&amp;Liens!E154,"✗ "&amp;Liens!E154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G159">
+        <f>IF(Liens!F154="","",IF(COUNTIF(Mots!B:B,Liens!F154)&gt;0,"✓ "&amp;Liens!F154,"✗ "&amp;Liens!F154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H159">
+        <f>IF(Liens!G154="","",IF(COUNTIF(Mots!B:B,Liens!G154)&gt;0,"✓ "&amp;Liens!G154,"✗ "&amp;Liens!G154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I159">
+        <f>IF(Liens!H154="","",IF(COUNTIF(Mots!B:B,Liens!H154)&gt;0,"✓ "&amp;Liens!H154,"✗ "&amp;Liens!H154&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>155</v>
+      </c>
+      <c r="B160">
+        <f>IF(Liens!A155="","",IF(COUNTIF(Mots!B:B,Liens!A155)&gt;0,"✓ "&amp;Liens!A155,"✗ "&amp;Liens!A155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C160">
+        <f>IF(Liens!B155="","",IF(COUNTIF(Mots!B:B,Liens!B155)&gt;0,"✓ "&amp;Liens!B155,"✗ "&amp;Liens!B155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D160">
+        <f>IF(Liens!C155="","",IF(COUNTIF(Mots!B:B,Liens!C155)&gt;0,"✓ "&amp;Liens!C155,"✗ "&amp;Liens!C155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E160">
+        <f>IF(Liens!D155="","",IF(COUNTIF(Mots!B:B,Liens!D155)&gt;0,"✓ "&amp;Liens!D155,"✗ "&amp;Liens!D155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F160">
+        <f>IF(Liens!E155="","",IF(COUNTIF(Mots!B:B,Liens!E155)&gt;0,"✓ "&amp;Liens!E155,"✗ "&amp;Liens!E155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G160">
+        <f>IF(Liens!F155="","",IF(COUNTIF(Mots!B:B,Liens!F155)&gt;0,"✓ "&amp;Liens!F155,"✗ "&amp;Liens!F155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H160">
+        <f>IF(Liens!G155="","",IF(COUNTIF(Mots!B:B,Liens!G155)&gt;0,"✓ "&amp;Liens!G155,"✗ "&amp;Liens!G155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I160">
+        <f>IF(Liens!H155="","",IF(COUNTIF(Mots!B:B,Liens!H155)&gt;0,"✓ "&amp;Liens!H155,"✗ "&amp;Liens!H155&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>156</v>
+      </c>
+      <c r="B161">
+        <f>IF(Liens!A156="","",IF(COUNTIF(Mots!B:B,Liens!A156)&gt;0,"✓ "&amp;Liens!A156,"✗ "&amp;Liens!A156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C161">
+        <f>IF(Liens!B156="","",IF(COUNTIF(Mots!B:B,Liens!B156)&gt;0,"✓ "&amp;Liens!B156,"✗ "&amp;Liens!B156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D161">
+        <f>IF(Liens!C156="","",IF(COUNTIF(Mots!B:B,Liens!C156)&gt;0,"✓ "&amp;Liens!C156,"✗ "&amp;Liens!C156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E161">
+        <f>IF(Liens!D156="","",IF(COUNTIF(Mots!B:B,Liens!D156)&gt;0,"✓ "&amp;Liens!D156,"✗ "&amp;Liens!D156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F161">
+        <f>IF(Liens!E156="","",IF(COUNTIF(Mots!B:B,Liens!E156)&gt;0,"✓ "&amp;Liens!E156,"✗ "&amp;Liens!E156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G161">
+        <f>IF(Liens!F156="","",IF(COUNTIF(Mots!B:B,Liens!F156)&gt;0,"✓ "&amp;Liens!F156,"✗ "&amp;Liens!F156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H161">
+        <f>IF(Liens!G156="","",IF(COUNTIF(Mots!B:B,Liens!G156)&gt;0,"✓ "&amp;Liens!G156,"✗ "&amp;Liens!G156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I161">
+        <f>IF(Liens!H156="","",IF(COUNTIF(Mots!B:B,Liens!H156)&gt;0,"✓ "&amp;Liens!H156,"✗ "&amp;Liens!H156&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>157</v>
+      </c>
+      <c r="B162">
+        <f>IF(Liens!A157="","",IF(COUNTIF(Mots!B:B,Liens!A157)&gt;0,"✓ "&amp;Liens!A157,"✗ "&amp;Liens!A157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C162">
+        <f>IF(Liens!B157="","",IF(COUNTIF(Mots!B:B,Liens!B157)&gt;0,"✓ "&amp;Liens!B157,"✗ "&amp;Liens!B157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D162">
+        <f>IF(Liens!C157="","",IF(COUNTIF(Mots!B:B,Liens!C157)&gt;0,"✓ "&amp;Liens!C157,"✗ "&amp;Liens!C157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E162">
+        <f>IF(Liens!D157="","",IF(COUNTIF(Mots!B:B,Liens!D157)&gt;0,"✓ "&amp;Liens!D157,"✗ "&amp;Liens!D157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F162">
+        <f>IF(Liens!E157="","",IF(COUNTIF(Mots!B:B,Liens!E157)&gt;0,"✓ "&amp;Liens!E157,"✗ "&amp;Liens!E157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G162">
+        <f>IF(Liens!F157="","",IF(COUNTIF(Mots!B:B,Liens!F157)&gt;0,"✓ "&amp;Liens!F157,"✗ "&amp;Liens!F157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H162">
+        <f>IF(Liens!G157="","",IF(COUNTIF(Mots!B:B,Liens!G157)&gt;0,"✓ "&amp;Liens!G157,"✗ "&amp;Liens!G157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I162">
+        <f>IF(Liens!H157="","",IF(COUNTIF(Mots!B:B,Liens!H157)&gt;0,"✓ "&amp;Liens!H157,"✗ "&amp;Liens!H157&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>158</v>
+      </c>
+      <c r="B163">
+        <f>IF(Liens!A158="","",IF(COUNTIF(Mots!B:B,Liens!A158)&gt;0,"✓ "&amp;Liens!A158,"✗ "&amp;Liens!A158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C163">
+        <f>IF(Liens!B158="","",IF(COUNTIF(Mots!B:B,Liens!B158)&gt;0,"✓ "&amp;Liens!B158,"✗ "&amp;Liens!B158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D163">
+        <f>IF(Liens!C158="","",IF(COUNTIF(Mots!B:B,Liens!C158)&gt;0,"✓ "&amp;Liens!C158,"✗ "&amp;Liens!C158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E163">
+        <f>IF(Liens!D158="","",IF(COUNTIF(Mots!B:B,Liens!D158)&gt;0,"✓ "&amp;Liens!D158,"✗ "&amp;Liens!D158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F163">
+        <f>IF(Liens!E158="","",IF(COUNTIF(Mots!B:B,Liens!E158)&gt;0,"✓ "&amp;Liens!E158,"✗ "&amp;Liens!E158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G163">
+        <f>IF(Liens!F158="","",IF(COUNTIF(Mots!B:B,Liens!F158)&gt;0,"✓ "&amp;Liens!F158,"✗ "&amp;Liens!F158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H163">
+        <f>IF(Liens!G158="","",IF(COUNTIF(Mots!B:B,Liens!G158)&gt;0,"✓ "&amp;Liens!G158,"✗ "&amp;Liens!G158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I163">
+        <f>IF(Liens!H158="","",IF(COUNTIF(Mots!B:B,Liens!H158)&gt;0,"✓ "&amp;Liens!H158,"✗ "&amp;Liens!H158&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>159</v>
+      </c>
+      <c r="B164">
+        <f>IF(Liens!A159="","",IF(COUNTIF(Mots!B:B,Liens!A159)&gt;0,"✓ "&amp;Liens!A159,"✗ "&amp;Liens!A159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C164">
+        <f>IF(Liens!B159="","",IF(COUNTIF(Mots!B:B,Liens!B159)&gt;0,"✓ "&amp;Liens!B159,"✗ "&amp;Liens!B159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D164">
+        <f>IF(Liens!C159="","",IF(COUNTIF(Mots!B:B,Liens!C159)&gt;0,"✓ "&amp;Liens!C159,"✗ "&amp;Liens!C159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E164">
+        <f>IF(Liens!D159="","",IF(COUNTIF(Mots!B:B,Liens!D159)&gt;0,"✓ "&amp;Liens!D159,"✗ "&amp;Liens!D159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F164">
+        <f>IF(Liens!E159="","",IF(COUNTIF(Mots!B:B,Liens!E159)&gt;0,"✓ "&amp;Liens!E159,"✗ "&amp;Liens!E159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G164">
+        <f>IF(Liens!F159="","",IF(COUNTIF(Mots!B:B,Liens!F159)&gt;0,"✓ "&amp;Liens!F159,"✗ "&amp;Liens!F159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H164">
+        <f>IF(Liens!G159="","",IF(COUNTIF(Mots!B:B,Liens!G159)&gt;0,"✓ "&amp;Liens!G159,"✗ "&amp;Liens!G159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I164">
+        <f>IF(Liens!H159="","",IF(COUNTIF(Mots!B:B,Liens!H159)&gt;0,"✓ "&amp;Liens!H159,"✗ "&amp;Liens!H159&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>160</v>
+      </c>
+      <c r="B165">
+        <f>IF(Liens!A160="","",IF(COUNTIF(Mots!B:B,Liens!A160)&gt;0,"✓ "&amp;Liens!A160,"✗ "&amp;Liens!A160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C165">
+        <f>IF(Liens!B160="","",IF(COUNTIF(Mots!B:B,Liens!B160)&gt;0,"✓ "&amp;Liens!B160,"✗ "&amp;Liens!B160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D165">
+        <f>IF(Liens!C160="","",IF(COUNTIF(Mots!B:B,Liens!C160)&gt;0,"✓ "&amp;Liens!C160,"✗ "&amp;Liens!C160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E165">
+        <f>IF(Liens!D160="","",IF(COUNTIF(Mots!B:B,Liens!D160)&gt;0,"✓ "&amp;Liens!D160,"✗ "&amp;Liens!D160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F165">
+        <f>IF(Liens!E160="","",IF(COUNTIF(Mots!B:B,Liens!E160)&gt;0,"✓ "&amp;Liens!E160,"✗ "&amp;Liens!E160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G165">
+        <f>IF(Liens!F160="","",IF(COUNTIF(Mots!B:B,Liens!F160)&gt;0,"✓ "&amp;Liens!F160,"✗ "&amp;Liens!F160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H165">
+        <f>IF(Liens!G160="","",IF(COUNTIF(Mots!B:B,Liens!G160)&gt;0,"✓ "&amp;Liens!G160,"✗ "&amp;Liens!G160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I165">
+        <f>IF(Liens!H160="","",IF(COUNTIF(Mots!B:B,Liens!H160)&gt;0,"✓ "&amp;Liens!H160,"✗ "&amp;Liens!H160&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>161</v>
+      </c>
+      <c r="B166">
+        <f>IF(Liens!A161="","",IF(COUNTIF(Mots!B:B,Liens!A161)&gt;0,"✓ "&amp;Liens!A161,"✗ "&amp;Liens!A161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C166">
+        <f>IF(Liens!B161="","",IF(COUNTIF(Mots!B:B,Liens!B161)&gt;0,"✓ "&amp;Liens!B161,"✗ "&amp;Liens!B161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D166">
+        <f>IF(Liens!C161="","",IF(COUNTIF(Mots!B:B,Liens!C161)&gt;0,"✓ "&amp;Liens!C161,"✗ "&amp;Liens!C161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E166">
+        <f>IF(Liens!D161="","",IF(COUNTIF(Mots!B:B,Liens!D161)&gt;0,"✓ "&amp;Liens!D161,"✗ "&amp;Liens!D161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F166">
+        <f>IF(Liens!E161="","",IF(COUNTIF(Mots!B:B,Liens!E161)&gt;0,"✓ "&amp;Liens!E161,"✗ "&amp;Liens!E161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G166">
+        <f>IF(Liens!F161="","",IF(COUNTIF(Mots!B:B,Liens!F161)&gt;0,"✓ "&amp;Liens!F161,"✗ "&amp;Liens!F161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H166">
+        <f>IF(Liens!G161="","",IF(COUNTIF(Mots!B:B,Liens!G161)&gt;0,"✓ "&amp;Liens!G161,"✗ "&amp;Liens!G161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I166">
+        <f>IF(Liens!H161="","",IF(COUNTIF(Mots!B:B,Liens!H161)&gt;0,"✓ "&amp;Liens!H161,"✗ "&amp;Liens!H161&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>162</v>
+      </c>
+      <c r="B167">
+        <f>IF(Liens!A162="","",IF(COUNTIF(Mots!B:B,Liens!A162)&gt;0,"✓ "&amp;Liens!A162,"✗ "&amp;Liens!A162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C167">
+        <f>IF(Liens!B162="","",IF(COUNTIF(Mots!B:B,Liens!B162)&gt;0,"✓ "&amp;Liens!B162,"✗ "&amp;Liens!B162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D167">
+        <f>IF(Liens!C162="","",IF(COUNTIF(Mots!B:B,Liens!C162)&gt;0,"✓ "&amp;Liens!C162,"✗ "&amp;Liens!C162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E167">
+        <f>IF(Liens!D162="","",IF(COUNTIF(Mots!B:B,Liens!D162)&gt;0,"✓ "&amp;Liens!D162,"✗ "&amp;Liens!D162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F167">
+        <f>IF(Liens!E162="","",IF(COUNTIF(Mots!B:B,Liens!E162)&gt;0,"✓ "&amp;Liens!E162,"✗ "&amp;Liens!E162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G167">
+        <f>IF(Liens!F162="","",IF(COUNTIF(Mots!B:B,Liens!F162)&gt;0,"✓ "&amp;Liens!F162,"✗ "&amp;Liens!F162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H167">
+        <f>IF(Liens!G162="","",IF(COUNTIF(Mots!B:B,Liens!G162)&gt;0,"✓ "&amp;Liens!G162,"✗ "&amp;Liens!G162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I167">
+        <f>IF(Liens!H162="","",IF(COUNTIF(Mots!B:B,Liens!H162)&gt;0,"✓ "&amp;Liens!H162,"✗ "&amp;Liens!H162&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168">
+        <f>IF(Liens!A163="","",IF(COUNTIF(Mots!B:B,Liens!A163)&gt;0,"✓ "&amp;Liens!A163,"✗ "&amp;Liens!A163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C168">
+        <f>IF(Liens!B163="","",IF(COUNTIF(Mots!B:B,Liens!B163)&gt;0,"✓ "&amp;Liens!B163,"✗ "&amp;Liens!B163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D168">
+        <f>IF(Liens!C163="","",IF(COUNTIF(Mots!B:B,Liens!C163)&gt;0,"✓ "&amp;Liens!C163,"✗ "&amp;Liens!C163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E168">
+        <f>IF(Liens!D163="","",IF(COUNTIF(Mots!B:B,Liens!D163)&gt;0,"✓ "&amp;Liens!D163,"✗ "&amp;Liens!D163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F168">
+        <f>IF(Liens!E163="","",IF(COUNTIF(Mots!B:B,Liens!E163)&gt;0,"✓ "&amp;Liens!E163,"✗ "&amp;Liens!E163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G168">
+        <f>IF(Liens!F163="","",IF(COUNTIF(Mots!B:B,Liens!F163)&gt;0,"✓ "&amp;Liens!F163,"✗ "&amp;Liens!F163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H168">
+        <f>IF(Liens!G163="","",IF(COUNTIF(Mots!B:B,Liens!G163)&gt;0,"✓ "&amp;Liens!G163,"✗ "&amp;Liens!G163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I168">
+        <f>IF(Liens!H163="","",IF(COUNTIF(Mots!B:B,Liens!H163)&gt;0,"✓ "&amp;Liens!H163,"✗ "&amp;Liens!H163&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169">
+        <f>IF(Liens!A164="","",IF(COUNTIF(Mots!B:B,Liens!A164)&gt;0,"✓ "&amp;Liens!A164,"✗ "&amp;Liens!A164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C169">
+        <f>IF(Liens!B164="","",IF(COUNTIF(Mots!B:B,Liens!B164)&gt;0,"✓ "&amp;Liens!B164,"✗ "&amp;Liens!B164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D169">
+        <f>IF(Liens!C164="","",IF(COUNTIF(Mots!B:B,Liens!C164)&gt;0,"✓ "&amp;Liens!C164,"✗ "&amp;Liens!C164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E169">
+        <f>IF(Liens!D164="","",IF(COUNTIF(Mots!B:B,Liens!D164)&gt;0,"✓ "&amp;Liens!D164,"✗ "&amp;Liens!D164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F169">
+        <f>IF(Liens!E164="","",IF(COUNTIF(Mots!B:B,Liens!E164)&gt;0,"✓ "&amp;Liens!E164,"✗ "&amp;Liens!E164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G169">
+        <f>IF(Liens!F164="","",IF(COUNTIF(Mots!B:B,Liens!F164)&gt;0,"✓ "&amp;Liens!F164,"✗ "&amp;Liens!F164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H169">
+        <f>IF(Liens!G164="","",IF(COUNTIF(Mots!B:B,Liens!G164)&gt;0,"✓ "&amp;Liens!G164,"✗ "&amp;Liens!G164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I169">
+        <f>IF(Liens!H164="","",IF(COUNTIF(Mots!B:B,Liens!H164)&gt;0,"✓ "&amp;Liens!H164,"✗ "&amp;Liens!H164&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>165</v>
+      </c>
+      <c r="B170">
+        <f>IF(Liens!A165="","",IF(COUNTIF(Mots!B:B,Liens!A165)&gt;0,"✓ "&amp;Liens!A165,"✗ "&amp;Liens!A165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C170">
+        <f>IF(Liens!B165="","",IF(COUNTIF(Mots!B:B,Liens!B165)&gt;0,"✓ "&amp;Liens!B165,"✗ "&amp;Liens!B165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D170">
+        <f>IF(Liens!C165="","",IF(COUNTIF(Mots!B:B,Liens!C165)&gt;0,"✓ "&amp;Liens!C165,"✗ "&amp;Liens!C165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E170">
+        <f>IF(Liens!D165="","",IF(COUNTIF(Mots!B:B,Liens!D165)&gt;0,"✓ "&amp;Liens!D165,"✗ "&amp;Liens!D165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F170">
+        <f>IF(Liens!E165="","",IF(COUNTIF(Mots!B:B,Liens!E165)&gt;0,"✓ "&amp;Liens!E165,"✗ "&amp;Liens!E165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G170">
+        <f>IF(Liens!F165="","",IF(COUNTIF(Mots!B:B,Liens!F165)&gt;0,"✓ "&amp;Liens!F165,"✗ "&amp;Liens!F165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H170">
+        <f>IF(Liens!G165="","",IF(COUNTIF(Mots!B:B,Liens!G165)&gt;0,"✓ "&amp;Liens!G165,"✗ "&amp;Liens!G165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I170">
+        <f>IF(Liens!H165="","",IF(COUNTIF(Mots!B:B,Liens!H165)&gt;0,"✓ "&amp;Liens!H165,"✗ "&amp;Liens!H165&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>166</v>
+      </c>
+      <c r="B171">
+        <f>IF(Liens!A166="","",IF(COUNTIF(Mots!B:B,Liens!A166)&gt;0,"✓ "&amp;Liens!A166,"✗ "&amp;Liens!A166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C171">
+        <f>IF(Liens!B166="","",IF(COUNTIF(Mots!B:B,Liens!B166)&gt;0,"✓ "&amp;Liens!B166,"✗ "&amp;Liens!B166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D171">
+        <f>IF(Liens!C166="","",IF(COUNTIF(Mots!B:B,Liens!C166)&gt;0,"✓ "&amp;Liens!C166,"✗ "&amp;Liens!C166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E171">
+        <f>IF(Liens!D166="","",IF(COUNTIF(Mots!B:B,Liens!D166)&gt;0,"✓ "&amp;Liens!D166,"✗ "&amp;Liens!D166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F171">
+        <f>IF(Liens!E166="","",IF(COUNTIF(Mots!B:B,Liens!E166)&gt;0,"✓ "&amp;Liens!E166,"✗ "&amp;Liens!E166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G171">
+        <f>IF(Liens!F166="","",IF(COUNTIF(Mots!B:B,Liens!F166)&gt;0,"✓ "&amp;Liens!F166,"✗ "&amp;Liens!F166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H171">
+        <f>IF(Liens!G166="","",IF(COUNTIF(Mots!B:B,Liens!G166)&gt;0,"✓ "&amp;Liens!G166,"✗ "&amp;Liens!G166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I171">
+        <f>IF(Liens!H166="","",IF(COUNTIF(Mots!B:B,Liens!H166)&gt;0,"✓ "&amp;Liens!H166,"✗ "&amp;Liens!H166&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>167</v>
+      </c>
+      <c r="B172">
+        <f>IF(Liens!A167="","",IF(COUNTIF(Mots!B:B,Liens!A167)&gt;0,"✓ "&amp;Liens!A167,"✗ "&amp;Liens!A167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C172">
+        <f>IF(Liens!B167="","",IF(COUNTIF(Mots!B:B,Liens!B167)&gt;0,"✓ "&amp;Liens!B167,"✗ "&amp;Liens!B167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D172">
+        <f>IF(Liens!C167="","",IF(COUNTIF(Mots!B:B,Liens!C167)&gt;0,"✓ "&amp;Liens!C167,"✗ "&amp;Liens!C167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E172">
+        <f>IF(Liens!D167="","",IF(COUNTIF(Mots!B:B,Liens!D167)&gt;0,"✓ "&amp;Liens!D167,"✗ "&amp;Liens!D167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F172">
+        <f>IF(Liens!E167="","",IF(COUNTIF(Mots!B:B,Liens!E167)&gt;0,"✓ "&amp;Liens!E167,"✗ "&amp;Liens!E167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G172">
+        <f>IF(Liens!F167="","",IF(COUNTIF(Mots!B:B,Liens!F167)&gt;0,"✓ "&amp;Liens!F167,"✗ "&amp;Liens!F167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H172">
+        <f>IF(Liens!G167="","",IF(COUNTIF(Mots!B:B,Liens!G167)&gt;0,"✓ "&amp;Liens!G167,"✗ "&amp;Liens!G167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I172">
+        <f>IF(Liens!H167="","",IF(COUNTIF(Mots!B:B,Liens!H167)&gt;0,"✓ "&amp;Liens!H167,"✗ "&amp;Liens!H167&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>168</v>
+      </c>
+      <c r="B173">
+        <f>IF(Liens!A168="","",IF(COUNTIF(Mots!B:B,Liens!A168)&gt;0,"✓ "&amp;Liens!A168,"✗ "&amp;Liens!A168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C173">
+        <f>IF(Liens!B168="","",IF(COUNTIF(Mots!B:B,Liens!B168)&gt;0,"✓ "&amp;Liens!B168,"✗ "&amp;Liens!B168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D173">
+        <f>IF(Liens!C168="","",IF(COUNTIF(Mots!B:B,Liens!C168)&gt;0,"✓ "&amp;Liens!C168,"✗ "&amp;Liens!C168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E173">
+        <f>IF(Liens!D168="","",IF(COUNTIF(Mots!B:B,Liens!D168)&gt;0,"✓ "&amp;Liens!D168,"✗ "&amp;Liens!D168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F173">
+        <f>IF(Liens!E168="","",IF(COUNTIF(Mots!B:B,Liens!E168)&gt;0,"✓ "&amp;Liens!E168,"✗ "&amp;Liens!E168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G173">
+        <f>IF(Liens!F168="","",IF(COUNTIF(Mots!B:B,Liens!F168)&gt;0,"✓ "&amp;Liens!F168,"✗ "&amp;Liens!F168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H173">
+        <f>IF(Liens!G168="","",IF(COUNTIF(Mots!B:B,Liens!G168)&gt;0,"✓ "&amp;Liens!G168,"✗ "&amp;Liens!G168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I173">
+        <f>IF(Liens!H168="","",IF(COUNTIF(Mots!B:B,Liens!H168)&gt;0,"✓ "&amp;Liens!H168,"✗ "&amp;Liens!H168&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>169</v>
+      </c>
+      <c r="B174">
+        <f>IF(Liens!A169="","",IF(COUNTIF(Mots!B:B,Liens!A169)&gt;0,"✓ "&amp;Liens!A169,"✗ "&amp;Liens!A169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C174">
+        <f>IF(Liens!B169="","",IF(COUNTIF(Mots!B:B,Liens!B169)&gt;0,"✓ "&amp;Liens!B169,"✗ "&amp;Liens!B169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D174">
+        <f>IF(Liens!C169="","",IF(COUNTIF(Mots!B:B,Liens!C169)&gt;0,"✓ "&amp;Liens!C169,"✗ "&amp;Liens!C169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E174">
+        <f>IF(Liens!D169="","",IF(COUNTIF(Mots!B:B,Liens!D169)&gt;0,"✓ "&amp;Liens!D169,"✗ "&amp;Liens!D169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F174">
+        <f>IF(Liens!E169="","",IF(COUNTIF(Mots!B:B,Liens!E169)&gt;0,"✓ "&amp;Liens!E169,"✗ "&amp;Liens!E169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G174">
+        <f>IF(Liens!F169="","",IF(COUNTIF(Mots!B:B,Liens!F169)&gt;0,"✓ "&amp;Liens!F169,"✗ "&amp;Liens!F169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H174">
+        <f>IF(Liens!G169="","",IF(COUNTIF(Mots!B:B,Liens!G169)&gt;0,"✓ "&amp;Liens!G169,"✗ "&amp;Liens!G169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I174">
+        <f>IF(Liens!H169="","",IF(COUNTIF(Mots!B:B,Liens!H169)&gt;0,"✓ "&amp;Liens!H169,"✗ "&amp;Liens!H169&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>170</v>
+      </c>
+      <c r="B175">
+        <f>IF(Liens!A170="","",IF(COUNTIF(Mots!B:B,Liens!A170)&gt;0,"✓ "&amp;Liens!A170,"✗ "&amp;Liens!A170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C175">
+        <f>IF(Liens!B170="","",IF(COUNTIF(Mots!B:B,Liens!B170)&gt;0,"✓ "&amp;Liens!B170,"✗ "&amp;Liens!B170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D175">
+        <f>IF(Liens!C170="","",IF(COUNTIF(Mots!B:B,Liens!C170)&gt;0,"✓ "&amp;Liens!C170,"✗ "&amp;Liens!C170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E175">
+        <f>IF(Liens!D170="","",IF(COUNTIF(Mots!B:B,Liens!D170)&gt;0,"✓ "&amp;Liens!D170,"✗ "&amp;Liens!D170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F175">
+        <f>IF(Liens!E170="","",IF(COUNTIF(Mots!B:B,Liens!E170)&gt;0,"✓ "&amp;Liens!E170,"✗ "&amp;Liens!E170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G175">
+        <f>IF(Liens!F170="","",IF(COUNTIF(Mots!B:B,Liens!F170)&gt;0,"✓ "&amp;Liens!F170,"✗ "&amp;Liens!F170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H175">
+        <f>IF(Liens!G170="","",IF(COUNTIF(Mots!B:B,Liens!G170)&gt;0,"✓ "&amp;Liens!G170,"✗ "&amp;Liens!G170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I175">
+        <f>IF(Liens!H170="","",IF(COUNTIF(Mots!B:B,Liens!H170)&gt;0,"✓ "&amp;Liens!H170,"✗ "&amp;Liens!H170&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176">
+        <f>IF(Liens!A171="","",IF(COUNTIF(Mots!B:B,Liens!A171)&gt;0,"✓ "&amp;Liens!A171,"✗ "&amp;Liens!A171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C176">
+        <f>IF(Liens!B171="","",IF(COUNTIF(Mots!B:B,Liens!B171)&gt;0,"✓ "&amp;Liens!B171,"✗ "&amp;Liens!B171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D176">
+        <f>IF(Liens!C171="","",IF(COUNTIF(Mots!B:B,Liens!C171)&gt;0,"✓ "&amp;Liens!C171,"✗ "&amp;Liens!C171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E176">
+        <f>IF(Liens!D171="","",IF(COUNTIF(Mots!B:B,Liens!D171)&gt;0,"✓ "&amp;Liens!D171,"✗ "&amp;Liens!D171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F176">
+        <f>IF(Liens!E171="","",IF(COUNTIF(Mots!B:B,Liens!E171)&gt;0,"✓ "&amp;Liens!E171,"✗ "&amp;Liens!E171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G176">
+        <f>IF(Liens!F171="","",IF(COUNTIF(Mots!B:B,Liens!F171)&gt;0,"✓ "&amp;Liens!F171,"✗ "&amp;Liens!F171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H176">
+        <f>IF(Liens!G171="","",IF(COUNTIF(Mots!B:B,Liens!G171)&gt;0,"✓ "&amp;Liens!G171,"✗ "&amp;Liens!G171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I176">
+        <f>IF(Liens!H171="","",IF(COUNTIF(Mots!B:B,Liens!H171)&gt;0,"✓ "&amp;Liens!H171,"✗ "&amp;Liens!H171&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>172</v>
+      </c>
+      <c r="B177">
+        <f>IF(Liens!A172="","",IF(COUNTIF(Mots!B:B,Liens!A172)&gt;0,"✓ "&amp;Liens!A172,"✗ "&amp;Liens!A172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C177">
+        <f>IF(Liens!B172="","",IF(COUNTIF(Mots!B:B,Liens!B172)&gt;0,"✓ "&amp;Liens!B172,"✗ "&amp;Liens!B172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D177">
+        <f>IF(Liens!C172="","",IF(COUNTIF(Mots!B:B,Liens!C172)&gt;0,"✓ "&amp;Liens!C172,"✗ "&amp;Liens!C172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E177">
+        <f>IF(Liens!D172="","",IF(COUNTIF(Mots!B:B,Liens!D172)&gt;0,"✓ "&amp;Liens!D172,"✗ "&amp;Liens!D172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F177">
+        <f>IF(Liens!E172="","",IF(COUNTIF(Mots!B:B,Liens!E172)&gt;0,"✓ "&amp;Liens!E172,"✗ "&amp;Liens!E172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G177">
+        <f>IF(Liens!F172="","",IF(COUNTIF(Mots!B:B,Liens!F172)&gt;0,"✓ "&amp;Liens!F172,"✗ "&amp;Liens!F172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H177">
+        <f>IF(Liens!G172="","",IF(COUNTIF(Mots!B:B,Liens!G172)&gt;0,"✓ "&amp;Liens!G172,"✗ "&amp;Liens!G172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I177">
+        <f>IF(Liens!H172="","",IF(COUNTIF(Mots!B:B,Liens!H172)&gt;0,"✓ "&amp;Liens!H172,"✗ "&amp;Liens!H172&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>173</v>
+      </c>
+      <c r="B178">
+        <f>IF(Liens!A173="","",IF(COUNTIF(Mots!B:B,Liens!A173)&gt;0,"✓ "&amp;Liens!A173,"✗ "&amp;Liens!A173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C178">
+        <f>IF(Liens!B173="","",IF(COUNTIF(Mots!B:B,Liens!B173)&gt;0,"✓ "&amp;Liens!B173,"✗ "&amp;Liens!B173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D178">
+        <f>IF(Liens!C173="","",IF(COUNTIF(Mots!B:B,Liens!C173)&gt;0,"✓ "&amp;Liens!C173,"✗ "&amp;Liens!C173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E178">
+        <f>IF(Liens!D173="","",IF(COUNTIF(Mots!B:B,Liens!D173)&gt;0,"✓ "&amp;Liens!D173,"✗ "&amp;Liens!D173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F178">
+        <f>IF(Liens!E173="","",IF(COUNTIF(Mots!B:B,Liens!E173)&gt;0,"✓ "&amp;Liens!E173,"✗ "&amp;Liens!E173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G178">
+        <f>IF(Liens!F173="","",IF(COUNTIF(Mots!B:B,Liens!F173)&gt;0,"✓ "&amp;Liens!F173,"✗ "&amp;Liens!F173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H178">
+        <f>IF(Liens!G173="","",IF(COUNTIF(Mots!B:B,Liens!G173)&gt;0,"✓ "&amp;Liens!G173,"✗ "&amp;Liens!G173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I178">
+        <f>IF(Liens!H173="","",IF(COUNTIF(Mots!B:B,Liens!H173)&gt;0,"✓ "&amp;Liens!H173,"✗ "&amp;Liens!H173&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>174</v>
+      </c>
+      <c r="B179">
+        <f>IF(Liens!A174="","",IF(COUNTIF(Mots!B:B,Liens!A174)&gt;0,"✓ "&amp;Liens!A174,"✗ "&amp;Liens!A174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C179">
+        <f>IF(Liens!B174="","",IF(COUNTIF(Mots!B:B,Liens!B174)&gt;0,"✓ "&amp;Liens!B174,"✗ "&amp;Liens!B174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D179">
+        <f>IF(Liens!C174="","",IF(COUNTIF(Mots!B:B,Liens!C174)&gt;0,"✓ "&amp;Liens!C174,"✗ "&amp;Liens!C174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E179">
+        <f>IF(Liens!D174="","",IF(COUNTIF(Mots!B:B,Liens!D174)&gt;0,"✓ "&amp;Liens!D174,"✗ "&amp;Liens!D174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F179">
+        <f>IF(Liens!E174="","",IF(COUNTIF(Mots!B:B,Liens!E174)&gt;0,"✓ "&amp;Liens!E174,"✗ "&amp;Liens!E174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G179">
+        <f>IF(Liens!F174="","",IF(COUNTIF(Mots!B:B,Liens!F174)&gt;0,"✓ "&amp;Liens!F174,"✗ "&amp;Liens!F174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H179">
+        <f>IF(Liens!G174="","",IF(COUNTIF(Mots!B:B,Liens!G174)&gt;0,"✓ "&amp;Liens!G174,"✗ "&amp;Liens!G174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I179">
+        <f>IF(Liens!H174="","",IF(COUNTIF(Mots!B:B,Liens!H174)&gt;0,"✓ "&amp;Liens!H174,"✗ "&amp;Liens!H174&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>175</v>
+      </c>
+      <c r="B180">
+        <f>IF(Liens!A175="","",IF(COUNTIF(Mots!B:B,Liens!A175)&gt;0,"✓ "&amp;Liens!A175,"✗ "&amp;Liens!A175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C180">
+        <f>IF(Liens!B175="","",IF(COUNTIF(Mots!B:B,Liens!B175)&gt;0,"✓ "&amp;Liens!B175,"✗ "&amp;Liens!B175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D180">
+        <f>IF(Liens!C175="","",IF(COUNTIF(Mots!B:B,Liens!C175)&gt;0,"✓ "&amp;Liens!C175,"✗ "&amp;Liens!C175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E180">
+        <f>IF(Liens!D175="","",IF(COUNTIF(Mots!B:B,Liens!D175)&gt;0,"✓ "&amp;Liens!D175,"✗ "&amp;Liens!D175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F180">
+        <f>IF(Liens!E175="","",IF(COUNTIF(Mots!B:B,Liens!E175)&gt;0,"✓ "&amp;Liens!E175,"✗ "&amp;Liens!E175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G180">
+        <f>IF(Liens!F175="","",IF(COUNTIF(Mots!B:B,Liens!F175)&gt;0,"✓ "&amp;Liens!F175,"✗ "&amp;Liens!F175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H180">
+        <f>IF(Liens!G175="","",IF(COUNTIF(Mots!B:B,Liens!G175)&gt;0,"✓ "&amp;Liens!G175,"✗ "&amp;Liens!G175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I180">
+        <f>IF(Liens!H175="","",IF(COUNTIF(Mots!B:B,Liens!H175)&gt;0,"✓ "&amp;Liens!H175,"✗ "&amp;Liens!H175&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>176</v>
+      </c>
+      <c r="B181">
+        <f>IF(Liens!A176="","",IF(COUNTIF(Mots!B:B,Liens!A176)&gt;0,"✓ "&amp;Liens!A176,"✗ "&amp;Liens!A176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C181">
+        <f>IF(Liens!B176="","",IF(COUNTIF(Mots!B:B,Liens!B176)&gt;0,"✓ "&amp;Liens!B176,"✗ "&amp;Liens!B176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D181">
+        <f>IF(Liens!C176="","",IF(COUNTIF(Mots!B:B,Liens!C176)&gt;0,"✓ "&amp;Liens!C176,"✗ "&amp;Liens!C176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E181">
+        <f>IF(Liens!D176="","",IF(COUNTIF(Mots!B:B,Liens!D176)&gt;0,"✓ "&amp;Liens!D176,"✗ "&amp;Liens!D176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F181">
+        <f>IF(Liens!E176="","",IF(COUNTIF(Mots!B:B,Liens!E176)&gt;0,"✓ "&amp;Liens!E176,"✗ "&amp;Liens!E176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G181">
+        <f>IF(Liens!F176="","",IF(COUNTIF(Mots!B:B,Liens!F176)&gt;0,"✓ "&amp;Liens!F176,"✗ "&amp;Liens!F176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H181">
+        <f>IF(Liens!G176="","",IF(COUNTIF(Mots!B:B,Liens!G176)&gt;0,"✓ "&amp;Liens!G176,"✗ "&amp;Liens!G176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I181">
+        <f>IF(Liens!H176="","",IF(COUNTIF(Mots!B:B,Liens!H176)&gt;0,"✓ "&amp;Liens!H176,"✗ "&amp;Liens!H176&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>177</v>
+      </c>
+      <c r="B182">
+        <f>IF(Liens!A177="","",IF(COUNTIF(Mots!B:B,Liens!A177)&gt;0,"✓ "&amp;Liens!A177,"✗ "&amp;Liens!A177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C182">
+        <f>IF(Liens!B177="","",IF(COUNTIF(Mots!B:B,Liens!B177)&gt;0,"✓ "&amp;Liens!B177,"✗ "&amp;Liens!B177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D182">
+        <f>IF(Liens!C177="","",IF(COUNTIF(Mots!B:B,Liens!C177)&gt;0,"✓ "&amp;Liens!C177,"✗ "&amp;Liens!C177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E182">
+        <f>IF(Liens!D177="","",IF(COUNTIF(Mots!B:B,Liens!D177)&gt;0,"✓ "&amp;Liens!D177,"✗ "&amp;Liens!D177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F182">
+        <f>IF(Liens!E177="","",IF(COUNTIF(Mots!B:B,Liens!E177)&gt;0,"✓ "&amp;Liens!E177,"✗ "&amp;Liens!E177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G182">
+        <f>IF(Liens!F177="","",IF(COUNTIF(Mots!B:B,Liens!F177)&gt;0,"✓ "&amp;Liens!F177,"✗ "&amp;Liens!F177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H182">
+        <f>IF(Liens!G177="","",IF(COUNTIF(Mots!B:B,Liens!G177)&gt;0,"✓ "&amp;Liens!G177,"✗ "&amp;Liens!G177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I182">
+        <f>IF(Liens!H177="","",IF(COUNTIF(Mots!B:B,Liens!H177)&gt;0,"✓ "&amp;Liens!H177,"✗ "&amp;Liens!H177&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>178</v>
+      </c>
+      <c r="B183">
+        <f>IF(Liens!A178="","",IF(COUNTIF(Mots!B:B,Liens!A178)&gt;0,"✓ "&amp;Liens!A178,"✗ "&amp;Liens!A178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C183">
+        <f>IF(Liens!B178="","",IF(COUNTIF(Mots!B:B,Liens!B178)&gt;0,"✓ "&amp;Liens!B178,"✗ "&amp;Liens!B178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D183">
+        <f>IF(Liens!C178="","",IF(COUNTIF(Mots!B:B,Liens!C178)&gt;0,"✓ "&amp;Liens!C178,"✗ "&amp;Liens!C178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E183">
+        <f>IF(Liens!D178="","",IF(COUNTIF(Mots!B:B,Liens!D178)&gt;0,"✓ "&amp;Liens!D178,"✗ "&amp;Liens!D178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F183">
+        <f>IF(Liens!E178="","",IF(COUNTIF(Mots!B:B,Liens!E178)&gt;0,"✓ "&amp;Liens!E178,"✗ "&amp;Liens!E178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G183">
+        <f>IF(Liens!F178="","",IF(COUNTIF(Mots!B:B,Liens!F178)&gt;0,"✓ "&amp;Liens!F178,"✗ "&amp;Liens!F178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H183">
+        <f>IF(Liens!G178="","",IF(COUNTIF(Mots!B:B,Liens!G178)&gt;0,"✓ "&amp;Liens!G178,"✗ "&amp;Liens!G178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I183">
+        <f>IF(Liens!H178="","",IF(COUNTIF(Mots!B:B,Liens!H178)&gt;0,"✓ "&amp;Liens!H178,"✗ "&amp;Liens!H178&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>179</v>
+      </c>
+      <c r="B184">
+        <f>IF(Liens!A179="","",IF(COUNTIF(Mots!B:B,Liens!A179)&gt;0,"✓ "&amp;Liens!A179,"✗ "&amp;Liens!A179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C184">
+        <f>IF(Liens!B179="","",IF(COUNTIF(Mots!B:B,Liens!B179)&gt;0,"✓ "&amp;Liens!B179,"✗ "&amp;Liens!B179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D184">
+        <f>IF(Liens!C179="","",IF(COUNTIF(Mots!B:B,Liens!C179)&gt;0,"✓ "&amp;Liens!C179,"✗ "&amp;Liens!C179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E184">
+        <f>IF(Liens!D179="","",IF(COUNTIF(Mots!B:B,Liens!D179)&gt;0,"✓ "&amp;Liens!D179,"✗ "&amp;Liens!D179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F184">
+        <f>IF(Liens!E179="","",IF(COUNTIF(Mots!B:B,Liens!E179)&gt;0,"✓ "&amp;Liens!E179,"✗ "&amp;Liens!E179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G184">
+        <f>IF(Liens!F179="","",IF(COUNTIF(Mots!B:B,Liens!F179)&gt;0,"✓ "&amp;Liens!F179,"✗ "&amp;Liens!F179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H184">
+        <f>IF(Liens!G179="","",IF(COUNTIF(Mots!B:B,Liens!G179)&gt;0,"✓ "&amp;Liens!G179,"✗ "&amp;Liens!G179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I184">
+        <f>IF(Liens!H179="","",IF(COUNTIF(Mots!B:B,Liens!H179)&gt;0,"✓ "&amp;Liens!H179,"✗ "&amp;Liens!H179&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>180</v>
+      </c>
+      <c r="B185">
+        <f>IF(Liens!A180="","",IF(COUNTIF(Mots!B:B,Liens!A180)&gt;0,"✓ "&amp;Liens!A180,"✗ "&amp;Liens!A180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C185">
+        <f>IF(Liens!B180="","",IF(COUNTIF(Mots!B:B,Liens!B180)&gt;0,"✓ "&amp;Liens!B180,"✗ "&amp;Liens!B180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D185">
+        <f>IF(Liens!C180="","",IF(COUNTIF(Mots!B:B,Liens!C180)&gt;0,"✓ "&amp;Liens!C180,"✗ "&amp;Liens!C180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E185">
+        <f>IF(Liens!D180="","",IF(COUNTIF(Mots!B:B,Liens!D180)&gt;0,"✓ "&amp;Liens!D180,"✗ "&amp;Liens!D180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F185">
+        <f>IF(Liens!E180="","",IF(COUNTIF(Mots!B:B,Liens!E180)&gt;0,"✓ "&amp;Liens!E180,"✗ "&amp;Liens!E180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G185">
+        <f>IF(Liens!F180="","",IF(COUNTIF(Mots!B:B,Liens!F180)&gt;0,"✓ "&amp;Liens!F180,"✗ "&amp;Liens!F180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H185">
+        <f>IF(Liens!G180="","",IF(COUNTIF(Mots!B:B,Liens!G180)&gt;0,"✓ "&amp;Liens!G180,"✗ "&amp;Liens!G180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I185">
+        <f>IF(Liens!H180="","",IF(COUNTIF(Mots!B:B,Liens!H180)&gt;0,"✓ "&amp;Liens!H180,"✗ "&amp;Liens!H180&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>181</v>
+      </c>
+      <c r="B186">
+        <f>IF(Liens!A181="","",IF(COUNTIF(Mots!B:B,Liens!A181)&gt;0,"✓ "&amp;Liens!A181,"✗ "&amp;Liens!A181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C186">
+        <f>IF(Liens!B181="","",IF(COUNTIF(Mots!B:B,Liens!B181)&gt;0,"✓ "&amp;Liens!B181,"✗ "&amp;Liens!B181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D186">
+        <f>IF(Liens!C181="","",IF(COUNTIF(Mots!B:B,Liens!C181)&gt;0,"✓ "&amp;Liens!C181,"✗ "&amp;Liens!C181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E186">
+        <f>IF(Liens!D181="","",IF(COUNTIF(Mots!B:B,Liens!D181)&gt;0,"✓ "&amp;Liens!D181,"✗ "&amp;Liens!D181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F186">
+        <f>IF(Liens!E181="","",IF(COUNTIF(Mots!B:B,Liens!E181)&gt;0,"✓ "&amp;Liens!E181,"✗ "&amp;Liens!E181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G186">
+        <f>IF(Liens!F181="","",IF(COUNTIF(Mots!B:B,Liens!F181)&gt;0,"✓ "&amp;Liens!F181,"✗ "&amp;Liens!F181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H186">
+        <f>IF(Liens!G181="","",IF(COUNTIF(Mots!B:B,Liens!G181)&gt;0,"✓ "&amp;Liens!G181,"✗ "&amp;Liens!G181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I186">
+        <f>IF(Liens!H181="","",IF(COUNTIF(Mots!B:B,Liens!H181)&gt;0,"✓ "&amp;Liens!H181,"✗ "&amp;Liens!H181&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>182</v>
+      </c>
+      <c r="B187">
+        <f>IF(Liens!A182="","",IF(COUNTIF(Mots!B:B,Liens!A182)&gt;0,"✓ "&amp;Liens!A182,"✗ "&amp;Liens!A182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C187">
+        <f>IF(Liens!B182="","",IF(COUNTIF(Mots!B:B,Liens!B182)&gt;0,"✓ "&amp;Liens!B182,"✗ "&amp;Liens!B182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D187">
+        <f>IF(Liens!C182="","",IF(COUNTIF(Mots!B:B,Liens!C182)&gt;0,"✓ "&amp;Liens!C182,"✗ "&amp;Liens!C182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E187">
+        <f>IF(Liens!D182="","",IF(COUNTIF(Mots!B:B,Liens!D182)&gt;0,"✓ "&amp;Liens!D182,"✗ "&amp;Liens!D182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F187">
+        <f>IF(Liens!E182="","",IF(COUNTIF(Mots!B:B,Liens!E182)&gt;0,"✓ "&amp;Liens!E182,"✗ "&amp;Liens!E182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G187">
+        <f>IF(Liens!F182="","",IF(COUNTIF(Mots!B:B,Liens!F182)&gt;0,"✓ "&amp;Liens!F182,"✗ "&amp;Liens!F182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H187">
+        <f>IF(Liens!G182="","",IF(COUNTIF(Mots!B:B,Liens!G182)&gt;0,"✓ "&amp;Liens!G182,"✗ "&amp;Liens!G182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I187">
+        <f>IF(Liens!H182="","",IF(COUNTIF(Mots!B:B,Liens!H182)&gt;0,"✓ "&amp;Liens!H182,"✗ "&amp;Liens!H182&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>183</v>
+      </c>
+      <c r="B188">
+        <f>IF(Liens!A183="","",IF(COUNTIF(Mots!B:B,Liens!A183)&gt;0,"✓ "&amp;Liens!A183,"✗ "&amp;Liens!A183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C188">
+        <f>IF(Liens!B183="","",IF(COUNTIF(Mots!B:B,Liens!B183)&gt;0,"✓ "&amp;Liens!B183,"✗ "&amp;Liens!B183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D188">
+        <f>IF(Liens!C183="","",IF(COUNTIF(Mots!B:B,Liens!C183)&gt;0,"✓ "&amp;Liens!C183,"✗ "&amp;Liens!C183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E188">
+        <f>IF(Liens!D183="","",IF(COUNTIF(Mots!B:B,Liens!D183)&gt;0,"✓ "&amp;Liens!D183,"✗ "&amp;Liens!D183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F188">
+        <f>IF(Liens!E183="","",IF(COUNTIF(Mots!B:B,Liens!E183)&gt;0,"✓ "&amp;Liens!E183,"✗ "&amp;Liens!E183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G188">
+        <f>IF(Liens!F183="","",IF(COUNTIF(Mots!B:B,Liens!F183)&gt;0,"✓ "&amp;Liens!F183,"✗ "&amp;Liens!F183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H188">
+        <f>IF(Liens!G183="","",IF(COUNTIF(Mots!B:B,Liens!G183)&gt;0,"✓ "&amp;Liens!G183,"✗ "&amp;Liens!G183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I188">
+        <f>IF(Liens!H183="","",IF(COUNTIF(Mots!B:B,Liens!H183)&gt;0,"✓ "&amp;Liens!H183,"✗ "&amp;Liens!H183&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>184</v>
+      </c>
+      <c r="B189">
+        <f>IF(Liens!A184="","",IF(COUNTIF(Mots!B:B,Liens!A184)&gt;0,"✓ "&amp;Liens!A184,"✗ "&amp;Liens!A184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C189">
+        <f>IF(Liens!B184="","",IF(COUNTIF(Mots!B:B,Liens!B184)&gt;0,"✓ "&amp;Liens!B184,"✗ "&amp;Liens!B184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D189">
+        <f>IF(Liens!C184="","",IF(COUNTIF(Mots!B:B,Liens!C184)&gt;0,"✓ "&amp;Liens!C184,"✗ "&amp;Liens!C184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E189">
+        <f>IF(Liens!D184="","",IF(COUNTIF(Mots!B:B,Liens!D184)&gt;0,"✓ "&amp;Liens!D184,"✗ "&amp;Liens!D184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F189">
+        <f>IF(Liens!E184="","",IF(COUNTIF(Mots!B:B,Liens!E184)&gt;0,"✓ "&amp;Liens!E184,"✗ "&amp;Liens!E184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G189">
+        <f>IF(Liens!F184="","",IF(COUNTIF(Mots!B:B,Liens!F184)&gt;0,"✓ "&amp;Liens!F184,"✗ "&amp;Liens!F184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H189">
+        <f>IF(Liens!G184="","",IF(COUNTIF(Mots!B:B,Liens!G184)&gt;0,"✓ "&amp;Liens!G184,"✗ "&amp;Liens!G184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I189">
+        <f>IF(Liens!H184="","",IF(COUNTIF(Mots!B:B,Liens!H184)&gt;0,"✓ "&amp;Liens!H184,"✗ "&amp;Liens!H184&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>185</v>
+      </c>
+      <c r="B190">
+        <f>IF(Liens!A185="","",IF(COUNTIF(Mots!B:B,Liens!A185)&gt;0,"✓ "&amp;Liens!A185,"✗ "&amp;Liens!A185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C190">
+        <f>IF(Liens!B185="","",IF(COUNTIF(Mots!B:B,Liens!B185)&gt;0,"✓ "&amp;Liens!B185,"✗ "&amp;Liens!B185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D190">
+        <f>IF(Liens!C185="","",IF(COUNTIF(Mots!B:B,Liens!C185)&gt;0,"✓ "&amp;Liens!C185,"✗ "&amp;Liens!C185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E190">
+        <f>IF(Liens!D185="","",IF(COUNTIF(Mots!B:B,Liens!D185)&gt;0,"✓ "&amp;Liens!D185,"✗ "&amp;Liens!D185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F190">
+        <f>IF(Liens!E185="","",IF(COUNTIF(Mots!B:B,Liens!E185)&gt;0,"✓ "&amp;Liens!E185,"✗ "&amp;Liens!E185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G190">
+        <f>IF(Liens!F185="","",IF(COUNTIF(Mots!B:B,Liens!F185)&gt;0,"✓ "&amp;Liens!F185,"✗ "&amp;Liens!F185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H190">
+        <f>IF(Liens!G185="","",IF(COUNTIF(Mots!B:B,Liens!G185)&gt;0,"✓ "&amp;Liens!G185,"✗ "&amp;Liens!G185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I190">
+        <f>IF(Liens!H185="","",IF(COUNTIF(Mots!B:B,Liens!H185)&gt;0,"✓ "&amp;Liens!H185,"✗ "&amp;Liens!H185&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>186</v>
+      </c>
+      <c r="B191">
+        <f>IF(Liens!A186="","",IF(COUNTIF(Mots!B:B,Liens!A186)&gt;0,"✓ "&amp;Liens!A186,"✗ "&amp;Liens!A186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C191">
+        <f>IF(Liens!B186="","",IF(COUNTIF(Mots!B:B,Liens!B186)&gt;0,"✓ "&amp;Liens!B186,"✗ "&amp;Liens!B186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D191">
+        <f>IF(Liens!C186="","",IF(COUNTIF(Mots!B:B,Liens!C186)&gt;0,"✓ "&amp;Liens!C186,"✗ "&amp;Liens!C186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E191">
+        <f>IF(Liens!D186="","",IF(COUNTIF(Mots!B:B,Liens!D186)&gt;0,"✓ "&amp;Liens!D186,"✗ "&amp;Liens!D186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F191">
+        <f>IF(Liens!E186="","",IF(COUNTIF(Mots!B:B,Liens!E186)&gt;0,"✓ "&amp;Liens!E186,"✗ "&amp;Liens!E186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G191">
+        <f>IF(Liens!F186="","",IF(COUNTIF(Mots!B:B,Liens!F186)&gt;0,"✓ "&amp;Liens!F186,"✗ "&amp;Liens!F186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H191">
+        <f>IF(Liens!G186="","",IF(COUNTIF(Mots!B:B,Liens!G186)&gt;0,"✓ "&amp;Liens!G186,"✗ "&amp;Liens!G186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I191">
+        <f>IF(Liens!H186="","",IF(COUNTIF(Mots!B:B,Liens!H186)&gt;0,"✓ "&amp;Liens!H186,"✗ "&amp;Liens!H186&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>187</v>
+      </c>
+      <c r="B192">
+        <f>IF(Liens!A187="","",IF(COUNTIF(Mots!B:B,Liens!A187)&gt;0,"✓ "&amp;Liens!A187,"✗ "&amp;Liens!A187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C192">
+        <f>IF(Liens!B187="","",IF(COUNTIF(Mots!B:B,Liens!B187)&gt;0,"✓ "&amp;Liens!B187,"✗ "&amp;Liens!B187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D192">
+        <f>IF(Liens!C187="","",IF(COUNTIF(Mots!B:B,Liens!C187)&gt;0,"✓ "&amp;Liens!C187,"✗ "&amp;Liens!C187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E192">
+        <f>IF(Liens!D187="","",IF(COUNTIF(Mots!B:B,Liens!D187)&gt;0,"✓ "&amp;Liens!D187,"✗ "&amp;Liens!D187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F192">
+        <f>IF(Liens!E187="","",IF(COUNTIF(Mots!B:B,Liens!E187)&gt;0,"✓ "&amp;Liens!E187,"✗ "&amp;Liens!E187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G192">
+        <f>IF(Liens!F187="","",IF(COUNTIF(Mots!B:B,Liens!F187)&gt;0,"✓ "&amp;Liens!F187,"✗ "&amp;Liens!F187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H192">
+        <f>IF(Liens!G187="","",IF(COUNTIF(Mots!B:B,Liens!G187)&gt;0,"✓ "&amp;Liens!G187,"✗ "&amp;Liens!G187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I192">
+        <f>IF(Liens!H187="","",IF(COUNTIF(Mots!B:B,Liens!H187)&gt;0,"✓ "&amp;Liens!H187,"✗ "&amp;Liens!H187&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>188</v>
+      </c>
+      <c r="B193">
+        <f>IF(Liens!A188="","",IF(COUNTIF(Mots!B:B,Liens!A188)&gt;0,"✓ "&amp;Liens!A188,"✗ "&amp;Liens!A188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C193">
+        <f>IF(Liens!B188="","",IF(COUNTIF(Mots!B:B,Liens!B188)&gt;0,"✓ "&amp;Liens!B188,"✗ "&amp;Liens!B188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D193">
+        <f>IF(Liens!C188="","",IF(COUNTIF(Mots!B:B,Liens!C188)&gt;0,"✓ "&amp;Liens!C188,"✗ "&amp;Liens!C188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E193">
+        <f>IF(Liens!D188="","",IF(COUNTIF(Mots!B:B,Liens!D188)&gt;0,"✓ "&amp;Liens!D188,"✗ "&amp;Liens!D188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F193">
+        <f>IF(Liens!E188="","",IF(COUNTIF(Mots!B:B,Liens!E188)&gt;0,"✓ "&amp;Liens!E188,"✗ "&amp;Liens!E188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G193">
+        <f>IF(Liens!F188="","",IF(COUNTIF(Mots!B:B,Liens!F188)&gt;0,"✓ "&amp;Liens!F188,"✗ "&amp;Liens!F188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H193">
+        <f>IF(Liens!G188="","",IF(COUNTIF(Mots!B:B,Liens!G188)&gt;0,"✓ "&amp;Liens!G188,"✗ "&amp;Liens!G188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I193">
+        <f>IF(Liens!H188="","",IF(COUNTIF(Mots!B:B,Liens!H188)&gt;0,"✓ "&amp;Liens!H188,"✗ "&amp;Liens!H188&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>189</v>
+      </c>
+      <c r="B194">
+        <f>IF(Liens!A189="","",IF(COUNTIF(Mots!B:B,Liens!A189)&gt;0,"✓ "&amp;Liens!A189,"✗ "&amp;Liens!A189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C194">
+        <f>IF(Liens!B189="","",IF(COUNTIF(Mots!B:B,Liens!B189)&gt;0,"✓ "&amp;Liens!B189,"✗ "&amp;Liens!B189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D194">
+        <f>IF(Liens!C189="","",IF(COUNTIF(Mots!B:B,Liens!C189)&gt;0,"✓ "&amp;Liens!C189,"✗ "&amp;Liens!C189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E194">
+        <f>IF(Liens!D189="","",IF(COUNTIF(Mots!B:B,Liens!D189)&gt;0,"✓ "&amp;Liens!D189,"✗ "&amp;Liens!D189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F194">
+        <f>IF(Liens!E189="","",IF(COUNTIF(Mots!B:B,Liens!E189)&gt;0,"✓ "&amp;Liens!E189,"✗ "&amp;Liens!E189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G194">
+        <f>IF(Liens!F189="","",IF(COUNTIF(Mots!B:B,Liens!F189)&gt;0,"✓ "&amp;Liens!F189,"✗ "&amp;Liens!F189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H194">
+        <f>IF(Liens!G189="","",IF(COUNTIF(Mots!B:B,Liens!G189)&gt;0,"✓ "&amp;Liens!G189,"✗ "&amp;Liens!G189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I194">
+        <f>IF(Liens!H189="","",IF(COUNTIF(Mots!B:B,Liens!H189)&gt;0,"✓ "&amp;Liens!H189,"✗ "&amp;Liens!H189&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>190</v>
+      </c>
+      <c r="B195">
+        <f>IF(Liens!A190="","",IF(COUNTIF(Mots!B:B,Liens!A190)&gt;0,"✓ "&amp;Liens!A190,"✗ "&amp;Liens!A190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C195">
+        <f>IF(Liens!B190="","",IF(COUNTIF(Mots!B:B,Liens!B190)&gt;0,"✓ "&amp;Liens!B190,"✗ "&amp;Liens!B190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D195">
+        <f>IF(Liens!C190="","",IF(COUNTIF(Mots!B:B,Liens!C190)&gt;0,"✓ "&amp;Liens!C190,"✗ "&amp;Liens!C190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E195">
+        <f>IF(Liens!D190="","",IF(COUNTIF(Mots!B:B,Liens!D190)&gt;0,"✓ "&amp;Liens!D190,"✗ "&amp;Liens!D190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F195">
+        <f>IF(Liens!E190="","",IF(COUNTIF(Mots!B:B,Liens!E190)&gt;0,"✓ "&amp;Liens!E190,"✗ "&amp;Liens!E190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G195">
+        <f>IF(Liens!F190="","",IF(COUNTIF(Mots!B:B,Liens!F190)&gt;0,"✓ "&amp;Liens!F190,"✗ "&amp;Liens!F190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H195">
+        <f>IF(Liens!G190="","",IF(COUNTIF(Mots!B:B,Liens!G190)&gt;0,"✓ "&amp;Liens!G190,"✗ "&amp;Liens!G190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I195">
+        <f>IF(Liens!H190="","",IF(COUNTIF(Mots!B:B,Liens!H190)&gt;0,"✓ "&amp;Liens!H190,"✗ "&amp;Liens!H190&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>191</v>
+      </c>
+      <c r="B196">
+        <f>IF(Liens!A191="","",IF(COUNTIF(Mots!B:B,Liens!A191)&gt;0,"✓ "&amp;Liens!A191,"✗ "&amp;Liens!A191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C196">
+        <f>IF(Liens!B191="","",IF(COUNTIF(Mots!B:B,Liens!B191)&gt;0,"✓ "&amp;Liens!B191,"✗ "&amp;Liens!B191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D196">
+        <f>IF(Liens!C191="","",IF(COUNTIF(Mots!B:B,Liens!C191)&gt;0,"✓ "&amp;Liens!C191,"✗ "&amp;Liens!C191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E196">
+        <f>IF(Liens!D191="","",IF(COUNTIF(Mots!B:B,Liens!D191)&gt;0,"✓ "&amp;Liens!D191,"✗ "&amp;Liens!D191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F196">
+        <f>IF(Liens!E191="","",IF(COUNTIF(Mots!B:B,Liens!E191)&gt;0,"✓ "&amp;Liens!E191,"✗ "&amp;Liens!E191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G196">
+        <f>IF(Liens!F191="","",IF(COUNTIF(Mots!B:B,Liens!F191)&gt;0,"✓ "&amp;Liens!F191,"✗ "&amp;Liens!F191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H196">
+        <f>IF(Liens!G191="","",IF(COUNTIF(Mots!B:B,Liens!G191)&gt;0,"✓ "&amp;Liens!G191,"✗ "&amp;Liens!G191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I196">
+        <f>IF(Liens!H191="","",IF(COUNTIF(Mots!B:B,Liens!H191)&gt;0,"✓ "&amp;Liens!H191,"✗ "&amp;Liens!H191&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>192</v>
+      </c>
+      <c r="B197">
+        <f>IF(Liens!A192="","",IF(COUNTIF(Mots!B:B,Liens!A192)&gt;0,"✓ "&amp;Liens!A192,"✗ "&amp;Liens!A192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C197">
+        <f>IF(Liens!B192="","",IF(COUNTIF(Mots!B:B,Liens!B192)&gt;0,"✓ "&amp;Liens!B192,"✗ "&amp;Liens!B192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D197">
+        <f>IF(Liens!C192="","",IF(COUNTIF(Mots!B:B,Liens!C192)&gt;0,"✓ "&amp;Liens!C192,"✗ "&amp;Liens!C192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E197">
+        <f>IF(Liens!D192="","",IF(COUNTIF(Mots!B:B,Liens!D192)&gt;0,"✓ "&amp;Liens!D192,"✗ "&amp;Liens!D192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F197">
+        <f>IF(Liens!E192="","",IF(COUNTIF(Mots!B:B,Liens!E192)&gt;0,"✓ "&amp;Liens!E192,"✗ "&amp;Liens!E192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G197">
+        <f>IF(Liens!F192="","",IF(COUNTIF(Mots!B:B,Liens!F192)&gt;0,"✓ "&amp;Liens!F192,"✗ "&amp;Liens!F192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H197">
+        <f>IF(Liens!G192="","",IF(COUNTIF(Mots!B:B,Liens!G192)&gt;0,"✓ "&amp;Liens!G192,"✗ "&amp;Liens!G192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I197">
+        <f>IF(Liens!H192="","",IF(COUNTIF(Mots!B:B,Liens!H192)&gt;0,"✓ "&amp;Liens!H192,"✗ "&amp;Liens!H192&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>193</v>
+      </c>
+      <c r="B198">
+        <f>IF(Liens!A193="","",IF(COUNTIF(Mots!B:B,Liens!A193)&gt;0,"✓ "&amp;Liens!A193,"✗ "&amp;Liens!A193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C198">
+        <f>IF(Liens!B193="","",IF(COUNTIF(Mots!B:B,Liens!B193)&gt;0,"✓ "&amp;Liens!B193,"✗ "&amp;Liens!B193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D198">
+        <f>IF(Liens!C193="","",IF(COUNTIF(Mots!B:B,Liens!C193)&gt;0,"✓ "&amp;Liens!C193,"✗ "&amp;Liens!C193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E198">
+        <f>IF(Liens!D193="","",IF(COUNTIF(Mots!B:B,Liens!D193)&gt;0,"✓ "&amp;Liens!D193,"✗ "&amp;Liens!D193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F198">
+        <f>IF(Liens!E193="","",IF(COUNTIF(Mots!B:B,Liens!E193)&gt;0,"✓ "&amp;Liens!E193,"✗ "&amp;Liens!E193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G198">
+        <f>IF(Liens!F193="","",IF(COUNTIF(Mots!B:B,Liens!F193)&gt;0,"✓ "&amp;Liens!F193,"✗ "&amp;Liens!F193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H198">
+        <f>IF(Liens!G193="","",IF(COUNTIF(Mots!B:B,Liens!G193)&gt;0,"✓ "&amp;Liens!G193,"✗ "&amp;Liens!G193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I198">
+        <f>IF(Liens!H193="","",IF(COUNTIF(Mots!B:B,Liens!H193)&gt;0,"✓ "&amp;Liens!H193,"✗ "&amp;Liens!H193&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>194</v>
+      </c>
+      <c r="B199">
+        <f>IF(Liens!A194="","",IF(COUNTIF(Mots!B:B,Liens!A194)&gt;0,"✓ "&amp;Liens!A194,"✗ "&amp;Liens!A194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C199">
+        <f>IF(Liens!B194="","",IF(COUNTIF(Mots!B:B,Liens!B194)&gt;0,"✓ "&amp;Liens!B194,"✗ "&amp;Liens!B194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D199">
+        <f>IF(Liens!C194="","",IF(COUNTIF(Mots!B:B,Liens!C194)&gt;0,"✓ "&amp;Liens!C194,"✗ "&amp;Liens!C194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E199">
+        <f>IF(Liens!D194="","",IF(COUNTIF(Mots!B:B,Liens!D194)&gt;0,"✓ "&amp;Liens!D194,"✗ "&amp;Liens!D194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F199">
+        <f>IF(Liens!E194="","",IF(COUNTIF(Mots!B:B,Liens!E194)&gt;0,"✓ "&amp;Liens!E194,"✗ "&amp;Liens!E194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G199">
+        <f>IF(Liens!F194="","",IF(COUNTIF(Mots!B:B,Liens!F194)&gt;0,"✓ "&amp;Liens!F194,"✗ "&amp;Liens!F194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H199">
+        <f>IF(Liens!G194="","",IF(COUNTIF(Mots!B:B,Liens!G194)&gt;0,"✓ "&amp;Liens!G194,"✗ "&amp;Liens!G194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I199">
+        <f>IF(Liens!H194="","",IF(COUNTIF(Mots!B:B,Liens!H194)&gt;0,"✓ "&amp;Liens!H194,"✗ "&amp;Liens!H194&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>195</v>
+      </c>
+      <c r="B200">
+        <f>IF(Liens!A195="","",IF(COUNTIF(Mots!B:B,Liens!A195)&gt;0,"✓ "&amp;Liens!A195,"✗ "&amp;Liens!A195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C200">
+        <f>IF(Liens!B195="","",IF(COUNTIF(Mots!B:B,Liens!B195)&gt;0,"✓ "&amp;Liens!B195,"✗ "&amp;Liens!B195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D200">
+        <f>IF(Liens!C195="","",IF(COUNTIF(Mots!B:B,Liens!C195)&gt;0,"✓ "&amp;Liens!C195,"✗ "&amp;Liens!C195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E200">
+        <f>IF(Liens!D195="","",IF(COUNTIF(Mots!B:B,Liens!D195)&gt;0,"✓ "&amp;Liens!D195,"✗ "&amp;Liens!D195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F200">
+        <f>IF(Liens!E195="","",IF(COUNTIF(Mots!B:B,Liens!E195)&gt;0,"✓ "&amp;Liens!E195,"✗ "&amp;Liens!E195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G200">
+        <f>IF(Liens!F195="","",IF(COUNTIF(Mots!B:B,Liens!F195)&gt;0,"✓ "&amp;Liens!F195,"✗ "&amp;Liens!F195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H200">
+        <f>IF(Liens!G195="","",IF(COUNTIF(Mots!B:B,Liens!G195)&gt;0,"✓ "&amp;Liens!G195,"✗ "&amp;Liens!G195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I200">
+        <f>IF(Liens!H195="","",IF(COUNTIF(Mots!B:B,Liens!H195)&gt;0,"✓ "&amp;Liens!H195,"✗ "&amp;Liens!H195&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>196</v>
+      </c>
+      <c r="B201">
+        <f>IF(Liens!A196="","",IF(COUNTIF(Mots!B:B,Liens!A196)&gt;0,"✓ "&amp;Liens!A196,"✗ "&amp;Liens!A196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C201">
+        <f>IF(Liens!B196="","",IF(COUNTIF(Mots!B:B,Liens!B196)&gt;0,"✓ "&amp;Liens!B196,"✗ "&amp;Liens!B196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D201">
+        <f>IF(Liens!C196="","",IF(COUNTIF(Mots!B:B,Liens!C196)&gt;0,"✓ "&amp;Liens!C196,"✗ "&amp;Liens!C196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E201">
+        <f>IF(Liens!D196="","",IF(COUNTIF(Mots!B:B,Liens!D196)&gt;0,"✓ "&amp;Liens!D196,"✗ "&amp;Liens!D196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F201">
+        <f>IF(Liens!E196="","",IF(COUNTIF(Mots!B:B,Liens!E196)&gt;0,"✓ "&amp;Liens!E196,"✗ "&amp;Liens!E196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G201">
+        <f>IF(Liens!F196="","",IF(COUNTIF(Mots!B:B,Liens!F196)&gt;0,"✓ "&amp;Liens!F196,"✗ "&amp;Liens!F196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H201">
+        <f>IF(Liens!G196="","",IF(COUNTIF(Mots!B:B,Liens!G196)&gt;0,"✓ "&amp;Liens!G196,"✗ "&amp;Liens!G196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I201">
+        <f>IF(Liens!H196="","",IF(COUNTIF(Mots!B:B,Liens!H196)&gt;0,"✓ "&amp;Liens!H196,"✗ "&amp;Liens!H196&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>197</v>
+      </c>
+      <c r="B202">
+        <f>IF(Liens!A197="","",IF(COUNTIF(Mots!B:B,Liens!A197)&gt;0,"✓ "&amp;Liens!A197,"✗ "&amp;Liens!A197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C202">
+        <f>IF(Liens!B197="","",IF(COUNTIF(Mots!B:B,Liens!B197)&gt;0,"✓ "&amp;Liens!B197,"✗ "&amp;Liens!B197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D202">
+        <f>IF(Liens!C197="","",IF(COUNTIF(Mots!B:B,Liens!C197)&gt;0,"✓ "&amp;Liens!C197,"✗ "&amp;Liens!C197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E202">
+        <f>IF(Liens!D197="","",IF(COUNTIF(Mots!B:B,Liens!D197)&gt;0,"✓ "&amp;Liens!D197,"✗ "&amp;Liens!D197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F202">
+        <f>IF(Liens!E197="","",IF(COUNTIF(Mots!B:B,Liens!E197)&gt;0,"✓ "&amp;Liens!E197,"✗ "&amp;Liens!E197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G202">
+        <f>IF(Liens!F197="","",IF(COUNTIF(Mots!B:B,Liens!F197)&gt;0,"✓ "&amp;Liens!F197,"✗ "&amp;Liens!F197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H202">
+        <f>IF(Liens!G197="","",IF(COUNTIF(Mots!B:B,Liens!G197)&gt;0,"✓ "&amp;Liens!G197,"✗ "&amp;Liens!G197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I202">
+        <f>IF(Liens!H197="","",IF(COUNTIF(Mots!B:B,Liens!H197)&gt;0,"✓ "&amp;Liens!H197,"✗ "&amp;Liens!H197&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>198</v>
+      </c>
+      <c r="B203">
+        <f>IF(Liens!A198="","",IF(COUNTIF(Mots!B:B,Liens!A198)&gt;0,"✓ "&amp;Liens!A198,"✗ "&amp;Liens!A198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C203">
+        <f>IF(Liens!B198="","",IF(COUNTIF(Mots!B:B,Liens!B198)&gt;0,"✓ "&amp;Liens!B198,"✗ "&amp;Liens!B198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D203">
+        <f>IF(Liens!C198="","",IF(COUNTIF(Mots!B:B,Liens!C198)&gt;0,"✓ "&amp;Liens!C198,"✗ "&amp;Liens!C198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E203">
+        <f>IF(Liens!D198="","",IF(COUNTIF(Mots!B:B,Liens!D198)&gt;0,"✓ "&amp;Liens!D198,"✗ "&amp;Liens!D198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F203">
+        <f>IF(Liens!E198="","",IF(COUNTIF(Mots!B:B,Liens!E198)&gt;0,"✓ "&amp;Liens!E198,"✗ "&amp;Liens!E198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G203">
+        <f>IF(Liens!F198="","",IF(COUNTIF(Mots!B:B,Liens!F198)&gt;0,"✓ "&amp;Liens!F198,"✗ "&amp;Liens!F198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H203">
+        <f>IF(Liens!G198="","",IF(COUNTIF(Mots!B:B,Liens!G198)&gt;0,"✓ "&amp;Liens!G198,"✗ "&amp;Liens!G198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I203">
+        <f>IF(Liens!H198="","",IF(COUNTIF(Mots!B:B,Liens!H198)&gt;0,"✓ "&amp;Liens!H198,"✗ "&amp;Liens!H198&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>199</v>
+      </c>
+      <c r="B204">
+        <f>IF(Liens!A199="","",IF(COUNTIF(Mots!B:B,Liens!A199)&gt;0,"✓ "&amp;Liens!A199,"✗ "&amp;Liens!A199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C204">
+        <f>IF(Liens!B199="","",IF(COUNTIF(Mots!B:B,Liens!B199)&gt;0,"✓ "&amp;Liens!B199,"✗ "&amp;Liens!B199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D204">
+        <f>IF(Liens!C199="","",IF(COUNTIF(Mots!B:B,Liens!C199)&gt;0,"✓ "&amp;Liens!C199,"✗ "&amp;Liens!C199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E204">
+        <f>IF(Liens!D199="","",IF(COUNTIF(Mots!B:B,Liens!D199)&gt;0,"✓ "&amp;Liens!D199,"✗ "&amp;Liens!D199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F204">
+        <f>IF(Liens!E199="","",IF(COUNTIF(Mots!B:B,Liens!E199)&gt;0,"✓ "&amp;Liens!E199,"✗ "&amp;Liens!E199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G204">
+        <f>IF(Liens!F199="","",IF(COUNTIF(Mots!B:B,Liens!F199)&gt;0,"✓ "&amp;Liens!F199,"✗ "&amp;Liens!F199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H204">
+        <f>IF(Liens!G199="","",IF(COUNTIF(Mots!B:B,Liens!G199)&gt;0,"✓ "&amp;Liens!G199,"✗ "&amp;Liens!G199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I204">
+        <f>IF(Liens!H199="","",IF(COUNTIF(Mots!B:B,Liens!H199)&gt;0,"✓ "&amp;Liens!H199,"✗ "&amp;Liens!H199&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>200</v>
+      </c>
+      <c r="B205">
+        <f>IF(Liens!A200="","",IF(COUNTIF(Mots!B:B,Liens!A200)&gt;0,"✓ "&amp;Liens!A200,"✗ "&amp;Liens!A200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C205">
+        <f>IF(Liens!B200="","",IF(COUNTIF(Mots!B:B,Liens!B200)&gt;0,"✓ "&amp;Liens!B200,"✗ "&amp;Liens!B200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D205">
+        <f>IF(Liens!C200="","",IF(COUNTIF(Mots!B:B,Liens!C200)&gt;0,"✓ "&amp;Liens!C200,"✗ "&amp;Liens!C200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E205">
+        <f>IF(Liens!D200="","",IF(COUNTIF(Mots!B:B,Liens!D200)&gt;0,"✓ "&amp;Liens!D200,"✗ "&amp;Liens!D200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F205">
+        <f>IF(Liens!E200="","",IF(COUNTIF(Mots!B:B,Liens!E200)&gt;0,"✓ "&amp;Liens!E200,"✗ "&amp;Liens!E200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G205">
+        <f>IF(Liens!F200="","",IF(COUNTIF(Mots!B:B,Liens!F200)&gt;0,"✓ "&amp;Liens!F200,"✗ "&amp;Liens!F200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H205">
+        <f>IF(Liens!G200="","",IF(COUNTIF(Mots!B:B,Liens!G200)&gt;0,"✓ "&amp;Liens!G200,"✗ "&amp;Liens!G200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I205">
+        <f>IF(Liens!H200="","",IF(COUNTIF(Mots!B:B,Liens!H200)&gt;0,"✓ "&amp;Liens!H200,"✗ "&amp;Liens!H200&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>201</v>
+      </c>
+      <c r="B206">
+        <f>IF(Liens!A201="","",IF(COUNTIF(Mots!B:B,Liens!A201)&gt;0,"✓ "&amp;Liens!A201,"✗ "&amp;Liens!A201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="C206">
+        <f>IF(Liens!B201="","",IF(COUNTIF(Mots!B:B,Liens!B201)&gt;0,"✓ "&amp;Liens!B201,"✗ "&amp;Liens!B201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="D206">
+        <f>IF(Liens!C201="","",IF(COUNTIF(Mots!B:B,Liens!C201)&gt;0,"✓ "&amp;Liens!C201,"✗ "&amp;Liens!C201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="E206">
+        <f>IF(Liens!D201="","",IF(COUNTIF(Mots!B:B,Liens!D201)&gt;0,"✓ "&amp;Liens!D201,"✗ "&amp;Liens!D201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="F206">
+        <f>IF(Liens!E201="","",IF(COUNTIF(Mots!B:B,Liens!E201)&gt;0,"✓ "&amp;Liens!E201,"✗ "&amp;Liens!E201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="G206">
+        <f>IF(Liens!F201="","",IF(COUNTIF(Mots!B:B,Liens!F201)&gt;0,"✓ "&amp;Liens!F201,"✗ "&amp;Liens!F201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="H206">
+        <f>IF(Liens!G201="","",IF(COUNTIF(Mots!B:B,Liens!G201)&gt;0,"✓ "&amp;Liens!G201,"✗ "&amp;Liens!G201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+      <c r="I206">
+        <f>IF(Liens!H201="","",IF(COUNTIF(Mots!B:B,Liens!H201)&gt;0,"✓ "&amp;Liens!H201,"✗ "&amp;Liens!H201&amp;" (introuvable)"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\version_actuelle_vocab-app-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72112704-EB2E-4C34-B460-6D1F06CCF654}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F8F726-E701-4EF5-A827-55302483EA22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2985" uniqueCount="1949">
   <si>
     <t>id</t>
   </si>
@@ -5869,6 +5869,12 @@
   </si>
   <si>
     <t>Pour souper; Denrées de base</t>
+  </si>
+  <si>
+    <t>a_emporter</t>
+  </si>
+  <si>
+    <t>tri</t>
   </si>
 </sst>
 </file>
@@ -5941,7 +5947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5949,10 +5955,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6666,22 +6673,22 @@
     </row>
     <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -6706,62 +6713,68 @@
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>110</v>
+        <v>98</v>
+      </c>
+      <c r="G5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>103</v>
+      </c>
+      <c r="G6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -6786,174 +6799,171 @@
     </row>
     <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>302</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G9" t="s">
-        <v>99</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D10" t="s">
-        <v>303</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>299</v>
       </c>
       <c r="F10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>306</v>
+        <v>206</v>
       </c>
       <c r="D12" t="s">
-        <v>307</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>308</v>
+        <v>207</v>
+      </c>
+      <c r="G12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>216</v>
-      </c>
-      <c r="G13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>216</v>
+      </c>
+      <c r="G14" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -6978,48 +6988,45 @@
     </row>
     <row r="17" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="D17" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
-      </c>
-      <c r="G17" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7047,68 +7054,68 @@
     </row>
     <row r="20" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>178</v>
+        <v>173</v>
+      </c>
+      <c r="G20" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>193</v>
-      </c>
-      <c r="G21" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7136,119 +7143,119 @@
     </row>
     <row r="24" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F25" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>157</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>1943</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="F26" s="8" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" t="s">
         <v>1888</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>1941</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>1942</v>
+      <c r="C27" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B28" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>1888</v>
       </c>
       <c r="C28" t="s">
-        <v>1894</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
         <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1889</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s">
         <v>1888</v>
       </c>
       <c r="C29" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="D29" t="s">
         <v>258</v>
@@ -7257,38 +7264,38 @@
         <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>1891</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>252</v>
+        <v>1894</v>
       </c>
       <c r="B30" t="s">
         <v>1888</v>
       </c>
       <c r="C30" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D30" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>256</v>
+        <v>1889</v>
       </c>
       <c r="B31" t="s">
         <v>1888</v>
       </c>
       <c r="C31" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="D31" t="s">
         <v>258</v>
@@ -7297,7 +7304,7 @@
         <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>259</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7322,22 +7329,22 @@
     </row>
     <row r="33" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s">
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E33" t="s">
-        <v>290</v>
-      </c>
-      <c r="F33" t="s">
-        <v>291</v>
+        <v>281</v>
+      </c>
+      <c r="G33" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7365,42 +7372,42 @@
     </row>
     <row r="35" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s">
         <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D35" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
-      </c>
-      <c r="G35" t="s">
-        <v>69</v>
+        <v>285</v>
+      </c>
+      <c r="F35" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s">
         <v>65</v>
       </c>
       <c r="C36" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7425,42 +7432,42 @@
     </row>
     <row r="38" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7508,157 +7515,157 @@
     </row>
     <row r="42" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
-      </c>
-      <c r="B42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" t="s">
         <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G42" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>141</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>156</v>
+        <v>142</v>
+      </c>
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" t="s">
-        <v>26</v>
-      </c>
-      <c r="F46" t="s">
-        <v>133</v>
-      </c>
-      <c r="G46" t="s">
-        <v>134</v>
+      <c r="C46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G47" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="F48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G48" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7865,9 +7872,9 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G58">
-    <sortCondition ref="B2:B58"/>
-    <sortCondition ref="C2:C58"/>
+  <sortState ref="A4:G58">
+    <sortCondition ref="B4:B58"/>
+    <sortCondition ref="C4:C58"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -7877,7 +7884,7 @@
           <x14:formula1>
             <xm:f>Catégories!$C$2:$C$25</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B58</xm:sqref>
+          <xm:sqref>B2:B41 B42:B58</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7900,7 +7907,7 @@
     <col min="11" max="11" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7934,8 +7941,11 @@
       <c r="K1" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1119</v>
       </c>
@@ -7958,7 +7968,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1876</v>
       </c>
@@ -7985,7 +7995,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1661</v>
       </c>
@@ -8015,7 +8025,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1818</v>
       </c>
@@ -8045,7 +8055,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1305</v>
       </c>
@@ -8072,7 +8082,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1248</v>
       </c>
@@ -8099,7 +8109,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1746</v>
       </c>
@@ -8129,7 +8139,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1846</v>
       </c>
@@ -8159,7 +8169,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1358</v>
       </c>
@@ -8186,7 +8196,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1774</v>
       </c>
@@ -8216,7 +8226,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1794</v>
       </c>
@@ -8246,7 +8256,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1796</v>
       </c>
@@ -8276,7 +8286,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1668</v>
       </c>
@@ -8303,7 +8313,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1779</v>
       </c>
@@ -8333,7 +8343,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1138</v>
       </c>
@@ -8620,7 +8630,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="8" t="s">
         <v>386</v>
       </c>
       <c r="K25" t="s">
@@ -9577,11 +9587,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J58" s="10"/>
+      <c r="J58" s="8"/>
       <c r="K58" t="s">
         <v>991</v>
       </c>
-      <c r="L58" s="10" t="s">
+      <c r="L58" s="8" t="s">
         <v>1931</v>
       </c>
     </row>
@@ -10076,7 +10086,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J75" s="8" t="s">
         <v>164</v>
       </c>
       <c r="K75" t="s">
@@ -16218,15 +16228,20 @@
   <sortState ref="A2:K307">
     <sortCondition ref="A2:A307"/>
   </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G124:G307" xr:uid="{5F269F85-1540-4200-A6D7-8EC9CEC1DA3A}">
+      <formula1>$C$2:$C$74</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{25701FED-E5A2-4CB6-9487-254CA9FABABE}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B729DD0C-2AC7-49A2-B311-8C6B292E8F50}">
           <x14:formula1>
-            <xm:f>'Sous-catégories'!$C$2:$C$72</xm:f>
+            <xm:f>'Sous-catégories'!$C$4:$C$72</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G122 G124:G307</xm:sqref>
+          <xm:sqref>G2:G122</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16969,17 +16984,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>1375</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16991,17 +17006,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>1377</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7570283-91E2-4E2E-8657-F4271E60AB2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A042E1CA-4533-4AB1-8F0F-2B09C1C92EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catégories" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="2249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3442" uniqueCount="2249">
   <si>
     <t>id</t>
   </si>
@@ -6862,7 +6862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6880,6 +6880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9030,7 +9031,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M368"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9083,7 +9083,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1591</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1624</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1623</v>
       </c>
@@ -9168,7 +9168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1723</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1724</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1719</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1720</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1722</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1730</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1727</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1728</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1729</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1731</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1732</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>993</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>992</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1735</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1744</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1743</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1840</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1845</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1741</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1740</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1739</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1742</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1736</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="18" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>2132</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="18" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>2133</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1854</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1787</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1850</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1745</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1746</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1748</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1747</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1751</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1749</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1750</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>969</v>
       </c>
@@ -10174,7 +10174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>972</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1858</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1859</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1867</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1239</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1222</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>302</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1231</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1243</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1227</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1247</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1235</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1017</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1021</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1013</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1001</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1009</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1005</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1571</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1573</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1572</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1574</v>
       </c>
@@ -10751,7 +10751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1562</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1563</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1564</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1566</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1567</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1570</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1569</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1568</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1565</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1621</v>
       </c>
@@ -11048,7 +11048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1620</v>
       </c>
@@ -11075,7 +11075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1622</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1694</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1688</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1689</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1690</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1693</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1696</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1695</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1699</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1700</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1692</v>
       </c>
@@ -11417,7 +11417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1691</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1702</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1701</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1698</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1697</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>982</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1774</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1686</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1682</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1683</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1684</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1685</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>707</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1754</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1755</v>
       </c>
@@ -11819,7 +11819,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1753</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1756</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1738</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1726</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1725</v>
       </c>
@@ -11945,7 +11945,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1716</v>
       </c>
@@ -11972,7 +11972,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1715</v>
       </c>
@@ -11999,7 +11999,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="12" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
         <v>2004</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1717</v>
       </c>
@@ -12046,7 +12046,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>856</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1187</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1183</v>
       </c>
@@ -12121,7 +12121,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1195</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1191</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1162</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1174</v>
       </c>
@@ -12217,7 +12217,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1178</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1146</v>
       </c>
@@ -12265,7 +12265,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1170</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1142</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1150</v>
       </c>
@@ -12337,7 +12337,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1166</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>1158</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1154</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1251</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1255</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>1885</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1899</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1900</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1905</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1904</v>
       </c>
@@ -12596,7 +12596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1901</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1902</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1903</v>
       </c>
@@ -12677,7 +12677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1627</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1625</v>
       </c>
@@ -12731,7 +12731,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>1626</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>1660</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>1658</v>
       </c>
@@ -12812,7 +12812,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>1657</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>1659</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>1661</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>616</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>1600</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1601</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1602</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1595</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>1593</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>1596</v>
       </c>
@@ -13076,7 +13076,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1599</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>1598</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>1594</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>1597</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>1884</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>1592</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>1872</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1874</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1878</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1895</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:13" s="12" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>1995</v>
       </c>
@@ -13372,7 +13372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1876</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1710</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1721</v>
       </c>
@@ -13453,7 +13453,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1714</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1713</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1712</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1718</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1711</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1705</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1709</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1708</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1704</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1703</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1706</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1707</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1607</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1606</v>
       </c>
@@ -13852,7 +13852,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1605</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1608</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1603</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1604</v>
       </c>
@@ -13957,7 +13957,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1590</v>
       </c>
@@ -13984,7 +13984,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1589</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1588</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1670</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1675</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1671</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>656</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1676</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1677</v>
       </c>
@@ -14194,7 +14194,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1672</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1674</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1678</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1673</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1669</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1119</v>
       </c>
@@ -14356,7 +14356,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1557</v>
       </c>
@@ -14380,7 +14380,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1101</v>
       </c>
@@ -14407,7 +14407,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1107</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="200" spans="1:11" s="6" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>1556</v>
       </c>
@@ -14460,7 +14460,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1555</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1111</v>
       </c>
@@ -14514,7 +14514,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1103</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1115</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1558</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1044</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>57</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1051</v>
       </c>
@@ -14658,7 +14658,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1055</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>730</v>
       </c>
@@ -14709,7 +14709,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1059</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1552</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1758</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1760</v>
       </c>
@@ -14817,7 +14817,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1759</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1769</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1768</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1763</v>
       </c>
@@ -14925,7 +14925,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1762</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1764</v>
       </c>
@@ -14979,7 +14979,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1761</v>
       </c>
@@ -15003,7 +15003,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1770</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1215</v>
       </c>
@@ -15054,7 +15054,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1203</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1211</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1207</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>726</v>
       </c>
@@ -15156,7 +15156,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1687</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>722</v>
       </c>
@@ -15210,7 +15210,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>718</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1767</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1827</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1757</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>946</v>
       </c>
@@ -15333,7 +15333,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1662</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1665</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1667</v>
       </c>
@@ -15414,7 +15414,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1663</v>
       </c>
@@ -15441,7 +15441,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1664</v>
       </c>
@@ -15468,7 +15468,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1668</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1666</v>
       </c>
@@ -15519,7 +15519,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1680</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1681</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1839</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1679</v>
       </c>
@@ -15627,7 +15627,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1226</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1653</v>
       </c>
@@ -15681,7 +15681,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>575</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1650</v>
       </c>
@@ -15732,7 +15732,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1639</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1640</v>
       </c>
@@ -15786,7 +15786,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1648</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1641</v>
       </c>
@@ -15840,7 +15840,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1654</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1655</v>
       </c>
@@ -15894,7 +15894,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>570</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1652</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>2003</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1647</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1649</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1643</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1642</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1645</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1644</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1656</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1646</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1651</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>579</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>997</v>
       </c>
@@ -16272,7 +16272,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>994</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1587</v>
       </c>
@@ -16323,7 +16323,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1586</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1771</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1554</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1553</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1765</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1619</v>
       </c>
@@ -16485,7 +16485,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1616</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1615</v>
       </c>
@@ -16539,7 +16539,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1618</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1617</v>
       </c>
@@ -16593,7 +16593,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1611</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1614</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1613</v>
       </c>
@@ -16671,7 +16671,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1610</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1612</v>
       </c>
@@ -16725,7 +16725,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1609</v>
       </c>
@@ -16752,7 +16752,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1766</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="289" spans="1:11" s="12" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="12" t="s">
         <v>1998</v>
       </c>
@@ -16805,7 +16805,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>978</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>964</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>104</v>
       </c>
@@ -16880,7 +16880,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>974</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1772</v>
       </c>
@@ -16928,7 +16928,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="295" spans="1:11" s="17" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="17" t="s">
         <v>2126</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>991</v>
       </c>
@@ -16978,7 +16978,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1199</v>
       </c>
@@ -17002,7 +17002,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1040</v>
       </c>
@@ -17026,7 +17026,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1025</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1036</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>12</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1032</v>
       </c>
@@ -17122,7 +17122,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1631</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>28</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1630</v>
       </c>
@@ -17200,7 +17200,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1637</v>
       </c>
@@ -17227,7 +17227,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1628</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1634</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1629</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1632</v>
       </c>
@@ -17335,7 +17335,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1633</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1638</v>
       </c>
@@ -17386,7 +17386,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1635</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1636</v>
       </c>
@@ -17439,7 +17439,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1733</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1734</v>
       </c>
@@ -17485,7 +17485,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1737</v>
       </c>
@@ -17511,7 +17511,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1752</v>
       </c>
@@ -17534,7 +17534,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1559</v>
       </c>
@@ -17557,7 +17557,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1561</v>
       </c>
@@ -17583,7 +17583,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="9" t="s">
         <v>1560</v>
       </c>
@@ -17606,7 +17606,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1576</v>
       </c>
@@ -17632,7 +17632,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1585</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="9" t="s">
         <v>1577</v>
       </c>
@@ -17684,7 +17684,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1575</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1580</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1582</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="9" t="s">
         <v>1584</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="s">
         <v>1578</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="s">
         <v>1581</v>
       </c>
@@ -17840,7 +17840,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="s">
         <v>1583</v>
       </c>
@@ -17866,7 +17866,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="s">
         <v>1579</v>
       </c>
@@ -17892,7 +17892,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="333" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="12" t="s">
         <v>1967</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:13" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="18" t="s">
         <v>2204</v>
       </c>
@@ -17941,7 +17941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="12" t="s">
         <v>1968</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="12" t="s">
         <v>1970</v>
       </c>
@@ -17990,7 +17990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:13" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="18" t="s">
         <v>2206</v>
       </c>
@@ -18003,6 +18003,9 @@
       <c r="D337" s="18" t="s">
         <v>2208</v>
       </c>
+      <c r="G337" s="19" t="s">
+        <v>731</v>
+      </c>
       <c r="J337" s="15" t="s">
         <v>2226</v>
       </c>
@@ -18010,7 +18013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="12" t="s">
         <v>1969</v>
       </c>
@@ -18036,7 +18039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="12" t="s">
         <v>1958</v>
       </c>
@@ -18056,7 +18059,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="340" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="12" t="s">
         <v>1959</v>
       </c>
@@ -18116,7 +18119,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="s">
         <v>1947</v>
       </c>
@@ -18136,7 +18139,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1948</v>
       </c>
@@ -18156,7 +18159,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1949</v>
       </c>
@@ -18196,7 +18199,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1956</v>
       </c>
@@ -18213,7 +18216,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="348" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" s="12" t="s">
         <v>2202</v>
       </c>
@@ -18273,7 +18276,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>2140</v>
       </c>
@@ -18293,7 +18296,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>2141</v>
       </c>
@@ -18313,7 +18316,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>2142</v>
       </c>
@@ -18333,7 +18336,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>2143</v>
       </c>
@@ -18350,7 +18353,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>2151</v>
       </c>
@@ -18367,7 +18370,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>2155</v>
       </c>
@@ -18387,7 +18390,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="357" spans="1:13" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="18" t="s">
         <v>2170</v>
       </c>
@@ -18407,7 +18410,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="358" spans="1:13" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="18" t="s">
         <v>2171</v>
       </c>
@@ -18427,7 +18430,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>2158</v>
       </c>
@@ -18444,7 +18447,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>2159</v>
       </c>
@@ -18461,7 +18464,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>2176</v>
       </c>
@@ -18484,7 +18487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>2177</v>
       </c>
@@ -18507,7 +18510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>2178</v>
       </c>
@@ -18530,7 +18533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>2186</v>
       </c>
@@ -18553,7 +18556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>2188</v>
       </c>
@@ -18576,7 +18579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>2189</v>
       </c>
@@ -18599,7 +18602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>2194</v>
       </c>
@@ -18619,7 +18622,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>2195</v>
       </c>
@@ -18640,13 +18643,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L368" xr:uid="{4212FD66-C6C4-4DFF-B892-CC5760CAC6FC}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="mes frère et sœurs"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L368" xr:uid="{4212FD66-C6C4-4DFF-B892-CC5760CAC6FC}"/>
   <sortState ref="A2:M332">
     <sortCondition ref="G2:G332"/>
     <sortCondition ref="M2:M332"/>
@@ -19553,17 +19550,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>1268</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -19575,17 +19572,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>1270</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A042E1CA-4533-4AB1-8F0F-2B09C1C92EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{073285C2-AAB4-48A7-928D-AC04D14F36D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6862,7 +6862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6880,6 +6880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -15671,7 +15672,7 @@
         <v>606</v>
       </c>
       <c r="G247" s="6" t="s">
-        <v>156</v>
+        <v>2167</v>
       </c>
       <c r="H247" s="6"/>
       <c r="J247" t="s">
@@ -15697,8 +15698,8 @@
       <c r="E248" t="s">
         <v>577</v>
       </c>
-      <c r="G248" t="s">
-        <v>156</v>
+      <c r="G248" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H248" s="6"/>
       <c r="K248" t="s">
@@ -15721,8 +15722,8 @@
       <c r="E249" t="s">
         <v>600</v>
       </c>
-      <c r="G249" t="s">
-        <v>156</v>
+      <c r="G249" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H249" s="6"/>
       <c r="J249" s="15" t="s">
@@ -15748,8 +15749,8 @@
       <c r="E250" t="s">
         <v>551</v>
       </c>
-      <c r="G250" t="s">
-        <v>156</v>
+      <c r="G250" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H250" s="6"/>
       <c r="J250" s="16" t="s">
@@ -15775,8 +15776,8 @@
       <c r="E251" t="s">
         <v>553</v>
       </c>
-      <c r="G251" t="s">
-        <v>156</v>
+      <c r="G251" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H251" s="6"/>
       <c r="J251" t="s">
@@ -15802,8 +15803,8 @@
       <c r="E252" t="s">
         <v>594</v>
       </c>
-      <c r="G252" t="s">
-        <v>156</v>
+      <c r="G252" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H252" s="6"/>
       <c r="J252" t="s">
@@ -15829,8 +15830,8 @@
       <c r="E253" t="s">
         <v>556</v>
       </c>
-      <c r="G253" t="s">
-        <v>156</v>
+      <c r="G253" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H253" s="6"/>
       <c r="J253" t="s">
@@ -15856,8 +15857,8 @@
       <c r="E254" t="s">
         <v>609</v>
       </c>
-      <c r="G254" t="s">
-        <v>156</v>
+      <c r="G254" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H254" s="6"/>
       <c r="J254" t="s">
@@ -15883,8 +15884,8 @@
       <c r="E255" t="s">
         <v>612</v>
       </c>
-      <c r="G255" t="s">
-        <v>156</v>
+      <c r="G255" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H255" s="6"/>
       <c r="J255" t="s">
@@ -15910,8 +15911,8 @@
       <c r="E256" t="s">
         <v>572</v>
       </c>
-      <c r="G256" t="s">
-        <v>156</v>
+      <c r="G256" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H256" s="6"/>
       <c r="J256" t="s">
@@ -15937,8 +15938,8 @@
       <c r="E257" t="s">
         <v>604</v>
       </c>
-      <c r="G257" t="s">
-        <v>156</v>
+      <c r="G257" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H257" s="6"/>
       <c r="J257" s="15" t="s">
@@ -15964,8 +15965,8 @@
       <c r="E258" t="s">
         <v>591</v>
       </c>
-      <c r="G258" t="s">
-        <v>156</v>
+      <c r="G258" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H258" s="6"/>
       <c r="J258" s="15" t="s">
@@ -15991,8 +15992,8 @@
       <c r="E259" t="s">
         <v>588</v>
       </c>
-      <c r="G259" t="s">
-        <v>156</v>
+      <c r="G259" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H259" s="6"/>
       <c r="J259" t="s">
@@ -16018,8 +16019,8 @@
       <c r="E260" t="s">
         <v>598</v>
       </c>
-      <c r="G260" t="s">
-        <v>156</v>
+      <c r="G260" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H260" s="6"/>
       <c r="J260" s="16" t="s">
@@ -16045,8 +16046,8 @@
       <c r="E261" t="s">
         <v>563</v>
       </c>
-      <c r="G261" t="s">
-        <v>156</v>
+      <c r="G261" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H261" s="6"/>
       <c r="J261" s="16" t="s">
@@ -16072,8 +16073,8 @@
       <c r="E262" t="s">
         <v>560</v>
       </c>
-      <c r="G262" t="s">
-        <v>156</v>
+      <c r="G262" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H262" s="6"/>
       <c r="J262" s="15" t="s">
@@ -16099,8 +16100,8 @@
       <c r="E263" t="s">
         <v>568</v>
       </c>
-      <c r="G263" t="s">
-        <v>156</v>
+      <c r="G263" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H263" s="6"/>
       <c r="J263" t="s">
@@ -16126,8 +16127,8 @@
       <c r="E264" t="s">
         <v>565</v>
       </c>
-      <c r="G264" t="s">
-        <v>156</v>
+      <c r="G264" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H264" s="6"/>
       <c r="J264" t="s">
@@ -16153,8 +16154,8 @@
       <c r="E265" t="s">
         <v>1804</v>
       </c>
-      <c r="G265" t="s">
-        <v>156</v>
+      <c r="G265" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H265" s="6"/>
       <c r="J265" t="s">
@@ -16180,8 +16181,8 @@
       <c r="E266" t="s">
         <v>585</v>
       </c>
-      <c r="G266" t="s">
-        <v>156</v>
+      <c r="G266" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H266" s="6"/>
       <c r="J266" t="s">
@@ -16207,8 +16208,8 @@
       <c r="E267" t="s">
         <v>602</v>
       </c>
-      <c r="G267" t="s">
-        <v>156</v>
+      <c r="G267" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H267" s="6"/>
       <c r="J267" s="15" t="s">
@@ -16234,8 +16235,8 @@
       <c r="E268" t="s">
         <v>581</v>
       </c>
-      <c r="G268" t="s">
-        <v>156</v>
+      <c r="G268" s="20" t="s">
+        <v>2167</v>
       </c>
       <c r="H268" s="6"/>
       <c r="J268" t="s">
@@ -19550,17 +19551,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>1268</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -19572,17 +19573,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B99A83CC-4BE5-4DA0-B64D-BA6E405C912D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8E5711-F255-4AEB-BFCD-91F812D921BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Validation" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Mots!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Mots!$A$1:$M$368</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -6919,7 +6919,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6937,6 +6937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -10381,153 +10382,177 @@
       </c>
       <c r="H45" s="6"/>
       <c r="J45" s="22"/>
+      <c r="M45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>2163</v>
+        <v>2139</v>
       </c>
       <c r="B46" t="s">
-        <v>2165</v>
+        <v>2143</v>
       </c>
       <c r="C46" t="s">
         <v>323</v>
       </c>
       <c r="D46" t="s">
-        <v>2167</v>
+        <v>2149</v>
       </c>
       <c r="G46" t="s">
         <v>2162</v>
       </c>
       <c r="H46" s="6"/>
-      <c r="J46" s="15" t="s">
-        <v>2228</v>
+      <c r="J46" s="23"/>
+      <c r="M46">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>2164</v>
+        <v>2136</v>
       </c>
       <c r="B47" t="s">
-        <v>2166</v>
+        <v>2140</v>
       </c>
       <c r="C47" t="s">
         <v>323</v>
       </c>
       <c r="D47" t="s">
-        <v>2168</v>
+        <v>2144</v>
       </c>
       <c r="G47" t="s">
         <v>2162</v>
       </c>
       <c r="H47" s="6"/>
       <c r="J47" s="15" t="s">
-        <v>2229</v>
+        <v>2225</v>
+      </c>
+      <c r="M47">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>2139</v>
+        <v>2163</v>
       </c>
       <c r="B48" t="s">
-        <v>2143</v>
+        <v>2165</v>
       </c>
       <c r="C48" t="s">
         <v>323</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>2149</v>
+        <v>2167</v>
       </c>
       <c r="G48" t="s">
         <v>2162</v>
       </c>
       <c r="H48" s="6"/>
-      <c r="J48" s="22"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="15" t="s">
+        <v>2228</v>
+      </c>
+      <c r="M48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>2151</v>
+        <v>2164</v>
       </c>
       <c r="B49" t="s">
-        <v>2152</v>
+        <v>2166</v>
       </c>
       <c r="C49" t="s">
         <v>323</v>
       </c>
       <c r="D49" t="s">
-        <v>2153</v>
+        <v>2168</v>
       </c>
       <c r="G49" t="s">
         <v>2162</v>
       </c>
       <c r="H49" s="6"/>
       <c r="J49" s="15" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2229</v>
+      </c>
+      <c r="M49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B50" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C50" t="s">
         <v>323</v>
       </c>
       <c r="D50" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="G50" t="s">
         <v>2162</v>
       </c>
       <c r="H50" s="6"/>
       <c r="J50" s="15" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2226</v>
+      </c>
+      <c r="M50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="B51" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C51" t="s">
         <v>323</v>
       </c>
       <c r="D51" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="G51" t="s">
         <v>2162</v>
       </c>
       <c r="H51" s="6"/>
       <c r="J51" s="15" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2227</v>
+      </c>
+      <c r="M51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>2137</v>
+        <v>2151</v>
       </c>
       <c r="B52" t="s">
-        <v>2141</v>
+        <v>2152</v>
       </c>
       <c r="C52" t="s">
         <v>323</v>
       </c>
       <c r="D52" t="s">
-        <v>2145</v>
+        <v>2153</v>
       </c>
       <c r="G52" t="s">
         <v>2162</v>
       </c>
       <c r="H52" s="6"/>
       <c r="J52" s="15" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2227</v>
+      </c>
+      <c r="M52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1238</v>
       </c>
@@ -10551,7 +10576,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1221</v>
       </c>
@@ -10575,7 +10600,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>302</v>
       </c>
@@ -10599,7 +10624,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1230</v>
       </c>
@@ -10623,7 +10648,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1242</v>
       </c>
@@ -10647,7 +10672,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1226</v>
       </c>
@@ -10671,7 +10696,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1246</v>
       </c>
@@ -10695,7 +10720,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1234</v>
       </c>
@@ -10719,7 +10744,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1016</v>
       </c>
@@ -10745,7 +10770,7 @@
       </c>
       <c r="L61" s="9"/>
     </row>
-    <row r="62" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1020</v>
       </c>
@@ -10770,7 +10795,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1012</v>
       </c>
@@ -10795,7 +10820,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1000</v>
       </c>
@@ -11826,753 +11851,774 @@
     </row>
     <row r="100" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1773</v>
+        <v>963</v>
       </c>
       <c r="B100" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C100" t="s">
         <v>323</v>
       </c>
       <c r="D100" t="s">
-        <v>966</v>
+        <v>1403</v>
       </c>
       <c r="E100" t="s">
-        <v>1774</v>
+        <v>964</v>
       </c>
       <c r="G100" t="s">
         <v>1830</v>
       </c>
       <c r="H100" s="6"/>
-      <c r="J100" s="15" t="s">
-        <v>2214</v>
-      </c>
+      <c r="J100" s="23"/>
       <c r="K100" t="s">
-        <v>1777</v>
+        <v>965</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1685</v>
+        <v>973</v>
       </c>
       <c r="B101" t="s">
-        <v>712</v>
+        <v>1466</v>
       </c>
       <c r="C101" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D101" t="s">
-        <v>1369</v>
+        <v>974</v>
       </c>
       <c r="E101" t="s">
-        <v>713</v>
+        <v>975</v>
       </c>
       <c r="G101" t="s">
-        <v>2256</v>
+        <v>1830</v>
       </c>
       <c r="H101" s="6"/>
-      <c r="J101" s="15" t="s">
-        <v>2021</v>
-      </c>
+      <c r="J101" s="23"/>
       <c r="K101" t="s">
-        <v>712</v>
+        <v>976</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1681</v>
+        <v>1773</v>
       </c>
       <c r="B102" t="s">
-        <v>699</v>
+        <v>1490</v>
       </c>
       <c r="C102" t="s">
         <v>323</v>
       </c>
       <c r="D102" t="s">
-        <v>1807</v>
+        <v>966</v>
       </c>
       <c r="E102" t="s">
-        <v>700</v>
+        <v>1774</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>2256</v>
+        <v>1830</v>
       </c>
       <c r="H102" s="6"/>
       <c r="J102" s="15" t="s">
-        <v>2022</v>
+        <v>2214</v>
       </c>
       <c r="K102" t="s">
-        <v>699</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B103" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C103" t="s">
         <v>323</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>1365</v>
+        <v>1807</v>
       </c>
       <c r="E103" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>2256</v>
       </c>
       <c r="H103" s="6"/>
       <c r="J103" s="15" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K103" t="s">
-        <v>701</v>
+        <v>699</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B104" t="s">
-        <v>1450</v>
+        <v>701</v>
       </c>
       <c r="C104" t="s">
         <v>323</v>
       </c>
       <c r="D104" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E104" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>2256</v>
       </c>
       <c r="H104" s="6"/>
-      <c r="J104" s="22" t="s">
-        <v>705</v>
+      <c r="J104" s="15" t="s">
+        <v>2023</v>
       </c>
       <c r="K104" t="s">
-        <v>703</v>
+        <v>701</v>
+      </c>
+      <c r="M104">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B105" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C105" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D105" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="E105" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G105" s="22" t="s">
         <v>2256</v>
       </c>
       <c r="H105" s="6"/>
       <c r="J105" s="15" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="K105" t="s">
-        <v>710</v>
+        <v>712</v>
+      </c>
+      <c r="M105">
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>706</v>
+        <v>1684</v>
       </c>
       <c r="B106" t="s">
-        <v>1451</v>
+        <v>710</v>
       </c>
       <c r="C106" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D106" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E106" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="G106" s="22" t="s">
         <v>2256</v>
       </c>
       <c r="H106" s="6"/>
-      <c r="J106" t="s">
-        <v>709</v>
+      <c r="J106" s="15" t="s">
+        <v>2024</v>
       </c>
       <c r="K106" t="s">
-        <v>707</v>
+        <v>710</v>
+      </c>
+      <c r="M106">
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1753</v>
+        <v>1683</v>
       </c>
       <c r="B107" t="s">
-        <v>888</v>
+        <v>1450</v>
       </c>
       <c r="C107" t="s">
         <v>323</v>
       </c>
       <c r="D107" t="s">
-        <v>889</v>
+        <v>1366</v>
       </c>
       <c r="E107" t="s">
-        <v>890</v>
+        <v>704</v>
       </c>
       <c r="G107" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
       <c r="H107" s="6"/>
-      <c r="J107" s="21"/>
+      <c r="J107" s="21" t="s">
+        <v>705</v>
+      </c>
       <c r="K107" t="s">
-        <v>891</v>
+        <v>703</v>
+      </c>
+      <c r="M107">
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1754</v>
+        <v>706</v>
       </c>
       <c r="B108" t="s">
-        <v>894</v>
+        <v>1451</v>
       </c>
       <c r="C108" t="s">
         <v>323</v>
       </c>
       <c r="D108" t="s">
-        <v>895</v>
+        <v>1367</v>
       </c>
       <c r="E108" t="s">
-        <v>896</v>
+        <v>708</v>
       </c>
       <c r="G108" s="22" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
       <c r="H108" s="6"/>
-      <c r="J108" s="21"/>
+      <c r="J108" s="21" t="s">
+        <v>709</v>
+      </c>
       <c r="K108" t="s">
-        <v>897</v>
+        <v>707</v>
+      </c>
+      <c r="M108">
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:13" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="G109" s="22" t="s">
         <v>2264</v>
       </c>
       <c r="J109" s="21"/>
       <c r="K109" s="12" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B110" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C110" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D110" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E110" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G110" s="22" t="s">
         <v>2264</v>
       </c>
       <c r="H110" s="6"/>
-      <c r="J110" t="s">
-        <v>901</v>
-      </c>
       <c r="K110" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1737</v>
+        <v>1752</v>
       </c>
       <c r="B111" t="s">
-        <v>1473</v>
+        <v>884</v>
       </c>
       <c r="C111" t="s">
         <v>323</v>
       </c>
       <c r="D111" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="E111" t="s">
-        <v>1819</v>
+        <v>886</v>
       </c>
       <c r="G111" s="22" t="s">
         <v>2264</v>
       </c>
       <c r="H111" s="6"/>
       <c r="K111" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1725</v>
+        <v>1755</v>
       </c>
       <c r="B112" t="s">
-        <v>867</v>
+        <v>898</v>
       </c>
       <c r="C112" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D112" t="s">
-        <v>868</v>
+        <v>899</v>
       </c>
       <c r="E112" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="G112" t="s">
-        <v>210</v>
+        <v>2264</v>
       </c>
       <c r="H112" s="6"/>
+      <c r="J112" t="s">
+        <v>901</v>
+      </c>
       <c r="K112" t="s">
-        <v>870</v>
+        <v>898</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1724</v>
+        <v>1737</v>
       </c>
       <c r="B113" t="s">
-        <v>851</v>
+        <v>1473</v>
       </c>
       <c r="C113" t="s">
         <v>323</v>
       </c>
       <c r="D113" t="s">
-        <v>852</v>
+        <v>892</v>
       </c>
       <c r="E113" t="s">
-        <v>853</v>
+        <v>1819</v>
       </c>
       <c r="G113" t="s">
-        <v>210</v>
+        <v>2264</v>
       </c>
       <c r="H113" s="6"/>
-      <c r="J113" s="22" t="s">
-        <v>854</v>
-      </c>
+      <c r="J113" s="22"/>
       <c r="K113" t="s">
-        <v>851</v>
+        <v>893</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="B114" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="C114" t="s">
         <v>323</v>
       </c>
       <c r="D114" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="E114" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="G114" t="s">
         <v>210</v>
       </c>
       <c r="H114" s="6"/>
-      <c r="J114" s="15" t="s">
-        <v>2025</v>
-      </c>
+      <c r="J114" s="23"/>
       <c r="K114" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
       <c r="B115" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C115" t="s">
         <v>323</v>
       </c>
       <c r="D115" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E115" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="G115" t="s">
         <v>210</v>
       </c>
       <c r="H115" s="6"/>
-      <c r="J115" s="15" t="s">
-        <v>2026</v>
+      <c r="J115" s="23" t="s">
+        <v>854</v>
       </c>
       <c r="K115" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B116" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C116" t="s">
         <v>323</v>
       </c>
       <c r="D116" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E116" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="G116" t="s">
         <v>210</v>
       </c>
       <c r="H116" s="6"/>
+      <c r="J116" s="15" t="s">
+        <v>2025</v>
+      </c>
       <c r="K116" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>855</v>
+        <v>1714</v>
       </c>
       <c r="B117" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="C117" t="s">
         <v>323</v>
       </c>
       <c r="D117" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="E117" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="G117" t="s">
         <v>210</v>
       </c>
       <c r="H117" s="6"/>
-      <c r="J117" s="22" t="s">
-        <v>859</v>
+      <c r="J117" s="15" t="s">
+        <v>2026</v>
       </c>
       <c r="K117" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>2000</v>
+        <v>1716</v>
       </c>
       <c r="B118" t="s">
-        <v>2001</v>
+        <v>863</v>
       </c>
       <c r="C118" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D118" t="s">
-        <v>2002</v>
+        <v>864</v>
       </c>
       <c r="E118" t="s">
-        <v>2003</v>
+        <v>865</v>
       </c>
       <c r="G118" t="s">
         <v>210</v>
       </c>
       <c r="H118" s="6"/>
-      <c r="J118" s="15" t="s">
-        <v>2027</v>
+      <c r="J118" s="23"/>
+      <c r="K118" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1186</v>
+        <v>855</v>
       </c>
       <c r="B119" t="s">
-        <v>1531</v>
+        <v>856</v>
       </c>
       <c r="C119" t="s">
         <v>323</v>
       </c>
       <c r="D119" t="s">
-        <v>1187</v>
+        <v>857</v>
       </c>
       <c r="E119" t="s">
-        <v>1188</v>
+        <v>858</v>
       </c>
       <c r="G119" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="H119" s="6"/>
+      <c r="J119" t="s">
+        <v>859</v>
+      </c>
       <c r="K119" t="s">
-        <v>1189</v>
+        <v>856</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1182</v>
+        <v>2000</v>
       </c>
       <c r="B120" t="s">
-        <v>1530</v>
+        <v>2001</v>
       </c>
       <c r="C120" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D120" t="s">
-        <v>1183</v>
+        <v>2002</v>
       </c>
       <c r="E120" t="s">
-        <v>1184</v>
+        <v>2003</v>
       </c>
       <c r="G120" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="H120" s="6"/>
-      <c r="K120" t="s">
-        <v>1185</v>
+      <c r="J120" s="15" t="s">
+        <v>2027</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="B121" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C121" t="s">
-        <v>1178</v>
+        <v>323</v>
       </c>
       <c r="D121" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="E121" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="G121" t="s">
         <v>291</v>
       </c>
       <c r="H121" s="6"/>
       <c r="K121" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="B122" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C122" t="s">
         <v>323</v>
       </c>
       <c r="D122" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
       <c r="E122" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="G122" t="s">
         <v>291</v>
       </c>
       <c r="H122" s="6"/>
       <c r="K122" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1161</v>
+        <v>1194</v>
       </c>
       <c r="B123" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="C123" t="s">
-        <v>538</v>
+        <v>1178</v>
       </c>
       <c r="D123" t="s">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="E123" t="s">
-        <v>1163</v>
+        <v>1196</v>
       </c>
       <c r="G123" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H123" s="6"/>
       <c r="K123" t="s">
-        <v>1164</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="B124" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="C124" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D124" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="E124" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="G124" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H124" s="6"/>
       <c r="K124" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1177</v>
+        <v>1161</v>
       </c>
       <c r="B125" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="C125" t="s">
-        <v>1178</v>
+        <v>538</v>
       </c>
       <c r="D125" t="s">
-        <v>1179</v>
+        <v>1162</v>
       </c>
       <c r="E125" t="s">
-        <v>1180</v>
+        <v>1163</v>
       </c>
       <c r="G125" t="s">
         <v>287</v>
       </c>
       <c r="H125" s="6"/>
       <c r="K125" t="s">
-        <v>1181</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="B126" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="C126" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D126" t="s">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="E126" t="s">
-        <v>1147</v>
+        <v>1175</v>
       </c>
       <c r="G126" t="s">
         <v>287</v>
       </c>
       <c r="H126" s="6"/>
       <c r="K126" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="B127" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C127" t="s">
-        <v>323</v>
+        <v>1178</v>
       </c>
       <c r="D127" t="s">
-        <v>1170</v>
+        <v>1179</v>
       </c>
       <c r="E127" t="s">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="G127" s="6" t="s">
         <v>287</v>
       </c>
       <c r="H127" s="6"/>
       <c r="K127" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B128" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C128" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D128" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="E128" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="G128" s="9" t="s">
         <v>287</v>
       </c>
       <c r="H128" s="9"/>
       <c r="K128" s="13" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1149</v>
+        <v>1169</v>
       </c>
       <c r="B129" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="C129" t="s">
         <v>323</v>
       </c>
       <c r="D129" t="s">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="E129" s="21" t="s">
-        <v>1151</v>
+        <v>1171</v>
       </c>
       <c r="G129" t="s">
         <v>287</v>
@@ -12580,24 +12626,24 @@
       <c r="H129" s="6"/>
       <c r="J129" s="21"/>
       <c r="K129" t="s">
-        <v>1152</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1165</v>
+        <v>1141</v>
       </c>
       <c r="B130" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="C130" t="s">
         <v>538</v>
       </c>
       <c r="D130" t="s">
-        <v>1166</v>
+        <v>1142</v>
       </c>
       <c r="E130" s="21" t="s">
-        <v>1167</v>
+        <v>1143</v>
       </c>
       <c r="G130" t="s">
         <v>287</v>
@@ -12605,24 +12651,24 @@
       <c r="H130" s="6"/>
       <c r="J130" s="21"/>
       <c r="K130" t="s">
-        <v>1168</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="B131" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C131" t="s">
         <v>323</v>
       </c>
       <c r="D131" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="E131" s="21" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
       <c r="G131" t="s">
         <v>287</v>
@@ -12630,24 +12676,24 @@
       <c r="H131" s="6"/>
       <c r="J131" s="21"/>
       <c r="K131" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="B132" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="C132" t="s">
         <v>538</v>
       </c>
       <c r="D132" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="E132" s="21" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="G132" t="s">
         <v>287</v>
@@ -12655,154 +12701,148 @@
       <c r="H132" s="6"/>
       <c r="J132" s="21"/>
       <c r="K132" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1250</v>
+        <v>1157</v>
       </c>
       <c r="B133" t="s">
-        <v>1547</v>
+        <v>1524</v>
       </c>
       <c r="C133" t="s">
         <v>323</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>1251</v>
+        <v>1158</v>
       </c>
       <c r="E133" s="21" t="s">
-        <v>1252</v>
+        <v>1159</v>
       </c>
       <c r="G133" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="H133" s="6"/>
       <c r="J133" s="21"/>
       <c r="K133" t="s">
-        <v>1253</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1254</v>
+        <v>1153</v>
       </c>
       <c r="B134" t="s">
-        <v>1548</v>
+        <v>1523</v>
       </c>
       <c r="C134" t="s">
         <v>538</v>
       </c>
       <c r="D134" t="s">
-        <v>1255</v>
+        <v>1154</v>
       </c>
       <c r="E134" s="21" t="s">
-        <v>1256</v>
+        <v>1155</v>
       </c>
       <c r="G134" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="H134" s="6"/>
       <c r="K134" t="s">
-        <v>1257</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1884</v>
+        <v>1250</v>
       </c>
       <c r="B135" t="s">
-        <v>2120</v>
+        <v>1547</v>
       </c>
       <c r="C135" t="s">
         <v>323</v>
       </c>
       <c r="D135" t="s">
-        <v>985</v>
+        <v>1251</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>986</v>
+        <v>1252</v>
       </c>
       <c r="G135" t="s">
-        <v>1886</v>
+        <v>308</v>
       </c>
       <c r="H135" s="6"/>
       <c r="J135" s="22"/>
       <c r="K135" t="s">
-        <v>1888</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1898</v>
+        <v>1254</v>
       </c>
       <c r="B136" t="s">
-        <v>1905</v>
+        <v>1548</v>
       </c>
       <c r="C136" t="s">
         <v>538</v>
       </c>
       <c r="D136" t="s">
-        <v>1912</v>
-      </c>
-      <c r="E136" s="5"/>
+        <v>1255</v>
+      </c>
+      <c r="E136" s="23" t="s">
+        <v>1256</v>
+      </c>
       <c r="G136" t="s">
-        <v>1886</v>
+        <v>308</v>
       </c>
       <c r="H136" s="6"/>
-      <c r="J136" s="15" t="s">
-        <v>2028</v>
-      </c>
+      <c r="J136" s="23"/>
       <c r="K136" t="s">
-        <v>1919</v>
-      </c>
-      <c r="M136">
-        <v>2</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1899</v>
+        <v>1884</v>
       </c>
       <c r="B137" t="s">
-        <v>1906</v>
+        <v>2120</v>
       </c>
       <c r="C137" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D137" t="s">
-        <v>1913</v>
-      </c>
-      <c r="E137" s="5"/>
+        <v>985</v>
+      </c>
+      <c r="E137" s="23" t="s">
+        <v>986</v>
+      </c>
       <c r="G137" t="s">
         <v>1886</v>
       </c>
       <c r="H137" s="6"/>
-      <c r="J137" s="15" t="s">
-        <v>2029</v>
-      </c>
+      <c r="J137" s="23"/>
       <c r="K137" t="s">
-        <v>1920</v>
+        <v>1888</v>
       </c>
       <c r="M137">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1904</v>
+        <v>1898</v>
       </c>
       <c r="B138" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C138" t="s">
         <v>538</v>
       </c>
       <c r="D138" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="E138" s="5"/>
       <c r="G138" t="s">
@@ -12810,27 +12850,27 @@
       </c>
       <c r="H138" s="6"/>
       <c r="J138" s="15" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="K138" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="M138">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1903</v>
+        <v>1899</v>
       </c>
       <c r="B139" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="C139" t="s">
         <v>538</v>
       </c>
       <c r="D139" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="E139" s="5"/>
       <c r="G139" t="s">
@@ -12838,75 +12878,83 @@
       </c>
       <c r="H139" s="6"/>
       <c r="J139" s="15" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="K139" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="M139">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>2169</v>
+        <v>1904</v>
       </c>
       <c r="B140" t="s">
-        <v>2172</v>
+        <v>1910</v>
       </c>
       <c r="C140" t="s">
         <v>538</v>
       </c>
       <c r="D140" t="s">
-        <v>2175</v>
-      </c>
+        <v>1914</v>
+      </c>
+      <c r="E140" s="5"/>
       <c r="G140" t="s">
         <v>1886</v>
       </c>
       <c r="H140" s="6"/>
       <c r="J140" s="15" t="s">
-        <v>2230</v>
+        <v>2030</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1922</v>
       </c>
       <c r="M140">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>2170</v>
+        <v>1903</v>
       </c>
       <c r="B141" t="s">
-        <v>2173</v>
+        <v>1907</v>
       </c>
       <c r="C141" t="s">
         <v>538</v>
       </c>
       <c r="D141" t="s">
-        <v>2176</v>
-      </c>
+        <v>1915</v>
+      </c>
+      <c r="E141" s="5"/>
       <c r="G141" t="s">
         <v>1886</v>
       </c>
       <c r="H141" s="6"/>
       <c r="J141" s="15" t="s">
-        <v>2231</v>
+        <v>2031</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1921</v>
       </c>
       <c r="M141">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="B142" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C142" t="s">
         <v>538</v>
       </c>
       <c r="D142" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="E142" s="22"/>
       <c r="G142" t="s">
@@ -12914,78 +12962,74 @@
       </c>
       <c r="H142" s="6"/>
       <c r="J142" s="15" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="M142">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1900</v>
+        <v>2170</v>
       </c>
       <c r="B143" t="s">
-        <v>1908</v>
+        <v>2173</v>
       </c>
       <c r="C143" t="s">
         <v>538</v>
       </c>
       <c r="D143" t="s">
-        <v>1916</v>
-      </c>
-      <c r="E143" s="5"/>
+        <v>2176</v>
+      </c>
+      <c r="E143" s="23"/>
       <c r="G143" t="s">
         <v>1886</v>
       </c>
       <c r="H143" s="6"/>
       <c r="J143" s="15" t="s">
-        <v>2032</v>
-      </c>
-      <c r="K143" t="s">
-        <v>1923</v>
+        <v>2231</v>
       </c>
       <c r="M143">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1901</v>
+        <v>2171</v>
       </c>
       <c r="B144" t="s">
-        <v>1911</v>
+        <v>2174</v>
       </c>
       <c r="C144" t="s">
         <v>538</v>
       </c>
       <c r="D144" t="s">
-        <v>1917</v>
-      </c>
-      <c r="E144" s="5"/>
+        <v>2177</v>
+      </c>
+      <c r="E144" s="23"/>
       <c r="G144" t="s">
         <v>1886</v>
       </c>
       <c r="H144" s="6"/>
-      <c r="J144" s="22"/>
-      <c r="K144" t="s">
-        <v>1924</v>
+      <c r="J144" s="15" t="s">
+        <v>2232</v>
       </c>
       <c r="M144">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B145" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="C145" t="s">
         <v>538</v>
       </c>
       <c r="D145" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="E145" s="5"/>
       <c r="G145" t="s">
@@ -12993,1363 +13037,1393 @@
       </c>
       <c r="H145" s="6"/>
       <c r="J145" s="15" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="K145" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="M145">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1709</v>
+        <v>1901</v>
       </c>
       <c r="B146" t="s">
-        <v>800</v>
+        <v>1911</v>
       </c>
       <c r="C146" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D146" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E146" t="s">
-        <v>801</v>
-      </c>
+        <v>1917</v>
+      </c>
+      <c r="E146" s="5"/>
       <c r="G146" t="s">
-        <v>2247</v>
+        <v>1886</v>
       </c>
       <c r="H146" s="6"/>
-      <c r="J146" s="15" t="s">
-        <v>2051</v>
-      </c>
+      <c r="J146" s="23"/>
       <c r="K146" t="s">
-        <v>800</v>
+        <v>1924</v>
+      </c>
+      <c r="M146">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1720</v>
+        <v>1902</v>
       </c>
       <c r="B147" t="s">
-        <v>817</v>
+        <v>1909</v>
       </c>
       <c r="C147" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D147" t="s">
-        <v>1795</v>
-      </c>
-      <c r="E147" t="s">
-        <v>1794</v>
-      </c>
+        <v>1918</v>
+      </c>
+      <c r="E147" s="5"/>
       <c r="G147" t="s">
-        <v>2247</v>
+        <v>1886</v>
       </c>
       <c r="H147" s="6"/>
       <c r="J147" s="15" t="s">
-        <v>2052</v>
+        <v>2033</v>
       </c>
       <c r="K147" t="s">
-        <v>817</v>
+        <v>1925</v>
+      </c>
+      <c r="M147">
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="B148" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="C148" t="s">
         <v>323</v>
       </c>
       <c r="D148" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="E148" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="G148" t="s">
         <v>2247</v>
       </c>
       <c r="H148" s="6"/>
-      <c r="J148" t="s">
-        <v>813</v>
+      <c r="J148" s="15" t="s">
+        <v>2051</v>
       </c>
       <c r="K148" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="B149" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="C149" t="s">
         <v>323</v>
       </c>
       <c r="D149" t="s">
-        <v>1383</v>
+        <v>1795</v>
       </c>
       <c r="E149" t="s">
-        <v>809</v>
+        <v>1794</v>
       </c>
       <c r="G149" t="s">
         <v>2247</v>
       </c>
       <c r="H149" s="6"/>
-      <c r="J149" s="22" t="s">
-        <v>810</v>
+      <c r="J149" s="15" t="s">
+        <v>2052</v>
       </c>
       <c r="K149" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B150" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="C150" t="s">
         <v>323</v>
       </c>
       <c r="D150" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="E150" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="G150" t="s">
         <v>2247</v>
       </c>
       <c r="H150" s="6"/>
       <c r="J150" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="K150" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
       <c r="B151" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C151" t="s">
         <v>323</v>
       </c>
       <c r="D151" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="E151" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="G151" t="s">
         <v>2247</v>
       </c>
       <c r="H151" s="6"/>
       <c r="J151" s="21" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="K151" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B152" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C152" t="s">
         <v>323</v>
       </c>
       <c r="D152" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E152" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G152" t="s">
         <v>2247</v>
       </c>
       <c r="H152" s="6"/>
       <c r="J152" s="21" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="K152" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1702</v>
+        <v>1717</v>
       </c>
       <c r="B153" t="s">
-        <v>779</v>
+        <v>814</v>
       </c>
       <c r="C153" t="s">
         <v>323</v>
       </c>
       <c r="D153" t="s">
-        <v>780</v>
+        <v>1385</v>
       </c>
       <c r="E153" t="s">
-        <v>1792</v>
+        <v>815</v>
       </c>
       <c r="G153" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="H153" s="6"/>
       <c r="J153" s="22" t="s">
-        <v>781</v>
+        <v>816</v>
       </c>
       <c r="K153" t="s">
-        <v>779</v>
-      </c>
-      <c r="M153">
-        <v>1</v>
+        <v>814</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1703</v>
+        <v>1710</v>
       </c>
       <c r="B154" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="C154" t="s">
         <v>323</v>
       </c>
       <c r="D154" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="E154" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
       <c r="G154" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="H154" s="6"/>
       <c r="J154" s="22" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
       <c r="K154" t="s">
-        <v>782</v>
-      </c>
-      <c r="M154">
-        <v>2</v>
+        <v>802</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="B155" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="C155" t="s">
-        <v>1178</v>
+        <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="E155" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="G155" t="s">
         <v>2246</v>
       </c>
       <c r="H155" s="6"/>
-      <c r="J155" s="15" t="s">
-        <v>2054</v>
+      <c r="J155" s="23" t="s">
+        <v>781</v>
       </c>
       <c r="K155" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="M155">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="B156" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="C156" t="s">
         <v>323</v>
       </c>
       <c r="D156" t="s">
-        <v>796</v>
+        <v>1379</v>
       </c>
       <c r="E156" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="G156" t="s">
         <v>2246</v>
       </c>
       <c r="H156" s="6"/>
-      <c r="J156" s="15" t="s">
-        <v>2055</v>
+      <c r="J156" s="23" t="s">
+        <v>784</v>
       </c>
       <c r="K156" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="M156">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="21" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="B157" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="C157" t="s">
-        <v>538</v>
+        <v>1178</v>
       </c>
       <c r="D157" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="E157" t="s">
-        <v>793</v>
+        <v>1793</v>
       </c>
       <c r="G157" t="s">
         <v>2246</v>
       </c>
       <c r="H157" s="6"/>
-      <c r="J157" s="22" t="s">
-        <v>794</v>
+      <c r="J157" s="15" t="s">
+        <v>2054</v>
       </c>
       <c r="K157" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="M157">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="B158" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="C158" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D158" s="22" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="E158" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="G158" t="s">
         <v>2246</v>
       </c>
       <c r="H158" s="6"/>
       <c r="J158" s="15" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="K158" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="M158">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B159" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C159" t="s">
         <v>538</v>
       </c>
       <c r="D159" t="s">
-        <v>1378</v>
+        <v>792</v>
       </c>
       <c r="E159" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="G159" t="s">
         <v>2246</v>
       </c>
       <c r="H159" s="6"/>
       <c r="J159" s="22" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="K159" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="M159">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1638</v>
+        <v>1704</v>
       </c>
       <c r="B160" t="s">
-        <v>549</v>
+        <v>785</v>
       </c>
       <c r="C160" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D160" t="s">
-        <v>1332</v>
+        <v>786</v>
       </c>
       <c r="E160" t="s">
-        <v>550</v>
+        <v>787</v>
       </c>
       <c r="G160" t="s">
-        <v>2160</v>
+        <v>2246</v>
       </c>
       <c r="H160" s="6"/>
-      <c r="J160" s="16" t="s">
-        <v>2080</v>
+      <c r="J160" s="15" t="s">
+        <v>2053</v>
       </c>
       <c r="K160" t="s">
-        <v>549</v>
+        <v>785</v>
       </c>
       <c r="M160">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:13" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
-        <v>1641</v>
+        <v>1705</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>558</v>
+        <v>788</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>1335</v>
+        <v>1378</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>559</v>
+        <v>789</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>2160</v>
-      </c>
-      <c r="J161" s="15" t="s">
-        <v>2084</v>
+        <v>2246</v>
+      </c>
+      <c r="J161" s="23" t="s">
+        <v>790</v>
       </c>
       <c r="K161" s="12" t="s">
-        <v>560</v>
+        <v>788</v>
       </c>
       <c r="M161" s="12">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1644</v>
+        <v>1638</v>
       </c>
       <c r="B162" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="C162" t="s">
         <v>323</v>
       </c>
       <c r="D162" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="E162" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="G162" t="s">
         <v>2160</v>
       </c>
       <c r="H162" s="6"/>
-      <c r="J162" s="22" t="s">
-        <v>568</v>
+      <c r="J162" s="16" t="s">
+        <v>2080</v>
       </c>
       <c r="K162" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="M162">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B163" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C163" t="s">
         <v>323</v>
       </c>
       <c r="D163" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E163" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G163" t="s">
         <v>2160</v>
       </c>
       <c r="H163" s="6"/>
-      <c r="J163" s="16" t="s">
-        <v>2112</v>
+      <c r="J163" s="15" t="s">
+        <v>2084</v>
       </c>
       <c r="K163" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M163">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B164" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C164" t="s">
         <v>323</v>
       </c>
       <c r="D164" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E164" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G164" t="s">
         <v>2160</v>
       </c>
       <c r="H164" s="6"/>
       <c r="J164" s="22" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K164" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M164">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="B165" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="C165" t="s">
         <v>323</v>
       </c>
       <c r="D165" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="E165" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="G165" t="s">
         <v>2160</v>
       </c>
       <c r="H165" s="6"/>
-      <c r="J165" t="s">
-        <v>553</v>
+      <c r="J165" s="16" t="s">
+        <v>2112</v>
       </c>
       <c r="K165" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="M165">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="B166" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="C166" t="s">
         <v>323</v>
       </c>
       <c r="D166" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E166" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="G166" t="s">
         <v>2160</v>
       </c>
       <c r="H166" s="6"/>
       <c r="J166" s="22" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="K166" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="M166">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1650</v>
+        <v>1639</v>
       </c>
       <c r="B167" t="s">
-        <v>600</v>
+        <v>551</v>
       </c>
       <c r="C167" t="s">
         <v>323</v>
       </c>
       <c r="D167" t="s">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="E167" t="s">
-        <v>601</v>
+        <v>552</v>
       </c>
       <c r="G167" t="s">
         <v>2160</v>
       </c>
       <c r="H167" s="6"/>
-      <c r="J167" s="15" t="s">
-        <v>2085</v>
+      <c r="J167" s="23" t="s">
+        <v>553</v>
       </c>
       <c r="K167" t="s">
-        <v>600</v>
+        <v>551</v>
       </c>
       <c r="M167">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1999</v>
+        <v>1640</v>
       </c>
       <c r="B168" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
       <c r="C168" t="s">
         <v>323</v>
       </c>
       <c r="D168" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="E168" t="s">
-        <v>590</v>
+        <v>555</v>
       </c>
       <c r="G168" s="9" t="s">
         <v>2160</v>
       </c>
       <c r="H168" s="9"/>
-      <c r="J168" s="15" t="s">
-        <v>2082</v>
+      <c r="J168" s="23" t="s">
+        <v>556</v>
       </c>
       <c r="K168" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="M168">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="B169" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="C169" t="s">
         <v>323</v>
       </c>
       <c r="D169" t="s">
-        <v>592</v>
+        <v>1344</v>
       </c>
       <c r="E169" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>2160</v>
       </c>
       <c r="H169" s="6"/>
-      <c r="J169" s="22" t="s">
-        <v>594</v>
+      <c r="J169" s="15" t="s">
+        <v>2085</v>
       </c>
       <c r="K169" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="M169">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B170" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C170" t="s">
         <v>323</v>
       </c>
       <c r="D170" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="E170" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G170" s="22" t="s">
         <v>2160</v>
       </c>
       <c r="H170" s="6"/>
       <c r="J170" s="15" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="K170" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="M170">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="B171" t="s">
-        <v>595</v>
+        <v>1445</v>
       </c>
       <c r="C171" t="s">
         <v>323</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>596</v>
+        <v>1349</v>
       </c>
       <c r="E171" t="s">
-        <v>597</v>
+        <v>1803</v>
       </c>
       <c r="G171" t="s">
         <v>2160</v>
       </c>
       <c r="H171" s="6"/>
-      <c r="J171" s="16" t="s">
-        <v>2083</v>
+      <c r="J171" s="23" t="s">
+        <v>614</v>
       </c>
       <c r="K171" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="M171">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1652</v>
+        <v>1999</v>
       </c>
       <c r="B172" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="C172" t="s">
         <v>323</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>1346</v>
+      <c r="D172" s="23" t="s">
+        <v>1342</v>
       </c>
       <c r="E172" t="s">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="G172" t="s">
         <v>2160</v>
       </c>
       <c r="H172" s="6"/>
-      <c r="J172" s="21" t="s">
-        <v>606</v>
+      <c r="J172" s="15" t="s">
+        <v>2082</v>
       </c>
       <c r="K172" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="M172">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="B173" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="C173" t="s">
         <v>323</v>
       </c>
       <c r="D173" t="s">
-        <v>1347</v>
+        <v>592</v>
       </c>
       <c r="E173" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="G173" t="s">
         <v>2160</v>
       </c>
       <c r="H173" s="6"/>
       <c r="J173" s="22" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="K173" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="M173">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1655</v>
+        <v>1649</v>
       </c>
       <c r="B174" t="s">
-        <v>1445</v>
+        <v>598</v>
       </c>
       <c r="C174" t="s">
         <v>323</v>
       </c>
       <c r="D174" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="E174" t="s">
-        <v>1803</v>
+        <v>599</v>
       </c>
       <c r="G174" t="s">
         <v>2160</v>
       </c>
       <c r="H174" s="6"/>
-      <c r="J174" s="22" t="s">
-        <v>614</v>
+      <c r="J174" s="15" t="s">
+        <v>2079</v>
       </c>
       <c r="K174" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
       <c r="M174">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1654</v>
+        <v>1648</v>
       </c>
       <c r="B175" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="C175" t="s">
         <v>323</v>
       </c>
       <c r="D175" t="s">
-        <v>1348</v>
+        <v>596</v>
       </c>
       <c r="E175" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="G175" t="s">
         <v>2160</v>
       </c>
       <c r="H175" s="6"/>
-      <c r="J175" s="22" t="s">
-        <v>612</v>
+      <c r="J175" s="16" t="s">
+        <v>2083</v>
       </c>
       <c r="K175" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="M175">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>578</v>
+        <v>1652</v>
       </c>
       <c r="B176" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="C176" t="s">
         <v>323</v>
       </c>
-      <c r="D176" t="s">
-        <v>1339</v>
+      <c r="D176" s="5" t="s">
+        <v>1346</v>
       </c>
       <c r="E176" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="G176" t="s">
         <v>2160</v>
       </c>
       <c r="H176" s="6"/>
       <c r="J176" s="22" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="K176" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="M176">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="B177" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="C177" t="s">
         <v>323</v>
       </c>
       <c r="D177" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="E177" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="G177" t="s">
         <v>2160</v>
       </c>
       <c r="H177" s="6"/>
       <c r="J177" s="22" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="K177" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="M177">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="B178" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="C178" t="s">
         <v>323</v>
       </c>
       <c r="D178" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="E178" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="G178" t="s">
         <v>2160</v>
       </c>
       <c r="H178" s="6"/>
-      <c r="J178" s="15" t="s">
-        <v>2081</v>
+      <c r="J178" s="23" t="s">
+        <v>612</v>
       </c>
       <c r="K178" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="M178">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B179" t="s">
-        <v>1443</v>
+        <v>579</v>
       </c>
       <c r="C179" t="s">
         <v>323</v>
       </c>
       <c r="D179" t="s">
-        <v>570</v>
+        <v>1339</v>
       </c>
       <c r="E179" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="G179" t="s">
         <v>2160</v>
       </c>
       <c r="H179" s="6"/>
       <c r="J179" s="22" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="K179" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="M179">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>574</v>
+        <v>1645</v>
       </c>
       <c r="B180" t="s">
-        <v>1444</v>
+        <v>583</v>
       </c>
       <c r="C180" t="s">
         <v>323</v>
       </c>
       <c r="D180" t="s">
-        <v>575</v>
+        <v>1340</v>
       </c>
       <c r="E180" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="G180" t="s">
         <v>2160</v>
       </c>
       <c r="H180" s="6"/>
+      <c r="J180" t="s">
+        <v>585</v>
+      </c>
       <c r="K180" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M180">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1646</v>
+        <v>569</v>
       </c>
       <c r="B181" t="s">
-        <v>586</v>
+        <v>1443</v>
       </c>
       <c r="C181" t="s">
         <v>323</v>
       </c>
       <c r="D181" t="s">
-        <v>1341</v>
+        <v>570</v>
       </c>
       <c r="E181" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="G181" t="s">
         <v>2160</v>
       </c>
       <c r="H181" s="6"/>
       <c r="J181" s="22" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="K181" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="M181">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1626</v>
+        <v>574</v>
       </c>
       <c r="B182" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C182" t="s">
         <v>323</v>
       </c>
       <c r="D182" t="s">
-        <v>1326</v>
+        <v>575</v>
       </c>
       <c r="E182" t="s">
-        <v>511</v>
+        <v>576</v>
       </c>
       <c r="G182" t="s">
-        <v>2267</v>
+        <v>2160</v>
       </c>
       <c r="H182" s="6"/>
-      <c r="J182" s="15" t="s">
-        <v>2215</v>
-      </c>
+      <c r="J182" s="23"/>
       <c r="K182" t="s">
-        <v>510</v>
+        <v>577</v>
+      </c>
+      <c r="M182">
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1624</v>
+        <v>1646</v>
       </c>
       <c r="B183" t="s">
-        <v>1440</v>
+        <v>586</v>
       </c>
       <c r="C183" t="s">
         <v>323</v>
       </c>
       <c r="D183" t="s">
-        <v>1324</v>
+        <v>1341</v>
       </c>
       <c r="E183" t="s">
-        <v>507</v>
+        <v>587</v>
       </c>
       <c r="G183" t="s">
-        <v>2267</v>
+        <v>2160</v>
       </c>
       <c r="H183" s="6"/>
-      <c r="J183" s="15" t="s">
-        <v>2034</v>
+      <c r="J183" s="23" t="s">
+        <v>588</v>
       </c>
       <c r="K183" t="s">
-        <v>506</v>
+        <v>586</v>
+      </c>
+      <c r="M183">
+        <v>22</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B184" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C184" t="s">
         <v>323</v>
       </c>
       <c r="D184" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E184" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G184" t="s">
         <v>2267</v>
       </c>
       <c r="H184" s="6"/>
       <c r="J184" s="15" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="K184" t="s">
-        <v>508</v>
+        <v>506</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1659</v>
+        <v>1625</v>
       </c>
       <c r="B185" t="s">
-        <v>627</v>
+        <v>1441</v>
       </c>
       <c r="C185" t="s">
         <v>323</v>
       </c>
       <c r="D185" t="s">
-        <v>628</v>
+        <v>1325</v>
       </c>
       <c r="E185" t="s">
-        <v>629</v>
+        <v>509</v>
       </c>
       <c r="G185" t="s">
-        <v>160</v>
+        <v>2267</v>
       </c>
       <c r="H185" s="6"/>
-      <c r="J185" t="s">
-        <v>630</v>
+      <c r="J185" s="15" t="s">
+        <v>2035</v>
       </c>
       <c r="K185" t="s">
-        <v>627</v>
+        <v>508</v>
+      </c>
+      <c r="M185">
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1657</v>
+        <v>1626</v>
       </c>
       <c r="B186" t="s">
-        <v>620</v>
+        <v>1442</v>
       </c>
       <c r="C186" t="s">
         <v>323</v>
       </c>
       <c r="D186" t="s">
-        <v>621</v>
+        <v>1326</v>
       </c>
       <c r="E186" t="s">
-        <v>622</v>
+        <v>511</v>
       </c>
       <c r="G186" t="s">
-        <v>160</v>
+        <v>2267</v>
       </c>
       <c r="H186" s="6"/>
-      <c r="J186" s="22" t="s">
-        <v>623</v>
+      <c r="J186" s="15" t="s">
+        <v>2215</v>
       </c>
       <c r="K186" t="s">
-        <v>620</v>
+        <v>510</v>
+      </c>
+      <c r="M186">
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1656</v>
+        <v>615</v>
       </c>
       <c r="B187" t="s">
-        <v>617</v>
+        <v>1446</v>
       </c>
       <c r="C187" t="s">
         <v>323</v>
       </c>
       <c r="D187" t="s">
-        <v>618</v>
+        <v>1350</v>
       </c>
       <c r="E187" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G187" t="s">
         <v>160</v>
       </c>
       <c r="H187" s="6"/>
       <c r="J187" s="15" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="K187" t="s">
-        <v>617</v>
+        <v>615</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="B188" t="s">
-        <v>1447</v>
+        <v>617</v>
       </c>
       <c r="C188" t="s">
         <v>323</v>
       </c>
       <c r="D188" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="E188" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="G188" t="s">
         <v>160</v>
       </c>
       <c r="H188" s="6"/>
       <c r="J188" s="15" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="K188" t="s">
-        <v>624</v>
+        <v>617</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="22" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B189" t="s">
-        <v>631</v>
+        <v>1447</v>
       </c>
       <c r="C189" t="s">
         <v>323</v>
       </c>
       <c r="D189" t="s">
-        <v>1351</v>
+        <v>625</v>
       </c>
       <c r="E189" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="G189" t="s">
         <v>160</v>
       </c>
       <c r="H189" s="6"/>
       <c r="J189" s="15" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="K189" t="s">
-        <v>631</v>
+        <v>624</v>
+      </c>
+      <c r="M189">
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>615</v>
+        <v>1660</v>
       </c>
       <c r="B190" t="s">
-        <v>1446</v>
+        <v>631</v>
       </c>
       <c r="C190" t="s">
         <v>323</v>
       </c>
       <c r="D190" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E190" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="G190" t="s">
         <v>160</v>
       </c>
       <c r="H190" s="6"/>
       <c r="J190" s="15" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="K190" t="s">
-        <v>615</v>
+        <v>631</v>
+      </c>
+      <c r="M190">
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1599</v>
+        <v>1657</v>
       </c>
       <c r="B191" t="s">
-        <v>435</v>
+        <v>620</v>
       </c>
       <c r="C191" t="s">
         <v>323</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>621</v>
       </c>
       <c r="E191" t="s">
-        <v>437</v>
+        <v>622</v>
       </c>
       <c r="G191" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="H191" s="6"/>
       <c r="J191" s="22" t="s">
-        <v>438</v>
+        <v>623</v>
       </c>
       <c r="K191" t="s">
-        <v>439</v>
+        <v>620</v>
+      </c>
+      <c r="M191">
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1600</v>
+        <v>1659</v>
       </c>
       <c r="B192" t="s">
-        <v>440</v>
+        <v>627</v>
       </c>
       <c r="C192" t="s">
         <v>323</v>
       </c>
       <c r="D192" t="s">
-        <v>1306</v>
+        <v>628</v>
       </c>
       <c r="E192" t="s">
-        <v>441</v>
+        <v>629</v>
       </c>
       <c r="G192" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="H192" s="6"/>
-      <c r="J192" s="22"/>
+      <c r="J192" s="22" t="s">
+        <v>630</v>
+      </c>
       <c r="K192" t="s">
-        <v>442</v>
+        <v>627</v>
+      </c>
+      <c r="M192">
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -14378,84 +14452,96 @@
       <c r="K193" t="s">
         <v>446</v>
       </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="B194" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="C194" t="s">
         <v>323</v>
       </c>
       <c r="D194" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="E194" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="G194" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H194" s="6"/>
-      <c r="J194" s="22" t="s">
-        <v>418</v>
-      </c>
+      <c r="J194" s="22"/>
       <c r="K194" t="s">
-        <v>419</v>
+        <v>442</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="B195" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="C195" t="s">
         <v>323</v>
       </c>
       <c r="D195" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="E195" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H195" s="6"/>
       <c r="J195" s="22" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="K195" t="s">
-        <v>408</v>
+        <v>439</v>
+      </c>
+      <c r="M195">
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="B196" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C196" t="s">
         <v>323</v>
       </c>
       <c r="D196" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="E196" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="G196" t="s">
         <v>112</v>
       </c>
       <c r="H196" s="6"/>
-      <c r="J196" s="22"/>
+      <c r="J196" s="22" t="s">
+        <v>411</v>
+      </c>
       <c r="K196" t="s">
-        <v>423</v>
+        <v>408</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -14484,49 +14570,53 @@
       <c r="K197" t="s">
         <v>1790</v>
       </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
     </row>
     <row r="198" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="B198" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C198" t="s">
         <v>323</v>
       </c>
       <c r="D198" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="E198" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="G198" t="s">
         <v>112</v>
       </c>
       <c r="H198" s="6"/>
-      <c r="J198" s="15" t="s">
-        <v>2041</v>
-      </c>
+      <c r="J198" s="23"/>
       <c r="K198" t="s">
-        <v>431</v>
+        <v>415</v>
+      </c>
+      <c r="M198">
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B199" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C199" t="s">
         <v>323</v>
       </c>
       <c r="D199" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="E199" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="G199" s="22" t="s">
         <v>112</v>
@@ -14534,1035 +14624,1108 @@
       <c r="H199" s="6"/>
       <c r="J199" s="22"/>
       <c r="K199" t="s">
-        <v>415</v>
+        <v>423</v>
+      </c>
+      <c r="M199">
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B200" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C200" t="s">
         <v>323</v>
       </c>
       <c r="D200" t="s">
-        <v>425</v>
+        <v>1272</v>
       </c>
       <c r="E200" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G200" s="22" t="s">
         <v>112</v>
       </c>
       <c r="H200" s="6"/>
-      <c r="J200" s="15" t="s">
-        <v>2042</v>
+      <c r="J200" s="23" t="s">
+        <v>418</v>
       </c>
       <c r="K200" t="s">
-        <v>427</v>
+        <v>419</v>
+      </c>
+      <c r="M200">
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:13" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>1883</v>
+        <v>1597</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>2119</v>
+        <v>428</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>323</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>987</v>
+        <v>429</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>988</v>
+        <v>430</v>
       </c>
       <c r="G201" s="22" t="s">
-        <v>1885</v>
-      </c>
-      <c r="J201" s="16" t="s">
-        <v>2043</v>
+        <v>112</v>
+      </c>
+      <c r="J201" s="15" t="s">
+        <v>2041</v>
       </c>
       <c r="K201" s="6" t="s">
-        <v>989</v>
+        <v>431</v>
       </c>
       <c r="M201" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="22" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="B202" t="s">
-        <v>1938</v>
+        <v>424</v>
       </c>
       <c r="C202" t="s">
         <v>323</v>
       </c>
       <c r="D202" t="s">
-        <v>1304</v>
+        <v>425</v>
       </c>
       <c r="E202" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="G202" s="22" t="s">
-        <v>1885</v>
+        <v>112</v>
       </c>
       <c r="H202" s="6"/>
       <c r="J202" s="15" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="K202" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="M202">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="11" t="s">
-        <v>1871</v>
+      <c r="A203" s="23" t="s">
+        <v>1883</v>
       </c>
       <c r="B203" t="s">
-        <v>1872</v>
+        <v>2119</v>
       </c>
       <c r="C203" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D203" t="s">
-        <v>1879</v>
+        <v>987</v>
       </c>
       <c r="E203" t="s">
-        <v>1880</v>
+        <v>988</v>
       </c>
       <c r="G203" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H203" s="6"/>
       <c r="J203" s="16" t="s">
-        <v>2045</v>
+        <v>2043</v>
+      </c>
+      <c r="K203" t="s">
+        <v>989</v>
       </c>
       <c r="M203">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1873</v>
+        <v>1591</v>
       </c>
       <c r="B204" t="s">
-        <v>1874</v>
+        <v>1938</v>
       </c>
       <c r="C204" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D204" t="s">
-        <v>1881</v>
+        <v>1304</v>
       </c>
       <c r="E204" t="s">
-        <v>1882</v>
+        <v>405</v>
       </c>
       <c r="G204" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H204" s="6"/>
-      <c r="J204" s="16" t="s">
-        <v>2046</v>
+      <c r="J204" s="15" t="s">
+        <v>2044</v>
+      </c>
+      <c r="K204" t="s">
+        <v>404</v>
       </c>
       <c r="M204">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>1877</v>
+      <c r="A205" s="11" t="s">
+        <v>1871</v>
       </c>
       <c r="B205" t="s">
-        <v>1878</v>
+        <v>1872</v>
       </c>
       <c r="C205" t="s">
         <v>538</v>
       </c>
       <c r="D205" t="s">
-        <v>1889</v>
+        <v>1879</v>
       </c>
       <c r="E205" t="s">
-        <v>1890</v>
+        <v>1880</v>
       </c>
       <c r="G205" t="s">
         <v>1885</v>
       </c>
       <c r="H205" s="6"/>
       <c r="J205" s="16" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="M205">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1894</v>
+        <v>1873</v>
       </c>
       <c r="B206" t="s">
-        <v>1893</v>
+        <v>1874</v>
       </c>
       <c r="C206" t="s">
         <v>538</v>
       </c>
       <c r="D206" t="s">
-        <v>1895</v>
+        <v>1881</v>
       </c>
       <c r="E206" t="s">
-        <v>1896</v>
+        <v>1882</v>
       </c>
       <c r="G206" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H206" s="6"/>
       <c r="J206" s="16" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="M206">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>2179</v>
+        <v>1877</v>
       </c>
       <c r="B207" t="s">
-        <v>2180</v>
+        <v>1878</v>
       </c>
       <c r="C207" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D207" t="s">
-        <v>2178</v>
+        <v>1889</v>
+      </c>
+      <c r="E207" t="s">
+        <v>1890</v>
       </c>
       <c r="G207" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H207" s="6"/>
-      <c r="J207" s="15" t="s">
-        <v>2233</v>
+      <c r="J207" s="16" t="s">
+        <v>2047</v>
       </c>
       <c r="M207">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1991</v>
+        <v>1894</v>
       </c>
       <c r="B208" t="s">
-        <v>1992</v>
+        <v>1893</v>
       </c>
       <c r="C208" t="s">
         <v>538</v>
       </c>
       <c r="D208" t="s">
-        <v>1993</v>
+        <v>1895</v>
+      </c>
+      <c r="E208" t="s">
+        <v>1896</v>
       </c>
       <c r="G208" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H208" s="6"/>
       <c r="J208" s="16" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="M208">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1875</v>
+        <v>2179</v>
       </c>
       <c r="B209" t="s">
-        <v>1876</v>
+        <v>2180</v>
       </c>
       <c r="C209" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D209" t="s">
-        <v>1891</v>
-      </c>
-      <c r="E209" t="s">
-        <v>1892</v>
+        <v>2178</v>
       </c>
       <c r="G209" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H209" s="6"/>
-      <c r="J209" s="16" t="s">
-        <v>2050</v>
+      <c r="J209" s="15" t="s">
+        <v>2233</v>
       </c>
       <c r="M209">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>2181</v>
+        <v>1991</v>
       </c>
       <c r="B210" t="s">
-        <v>2184</v>
+        <v>1992</v>
       </c>
       <c r="C210" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D210" t="s">
-        <v>2183</v>
+        <v>1993</v>
       </c>
       <c r="G210" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H210" s="6"/>
-      <c r="J210" s="15" t="s">
-        <v>2234</v>
+      <c r="J210" s="16" t="s">
+        <v>2049</v>
       </c>
       <c r="M210">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>2182</v>
+        <v>1875</v>
       </c>
       <c r="B211" t="s">
-        <v>2185</v>
+        <v>1876</v>
       </c>
       <c r="C211" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D211" t="s">
-        <v>2186</v>
+        <v>1891</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1892</v>
       </c>
       <c r="G211" s="22" t="s">
         <v>1885</v>
       </c>
       <c r="H211" s="6"/>
-      <c r="J211" s="15" t="s">
-        <v>2235</v>
+      <c r="J211" s="16" t="s">
+        <v>2050</v>
       </c>
       <c r="M211">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1606</v>
+        <v>2181</v>
       </c>
       <c r="B212" t="s">
-        <v>460</v>
+        <v>2184</v>
       </c>
       <c r="C212" t="s">
         <v>323</v>
       </c>
       <c r="D212" t="s">
-        <v>1308</v>
-      </c>
-      <c r="E212" t="s">
-        <v>461</v>
+        <v>2183</v>
       </c>
       <c r="G212" t="s">
-        <v>120</v>
+        <v>1885</v>
       </c>
       <c r="H212" s="6"/>
       <c r="J212" s="15" t="s">
-        <v>2056</v>
-      </c>
-      <c r="K212" t="s">
-        <v>462</v>
+        <v>2234</v>
+      </c>
+      <c r="M212">
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1605</v>
+        <v>2182</v>
       </c>
       <c r="B213" t="s">
-        <v>457</v>
+        <v>2185</v>
       </c>
       <c r="C213" t="s">
         <v>323</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="E213" t="s">
-        <v>458</v>
+        <v>2186</v>
       </c>
       <c r="G213" t="s">
-        <v>120</v>
+        <v>1885</v>
       </c>
       <c r="H213" s="6"/>
       <c r="J213" s="15" t="s">
-        <v>2057</v>
-      </c>
-      <c r="K213" t="s">
-        <v>459</v>
+        <v>2235</v>
+      </c>
+      <c r="M213">
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="B214" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C214" t="s">
         <v>323</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E214" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="G214" t="s">
         <v>120</v>
       </c>
       <c r="H214" s="6"/>
-      <c r="J214" s="15" t="s">
-        <v>2058</v>
+      <c r="J214" s="23" t="s">
+        <v>466</v>
       </c>
       <c r="K214" t="s">
-        <v>456</v>
+        <v>467</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="B215" t="s">
-        <v>463</v>
+        <v>1791</v>
       </c>
       <c r="C215" t="s">
         <v>323</v>
       </c>
       <c r="D215" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="E215" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="G215" s="6" t="s">
         <v>120</v>
       </c>
       <c r="H215" s="6"/>
-      <c r="J215" s="22" t="s">
-        <v>466</v>
+      <c r="J215" s="15" t="s">
+        <v>2059</v>
       </c>
       <c r="K215" t="s">
-        <v>467</v>
+        <v>449</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B216" t="s">
-        <v>1791</v>
+        <v>453</v>
       </c>
       <c r="C216" t="s">
         <v>323</v>
       </c>
       <c r="D216" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E216" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G216" t="s">
         <v>120</v>
       </c>
       <c r="H216" s="6"/>
       <c r="J216" s="15" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="K216" t="s">
-        <v>449</v>
+        <v>456</v>
+      </c>
+      <c r="M216">
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B217" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C217" t="s">
         <v>323</v>
       </c>
       <c r="D217" t="s">
-        <v>1307</v>
+        <v>1273</v>
       </c>
       <c r="E217" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="G217" t="s">
         <v>120</v>
       </c>
       <c r="H217" s="6"/>
-      <c r="J217" s="22"/>
+      <c r="J217" s="15" t="s">
+        <v>2057</v>
+      </c>
       <c r="K217" t="s">
-        <v>452</v>
+        <v>459</v>
+      </c>
+      <c r="M217">
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>2188</v>
+        <v>1606</v>
       </c>
       <c r="B218" t="s">
-        <v>2190</v>
+        <v>460</v>
       </c>
       <c r="C218" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D218" t="s">
-        <v>2191</v>
+        <v>1308</v>
+      </c>
+      <c r="E218" t="s">
+        <v>461</v>
       </c>
       <c r="G218" t="s">
-        <v>2245</v>
+        <v>120</v>
       </c>
       <c r="H218" s="6"/>
       <c r="J218" s="15" t="s">
-        <v>2237</v>
+        <v>2056</v>
+      </c>
+      <c r="K218" t="s">
+        <v>462</v>
+      </c>
+      <c r="M218">
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
       <c r="B219" t="s">
-        <v>1939</v>
+        <v>450</v>
       </c>
       <c r="C219" t="s">
         <v>323</v>
       </c>
       <c r="D219" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="E219" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="G219" s="22" t="s">
-        <v>2245</v>
+        <v>120</v>
       </c>
       <c r="H219" s="6"/>
-      <c r="J219" s="15" t="s">
-        <v>2060</v>
-      </c>
+      <c r="J219" s="23"/>
       <c r="K219" t="s">
-        <v>397</v>
+        <v>452</v>
+      </c>
+      <c r="M219">
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B220" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="C220" t="s">
         <v>538</v>
       </c>
       <c r="D220" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="G220" s="22" t="s">
         <v>2245</v>
       </c>
       <c r="H220" s="6"/>
       <c r="J220" s="15" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B221" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C221" t="s">
         <v>323</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E221" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G221" s="22" t="s">
         <v>2245</v>
       </c>
       <c r="H221" s="6"/>
       <c r="J221" s="15" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="K221" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="222" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1587</v>
+        <v>2187</v>
       </c>
       <c r="B222" t="s">
-        <v>392</v>
+        <v>2189</v>
       </c>
       <c r="C222" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D222" t="s">
-        <v>1299</v>
-      </c>
-      <c r="E222" t="s">
-        <v>393</v>
+        <v>2192</v>
       </c>
       <c r="G222" s="22" t="s">
         <v>2245</v>
       </c>
       <c r="H222" s="6"/>
-      <c r="K222" t="s">
-        <v>394</v>
+      <c r="J222" s="15" t="s">
+        <v>2236</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1669</v>
+        <v>1588</v>
       </c>
       <c r="B223" t="s">
-        <v>659</v>
+        <v>1940</v>
       </c>
       <c r="C223" t="s">
         <v>323</v>
       </c>
       <c r="D223" t="s">
-        <v>660</v>
+        <v>1301</v>
       </c>
       <c r="E223" t="s">
-        <v>661</v>
+        <v>396</v>
       </c>
       <c r="G223" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="H223" s="6"/>
-      <c r="J223" t="s">
-        <v>662</v>
+      <c r="J223" s="15" t="s">
+        <v>2061</v>
       </c>
       <c r="K223" t="s">
-        <v>659</v>
+        <v>395</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1674</v>
+        <v>1587</v>
       </c>
       <c r="B224" t="s">
-        <v>676</v>
+        <v>392</v>
       </c>
       <c r="C224" t="s">
         <v>323</v>
       </c>
       <c r="D224" t="s">
-        <v>1358</v>
+        <v>1299</v>
       </c>
       <c r="E224" t="s">
-        <v>677</v>
+        <v>393</v>
       </c>
       <c r="G224" s="22" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="H224" s="6"/>
-      <c r="J224" s="22" t="s">
-        <v>678</v>
-      </c>
+      <c r="J224" s="22"/>
       <c r="K224" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1670</v>
+        <v>655</v>
       </c>
       <c r="B225" t="s">
-        <v>663</v>
+        <v>1448</v>
       </c>
       <c r="C225" t="s">
         <v>323</v>
       </c>
       <c r="D225" t="s">
-        <v>664</v>
+        <v>1355</v>
       </c>
       <c r="E225" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="G225" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H225" s="6"/>
-      <c r="J225" s="15" t="s">
-        <v>2062</v>
-      </c>
+      <c r="J225" s="23"/>
       <c r="K225" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>655</v>
+        <v>1671</v>
       </c>
       <c r="B226" t="s">
-        <v>1448</v>
+        <v>666</v>
       </c>
       <c r="C226" t="s">
         <v>323</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E226" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="G226" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H226" s="6"/>
-      <c r="J226" s="22"/>
+      <c r="J226" s="22" t="s">
+        <v>668</v>
+      </c>
       <c r="K226" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+      <c r="M226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="B227" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C227" t="s">
         <v>323</v>
       </c>
       <c r="D227" t="s">
-        <v>1359</v>
+        <v>670</v>
       </c>
       <c r="E227" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="G227" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H227" s="6"/>
       <c r="J227" s="15" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="K227" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+      <c r="M227">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="B228" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="C228" t="s">
         <v>323</v>
       </c>
       <c r="D228" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="E228" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="G228" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H228" s="6"/>
       <c r="J228" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="K228" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+      <c r="M228">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="B229" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="C229" t="s">
         <v>323</v>
       </c>
       <c r="D229" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E229" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="G229" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H229" s="6"/>
-      <c r="J229" t="s">
-        <v>668</v>
+      <c r="J229" s="15" t="s">
+        <v>2066</v>
       </c>
       <c r="K229" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>657</v>
+      </c>
+      <c r="M229">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="B230" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="C230" t="s">
         <v>323</v>
       </c>
       <c r="D230" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="E230" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="G230" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H230" s="6"/>
-      <c r="J230" s="22" t="s">
-        <v>675</v>
+      <c r="J230" s="15" t="s">
+        <v>2062</v>
       </c>
       <c r="K230" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>663</v>
+      </c>
+      <c r="M230">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="B231" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="C231" t="s">
         <v>323</v>
       </c>
       <c r="D231" t="s">
-        <v>1360</v>
+        <v>660</v>
       </c>
       <c r="E231" t="s">
-        <v>1806</v>
+        <v>661</v>
       </c>
       <c r="G231" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H231" s="6"/>
-      <c r="J231" s="15" t="s">
-        <v>2064</v>
+      <c r="J231" s="23" t="s">
+        <v>662</v>
       </c>
       <c r="K231" t="s">
+        <v>659</v>
+      </c>
+      <c r="M231">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B232" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>1672</v>
-      </c>
-      <c r="B232" t="s">
-        <v>669</v>
-      </c>
       <c r="C232" t="s">
         <v>323</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>670</v>
+        <v>1360</v>
       </c>
       <c r="E232" t="s">
-        <v>671</v>
+        <v>1806</v>
       </c>
       <c r="G232" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H232" s="6"/>
       <c r="J232" s="15" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="K232" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>685</v>
+      </c>
+      <c r="M232">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1668</v>
+        <v>1676</v>
       </c>
       <c r="B233" t="s">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="C233" t="s">
         <v>323</v>
       </c>
       <c r="D233" s="21" t="s">
-        <v>1356</v>
+        <v>682</v>
       </c>
       <c r="E233" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="G233" s="22" t="s">
         <v>2255</v>
       </c>
       <c r="H233" s="6"/>
-      <c r="J233" s="15" t="s">
-        <v>2066</v>
+      <c r="J233" s="23" t="s">
+        <v>684</v>
       </c>
       <c r="K233" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>681</v>
+      </c>
+      <c r="M233">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1118</v>
+        <v>1675</v>
       </c>
       <c r="B234" t="s">
-        <v>1519</v>
+        <v>679</v>
       </c>
       <c r="C234" t="s">
         <v>323</v>
       </c>
       <c r="D234" t="s">
-        <v>1119</v>
+        <v>1359</v>
       </c>
       <c r="E234" t="s">
-        <v>1120</v>
+        <v>680</v>
       </c>
       <c r="G234" t="s">
-        <v>277</v>
+        <v>2255</v>
       </c>
       <c r="H234" s="6"/>
-      <c r="J234" t="s">
-        <v>1121</v>
+      <c r="J234" s="15" t="s">
+        <v>2063</v>
       </c>
       <c r="K234" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>679</v>
+      </c>
+      <c r="M234">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1556</v>
+        <v>1674</v>
       </c>
       <c r="B235" t="s">
-        <v>1126</v>
+        <v>676</v>
       </c>
       <c r="C235" t="s">
         <v>323</v>
       </c>
       <c r="D235" t="s">
-        <v>1127</v>
+        <v>1358</v>
       </c>
       <c r="E235" t="s">
-        <v>1128</v>
+        <v>677</v>
       </c>
       <c r="G235" t="s">
-        <v>277</v>
+        <v>2255</v>
       </c>
       <c r="H235" s="6"/>
-      <c r="J235" s="22"/>
+      <c r="J235" s="22" t="s">
+        <v>678</v>
+      </c>
       <c r="K235" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>676</v>
+      </c>
+      <c r="M235">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1100</v>
+        <v>1114</v>
       </c>
       <c r="B236" t="s">
-        <v>63</v>
+        <v>1518</v>
       </c>
       <c r="C236" t="s">
         <v>323</v>
       </c>
       <c r="D236" t="s">
-        <v>1421</v>
+        <v>1115</v>
       </c>
       <c r="E236" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="G236" t="s">
         <v>277</v>
       </c>
       <c r="H236" s="6"/>
-      <c r="J236" s="15" t="s">
-        <v>2067</v>
-      </c>
+      <c r="J236" s="23"/>
       <c r="K236" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="B237" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="C237" t="s">
         <v>323</v>
       </c>
       <c r="D237" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="E237" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="G237" t="s">
         <v>277</v>
       </c>
       <c r="H237" s="6"/>
-      <c r="J237" s="15" t="s">
-        <v>2068</v>
+      <c r="J237" s="23" t="s">
+        <v>1121</v>
       </c>
       <c r="K237" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1118</v>
+      </c>
+      <c r="M237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1555</v>
+        <v>1100</v>
       </c>
       <c r="B238" t="s">
-        <v>1124</v>
+        <v>63</v>
       </c>
       <c r="C238" t="s">
         <v>323</v>
       </c>
       <c r="D238" t="s">
-        <v>1812</v>
+        <v>1421</v>
       </c>
       <c r="E238" t="s">
-        <v>1813</v>
+        <v>1101</v>
       </c>
       <c r="G238" t="s">
         <v>277</v>
       </c>
       <c r="H238" s="6"/>
-      <c r="J238" t="s">
-        <v>1125</v>
+      <c r="J238" s="15" t="s">
+        <v>2067</v>
       </c>
       <c r="K238" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1100</v>
+      </c>
+      <c r="M238">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1554</v>
       </c>
@@ -15588,195 +15751,221 @@
       <c r="K239" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M239">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="B240" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C240" t="s">
         <v>323</v>
       </c>
       <c r="D240" t="s">
-        <v>1809</v>
+        <v>1108</v>
       </c>
       <c r="E240" t="s">
-        <v>1810</v>
+        <v>1109</v>
       </c>
       <c r="G240" t="s">
         <v>277</v>
       </c>
       <c r="H240" s="6"/>
-      <c r="J240" s="21" t="s">
-        <v>1113</v>
+      <c r="J240" s="15" t="s">
+        <v>2068</v>
       </c>
       <c r="K240" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1107</v>
+      </c>
+      <c r="M240">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1102</v>
+        <v>1555</v>
       </c>
       <c r="B241" t="s">
-        <v>1515</v>
+        <v>1124</v>
       </c>
       <c r="C241" t="s">
         <v>323</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>1103</v>
+        <v>1812</v>
       </c>
       <c r="E241" t="s">
-        <v>1104</v>
+        <v>1813</v>
       </c>
       <c r="G241" t="s">
         <v>277</v>
       </c>
       <c r="H241" s="6"/>
+      <c r="J241" t="s">
+        <v>1125</v>
+      </c>
       <c r="K241" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1124</v>
+      </c>
+      <c r="M241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B242" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C242" t="s">
         <v>323</v>
       </c>
       <c r="D242" t="s">
-        <v>1115</v>
+        <v>1809</v>
       </c>
       <c r="E242" t="s">
-        <v>1116</v>
+        <v>1810</v>
       </c>
       <c r="G242" t="s">
         <v>277</v>
       </c>
       <c r="H242" s="6"/>
-      <c r="J242" s="21"/>
+      <c r="J242" s="21" t="s">
+        <v>1113</v>
+      </c>
       <c r="K242" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="243" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1110</v>
+      </c>
+      <c r="M242">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1557</v>
+        <v>1102</v>
       </c>
       <c r="B243" t="s">
-        <v>1130</v>
+        <v>1515</v>
       </c>
       <c r="C243" t="s">
         <v>323</v>
       </c>
       <c r="D243" t="s">
-        <v>1131</v>
+        <v>1103</v>
       </c>
       <c r="E243" t="s">
-        <v>1132</v>
+        <v>1104</v>
       </c>
       <c r="G243" t="s">
         <v>277</v>
       </c>
       <c r="H243" s="6"/>
       <c r="K243" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1105</v>
+      </c>
+      <c r="M243">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1043</v>
+        <v>1556</v>
       </c>
       <c r="B244" t="s">
-        <v>1508</v>
+        <v>1126</v>
       </c>
       <c r="C244" t="s">
         <v>323</v>
       </c>
       <c r="D244" t="s">
-        <v>1044</v>
+        <v>1127</v>
       </c>
       <c r="E244" t="s">
-        <v>1045</v>
+        <v>1128</v>
       </c>
       <c r="G244" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H244" s="6"/>
       <c r="J244" s="9"/>
       <c r="K244" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1129</v>
+      </c>
+      <c r="M244">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>57</v>
+        <v>1557</v>
       </c>
       <c r="B245" t="s">
-        <v>1509</v>
+        <v>1130</v>
       </c>
       <c r="C245" t="s">
         <v>323</v>
       </c>
       <c r="D245" t="s">
-        <v>1047</v>
+        <v>1131</v>
       </c>
       <c r="E245" t="s">
-        <v>1048</v>
+        <v>1132</v>
       </c>
       <c r="G245" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H245" s="6"/>
       <c r="K245" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="246" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1133</v>
+      </c>
+      <c r="M245">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="B246" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C246" t="s">
         <v>323</v>
       </c>
       <c r="D246" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="E246" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="G246" t="s">
         <v>259</v>
       </c>
       <c r="H246" s="6"/>
       <c r="K246" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="247" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1054</v>
+        <v>57</v>
       </c>
       <c r="B247" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C247" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D247" s="9" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="E247" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="G247" t="s">
         <v>259</v>
@@ -15784,91 +15973,90 @@
       <c r="H247" s="6"/>
       <c r="J247" s="22"/>
       <c r="K247" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C248" t="s">
+        <v>323</v>
+      </c>
+      <c r="D248" s="21" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G248" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H248" s="6"/>
+      <c r="J248" s="23"/>
+      <c r="K248" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C249" t="s">
+        <v>538</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E249" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G249" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="H249" s="6"/>
+      <c r="J249" s="22"/>
+      <c r="K249" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
+    <row r="250" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
         <v>1058</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B250" t="s">
         <v>1059</v>
       </c>
-      <c r="C248" t="s">
-        <v>323</v>
-      </c>
-      <c r="D248" s="21" t="s">
+      <c r="C250" t="s">
+        <v>323</v>
+      </c>
+      <c r="D250" t="s">
         <v>1405</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E250" t="s">
         <v>1060</v>
-      </c>
-      <c r="G248" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H248" s="6"/>
-      <c r="J248" s="15" t="s">
-        <v>2067</v>
-      </c>
-      <c r="K248" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="249" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>1551</v>
-      </c>
-      <c r="B249" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C249" t="s">
-        <v>1829</v>
-      </c>
-      <c r="D249" t="s">
-        <v>1407</v>
-      </c>
-      <c r="E249" t="s">
-        <v>1065</v>
-      </c>
-      <c r="G249" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="H249" s="6"/>
-      <c r="J249" s="22" t="s">
-        <v>1066</v>
-      </c>
-      <c r="K249" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>1757</v>
-      </c>
-      <c r="B250" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C250" t="s">
-        <v>323</v>
-      </c>
-      <c r="D250" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E250" t="s">
-        <v>1062</v>
       </c>
       <c r="G250" s="20" t="s">
         <v>264</v>
       </c>
       <c r="H250" s="6"/>
-      <c r="J250" s="22" t="s">
-        <v>1063</v>
+      <c r="J250" s="15" t="s">
+        <v>2067</v>
       </c>
       <c r="K250" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="251" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1759</v>
       </c>
@@ -15894,463 +16082,514 @@
       <c r="K251" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1758</v>
+        <v>1769</v>
       </c>
       <c r="B252" t="s">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="C252" t="s">
         <v>323</v>
       </c>
       <c r="D252" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="E252" t="s">
-        <v>1068</v>
+        <v>1087</v>
       </c>
       <c r="G252" s="20" t="s">
         <v>264</v>
       </c>
       <c r="H252" s="6"/>
       <c r="J252" s="22" t="s">
-        <v>1069</v>
+        <v>1088</v>
       </c>
       <c r="K252" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="253" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+      <c r="M252">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1768</v>
+        <v>1757</v>
       </c>
       <c r="B253" t="s">
-        <v>1512</v>
+        <v>1061</v>
       </c>
       <c r="C253" t="s">
         <v>323</v>
       </c>
       <c r="D253" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E253" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="G253" s="20" t="s">
         <v>264</v>
       </c>
       <c r="H253" s="6"/>
       <c r="J253" s="22" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="K253" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="254" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1061</v>
+      </c>
+      <c r="M253">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1767</v>
+        <v>1551</v>
       </c>
       <c r="B254" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="C254" t="s">
-        <v>323</v>
+        <v>1829</v>
       </c>
       <c r="D254" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="E254" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="G254" s="20" t="s">
         <v>264</v>
       </c>
       <c r="H254" s="6"/>
-      <c r="J254" s="15" t="s">
-        <v>2071</v>
+      <c r="J254" s="23" t="s">
+        <v>1066</v>
       </c>
       <c r="K254" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="255" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1064</v>
+      </c>
+      <c r="M254">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="B255" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="C255" t="s">
         <v>323</v>
       </c>
       <c r="D255" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="E255" t="s">
-        <v>1083</v>
+        <v>1068</v>
       </c>
       <c r="G255" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H255" s="6"/>
-      <c r="J255" s="15" t="s">
-        <v>2072</v>
+      <c r="J255" s="23" t="s">
+        <v>1069</v>
       </c>
       <c r="K255" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="256" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1067</v>
+      </c>
+      <c r="M255">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1761</v>
+        <v>1768</v>
       </c>
       <c r="B256" t="s">
-        <v>1079</v>
+        <v>1512</v>
       </c>
       <c r="C256" t="s">
         <v>323</v>
       </c>
       <c r="D256" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="E256" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="G256" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H256" s="6"/>
       <c r="J256" s="22" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="K256" t="s">
-        <v>1079</v>
+        <v>1073</v>
+      </c>
+      <c r="M256">
+        <v>7</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="B257" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
       <c r="C257" t="s">
         <v>323</v>
       </c>
       <c r="D257" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="E257" t="s">
-        <v>1085</v>
+        <v>1072</v>
       </c>
       <c r="G257" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H257" s="6"/>
       <c r="J257" s="15" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="K257" t="s">
-        <v>1084</v>
+        <v>1071</v>
+      </c>
+      <c r="M257">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B258" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C258" t="s">
         <v>323</v>
       </c>
       <c r="D258" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="E258" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="G258" s="20" t="s">
         <v>268</v>
       </c>
       <c r="H258" s="6"/>
-      <c r="J258" s="22"/>
+      <c r="J258" s="22" t="s">
+        <v>1081</v>
+      </c>
       <c r="K258" t="s">
-        <v>1078</v>
+        <v>1079</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1769</v>
+        <v>1760</v>
       </c>
       <c r="B259" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="C259" t="s">
         <v>323</v>
       </c>
       <c r="D259" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="E259" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="G259" s="20" t="s">
         <v>268</v>
       </c>
       <c r="H259" s="6"/>
-      <c r="J259" s="22" t="s">
-        <v>1088</v>
-      </c>
+      <c r="J259" s="22"/>
       <c r="K259" t="s">
-        <v>1086</v>
+        <v>1078</v>
+      </c>
+      <c r="M259">
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1963</v>
+        <v>1763</v>
       </c>
       <c r="B260" t="s">
-        <v>1967</v>
+        <v>1084</v>
       </c>
       <c r="C260" t="s">
         <v>323</v>
       </c>
       <c r="D260" t="s">
-        <v>1971</v>
+        <v>1415</v>
       </c>
       <c r="E260" t="s">
-        <v>1975</v>
+        <v>1085</v>
       </c>
       <c r="G260" s="20" t="s">
-        <v>2249</v>
+        <v>268</v>
       </c>
       <c r="H260" s="6"/>
       <c r="J260" s="15" t="s">
-        <v>2216</v>
+        <v>2073</v>
+      </c>
+      <c r="K260" t="s">
+        <v>1084</v>
       </c>
       <c r="M260">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1964</v>
+        <v>1762</v>
       </c>
       <c r="B261" t="s">
-        <v>1968</v>
+        <v>1082</v>
       </c>
       <c r="C261" t="s">
         <v>323</v>
       </c>
       <c r="D261" t="s">
-        <v>1973</v>
+        <v>1413</v>
       </c>
       <c r="E261" t="s">
-        <v>1978</v>
+        <v>1083</v>
       </c>
       <c r="G261" s="22" t="s">
-        <v>2249</v>
+        <v>268</v>
       </c>
       <c r="H261" s="6"/>
-      <c r="J261" s="22"/>
+      <c r="J261" s="15" t="s">
+        <v>2072</v>
+      </c>
+      <c r="K261" t="s">
+        <v>1082</v>
+      </c>
       <c r="M261">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1966</v>
+        <v>729</v>
       </c>
       <c r="B262" t="s">
-        <v>1969</v>
+        <v>730</v>
       </c>
       <c r="C262" t="s">
         <v>323</v>
       </c>
       <c r="D262" t="s">
-        <v>1972</v>
+        <v>1815</v>
       </c>
       <c r="E262" t="s">
-        <v>1976</v>
+        <v>1816</v>
       </c>
       <c r="G262" s="22" t="s">
         <v>2249</v>
       </c>
       <c r="H262" s="6"/>
       <c r="J262" s="15" t="s">
-        <v>2218</v>
+        <v>2069</v>
+      </c>
+      <c r="K262" t="s">
+        <v>730</v>
       </c>
       <c r="M262">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B263" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C263" t="s">
         <v>323</v>
       </c>
       <c r="D263" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="E263" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="G263" s="22" t="s">
         <v>2249</v>
       </c>
       <c r="H263" s="6"/>
       <c r="J263" s="15" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="M263">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>2197</v>
+        <v>1964</v>
       </c>
       <c r="B264" t="s">
-        <v>2198</v>
+        <v>1968</v>
       </c>
       <c r="C264" t="s">
         <v>323</v>
       </c>
       <c r="D264" t="s">
-        <v>2202</v>
+        <v>1973</v>
+      </c>
+      <c r="E264" t="s">
+        <v>1978</v>
       </c>
       <c r="G264" s="22" t="s">
         <v>2249</v>
       </c>
       <c r="H264" s="6"/>
-      <c r="J264" s="15" t="s">
-        <v>2217</v>
-      </c>
+      <c r="J264" s="23"/>
       <c r="M264">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>2199</v>
+        <v>1966</v>
       </c>
       <c r="B265" t="s">
-        <v>2200</v>
+        <v>1969</v>
       </c>
       <c r="C265" t="s">
         <v>323</v>
       </c>
       <c r="D265" t="s">
-        <v>2201</v>
+        <v>1972</v>
+      </c>
+      <c r="E265" t="s">
+        <v>1976</v>
       </c>
       <c r="G265" s="22" t="s">
         <v>2249</v>
       </c>
       <c r="H265" s="6"/>
       <c r="J265" s="15" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="M265">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>729</v>
+        <v>1965</v>
       </c>
       <c r="B266" t="s">
-        <v>730</v>
+        <v>1970</v>
       </c>
       <c r="C266" t="s">
         <v>323</v>
       </c>
       <c r="D266" t="s">
-        <v>1815</v>
+        <v>1974</v>
       </c>
       <c r="E266" t="s">
-        <v>1816</v>
+        <v>1977</v>
       </c>
       <c r="G266" s="22" t="s">
         <v>2249</v>
       </c>
       <c r="H266" s="6"/>
       <c r="J266" s="15" t="s">
-        <v>2069</v>
-      </c>
-      <c r="K266" t="s">
-        <v>730</v>
+        <v>2220</v>
+      </c>
+      <c r="M266">
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1951</v>
+        <v>2197</v>
       </c>
       <c r="B267" t="s">
-        <v>1958</v>
+        <v>2198</v>
       </c>
       <c r="C267" t="s">
         <v>323</v>
       </c>
       <c r="D267" t="s">
-        <v>1986</v>
+        <v>2202</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="H267" s="6"/>
       <c r="J267" s="15" t="s">
-        <v>2221</v>
+        <v>2217</v>
+      </c>
+      <c r="M267">
+        <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1941</v>
+        <v>2199</v>
       </c>
       <c r="B268" t="s">
-        <v>1946</v>
+        <v>2200</v>
       </c>
       <c r="C268" t="s">
         <v>323</v>
       </c>
       <c r="D268" t="s">
-        <v>1981</v>
+        <v>2201</v>
       </c>
       <c r="G268" s="22" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="H268" s="6"/>
       <c r="J268" s="15" t="s">
-        <v>2105</v>
+        <v>2219</v>
+      </c>
+      <c r="M268">
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1961</v>
+        <v>1941</v>
       </c>
       <c r="B269" t="s">
-        <v>1962</v>
+        <v>1946</v>
       </c>
       <c r="C269" t="s">
         <v>323</v>
       </c>
       <c r="D269" t="s">
-        <v>1990</v>
+        <v>1981</v>
       </c>
       <c r="G269" s="22" t="s">
         <v>2251</v>
       </c>
       <c r="H269" s="6"/>
       <c r="J269" s="15" t="s">
-        <v>2224</v>
+        <v>2105</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -16373,106 +16612,121 @@
       <c r="J270" s="15" t="s">
         <v>2106</v>
       </c>
+      <c r="M270">
+        <v>2</v>
+      </c>
     </row>
     <row r="271" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="B271" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="C271" t="s">
         <v>323</v>
       </c>
       <c r="D271" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G271" s="22" t="s">
         <v>2251</v>
       </c>
       <c r="H271" s="6"/>
       <c r="J271" s="15" t="s">
-        <v>2223</v>
+        <v>2224</v>
+      </c>
+      <c r="M271">
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C272" t="s">
+        <v>323</v>
+      </c>
+      <c r="D272" t="s">
+        <v>1986</v>
+      </c>
+      <c r="G272" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H272" s="6"/>
+      <c r="J272" s="15" t="s">
+        <v>2221</v>
+      </c>
+      <c r="M272">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C273" t="s">
+        <v>323</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G273" s="22" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H273" s="6"/>
+      <c r="J273" s="15" t="s">
+        <v>2223</v>
+      </c>
+      <c r="M273">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
         <v>2154</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B274" t="s">
         <v>2156</v>
       </c>
-      <c r="C272" t="s">
-        <v>323</v>
-      </c>
-      <c r="D272" t="s">
+      <c r="C274" t="s">
+        <v>323</v>
+      </c>
+      <c r="D274" t="s">
         <v>2159</v>
       </c>
-      <c r="G272" t="s">
+      <c r="G274" t="s">
         <v>2266</v>
       </c>
-      <c r="H272" s="6"/>
-    </row>
-    <row r="273" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
+      <c r="H274" s="6"/>
+      <c r="J274" s="23"/>
+    </row>
+    <row r="275" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
         <v>2155</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B275" t="s">
         <v>2157</v>
       </c>
-      <c r="C273" t="s">
-        <v>323</v>
-      </c>
-      <c r="D273" t="s">
+      <c r="C275" t="s">
+        <v>323</v>
+      </c>
+      <c r="D275" t="s">
         <v>2158</v>
       </c>
-      <c r="G273" s="22" t="s">
+      <c r="G275" s="22" t="s">
         <v>2266</v>
-      </c>
-      <c r="H273" s="6"/>
-      <c r="J273" s="22"/>
-    </row>
-    <row r="274" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>2195</v>
-      </c>
-      <c r="B274" t="s">
-        <v>2196</v>
-      </c>
-      <c r="C274" t="s">
-        <v>323</v>
-      </c>
-      <c r="D274" t="s">
-        <v>1988</v>
-      </c>
-      <c r="G274" t="s">
-        <v>2252</v>
-      </c>
-      <c r="H274" s="6"/>
-      <c r="J274" s="15" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="275" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1959</v>
-      </c>
-      <c r="C275" t="s">
-        <v>323</v>
-      </c>
-      <c r="D275" t="s">
-        <v>1987</v>
-      </c>
-      <c r="G275" s="22" t="s">
-        <v>2252</v>
       </c>
       <c r="H275" s="6"/>
       <c r="J275" s="22"/>
     </row>
-    <row r="276" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1943</v>
       </c>
@@ -16492,8 +16746,11 @@
       <c r="J276" s="15" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1944</v>
       </c>
@@ -16513,367 +16770,368 @@
       <c r="J277" s="15" t="s">
         <v>2107</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1945</v>
+        <v>1952</v>
       </c>
       <c r="B278" t="s">
-        <v>1950</v>
+        <v>1959</v>
       </c>
       <c r="C278" t="s">
         <v>323</v>
       </c>
       <c r="D278" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="G278" s="22" t="s">
         <v>2252</v>
       </c>
       <c r="H278" s="6"/>
-      <c r="J278" s="15" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J278" s="23"/>
+      <c r="M278">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="B279" t="s">
-        <v>1957</v>
+        <v>1950</v>
       </c>
       <c r="C279" t="s">
         <v>323</v>
       </c>
       <c r="D279" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="G279" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="H279" s="6"/>
       <c r="J279" s="15" t="s">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2108</v>
+      </c>
+      <c r="M279">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1954</v>
+        <v>2195</v>
       </c>
       <c r="B280" t="s">
-        <v>1956</v>
+        <v>2196</v>
       </c>
       <c r="C280" t="s">
         <v>323</v>
       </c>
       <c r="D280" t="s">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="G280" s="22" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="15" t="s">
+        <v>2222</v>
+      </c>
+      <c r="M280">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C281" t="s">
+        <v>323</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1980</v>
+      </c>
+      <c r="G281" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H281" s="6"/>
+      <c r="J281" s="15" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C282" t="s">
+        <v>323</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1979</v>
+      </c>
+      <c r="G282" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H282" s="6"/>
+      <c r="J282" s="15" t="s">
         <v>2103</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
+    <row r="283" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
         <v>1214</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B283" t="s">
         <v>1538</v>
       </c>
-      <c r="C281" t="s">
-        <v>323</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="C283" t="s">
+        <v>323</v>
+      </c>
+      <c r="D283" t="s">
         <v>1215</v>
       </c>
-      <c r="E281" t="s">
+      <c r="E283" t="s">
         <v>1216</v>
-      </c>
-      <c r="G281" t="s">
-        <v>299</v>
-      </c>
-      <c r="H281" s="6"/>
-      <c r="J281" s="21"/>
-      <c r="K281" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B282" t="s">
-        <v>1535</v>
-      </c>
-      <c r="C282" t="s">
-        <v>323</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G282" t="s">
-        <v>299</v>
-      </c>
-      <c r="H282" s="6"/>
-      <c r="J282" s="22"/>
-      <c r="K282" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C283" t="s">
-        <v>323</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1211</v>
-      </c>
-      <c r="E283" t="s">
-        <v>1212</v>
       </c>
       <c r="G283" t="s">
         <v>299</v>
       </c>
       <c r="H283" s="6"/>
-      <c r="J283" s="16" t="s">
-        <v>2074</v>
-      </c>
+      <c r="J283" s="23"/>
       <c r="K283" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="B284" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C284" t="s">
         <v>323</v>
       </c>
       <c r="D284" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E284" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="G284" t="s">
         <v>299</v>
       </c>
       <c r="H284" s="6"/>
       <c r="K284" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C285" t="s">
+        <v>323</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E285" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G285" t="s">
+        <v>299</v>
+      </c>
+      <c r="H285" s="6"/>
+      <c r="J285" s="16" t="s">
+        <v>2074</v>
+      </c>
+      <c r="K285" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C286" t="s">
+        <v>323</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G286" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="H286" s="6"/>
+      <c r="K286" t="s">
         <v>1209</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
+    <row r="287" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
         <v>725</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B287" t="s">
         <v>726</v>
       </c>
-      <c r="C285" t="s">
-        <v>323</v>
-      </c>
-      <c r="D285" t="s">
+      <c r="C287" t="s">
+        <v>323</v>
+      </c>
+      <c r="D287" t="s">
         <v>1373</v>
       </c>
-      <c r="E285" t="s">
+      <c r="E287" t="s">
         <v>727</v>
-      </c>
-      <c r="G285" t="s">
-        <v>2257</v>
-      </c>
-      <c r="H285" s="6"/>
-      <c r="J285" t="s">
-        <v>728</v>
-      </c>
-      <c r="K285" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>1686</v>
-      </c>
-      <c r="B286" t="s">
-        <v>714</v>
-      </c>
-      <c r="C286" t="s">
-        <v>323</v>
-      </c>
-      <c r="D286" t="s">
-        <v>1370</v>
-      </c>
-      <c r="E286" t="s">
-        <v>715</v>
-      </c>
-      <c r="G286" s="22" t="s">
-        <v>2257</v>
-      </c>
-      <c r="H286" s="6"/>
-      <c r="J286" t="s">
-        <v>716</v>
-      </c>
-      <c r="K286" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>721</v>
-      </c>
-      <c r="B287" t="s">
-        <v>1453</v>
-      </c>
-      <c r="C287" t="s">
-        <v>323</v>
-      </c>
-      <c r="D287" t="s">
-        <v>1372</v>
-      </c>
-      <c r="E287" t="s">
-        <v>723</v>
       </c>
       <c r="G287" s="22" t="s">
         <v>2257</v>
       </c>
       <c r="H287" s="6"/>
       <c r="J287" s="21" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="K287" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>717</v>
+        <v>1686</v>
       </c>
       <c r="B288" t="s">
-        <v>1452</v>
+        <v>714</v>
       </c>
       <c r="C288" t="s">
         <v>323</v>
       </c>
       <c r="D288" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E288" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G288" s="22" t="s">
         <v>2257</v>
       </c>
       <c r="H288" s="6"/>
       <c r="J288" t="s">
+        <v>716</v>
+      </c>
+      <c r="K288" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>721</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C289" t="s">
+        <v>323</v>
+      </c>
+      <c r="D289" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E289" t="s">
+        <v>723</v>
+      </c>
+      <c r="G289" s="17" t="s">
+        <v>2257</v>
+      </c>
+      <c r="H289" s="6"/>
+      <c r="J289" s="21" t="s">
+        <v>724</v>
+      </c>
+      <c r="K289" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C290" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D290" s="23" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="G290" s="17" t="s">
+        <v>2257</v>
+      </c>
+      <c r="J290" s="21" t="s">
         <v>720</v>
       </c>
-      <c r="K288" t="s">
+      <c r="K290" s="12" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
+    <row r="291" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
         <v>1766</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B291" t="s">
         <v>949</v>
       </c>
-      <c r="C289" t="s">
+      <c r="C291" t="s">
         <v>538</v>
       </c>
-      <c r="D289" s="22" t="s">
+      <c r="D291" t="s">
         <v>946</v>
       </c>
-      <c r="E289" t="s">
+      <c r="E291" t="s">
         <v>947</v>
-      </c>
-      <c r="G289" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="H289" s="6"/>
-      <c r="J289" s="21"/>
-      <c r="K289" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11" s="12" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="12" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B290" s="12" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C290" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="D290" s="5" t="s">
-        <v>1401</v>
-      </c>
-      <c r="E290" s="12" t="s">
-        <v>1828</v>
-      </c>
-      <c r="G290" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="J290" s="21"/>
-      <c r="K290" s="12" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>1756</v>
-      </c>
-      <c r="B291" t="s">
-        <v>940</v>
-      </c>
-      <c r="C291" t="s">
-        <v>323</v>
-      </c>
-      <c r="D291" t="s">
-        <v>941</v>
-      </c>
-      <c r="E291" t="s">
-        <v>942</v>
       </c>
       <c r="G291" s="17" t="s">
         <v>235</v>
       </c>
       <c r="H291" s="6"/>
       <c r="K291" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>945</v>
+        <v>1826</v>
       </c>
       <c r="B292" t="s">
-        <v>944</v>
+        <v>1827</v>
       </c>
       <c r="C292" t="s">
-        <v>323</v>
-      </c>
-      <c r="D292" t="s">
-        <v>1400</v>
+        <v>538</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>1401</v>
       </c>
       <c r="E292" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="G292" s="17" t="s">
         <v>235</v>
@@ -16881,91 +17139,89 @@
       <c r="H292" s="6"/>
       <c r="J292" s="22"/>
       <c r="K292" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B293" t="s">
+        <v>940</v>
+      </c>
+      <c r="C293" t="s">
+        <v>323</v>
+      </c>
+      <c r="D293" t="s">
+        <v>941</v>
+      </c>
+      <c r="E293" t="s">
+        <v>942</v>
+      </c>
+      <c r="G293" t="s">
+        <v>235</v>
+      </c>
+      <c r="H293" s="6"/>
+      <c r="J293" s="23"/>
+      <c r="K293" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
         <v>945</v>
       </c>
-    </row>
-    <row r="293" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
+      <c r="B294" t="s">
+        <v>944</v>
+      </c>
+      <c r="C294" t="s">
+        <v>323</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1825</v>
+      </c>
+      <c r="G294" t="s">
+        <v>235</v>
+      </c>
+      <c r="H294" s="6"/>
+      <c r="K294" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
         <v>1661</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B295" t="s">
         <v>633</v>
       </c>
-      <c r="C293" t="s">
-        <v>323</v>
-      </c>
-      <c r="D293" t="s">
+      <c r="C295" t="s">
+        <v>323</v>
+      </c>
+      <c r="D295" t="s">
         <v>634</v>
       </c>
-      <c r="E293" t="s">
+      <c r="E295" t="s">
         <v>635</v>
-      </c>
-      <c r="G293" t="s">
-        <v>165</v>
-      </c>
-      <c r="H293" s="6"/>
-      <c r="J293" s="15" t="s">
-        <v>2075</v>
-      </c>
-      <c r="K293" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>1664</v>
-      </c>
-      <c r="B294" t="s">
-        <v>641</v>
-      </c>
-      <c r="C294" t="s">
-        <v>538</v>
-      </c>
-      <c r="D294" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E294" t="s">
-        <v>642</v>
-      </c>
-      <c r="G294" t="s">
-        <v>165</v>
-      </c>
-      <c r="H294" s="6"/>
-      <c r="J294" t="s">
-        <v>643</v>
-      </c>
-      <c r="K294" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B295" t="s">
-        <v>647</v>
-      </c>
-      <c r="C295" t="s">
-        <v>323</v>
-      </c>
-      <c r="D295" t="s">
-        <v>648</v>
-      </c>
-      <c r="E295" t="s">
-        <v>649</v>
       </c>
       <c r="G295" t="s">
         <v>165</v>
       </c>
       <c r="H295" s="6"/>
-      <c r="J295" t="s">
-        <v>650</v>
+      <c r="J295" s="15" t="s">
+        <v>2075</v>
       </c>
       <c r="K295" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="17" t="s">
         <v>1662</v>
       </c>
@@ -16990,8 +17246,11 @@
       <c r="K296" s="17" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="297" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M296" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1663</v>
       </c>
@@ -17017,403 +17276,431 @@
       <c r="K297" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="298" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M297">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B298" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C298" t="s">
         <v>323</v>
       </c>
       <c r="D298" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="E298" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="G298" t="s">
         <v>165</v>
       </c>
       <c r="H298" s="6"/>
-      <c r="J298" s="22"/>
+      <c r="J298" s="16" t="s">
+        <v>2077</v>
+      </c>
       <c r="K298" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="M298">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B299" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C299" t="s">
         <v>323</v>
       </c>
       <c r="D299" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E299" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="G299" t="s">
         <v>165</v>
       </c>
       <c r="H299" s="6"/>
-      <c r="J299" s="16" t="s">
-        <v>2077</v>
+      <c r="J299" s="23" t="s">
+        <v>650</v>
       </c>
       <c r="K299" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="300" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+      <c r="M299">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>1679</v>
+        <v>1667</v>
       </c>
       <c r="B300" t="s">
-        <v>694</v>
+        <v>651</v>
       </c>
       <c r="C300" t="s">
         <v>323</v>
       </c>
       <c r="D300" t="s">
-        <v>1804</v>
+        <v>652</v>
       </c>
       <c r="E300" t="s">
-        <v>1805</v>
+        <v>653</v>
       </c>
       <c r="G300" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H300" s="6"/>
-      <c r="J300" t="s">
-        <v>695</v>
-      </c>
       <c r="K300" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="301" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+      <c r="M300">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>1680</v>
+        <v>1664</v>
       </c>
       <c r="B301" t="s">
-        <v>1449</v>
+        <v>641</v>
       </c>
       <c r="C301" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D301" t="s">
-        <v>1364</v>
+        <v>1354</v>
       </c>
       <c r="E301" t="s">
-        <v>697</v>
+        <v>642</v>
       </c>
       <c r="G301" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H301" s="6"/>
       <c r="J301" t="s">
-        <v>698</v>
+        <v>643</v>
       </c>
       <c r="K301" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="302" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+      <c r="M301">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>1838</v>
+        <v>1679</v>
       </c>
       <c r="B302" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="C302" t="s">
         <v>323</v>
       </c>
       <c r="D302" t="s">
-        <v>1361</v>
+        <v>1804</v>
       </c>
       <c r="E302" t="s">
-        <v>687</v>
+        <v>1805</v>
       </c>
       <c r="G302" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H302" s="6"/>
       <c r="J302" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="K302" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>694</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="B303" t="s">
-        <v>691</v>
+        <v>1449</v>
       </c>
       <c r="C303" t="s">
         <v>323</v>
       </c>
       <c r="D303" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E303" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="G303" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H303" s="6"/>
       <c r="J303" s="22" t="s">
+        <v>698</v>
+      </c>
+      <c r="K303" t="s">
+        <v>696</v>
+      </c>
+      <c r="M303">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B304" t="s">
+        <v>686</v>
+      </c>
+      <c r="C304" t="s">
+        <v>323</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E304" t="s">
+        <v>687</v>
+      </c>
+      <c r="G304" t="s">
+        <v>174</v>
+      </c>
+      <c r="H304" s="6"/>
+      <c r="J304" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="K304" t="s">
+        <v>686</v>
+      </c>
+      <c r="M304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B305" t="s">
+        <v>691</v>
+      </c>
+      <c r="C305" t="s">
+        <v>323</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E305" t="s">
+        <v>692</v>
+      </c>
+      <c r="G305" t="s">
+        <v>174</v>
+      </c>
+      <c r="H305" s="6"/>
+      <c r="J305" s="23" t="s">
         <v>693</v>
       </c>
-      <c r="K303" t="s">
+      <c r="K305" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="304" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
+      <c r="M305">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
         <v>1225</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B306" t="s">
         <v>1540</v>
       </c>
-      <c r="C304" t="s">
-        <v>323</v>
-      </c>
-      <c r="D304" t="s">
+      <c r="C306" t="s">
+        <v>323</v>
+      </c>
+      <c r="D306" t="s">
         <v>1362</v>
       </c>
-      <c r="E304" t="s">
+      <c r="E306" t="s">
         <v>690</v>
       </c>
-      <c r="G304" t="s">
+      <c r="G306" t="s">
         <v>1833</v>
       </c>
-      <c r="H304" s="6"/>
-      <c r="J304" s="15" t="s">
+      <c r="H306" s="6"/>
+      <c r="J306" s="15" t="s">
         <v>2078</v>
       </c>
-      <c r="K304" t="s">
+      <c r="K306" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="305" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
+      <c r="M306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
         <v>996</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B307" t="s">
         <v>1496</v>
       </c>
-      <c r="C305" t="s">
-        <v>323</v>
-      </c>
-      <c r="D305" t="s">
+      <c r="C307" t="s">
+        <v>323</v>
+      </c>
+      <c r="D307" t="s">
         <v>997</v>
       </c>
-      <c r="E305" t="s">
+      <c r="E307" t="s">
         <v>998</v>
       </c>
-      <c r="G305" t="s">
+      <c r="G307" t="s">
         <v>246</v>
-      </c>
-      <c r="H305" s="6"/>
-      <c r="J305" s="15" t="s">
-        <v>2086</v>
-      </c>
-      <c r="K305" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>993</v>
-      </c>
-      <c r="B306" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C306" t="s">
-        <v>323</v>
-      </c>
-      <c r="D306" t="s">
-        <v>994</v>
-      </c>
-      <c r="E306" t="s">
-        <v>995</v>
-      </c>
-      <c r="G306" t="s">
-        <v>1780</v>
-      </c>
-      <c r="H306" s="6"/>
-      <c r="J306" s="22"/>
-      <c r="K306" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B307" t="s">
-        <v>2123</v>
-      </c>
-      <c r="C307" t="s">
-        <v>323</v>
-      </c>
-      <c r="D307" t="s">
-        <v>2124</v>
-      </c>
-      <c r="E307" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G307" t="s">
-        <v>1780</v>
       </c>
       <c r="H307" s="6"/>
       <c r="J307" s="15" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2086</v>
+      </c>
+      <c r="K307" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>1771</v>
+        <v>993</v>
       </c>
       <c r="B308" t="s">
-        <v>1772</v>
+        <v>1495</v>
       </c>
       <c r="C308" t="s">
         <v>323</v>
       </c>
       <c r="D308" t="s">
-        <v>1775</v>
+        <v>994</v>
       </c>
       <c r="E308" t="s">
-        <v>1776</v>
+        <v>995</v>
       </c>
       <c r="G308" t="s">
         <v>1780</v>
       </c>
       <c r="H308" s="6"/>
       <c r="K308" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B309" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C309" t="s">
+        <v>323</v>
+      </c>
+      <c r="D309" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E309" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H309" s="6"/>
+      <c r="J309" s="15" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C310" t="s">
+        <v>323</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G310" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H310" s="6"/>
+      <c r="K310" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
+    <row r="311" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
         <v>1586</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B311" t="s">
         <v>389</v>
       </c>
-      <c r="C309" t="s">
-        <v>323</v>
-      </c>
-      <c r="D309" t="s">
+      <c r="C311" t="s">
+        <v>323</v>
+      </c>
+      <c r="D311" t="s">
         <v>1298</v>
       </c>
-      <c r="E309" t="s">
+      <c r="E311" t="s">
         <v>390</v>
       </c>
-      <c r="G309" t="s">
+      <c r="G311" t="s">
         <v>97</v>
-      </c>
-      <c r="H309" s="6"/>
-      <c r="J309" t="s">
-        <v>391</v>
-      </c>
-      <c r="K309" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B310" t="s">
-        <v>386</v>
-      </c>
-      <c r="C310" t="s">
-        <v>323</v>
-      </c>
-      <c r="D310" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E310" t="s">
-        <v>387</v>
-      </c>
-      <c r="G310" t="s">
-        <v>97</v>
-      </c>
-      <c r="H310" s="6"/>
-      <c r="J310" t="s">
-        <v>388</v>
-      </c>
-      <c r="K310" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>1770</v>
-      </c>
-      <c r="B311" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C311" t="s">
-        <v>323</v>
-      </c>
-      <c r="D311" t="s">
-        <v>1419</v>
-      </c>
-      <c r="E311" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G311" t="s">
-        <v>2260</v>
       </c>
       <c r="H311" s="6"/>
       <c r="J311" s="21" t="s">
-        <v>1096</v>
+        <v>391</v>
       </c>
       <c r="K311" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>1553</v>
+        <v>1585</v>
       </c>
       <c r="B312" t="s">
-        <v>1514</v>
+        <v>386</v>
       </c>
       <c r="C312" t="s">
         <v>323</v>
       </c>
       <c r="D312" t="s">
-        <v>1420</v>
+        <v>1297</v>
       </c>
       <c r="E312" t="s">
-        <v>1098</v>
+        <v>387</v>
       </c>
       <c r="G312" s="22" t="s">
-        <v>2260</v>
+        <v>97</v>
       </c>
       <c r="H312" s="6"/>
       <c r="J312" s="22" t="s">
-        <v>1099</v>
+        <v>388</v>
       </c>
       <c r="K312" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1552</v>
       </c>
@@ -17439,113 +17726,128 @@
       <c r="K313" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="314" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="B314" t="s">
-        <v>1513</v>
+        <v>1094</v>
       </c>
       <c r="C314" t="s">
         <v>323</v>
       </c>
       <c r="D314" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="E314" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="G314" s="22" t="s">
         <v>2260</v>
       </c>
       <c r="H314" s="6"/>
       <c r="J314" s="21" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K314" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M314">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C315" t="s">
+        <v>323</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E315" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G315" s="9" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J315" t="s">
         <v>1093</v>
       </c>
-      <c r="K314" t="s">
+      <c r="K315" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
+      <c r="M315">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C316" t="s">
+        <v>323</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E316" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G316" s="22" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J316" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K316" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M316">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
         <v>1618</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B317" t="s">
         <v>1435</v>
       </c>
-      <c r="C315" t="s">
-        <v>323</v>
-      </c>
-      <c r="D315" t="s">
+      <c r="C317" t="s">
+        <v>323</v>
+      </c>
+      <c r="D317" s="9" t="s">
         <v>1318</v>
       </c>
-      <c r="E315" t="s">
+      <c r="E317" t="s">
         <v>493</v>
-      </c>
-      <c r="G315" s="9" t="s">
-        <v>2263</v>
-      </c>
-      <c r="J315" t="s">
-        <v>494</v>
-      </c>
-      <c r="K315" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>1615</v>
-      </c>
-      <c r="B316" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C316" t="s">
-        <v>323</v>
-      </c>
-      <c r="D316" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E316" t="s">
-        <v>486</v>
-      </c>
-      <c r="G316" s="22" t="s">
-        <v>2263</v>
-      </c>
-      <c r="J316" s="22" t="s">
-        <v>487</v>
-      </c>
-      <c r="K316" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B317" t="s">
-        <v>1431</v>
-      </c>
-      <c r="C317" t="s">
-        <v>323</v>
-      </c>
-      <c r="D317" s="9" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E317" t="s">
-        <v>1800</v>
       </c>
       <c r="G317" s="22" t="s">
         <v>2263</v>
       </c>
-      <c r="J317" s="15" t="s">
-        <v>2088</v>
+      <c r="J317" s="23" t="s">
+        <v>494</v>
       </c>
       <c r="K317" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="M317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1617</v>
       </c>
@@ -17570,83 +17872,98 @@
       <c r="K318" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="B319" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C319" t="s">
         <v>323</v>
       </c>
       <c r="D319" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E319" t="s">
-        <v>489</v>
+        <v>1800</v>
       </c>
       <c r="G319" s="22" t="s">
         <v>2263</v>
       </c>
-      <c r="J319" s="16" t="s">
+      <c r="J319" s="15" t="s">
+        <v>2088</v>
+      </c>
+      <c r="K319" t="s">
+        <v>484</v>
+      </c>
+      <c r="M319">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C320" t="s">
+        <v>323</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E320" t="s">
+        <v>486</v>
+      </c>
+      <c r="G320" s="9" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J320" t="s">
+        <v>487</v>
+      </c>
+      <c r="K320" t="s">
+        <v>485</v>
+      </c>
+      <c r="M320">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C321" t="s">
+        <v>323</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E321" t="s">
+        <v>489</v>
+      </c>
+      <c r="G321" s="22" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J321" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="K319" t="s">
+      <c r="K321" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>1610</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C320" t="s">
-        <v>323</v>
-      </c>
-      <c r="D320" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E320" t="s">
-        <v>474</v>
-      </c>
-      <c r="G320" s="9" t="s">
-        <v>2262</v>
-      </c>
-      <c r="K320" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C321" t="s">
-        <v>323</v>
-      </c>
-      <c r="D321" t="s">
-        <v>1312</v>
-      </c>
-      <c r="E321" t="s">
-        <v>482</v>
-      </c>
-      <c r="G321" s="22" t="s">
-        <v>2262</v>
-      </c>
-      <c r="J321" t="s">
-        <v>483</v>
-      </c>
-      <c r="K321" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M321">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="9" t="s">
         <v>1612</v>
       </c>
@@ -17671,235 +17988,267 @@
       <c r="K322" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B323" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C323" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D323" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E323" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G323" s="22" t="s">
         <v>2262</v>
       </c>
       <c r="J323" s="22" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="K323" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+      <c r="M323">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B324" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C324" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D324" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E324" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G324" s="22" t="s">
         <v>2262</v>
       </c>
-      <c r="J324" s="16" t="s">
-        <v>2091</v>
-      </c>
+      <c r="J324" s="23"/>
       <c r="K324" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+        <v>475</v>
+      </c>
+      <c r="M324">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" s="9" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B325" s="9" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C325" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D325" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E325" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G325" s="22" t="s">
         <v>2262</v>
       </c>
       <c r="J325" s="22" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K325" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+      <c r="M325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>1765</v>
+        <v>1611</v>
       </c>
       <c r="B326" t="s">
-        <v>961</v>
+        <v>1428</v>
       </c>
       <c r="C326" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D326" t="s">
-        <v>1402</v>
+        <v>1310</v>
       </c>
       <c r="E326" t="s">
-        <v>962</v>
+        <v>477</v>
       </c>
       <c r="G326" s="9" t="s">
-        <v>2259</v>
-      </c>
-      <c r="J326" s="15" t="s">
-        <v>2092</v>
+        <v>2262</v>
+      </c>
+      <c r="J326" s="16" t="s">
+        <v>2091</v>
       </c>
       <c r="K326" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+      <c r="M326">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>977</v>
+        <v>1613</v>
       </c>
       <c r="B327" t="s">
-        <v>1493</v>
+        <v>1430</v>
       </c>
       <c r="C327" t="s">
         <v>323</v>
       </c>
       <c r="D327" t="s">
-        <v>978</v>
+        <v>1312</v>
       </c>
       <c r="E327" t="s">
-        <v>979</v>
+        <v>482</v>
       </c>
       <c r="G327" s="22" t="s">
-        <v>2259</v>
-      </c>
-      <c r="J327" s="22"/>
+        <v>2262</v>
+      </c>
+      <c r="J327" s="22" t="s">
+        <v>483</v>
+      </c>
       <c r="K327" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+      <c r="M327">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>1994</v>
+        <v>104</v>
       </c>
       <c r="B328" t="s">
-        <v>1995</v>
+        <v>951</v>
       </c>
       <c r="C328" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D328" t="s">
-        <v>1996</v>
+        <v>952</v>
       </c>
       <c r="E328" t="s">
-        <v>1997</v>
+        <v>953</v>
       </c>
       <c r="G328" s="22" t="s">
         <v>2259</v>
       </c>
-      <c r="J328" s="16" t="s">
-        <v>2093</v>
+      <c r="J328" s="23" t="s">
+        <v>954</v>
       </c>
       <c r="K328" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+        <v>955</v>
+      </c>
+      <c r="M328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="s">
-        <v>963</v>
+        <v>1994</v>
       </c>
       <c r="B329" t="s">
-        <v>1489</v>
+        <v>1995</v>
       </c>
       <c r="C329" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D329" t="s">
-        <v>1403</v>
+        <v>1996</v>
       </c>
       <c r="E329" t="s">
-        <v>964</v>
+        <v>1997</v>
       </c>
       <c r="G329" s="22" t="s">
         <v>2259</v>
       </c>
-      <c r="J329" s="9"/>
+      <c r="J329" s="16" t="s">
+        <v>2093</v>
+      </c>
       <c r="K329" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2121</v>
+      </c>
+      <c r="M329">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="s">
-        <v>104</v>
+        <v>1765</v>
       </c>
       <c r="B330" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="C330" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D330" t="s">
-        <v>952</v>
+        <v>1402</v>
       </c>
       <c r="E330" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="G330" s="22" t="s">
         <v>2259</v>
       </c>
-      <c r="J330" s="21" t="s">
-        <v>954</v>
+      <c r="J330" s="15" t="s">
+        <v>2092</v>
       </c>
       <c r="K330" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+        <v>961</v>
+      </c>
+      <c r="M330">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="B331" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D331" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E331" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="G331" s="22" t="s">
         <v>2259</v>
       </c>
       <c r="K331" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+        <v>980</v>
+      </c>
+      <c r="M331">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="s">
         <v>990</v>
       </c>
@@ -17924,8 +18273,11 @@
       <c r="K332" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M332">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" s="9" t="s">
         <v>1198</v>
       </c>
@@ -17948,7 +18300,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="334" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="12" t="s">
         <v>1039</v>
       </c>
@@ -17972,7 +18324,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="335" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="18" t="s">
         <v>1024</v>
       </c>
@@ -17996,7 +18348,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="336" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="12" t="s">
         <v>1035</v>
       </c>
@@ -18019,7 +18371,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="337" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="12" t="s">
         <v>12</v>
       </c>
@@ -18043,7 +18395,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="338" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="18" t="s">
         <v>1031</v>
       </c>
@@ -18067,314 +18419,351 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="339" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="12" t="s">
-        <v>1630</v>
+        <v>28</v>
       </c>
       <c r="B339" s="12" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="C339" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="E339" s="12" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="G339" s="12" t="s">
         <v>2254</v>
       </c>
-      <c r="J339" s="15" t="s">
-        <v>2094</v>
-      </c>
+      <c r="J339" s="23"/>
       <c r="K339" s="12" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+      <c r="M339" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="12" t="s">
-        <v>28</v>
+        <v>1627</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C340" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D340" s="12" t="s">
-        <v>513</v>
+        <v>1549</v>
       </c>
       <c r="E340" s="12" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G340" s="22" t="s">
         <v>2254</v>
       </c>
-      <c r="J340" s="21"/>
+      <c r="J340" s="21" t="s">
+        <v>518</v>
+      </c>
       <c r="K340" s="12" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+      <c r="M340" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B341" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C341" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D341" t="s">
-        <v>1327</v>
+        <v>520</v>
       </c>
       <c r="E341" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G341" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="J341" s="21" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K341" t="s">
+        <v>519</v>
+      </c>
+      <c r="M341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A342" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B342" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A342" s="9" t="s">
-        <v>1636</v>
-      </c>
-      <c r="B342" t="s">
-        <v>544</v>
-      </c>
       <c r="C342" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D342" t="s">
-        <v>1274</v>
+        <v>1327</v>
       </c>
       <c r="E342" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="G342" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="J342" s="21" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="K342" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+      <c r="M342">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="B343" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="C343" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D343" t="s">
-        <v>1549</v>
+        <v>527</v>
       </c>
       <c r="E343" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="G343" s="22" t="s">
         <v>2254</v>
       </c>
-      <c r="J343" s="21" t="s">
-        <v>518</v>
+      <c r="J343" s="15" t="s">
+        <v>2094</v>
       </c>
       <c r="K343" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="M343">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B344" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C344" s="12" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D344" t="s">
-        <v>1330</v>
+        <v>539</v>
       </c>
       <c r="E344" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="G344" s="22" t="s">
         <v>2254</v>
       </c>
-      <c r="J344" s="21" t="s">
-        <v>536</v>
+      <c r="J344" s="15" t="s">
+        <v>2096</v>
       </c>
       <c r="K344" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+      <c r="M344">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="B345" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C345" s="12" t="s">
         <v>323</v>
       </c>
       <c r="D345" t="s">
-        <v>520</v>
+        <v>1274</v>
       </c>
       <c r="E345" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="G345" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="J345" s="21" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="K345" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+      <c r="M345">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="B346" s="12" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C346" s="12" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D346" t="s">
-        <v>1328</v>
+        <v>542</v>
       </c>
       <c r="E346" t="s">
-        <v>530</v>
+        <v>1802</v>
       </c>
       <c r="G346" s="22" t="s">
         <v>2254</v>
       </c>
-      <c r="J346" s="15" t="s">
-        <v>2095</v>
+      <c r="J346" s="23" t="s">
+        <v>543</v>
       </c>
       <c r="K346" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+      <c r="M346">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="C347" s="12" t="s">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="D347" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E347" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="G347" s="22" t="s">
         <v>2254</v>
       </c>
+      <c r="J347" s="15" t="s">
+        <v>1998</v>
+      </c>
       <c r="K347" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+      <c r="M347">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" s="12" t="s">
-        <v>1637</v>
+        <v>1631</v>
       </c>
       <c r="B348" s="12" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D348" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="E348" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="G348" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="J348" s="15" t="s">
-        <v>1998</v>
+        <v>2095</v>
       </c>
       <c r="K348" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="M348">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="B349" s="12" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C349" s="12" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D349" t="s">
-        <v>539</v>
+        <v>1329</v>
       </c>
       <c r="E349" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G349" s="22" t="s">
         <v>2254</v>
       </c>
-      <c r="J349" s="15" t="s">
-        <v>2096</v>
-      </c>
+      <c r="J349" s="23"/>
       <c r="K349" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+      <c r="M349">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B350" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C350" s="12" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="D350" t="s">
-        <v>542</v>
+        <v>1330</v>
       </c>
       <c r="E350" t="s">
-        <v>1802</v>
+        <v>535</v>
       </c>
       <c r="G350" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="J350" s="21" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="K350" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+      <c r="M350">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1732</v>
       </c>
@@ -18398,7 +18787,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1733</v>
       </c>
@@ -18834,7 +19223,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{015C06A3-D7D4-4444-A0A7-CA24E18288C7}"/>
+  <autoFilter ref="A1:M368" xr:uid="{015C06A3-D7D4-4444-A0A7-CA24E18288C7}"/>
   <sortState ref="A2:M368">
     <sortCondition ref="G2:G368"/>
     <sortCondition ref="M2:M368"/>
@@ -18842,59 +19231,59 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="J83" r:id="rId1" display="https://github.com/olaf-programmeur/images/blob/main/famille.jpg" xr:uid="{5AC8663B-7BE4-408F-A638-85FD270E92CF}"/>
-    <hyperlink ref="J279" r:id="rId2" display="https://github.com/olaf-programmeur/images/blob/main/germaine.jpg" xr:uid="{2E7B80A8-5AF4-4177-85E3-38D800D99AA9}"/>
-    <hyperlink ref="J280" r:id="rId3" display="https://github.com/olaf-programmeur/images/blob/main/no%C3%ABl.jpg" xr:uid="{7B8768BF-49BF-4B35-8FD8-92A79315EF90}"/>
-    <hyperlink ref="J268" r:id="rId4" display="https://github.com/olaf-programmeur/images/blob/main/claudia.jpg" xr:uid="{3096E645-32F3-4241-B925-6E3CA72A5839}"/>
+    <hyperlink ref="J281" r:id="rId2" display="https://github.com/olaf-programmeur/images/blob/main/germaine.jpg" xr:uid="{2E7B80A8-5AF4-4177-85E3-38D800D99AA9}"/>
+    <hyperlink ref="J282" r:id="rId3" display="https://github.com/olaf-programmeur/images/blob/main/no%C3%ABl.jpg" xr:uid="{7B8768BF-49BF-4B35-8FD8-92A79315EF90}"/>
+    <hyperlink ref="J269" r:id="rId4" display="https://github.com/olaf-programmeur/images/blob/main/claudia.jpg" xr:uid="{3096E645-32F3-4241-B925-6E3CA72A5839}"/>
     <hyperlink ref="J270" r:id="rId5" xr:uid="{CB778D1A-EE00-4E7F-AAD2-7F5E59B63AEB}"/>
     <hyperlink ref="J277" r:id="rId6" display="https://github.com/olaf-programmeur/images/blob/main/melwyn.jpg" xr:uid="{CD6B87D8-635B-4E65-96B0-18C887C40FD4}"/>
-    <hyperlink ref="J278" r:id="rId7" display="https://github.com/olaf-programmeur/images/blob/main/yanis.jpg" xr:uid="{7CB58E10-B622-4B39-9F16-2968CA05B6B0}"/>
-    <hyperlink ref="J183" r:id="rId8" display="https://github.com/olaf-programmeur/images/blob/main/lave_linge.jpg" xr:uid="{FC6BD14E-6B80-4009-9A6D-835AC1D3DD2F}"/>
-    <hyperlink ref="J348" r:id="rId9" xr:uid="{0D7F0DE4-F86B-4D1E-8E46-55DA62F479D2}"/>
+    <hyperlink ref="J279" r:id="rId7" display="https://github.com/olaf-programmeur/images/blob/main/yanis.jpg" xr:uid="{7CB58E10-B622-4B39-9F16-2968CA05B6B0}"/>
+    <hyperlink ref="J184" r:id="rId8" display="https://github.com/olaf-programmeur/images/blob/main/lave_linge.jpg" xr:uid="{FC6BD14E-6B80-4009-9A6D-835AC1D3DD2F}"/>
+    <hyperlink ref="J347" r:id="rId9" xr:uid="{0D7F0DE4-F86B-4D1E-8E46-55DA62F479D2}"/>
     <hyperlink ref="J365" r:id="rId10" display="https://github.com/olaf-programmeur/images/blob/main/blanc_poulet.png" xr:uid="{8DBE3221-2A5A-4286-B320-D09BCCEE31F4}"/>
     <hyperlink ref="J367" r:id="rId11" display="https://github.com/olaf-programmeur/images/blob/main/cotelette_porc.jpg" xr:uid="{B664C4BC-663F-48E1-A80C-14A33785A5C7}"/>
     <hyperlink ref="J363" r:id="rId12" display="https://github.com/olaf-programmeur/images/blob/main/r%C3%B4ti_boeuf.jpg" xr:uid="{18FC33FD-FF80-40EF-A805-6B3C52E2EFF4}"/>
     <hyperlink ref="J361" r:id="rId13" display="https://github.com/olaf-programmeur/images/blob/main/poulet_entier.jpg" xr:uid="{4FEB8902-7D83-41FE-A9B7-1646A44F4BD1}"/>
     <hyperlink ref="J358" r:id="rId14" display="https://github.com/olaf-programmeur/images/blob/main/vache.jpg" xr:uid="{D173A577-6B82-4350-AFD6-C2078FFE3271}"/>
     <hyperlink ref="J353" r:id="rId15" display="https://github.com/olaf-programmeur/images/blob/main/arbre.jpg" xr:uid="{6A3BCB59-5C7E-4916-951B-F46FA8658F4B}"/>
-    <hyperlink ref="J349" r:id="rId16" xr:uid="{B49A8FA5-2203-4FB7-B621-672729AD06F4}"/>
-    <hyperlink ref="J346" r:id="rId17" display="https://github.com/olaf-programmeur/images/blob/main/mur.jpg" xr:uid="{587EEA60-F594-4016-803C-CEB66BA1E5BF}"/>
-    <hyperlink ref="J339" r:id="rId18" display="https://github.com/olaf-programmeur/images/blob/main/fenetre.jpg" xr:uid="{53E2D24E-B720-42FE-B37D-24B6C52BACAF}"/>
-    <hyperlink ref="J184" r:id="rId19" display="https://github.com/olaf-programmeur/images/blob/main/s%C3%A8che_linge.jpg" xr:uid="{029644CA-FA19-4AB5-BFB7-7BFD3C6E6F4B}"/>
-    <hyperlink ref="J146" r:id="rId20" display="https://github.com/olaf-programmeur/images/blob/main/batterie.jpg" xr:uid="{332B5C86-AAEA-4A7C-AA3B-4FB39A4D1019}"/>
-    <hyperlink ref="J147" r:id="rId21" display="https://github.com/olaf-programmeur/images/blob/main/grosse_caisse.jpg" xr:uid="{71D51027-C922-4602-8582-3F2E3E5CB2A0}"/>
-    <hyperlink ref="J158" r:id="rId22" display="https://github.com/olaf-programmeur/images/blob/main/basse.jpg" xr:uid="{F8BFD881-7F63-49CC-B835-919A654BF96B}"/>
-    <hyperlink ref="J155" r:id="rId23" display="https://github.com/olaf-programmeur/images/blob/main/alto.jpg" xr:uid="{7A0BD9D0-1209-4507-8CED-8013F4979FC8}"/>
-    <hyperlink ref="J156" r:id="rId24" display="https://github.com/olaf-programmeur/images/blob/main/baryton.webp" xr:uid="{8C3FA86E-86C2-414F-96EB-80EC0F231C3F}"/>
-    <hyperlink ref="J212" r:id="rId25" display="https://github.com/olaf-programmeur/images/blob/main/cuisse.jpg" xr:uid="{7F69A20C-4787-4AFE-A184-7F4999281637}"/>
-    <hyperlink ref="J213" r:id="rId26" display="https://github.com/olaf-programmeur/images/blob/main/jambe.jpg" xr:uid="{0D5307E4-DD90-4E01-BAA8-C30063A487C4}"/>
-    <hyperlink ref="J214" r:id="rId27" display="https://github.com/olaf-programmeur/images/blob/main/bras.jpg" xr:uid="{EF25790D-C418-40F0-98C2-77447ACAB26F}"/>
-    <hyperlink ref="J216" r:id="rId28" display="https://github.com/olaf-programmeur/images/blob/main/main.jpg" xr:uid="{743DFD2F-DCFD-447B-8F78-D5BB7B58D12E}"/>
-    <hyperlink ref="J219" r:id="rId29" display="https://github.com/olaf-programmeur/images/blob/main/lasagnes.jpg" xr:uid="{C6713C28-E823-4639-8FE0-90A3F03A3966}"/>
-    <hyperlink ref="J221" r:id="rId30" display="https://github.com/olaf-programmeur/images/blob/main/spaghetti.jpg" xr:uid="{74A495BA-1B4B-43CA-ACD7-B5F50E708733}"/>
-    <hyperlink ref="J225" r:id="rId31" display="https://github.com/olaf-programmeur/images/blob/main/douche.jpg" xr:uid="{7A910F21-AB83-46F9-81FF-E15C13D9B405}"/>
-    <hyperlink ref="J227" r:id="rId32" display="https://github.com/olaf-programmeur/images/blob/main/dentifrice.jpg" xr:uid="{FF1FF7B6-276E-43FF-8D8C-D8C19E633D4A}"/>
-    <hyperlink ref="J231" r:id="rId33" display="https://github.com/olaf-programmeur/images/blob/main/rasoir.jpg" xr:uid="{58A797E6-3BC1-42F4-B3CE-DEE98E279D91}"/>
-    <hyperlink ref="J232" r:id="rId34" display="https://github.com/olaf-programmeur/images/blob/main/savon.png" xr:uid="{122E5EFD-613E-43DA-BD11-6341AB1C8B08}"/>
-    <hyperlink ref="J233" r:id="rId35" display="https://github.com/olaf-programmeur/images/blob/main/wc.jpg" xr:uid="{22E5A069-102E-476A-8B3B-3E577EC5F3D7}"/>
-    <hyperlink ref="J236" r:id="rId36" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{42632286-CE34-4B90-BF76-FA1487C3382B}"/>
-    <hyperlink ref="J237" r:id="rId37" display="https://github.com/olaf-programmeur/images/blob/main/car%20postal.jpg" xr:uid="{6D5FAF44-8155-4328-9374-9C7549029005}"/>
-    <hyperlink ref="J266" r:id="rId38" display="https://github.com/olaf-programmeur/images/blob/main/famille_herv%C3%A9.jpg" xr:uid="{6DA707CF-199A-414A-AD98-B47DEAF42FCE}"/>
-    <hyperlink ref="J248" r:id="rId39" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{66B713BF-A7DF-43A4-BBA3-46CFF8175001}"/>
+    <hyperlink ref="J344" r:id="rId16" xr:uid="{B49A8FA5-2203-4FB7-B621-672729AD06F4}"/>
+    <hyperlink ref="J348" r:id="rId17" display="https://github.com/olaf-programmeur/images/blob/main/mur.jpg" xr:uid="{587EEA60-F594-4016-803C-CEB66BA1E5BF}"/>
+    <hyperlink ref="J343" r:id="rId18" display="https://github.com/olaf-programmeur/images/blob/main/fenetre.jpg" xr:uid="{53E2D24E-B720-42FE-B37D-24B6C52BACAF}"/>
+    <hyperlink ref="J185" r:id="rId19" display="https://github.com/olaf-programmeur/images/blob/main/s%C3%A8che_linge.jpg" xr:uid="{029644CA-FA19-4AB5-BFB7-7BFD3C6E6F4B}"/>
+    <hyperlink ref="J148" r:id="rId20" display="https://github.com/olaf-programmeur/images/blob/main/batterie.jpg" xr:uid="{332B5C86-AAEA-4A7C-AA3B-4FB39A4D1019}"/>
+    <hyperlink ref="J149" r:id="rId21" display="https://github.com/olaf-programmeur/images/blob/main/grosse_caisse.jpg" xr:uid="{71D51027-C922-4602-8582-3F2E3E5CB2A0}"/>
+    <hyperlink ref="J160" r:id="rId22" display="https://github.com/olaf-programmeur/images/blob/main/basse.jpg" xr:uid="{F8BFD881-7F63-49CC-B835-919A654BF96B}"/>
+    <hyperlink ref="J157" r:id="rId23" display="https://github.com/olaf-programmeur/images/blob/main/alto.jpg" xr:uid="{7A0BD9D0-1209-4507-8CED-8013F4979FC8}"/>
+    <hyperlink ref="J158" r:id="rId24" display="https://github.com/olaf-programmeur/images/blob/main/baryton.webp" xr:uid="{8C3FA86E-86C2-414F-96EB-80EC0F231C3F}"/>
+    <hyperlink ref="J218" r:id="rId25" display="https://github.com/olaf-programmeur/images/blob/main/cuisse.jpg" xr:uid="{7F69A20C-4787-4AFE-A184-7F4999281637}"/>
+    <hyperlink ref="J217" r:id="rId26" display="https://github.com/olaf-programmeur/images/blob/main/jambe.jpg" xr:uid="{0D5307E4-DD90-4E01-BAA8-C30063A487C4}"/>
+    <hyperlink ref="J216" r:id="rId27" display="https://github.com/olaf-programmeur/images/blob/main/bras.jpg" xr:uid="{EF25790D-C418-40F0-98C2-77447ACAB26F}"/>
+    <hyperlink ref="J215" r:id="rId28" display="https://github.com/olaf-programmeur/images/blob/main/main.jpg" xr:uid="{743DFD2F-DCFD-447B-8F78-D5BB7B58D12E}"/>
+    <hyperlink ref="J221" r:id="rId29" display="https://github.com/olaf-programmeur/images/blob/main/lasagnes.jpg" xr:uid="{C6713C28-E823-4639-8FE0-90A3F03A3966}"/>
+    <hyperlink ref="J223" r:id="rId30" display="https://github.com/olaf-programmeur/images/blob/main/spaghetti.jpg" xr:uid="{74A495BA-1B4B-43CA-ACD7-B5F50E708733}"/>
+    <hyperlink ref="J230" r:id="rId31" display="https://github.com/olaf-programmeur/images/blob/main/douche.jpg" xr:uid="{7A910F21-AB83-46F9-81FF-E15C13D9B405}"/>
+    <hyperlink ref="J234" r:id="rId32" display="https://github.com/olaf-programmeur/images/blob/main/dentifrice.jpg" xr:uid="{FF1FF7B6-276E-43FF-8D8C-D8C19E633D4A}"/>
+    <hyperlink ref="J232" r:id="rId33" display="https://github.com/olaf-programmeur/images/blob/main/rasoir.jpg" xr:uid="{58A797E6-3BC1-42F4-B3CE-DEE98E279D91}"/>
+    <hyperlink ref="J227" r:id="rId34" display="https://github.com/olaf-programmeur/images/blob/main/savon.png" xr:uid="{122E5EFD-613E-43DA-BD11-6341AB1C8B08}"/>
+    <hyperlink ref="J229" r:id="rId35" display="https://github.com/olaf-programmeur/images/blob/main/wc.jpg" xr:uid="{22E5A069-102E-476A-8B3B-3E577EC5F3D7}"/>
+    <hyperlink ref="J238" r:id="rId36" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{42632286-CE34-4B90-BF76-FA1487C3382B}"/>
+    <hyperlink ref="J240" r:id="rId37" display="https://github.com/olaf-programmeur/images/blob/main/car%20postal.jpg" xr:uid="{6D5FAF44-8155-4328-9374-9C7549029005}"/>
+    <hyperlink ref="J262" r:id="rId38" display="https://github.com/olaf-programmeur/images/blob/main/famille_herv%C3%A9.jpg" xr:uid="{6DA707CF-199A-414A-AD98-B47DEAF42FCE}"/>
+    <hyperlink ref="J250" r:id="rId39" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{66B713BF-A7DF-43A4-BBA3-46CFF8175001}"/>
     <hyperlink ref="J251" r:id="rId40" display="https://github.com/olaf-programmeur/images/blob/main/pare_brise.jpg" xr:uid="{F6A24B65-2589-4264-9672-CB51F3400B56}"/>
-    <hyperlink ref="J254" r:id="rId41" display="https://github.com/olaf-programmeur/images/blob/main/pneu.jpg" xr:uid="{3187882F-747C-4E33-B6B3-244E0010F89B}"/>
-    <hyperlink ref="J255" r:id="rId42" display="https://github.com/olaf-programmeur/images/blob/main/coffre_dacia.jpg" xr:uid="{AB6806C1-DC5E-4AA8-AB30-9948CFB36CE1}"/>
-    <hyperlink ref="J257" r:id="rId43" display="https://github.com/olaf-programmeur/images/blob/main/tableau_bord.jpg" xr:uid="{BE50E3CC-EC46-4D7C-9C85-25069D09F961}"/>
-    <hyperlink ref="J293" r:id="rId44" display="https://github.com/olaf-programmeur/images/blob/main/chambre.jpg" xr:uid="{A60CDDC8-BEAC-401F-A566-3B174470D594}"/>
+    <hyperlink ref="J257" r:id="rId41" display="https://github.com/olaf-programmeur/images/blob/main/pneu.jpg" xr:uid="{3187882F-747C-4E33-B6B3-244E0010F89B}"/>
+    <hyperlink ref="J261" r:id="rId42" display="https://github.com/olaf-programmeur/images/blob/main/coffre_dacia.jpg" xr:uid="{AB6806C1-DC5E-4AA8-AB30-9948CFB36CE1}"/>
+    <hyperlink ref="J260" r:id="rId43" display="https://github.com/olaf-programmeur/images/blob/main/tableau_bord.jpg" xr:uid="{BE50E3CC-EC46-4D7C-9C85-25069D09F961}"/>
+    <hyperlink ref="J295" r:id="rId44" display="https://github.com/olaf-programmeur/images/blob/main/chambre.jpg" xr:uid="{A60CDDC8-BEAC-401F-A566-3B174470D594}"/>
     <hyperlink ref="J297" r:id="rId45" display="https://github.com/olaf-programmeur/images/blob/main/matelas.jpg" xr:uid="{FAEC7047-DB8A-4E10-AF56-4DF63C7EF53B}"/>
-    <hyperlink ref="J304" r:id="rId46" display="https://github.com/olaf-programmeur/images/blob/main/ordinateur.jpg" xr:uid="{106B35C9-4162-4904-8915-FFA2E2757B8B}"/>
-    <hyperlink ref="J170" r:id="rId47" display="https://github.com/olaf-programmeur/images/blob/main/cuill%C3%A8res.jpg" xr:uid="{9E41DDDC-A6C6-4BDD-A70E-926C5037925B}"/>
-    <hyperlink ref="J178" r:id="rId48" display="https://github.com/olaf-programmeur/images/blob/main/tasse.jpg" xr:uid="{7C46C278-CCC0-4777-88CA-0530390F1EB2}"/>
-    <hyperlink ref="J168" r:id="rId49" xr:uid="{9779163C-1BBF-40D4-A592-FE5E38CF8BC1}"/>
-    <hyperlink ref="J161" r:id="rId50" display="https://github.com/olaf-programmeur/images/blob/main/frigo.jpg" xr:uid="{57EEF2DF-E734-4095-9D25-B5B9EC943262}"/>
-    <hyperlink ref="J167" r:id="rId51" display="https://github.com/olaf-programmeur/images/blob/main/verres.jpg" xr:uid="{7A751B89-B8B9-412D-A975-A601728A0697}"/>
+    <hyperlink ref="J306" r:id="rId46" display="https://github.com/olaf-programmeur/images/blob/main/ordinateur.jpg" xr:uid="{106B35C9-4162-4904-8915-FFA2E2757B8B}"/>
+    <hyperlink ref="J174" r:id="rId47" display="https://github.com/olaf-programmeur/images/blob/main/cuill%C3%A8res.jpg" xr:uid="{9E41DDDC-A6C6-4BDD-A70E-926C5037925B}"/>
+    <hyperlink ref="J170" r:id="rId48" display="https://github.com/olaf-programmeur/images/blob/main/tasse.jpg" xr:uid="{7C46C278-CCC0-4777-88CA-0530390F1EB2}"/>
+    <hyperlink ref="J172" r:id="rId49" xr:uid="{9779163C-1BBF-40D4-A592-FE5E38CF8BC1}"/>
+    <hyperlink ref="J163" r:id="rId50" display="https://github.com/olaf-programmeur/images/blob/main/frigo.jpg" xr:uid="{57EEF2DF-E734-4095-9D25-B5B9EC943262}"/>
+    <hyperlink ref="J169" r:id="rId51" display="https://github.com/olaf-programmeur/images/blob/main/verres.jpg" xr:uid="{7A751B89-B8B9-412D-A975-A601728A0697}"/>
     <hyperlink ref="J313" r:id="rId52" display="https://github.com/olaf-programmeur/images/blob/main/essence_sans_plomb.jpg" xr:uid="{9DE12D4E-C391-4C17-A428-4836AACE04DB}"/>
-    <hyperlink ref="J317" r:id="rId53" display="https://github.com/olaf-programmeur/images/blob/main/pantalon.jpg" xr:uid="{72159F26-849C-4C24-A68F-38959EECEAB6}"/>
-    <hyperlink ref="J326" r:id="rId54" display="https://github.com/olaf-programmeur/images/blob/main/saucisse.jpg" xr:uid="{8BA85415-E506-4FBE-8596-6C9455FBF580}"/>
+    <hyperlink ref="J319" r:id="rId53" display="https://github.com/olaf-programmeur/images/blob/main/pantalon.jpg" xr:uid="{72159F26-849C-4C24-A68F-38959EECEAB6}"/>
+    <hyperlink ref="J330" r:id="rId54" display="https://github.com/olaf-programmeur/images/blob/main/saucisse.jpg" xr:uid="{8BA85415-E506-4FBE-8596-6C9455FBF580}"/>
     <hyperlink ref="J13" r:id="rId55" display="https://github.com/olaf-programmeur/images/blob/main/brosses_instruments.jpg" xr:uid="{0EA707BC-6708-403B-AAFE-E4386C76CD30}"/>
     <hyperlink ref="J15" r:id="rId56" display="https://github.com/olaf-programmeur/images/blob/main/uniforme_contheysanne.jpg" xr:uid="{990253A1-DD44-4C1D-8A7C-7E08A0B18916}"/>
     <hyperlink ref="J31" r:id="rId57" display="https://github.com/olaf-programmeur/images/blob/main/chevreuil.jpg" xr:uid="{61121F54-2FB3-4AC3-B93D-984AA43EE9D6}"/>
@@ -18906,56 +19295,56 @@
     <hyperlink ref="J79" r:id="rId63" display="https://github.com/olaf-programmeur/images/blob/main/sirop.webp" xr:uid="{E164FFCD-B48A-4236-AB2C-2EC574167F47}"/>
     <hyperlink ref="J80" r:id="rId64" display="https://github.com/olaf-programmeur/images/blob/main/baskets.jpg" xr:uid="{F09AB7CB-2BBD-4D3D-9DB4-58519F918CBE}"/>
     <hyperlink ref="J82" r:id="rId65" display="https://github.com/olaf-programmeur/images/blob/main/botillons.jpg" xr:uid="{E3D9CF8A-EC5B-4C21-AE42-81EAED03C826}"/>
-    <hyperlink ref="J101" r:id="rId66" display="https://github.com/olaf-programmeur/images/blob/main/thujas.jpg" xr:uid="{61B05A21-8238-4935-B146-C91AFFF16EB0}"/>
-    <hyperlink ref="J102" r:id="rId67" display="https://github.com/olaf-programmeur/images/blob/main/pelouse.jpg" xr:uid="{3DF10915-2980-4265-A3E4-E2ED5D5D22A7}"/>
-    <hyperlink ref="J103" r:id="rId68" display="https://github.com/olaf-programmeur/images/blob/main/table_jardin.jpg" xr:uid="{B3D4B092-615E-43B3-A45F-AD02E1C7CF57}"/>
-    <hyperlink ref="J105" r:id="rId69" display="https://github.com/olaf-programmeur/images/blob/main/arrosage.jpg" xr:uid="{6D35F4CA-DE8A-4413-9270-43AF2DF8FCA7}"/>
-    <hyperlink ref="J114" r:id="rId70" display="https://github.com/olaf-programmeur/images/blob/main/ciel.jpg" xr:uid="{0C3AAF7A-0049-4090-98A2-062C3AB8C49B}"/>
-    <hyperlink ref="J115" r:id="rId71" display="https://github.com/olaf-programmeur/images/blob/main/feu.jpg" xr:uid="{B53FC550-3981-43F7-BFD1-FBC984824DC0}"/>
-    <hyperlink ref="J118" r:id="rId72" display="https://github.com/olaf-programmeur/images/blob/main/incendie.jpg" xr:uid="{D33699A2-17D5-4D1F-9E45-91538013A790}"/>
-    <hyperlink ref="J202" r:id="rId73" display="https://github.com/olaf-programmeur/images/blob/main/pomme_terre.jpg" xr:uid="{A4C36682-EB03-4230-B723-DA16513496DB}"/>
-    <hyperlink ref="J187" r:id="rId74" display="https://github.com/olaf-programmeur/images/blob/main/canap%C3%A9.jpg" xr:uid="{19EF0F4B-32A1-4B2B-BE17-D29B9945856D}"/>
-    <hyperlink ref="J189" r:id="rId75" display="https://github.com/olaf-programmeur/images/blob/main/meuble_salon.jpg" xr:uid="{32CF85D7-C1C4-4859-938E-426775026EB3}"/>
+    <hyperlink ref="J105" r:id="rId66" display="https://github.com/olaf-programmeur/images/blob/main/thujas.jpg" xr:uid="{61B05A21-8238-4935-B146-C91AFFF16EB0}"/>
+    <hyperlink ref="J103" r:id="rId67" display="https://github.com/olaf-programmeur/images/blob/main/pelouse.jpg" xr:uid="{3DF10915-2980-4265-A3E4-E2ED5D5D22A7}"/>
+    <hyperlink ref="J104" r:id="rId68" display="https://github.com/olaf-programmeur/images/blob/main/table_jardin.jpg" xr:uid="{B3D4B092-615E-43B3-A45F-AD02E1C7CF57}"/>
+    <hyperlink ref="J106" r:id="rId69" display="https://github.com/olaf-programmeur/images/blob/main/arrosage.jpg" xr:uid="{6D35F4CA-DE8A-4413-9270-43AF2DF8FCA7}"/>
+    <hyperlink ref="J116" r:id="rId70" display="https://github.com/olaf-programmeur/images/blob/main/ciel.jpg" xr:uid="{0C3AAF7A-0049-4090-98A2-062C3AB8C49B}"/>
+    <hyperlink ref="J117" r:id="rId71" display="https://github.com/olaf-programmeur/images/blob/main/feu.jpg" xr:uid="{B53FC550-3981-43F7-BFD1-FBC984824DC0}"/>
+    <hyperlink ref="J120" r:id="rId72" display="https://github.com/olaf-programmeur/images/blob/main/incendie.jpg" xr:uid="{D33699A2-17D5-4D1F-9E45-91538013A790}"/>
+    <hyperlink ref="J204" r:id="rId73" display="https://github.com/olaf-programmeur/images/blob/main/pomme_terre.jpg" xr:uid="{A4C36682-EB03-4230-B723-DA16513496DB}"/>
+    <hyperlink ref="J188" r:id="rId74" display="https://github.com/olaf-programmeur/images/blob/main/canap%C3%A9.jpg" xr:uid="{19EF0F4B-32A1-4B2B-BE17-D29B9945856D}"/>
+    <hyperlink ref="J190" r:id="rId75" display="https://github.com/olaf-programmeur/images/blob/main/meuble_salon.jpg" xr:uid="{32CF85D7-C1C4-4859-938E-426775026EB3}"/>
     <hyperlink ref="J193" r:id="rId76" display="https://github.com/olaf-programmeur/images/blob/main/ventre.jpg" xr:uid="{F7C358E3-5EF3-4C2E-814C-EB548E2B0F08}"/>
     <hyperlink ref="J197" r:id="rId77" display="https://github.com/olaf-programmeur/images/blob/main/ventre.jpg" xr:uid="{85EEC448-4DC2-467E-A22A-6564E5B84CE7}"/>
-    <hyperlink ref="J198" r:id="rId78" display="https://github.com/olaf-programmeur/images/blob/main/dents.jpg" xr:uid="{E934A777-D378-44CC-BDAD-4C610CEB108A}"/>
-    <hyperlink ref="J200" r:id="rId79" display="https://github.com/olaf-programmeur/images/blob/main/oreille.jpg" xr:uid="{C1440963-B371-4D18-8673-7735F862D76C}"/>
-    <hyperlink ref="J201" r:id="rId80" display="https://github.com/olaf-programmeur/images/blob/main/legumes.webp" xr:uid="{30E68B4E-796A-4F25-BF68-928BD963ECA6}"/>
-    <hyperlink ref="J203" r:id="rId81" display="https://github.com/olaf-programmeur/images/blob/main/carottes.jpg" xr:uid="{4A842181-3070-4E8E-942D-6E149E4F7811}"/>
-    <hyperlink ref="J204" r:id="rId82" display="https://github.com/olaf-programmeur/images/blob/main/tomate.jpg" xr:uid="{0EE5EFAC-F5FF-4855-A088-BEEA25930A2C}"/>
-    <hyperlink ref="J205" r:id="rId83" display="https://github.com/olaf-programmeur/images/blob/main/chou_fleur.jpg" xr:uid="{36610DA1-73C2-415D-AA34-40E62585D87D}"/>
-    <hyperlink ref="J206" r:id="rId84" display="https://github.com/olaf-programmeur/images/blob/main/poireau.jpg" xr:uid="{9F7E2621-9468-47EE-B4B7-B3E3C0BE01DE}"/>
-    <hyperlink ref="J208" r:id="rId85" display="https://github.com/olaf-programmeur/images/blob/main/asperge.jpg" xr:uid="{9BD74A1C-7464-4645-B8EE-E10889B65BC3}"/>
-    <hyperlink ref="J209" r:id="rId86" display="https://github.com/olaf-programmeur/images/blob/main/courgette.jpg" xr:uid="{77AD92C4-A934-4AA0-A18D-33901F07A316}"/>
-    <hyperlink ref="J283" r:id="rId87" display="https://github.com/olaf-programmeur/images/blob/main/policier.jpg" xr:uid="{D7A9F694-070A-4D20-989A-3FF659412B59}"/>
-    <hyperlink ref="J299" r:id="rId88" display="https://github.com/olaf-programmeur/images/blob/main/oreillers.jpg" xr:uid="{868F1AD6-0136-444A-9BD0-81EC1AA90EEE}"/>
-    <hyperlink ref="J160" r:id="rId89" display="https://github.com/olaf-programmeur/images/blob/main/cuisine.jpg" xr:uid="{CC56F71D-7498-46DD-BF9F-121CDF28A94E}"/>
-    <hyperlink ref="J163" r:id="rId90" xr:uid="{8560A2F4-CC49-4D6C-ADC5-8D354183A9BA}"/>
-    <hyperlink ref="J305" r:id="rId91" display="https://github.com/olaf-programmeur/images/blob/main/tarte_pomme.jpg" xr:uid="{D6A83C1A-7FCB-401D-9D14-2ACA729502F9}"/>
+    <hyperlink ref="J201" r:id="rId78" display="https://github.com/olaf-programmeur/images/blob/main/dents.jpg" xr:uid="{E934A777-D378-44CC-BDAD-4C610CEB108A}"/>
+    <hyperlink ref="J202" r:id="rId79" display="https://github.com/olaf-programmeur/images/blob/main/oreille.jpg" xr:uid="{C1440963-B371-4D18-8673-7735F862D76C}"/>
+    <hyperlink ref="J203" r:id="rId80" display="https://github.com/olaf-programmeur/images/blob/main/legumes.webp" xr:uid="{30E68B4E-796A-4F25-BF68-928BD963ECA6}"/>
+    <hyperlink ref="J205" r:id="rId81" display="https://github.com/olaf-programmeur/images/blob/main/carottes.jpg" xr:uid="{4A842181-3070-4E8E-942D-6E149E4F7811}"/>
+    <hyperlink ref="J206" r:id="rId82" display="https://github.com/olaf-programmeur/images/blob/main/tomate.jpg" xr:uid="{0EE5EFAC-F5FF-4855-A088-BEEA25930A2C}"/>
+    <hyperlink ref="J207" r:id="rId83" display="https://github.com/olaf-programmeur/images/blob/main/chou_fleur.jpg" xr:uid="{36610DA1-73C2-415D-AA34-40E62585D87D}"/>
+    <hyperlink ref="J208" r:id="rId84" display="https://github.com/olaf-programmeur/images/blob/main/poireau.jpg" xr:uid="{9F7E2621-9468-47EE-B4B7-B3E3C0BE01DE}"/>
+    <hyperlink ref="J210" r:id="rId85" display="https://github.com/olaf-programmeur/images/blob/main/asperge.jpg" xr:uid="{9BD74A1C-7464-4645-B8EE-E10889B65BC3}"/>
+    <hyperlink ref="J211" r:id="rId86" display="https://github.com/olaf-programmeur/images/blob/main/courgette.jpg" xr:uid="{77AD92C4-A934-4AA0-A18D-33901F07A316}"/>
+    <hyperlink ref="J285" r:id="rId87" display="https://github.com/olaf-programmeur/images/blob/main/policier.jpg" xr:uid="{D7A9F694-070A-4D20-989A-3FF659412B59}"/>
+    <hyperlink ref="J298" r:id="rId88" display="https://github.com/olaf-programmeur/images/blob/main/oreillers.jpg" xr:uid="{868F1AD6-0136-444A-9BD0-81EC1AA90EEE}"/>
+    <hyperlink ref="J162" r:id="rId89" display="https://github.com/olaf-programmeur/images/blob/main/cuisine.jpg" xr:uid="{CC56F71D-7498-46DD-BF9F-121CDF28A94E}"/>
+    <hyperlink ref="J165" r:id="rId90" xr:uid="{8560A2F4-CC49-4D6C-ADC5-8D354183A9BA}"/>
+    <hyperlink ref="J307" r:id="rId91" display="https://github.com/olaf-programmeur/images/blob/main/tarte_pomme.jpg" xr:uid="{D6A83C1A-7FCB-401D-9D14-2ACA729502F9}"/>
     <hyperlink ref="J318" r:id="rId92" display="https://github.com/olaf-programmeur/images/blob/main/bas.jpg" xr:uid="{BB02D915-28BA-4162-BA67-75B53E299E22}"/>
-    <hyperlink ref="J319" r:id="rId93" display="https://github.com/olaf-programmeur/images/blob/main/cuissette.jpg" xr:uid="{F5D162FE-A2F1-4052-8ADC-59A120558A27}"/>
-    <hyperlink ref="J324" r:id="rId94" display="https://github.com/olaf-programmeur/images/blob/main/pull.jpg" xr:uid="{B387511F-FBD8-4841-9A31-4D8913435322}"/>
-    <hyperlink ref="J328" r:id="rId95" xr:uid="{8F3F7528-BDF0-480E-9BE8-4095253B9A60}"/>
-    <hyperlink ref="J171" r:id="rId96" display="https://github.com/olaf-programmeur/images/blob/main/couteau.webp" xr:uid="{38DBBFDC-632D-4FB4-86D1-BAAD947C780E}"/>
-    <hyperlink ref="J188" r:id="rId97" display="https://github.com/olaf-programmeur/images/blob/main/fauteuil.jpg" xr:uid="{E24D4E2E-A247-4FDA-A691-958623E2993C}"/>
-    <hyperlink ref="J136" r:id="rId98" display="https://github.com/olaf-programmeur/images/blob/main/pomme.jpg" xr:uid="{3637EC4A-0003-4AFC-9F5A-D7C5A1C52A60}"/>
-    <hyperlink ref="J137" r:id="rId99" display="https://github.com/olaf-programmeur/images/blob/main/poire.jpg" xr:uid="{AC46D50A-7112-4586-860B-4F7911051ADF}"/>
-    <hyperlink ref="J138" r:id="rId100" display="https://github.com/olaf-programmeur/images/blob/main/pruneau.jpg" xr:uid="{C5DD03B9-1159-4378-AAB4-160F23987DA3}"/>
-    <hyperlink ref="J139" r:id="rId101" display="https://github.com/olaf-programmeur/images/blob/main/cerise.jpg" xr:uid="{36D4DC98-15FC-4FEA-AF43-19BC1C487F20}"/>
-    <hyperlink ref="J143" r:id="rId102" display="https://github.com/olaf-programmeur/images/blob/main/banane.jpg" xr:uid="{920D4AB1-CE21-4124-87EA-93375D37EC03}"/>
-    <hyperlink ref="J145" r:id="rId103" display="https://github.com/olaf-programmeur/images/blob/main/mandarine.jpg" xr:uid="{F22B2A92-9EF5-430C-B9B0-28004020C747}"/>
+    <hyperlink ref="J321" r:id="rId93" display="https://github.com/olaf-programmeur/images/blob/main/cuissette.jpg" xr:uid="{F5D162FE-A2F1-4052-8ADC-59A120558A27}"/>
+    <hyperlink ref="J326" r:id="rId94" display="https://github.com/olaf-programmeur/images/blob/main/pull.jpg" xr:uid="{B387511F-FBD8-4841-9A31-4D8913435322}"/>
+    <hyperlink ref="J329" r:id="rId95" xr:uid="{8F3F7528-BDF0-480E-9BE8-4095253B9A60}"/>
+    <hyperlink ref="J175" r:id="rId96" display="https://github.com/olaf-programmeur/images/blob/main/couteau.webp" xr:uid="{38DBBFDC-632D-4FB4-86D1-BAAD947C780E}"/>
+    <hyperlink ref="J189" r:id="rId97" display="https://github.com/olaf-programmeur/images/blob/main/fauteuil.jpg" xr:uid="{E24D4E2E-A247-4FDA-A691-958623E2993C}"/>
+    <hyperlink ref="J138" r:id="rId98" display="https://github.com/olaf-programmeur/images/blob/main/pomme.jpg" xr:uid="{3637EC4A-0003-4AFC-9F5A-D7C5A1C52A60}"/>
+    <hyperlink ref="J139" r:id="rId99" display="https://github.com/olaf-programmeur/images/blob/main/poire.jpg" xr:uid="{AC46D50A-7112-4586-860B-4F7911051ADF}"/>
+    <hyperlink ref="J140" r:id="rId100" display="https://github.com/olaf-programmeur/images/blob/main/pruneau.jpg" xr:uid="{C5DD03B9-1159-4378-AAB4-160F23987DA3}"/>
+    <hyperlink ref="J141" r:id="rId101" display="https://github.com/olaf-programmeur/images/blob/main/cerise.jpg" xr:uid="{36D4DC98-15FC-4FEA-AF43-19BC1C487F20}"/>
+    <hyperlink ref="J145" r:id="rId102" display="https://github.com/olaf-programmeur/images/blob/main/banane.jpg" xr:uid="{920D4AB1-CE21-4124-87EA-93375D37EC03}"/>
+    <hyperlink ref="J147" r:id="rId103" display="https://github.com/olaf-programmeur/images/blob/main/mandarine.jpg" xr:uid="{F22B2A92-9EF5-430C-B9B0-28004020C747}"/>
     <hyperlink ref="J2" r:id="rId104" display="https://github.com/olaf-programmeur/images/blob/main/sandwich.jpg" xr:uid="{4203F942-6923-415F-86A7-DF33516D7E7D}"/>
     <hyperlink ref="J3" r:id="rId105" display="https://github.com/olaf-programmeur/images/blob/main/casquette.jpg" xr:uid="{065B8976-0210-46DC-BDA0-0F64BF80D817}"/>
     <hyperlink ref="J9" r:id="rId106" display="https://github.com/olaf-programmeur/images/blob/main/coulisses.jpg" xr:uid="{96C168EC-C14C-471A-960E-A7A71729E4ED}"/>
     <hyperlink ref="J74" r:id="rId107" display="https://github.com/olaf-programmeur/images/blob/main/coca_cola.jpg" xr:uid="{73E58CED-BED7-4790-800A-CD1DCD8881B5}"/>
     <hyperlink ref="J95" r:id="rId108" display="https://github.com/olaf-programmeur/images/blob/main/tante.jpg" xr:uid="{95300EA5-4B13-4027-8832-F58D978F6B28}"/>
-    <hyperlink ref="J190" r:id="rId109" display="https://github.com/olaf-programmeur/images/blob/main/salon.jpg" xr:uid="{FE322213-46FC-46F3-BC83-2AC0C1F3882C}"/>
+    <hyperlink ref="J187" r:id="rId109" display="https://github.com/olaf-programmeur/images/blob/main/salon.jpg" xr:uid="{FE322213-46FC-46F3-BC83-2AC0C1F3882C}"/>
     <hyperlink ref="J41" r:id="rId110" xr:uid="{DC79D1A3-109E-4EE4-BF3C-C1EEED4B0DED}"/>
     <hyperlink ref="J40" r:id="rId111" xr:uid="{2AA27B71-9A29-4216-A48E-9B95E836CFBB}"/>
     <hyperlink ref="J42" r:id="rId112" xr:uid="{B6693184-F75B-427B-9AFA-00C306B7916E}"/>
     <hyperlink ref="J43" r:id="rId113" xr:uid="{3A5E55F7-F9CF-4D08-AA81-C3D8E933F698}"/>
     <hyperlink ref="J44" r:id="rId114" xr:uid="{711E3821-4194-4BF4-88F5-74321C67729C}"/>
-    <hyperlink ref="J307" r:id="rId115" xr:uid="{51D58C29-4045-4E12-916E-0890AE387670}"/>
+    <hyperlink ref="J309" r:id="rId115" xr:uid="{51D58C29-4045-4E12-916E-0890AE387670}"/>
     <hyperlink ref="J276" r:id="rId116" xr:uid="{FA3C9936-A37B-44FE-A3AE-B68D33519D61}"/>
     <hyperlink ref="J99" r:id="rId117" display="https://github.com/olaf-programmeur/images/blob/main/viandes.jpg" xr:uid="{C6C3DDDD-31C2-4338-9CFF-BEE239E3D7CB}"/>
     <hyperlink ref="J25" r:id="rId118" display="https://github.com/olaf-programmeur/images/blob/main/chien.jpg" xr:uid="{B86D919F-8217-4D7F-B666-93B877031194}"/>
@@ -18963,31 +19352,31 @@
     <hyperlink ref="J29" r:id="rId120" display="https://github.com/olaf-programmeur/images/blob/main/marmotte.jpg" xr:uid="{F687C294-F572-475B-AFCE-E46E75695356}"/>
     <hyperlink ref="J30" r:id="rId121" display="https://github.com/olaf-programmeur/images/blob/main/loup.jpg" xr:uid="{48A775DA-9309-4365-8286-D46C9210553B}"/>
     <hyperlink ref="J32" r:id="rId122" display="https://github.com/olaf-programmeur/images/blob/main/biche.jpg" xr:uid="{8F13698E-303D-4AB9-87E4-4A3C9E3CBE1D}"/>
-    <hyperlink ref="J100" r:id="rId123" display="https://github.com/olaf-programmeur/images/blob/main/oeuf.jpg" xr:uid="{AB36AF05-CE27-469C-A389-F137AC6699D0}"/>
-    <hyperlink ref="J182" r:id="rId124" display="https://github.com/olaf-programmeur/images/blob/main/laura_star.jpg" xr:uid="{D305C3B9-0CBD-434F-B21E-ED312EFC16A5}"/>
-    <hyperlink ref="J260" r:id="rId125" display="https://github.com/olaf-programmeur/images/blob/main/mathilde.jpg" xr:uid="{D8FFFA1F-EEF3-4AC4-80B1-305AC43458FE}"/>
-    <hyperlink ref="J262" r:id="rId126" display="https://github.com/olaf-programmeur/images/blob/main/emma.jpeg" xr:uid="{C0DE091D-F71D-423C-B3E2-E3D5C8568367}"/>
-    <hyperlink ref="J263" r:id="rId127" display="https://github.com/olaf-programmeur/images/blob/main/loic.jpg" xr:uid="{98CD5A56-EE12-46D0-851B-46FF90465BB7}"/>
-    <hyperlink ref="J267" r:id="rId128" display="https://github.com/olaf-programmeur/images/blob/main/barbara.jpg" xr:uid="{FB5E9D99-3034-45ED-B5A8-4196BAF613E6}"/>
-    <hyperlink ref="J274" r:id="rId129" display="https://github.com/olaf-programmeur/images/blob/main/alison.jpg" xr:uid="{1A01A952-3795-4EAB-A237-062CC4D64B69}"/>
-    <hyperlink ref="J271" r:id="rId130" display="https://github.com/olaf-programmeur/images/blob/main/sandrine.jpg" xr:uid="{AA8F1D5E-21A1-4DF4-97B8-BC4400A8C63E}"/>
-    <hyperlink ref="J269" r:id="rId131" display="https://github.com/olaf-programmeur/images/blob/main/olivier.jpg" xr:uid="{7A079B6C-CAEF-487A-9835-CDD17CE4E3FF}"/>
-    <hyperlink ref="J51" r:id="rId132" display="https://github.com/olaf-programmeur/images/blob/main/kpt_ass.png" xr:uid="{739DD512-7187-4ABE-80D2-AB3A75A97B9A}"/>
-    <hyperlink ref="J52" r:id="rId133" display="https://github.com/olaf-programmeur/images/blob/main/mobiliere_ass.png" xr:uid="{FA90ED60-5F49-40C3-8120-9748EC5C0DF6}"/>
-    <hyperlink ref="J50" r:id="rId134" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{51402ACF-C4AF-4E8E-83F6-C10D822E38CB}"/>
-    <hyperlink ref="J49" r:id="rId135" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{D398F53D-8CD1-4BCF-B123-DE35DBD79DDC}"/>
-    <hyperlink ref="J46" r:id="rId136" display="https://github.com/olaf-programmeur/images/blob/main/migros.jpg" xr:uid="{F0E23162-8F08-4FE4-A006-E6DB539A7708}"/>
-    <hyperlink ref="J47" r:id="rId137" display="https://github.com/olaf-programmeur/images/blob/main/raiffeisen.jpg" xr:uid="{714C2B4D-0898-41DB-8A05-E175F7FEBA1B}"/>
-    <hyperlink ref="J140" r:id="rId138" display="https://github.com/olaf-programmeur/images/blob/main/abricot.jpg" xr:uid="{C3A11FAC-028D-46A8-9D2E-0E8E473F0783}"/>
-    <hyperlink ref="J141" r:id="rId139" display="https://github.com/olaf-programmeur/images/blob/main/fraise.jpg" xr:uid="{DCD5D703-E51C-401B-8D37-48A6A98D3753}"/>
-    <hyperlink ref="J142" r:id="rId140" display="https://github.com/olaf-programmeur/images/blob/main/framboise.jpg" xr:uid="{8F33BC22-79D7-49B2-AD38-AC7B2DE00CC4}"/>
-    <hyperlink ref="J207" r:id="rId141" display="https://github.com/olaf-programmeur/images/blob/main/brocoli.jpg" xr:uid="{1DE00C68-E4E5-4E46-B2C4-D8339857392A}"/>
-    <hyperlink ref="J210" r:id="rId142" display="https://github.com/olaf-programmeur/images/blob/main/salade.jpg" xr:uid="{29F90ACB-2CDE-442C-B8D6-496883B4292C}"/>
-    <hyperlink ref="J211" r:id="rId143" display="https://github.com/olaf-programmeur/images/blob/main/betterave.jpg" xr:uid="{0BDF27A7-4A52-40CA-87C1-C6B42A43DFAE}"/>
-    <hyperlink ref="J220" r:id="rId144" display="https://github.com/olaf-programmeur/images/blob/main/pennes.jpg" xr:uid="{02C2C23C-A0CD-4BB3-BFA5-6CDC3A550DBF}"/>
-    <hyperlink ref="J218" r:id="rId145" display="https://github.com/olaf-programmeur/images/blob/main/cornettes.jpg" xr:uid="{C29F3D59-2ED2-421C-A66E-AD8EA0124A11}"/>
-    <hyperlink ref="J264" r:id="rId146" display="https://github.com/olaf-programmeur/images/blob/main/Emile.jpg" xr:uid="{813C8E7F-A1F1-4FB3-9FDC-B446EAD87FFC}"/>
-    <hyperlink ref="J265" r:id="rId147" display="https://github.com/olaf-programmeur/images/blob/main/paul.jpg" xr:uid="{77CE3C10-4D9A-4A0A-9583-2D36B1C462FD}"/>
+    <hyperlink ref="J102" r:id="rId123" display="https://github.com/olaf-programmeur/images/blob/main/oeuf.jpg" xr:uid="{AB36AF05-CE27-469C-A389-F137AC6699D0}"/>
+    <hyperlink ref="J186" r:id="rId124" display="https://github.com/olaf-programmeur/images/blob/main/laura_star.jpg" xr:uid="{D305C3B9-0CBD-434F-B21E-ED312EFC16A5}"/>
+    <hyperlink ref="J263" r:id="rId125" display="https://github.com/olaf-programmeur/images/blob/main/mathilde.jpg" xr:uid="{D8FFFA1F-EEF3-4AC4-80B1-305AC43458FE}"/>
+    <hyperlink ref="J265" r:id="rId126" display="https://github.com/olaf-programmeur/images/blob/main/emma.jpeg" xr:uid="{C0DE091D-F71D-423C-B3E2-E3D5C8568367}"/>
+    <hyperlink ref="J266" r:id="rId127" display="https://github.com/olaf-programmeur/images/blob/main/loic.jpg" xr:uid="{98CD5A56-EE12-46D0-851B-46FF90465BB7}"/>
+    <hyperlink ref="J272" r:id="rId128" display="https://github.com/olaf-programmeur/images/blob/main/barbara.jpg" xr:uid="{FB5E9D99-3034-45ED-B5A8-4196BAF613E6}"/>
+    <hyperlink ref="J280" r:id="rId129" display="https://github.com/olaf-programmeur/images/blob/main/alison.jpg" xr:uid="{1A01A952-3795-4EAB-A237-062CC4D64B69}"/>
+    <hyperlink ref="J273" r:id="rId130" display="https://github.com/olaf-programmeur/images/blob/main/sandrine.jpg" xr:uid="{AA8F1D5E-21A1-4DF4-97B8-BC4400A8C63E}"/>
+    <hyperlink ref="J271" r:id="rId131" display="https://github.com/olaf-programmeur/images/blob/main/olivier.jpg" xr:uid="{7A079B6C-CAEF-487A-9835-CDD17CE4E3FF}"/>
+    <hyperlink ref="J47" r:id="rId132" display="https://github.com/olaf-programmeur/images/blob/main/kpt_ass.png" xr:uid="{739DD512-7187-4ABE-80D2-AB3A75A97B9A}"/>
+    <hyperlink ref="J50" r:id="rId133" display="https://github.com/olaf-programmeur/images/blob/main/mobiliere_ass.png" xr:uid="{FA90ED60-5F49-40C3-8120-9748EC5C0DF6}"/>
+    <hyperlink ref="J51" r:id="rId134" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{51402ACF-C4AF-4E8E-83F6-C10D822E38CB}"/>
+    <hyperlink ref="J52" r:id="rId135" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{D398F53D-8CD1-4BCF-B123-DE35DBD79DDC}"/>
+    <hyperlink ref="J48" r:id="rId136" display="https://github.com/olaf-programmeur/images/blob/main/migros.jpg" xr:uid="{F0E23162-8F08-4FE4-A006-E6DB539A7708}"/>
+    <hyperlink ref="J49" r:id="rId137" display="https://github.com/olaf-programmeur/images/blob/main/raiffeisen.jpg" xr:uid="{714C2B4D-0898-41DB-8A05-E175F7FEBA1B}"/>
+    <hyperlink ref="J142" r:id="rId138" display="https://github.com/olaf-programmeur/images/blob/main/abricot.jpg" xr:uid="{C3A11FAC-028D-46A8-9D2E-0E8E473F0783}"/>
+    <hyperlink ref="J143" r:id="rId139" display="https://github.com/olaf-programmeur/images/blob/main/fraise.jpg" xr:uid="{DCD5D703-E51C-401B-8D37-48A6A98D3753}"/>
+    <hyperlink ref="J144" r:id="rId140" display="https://github.com/olaf-programmeur/images/blob/main/framboise.jpg" xr:uid="{8F33BC22-79D7-49B2-AD38-AC7B2DE00CC4}"/>
+    <hyperlink ref="J209" r:id="rId141" display="https://github.com/olaf-programmeur/images/blob/main/brocoli.jpg" xr:uid="{1DE00C68-E4E5-4E46-B2C4-D8339857392A}"/>
+    <hyperlink ref="J212" r:id="rId142" display="https://github.com/olaf-programmeur/images/blob/main/salade.jpg" xr:uid="{29F90ACB-2CDE-442C-B8D6-496883B4292C}"/>
+    <hyperlink ref="J213" r:id="rId143" display="https://github.com/olaf-programmeur/images/blob/main/betterave.jpg" xr:uid="{0BDF27A7-4A52-40CA-87C1-C6B42A43DFAE}"/>
+    <hyperlink ref="J222" r:id="rId144" display="https://github.com/olaf-programmeur/images/blob/main/pennes.jpg" xr:uid="{02C2C23C-A0CD-4BB3-BFA5-6CDC3A550DBF}"/>
+    <hyperlink ref="J220" r:id="rId145" display="https://github.com/olaf-programmeur/images/blob/main/cornettes.jpg" xr:uid="{C29F3D59-2ED2-421C-A66E-AD8EA0124A11}"/>
+    <hyperlink ref="J267" r:id="rId146" display="https://github.com/olaf-programmeur/images/blob/main/Emile.jpg" xr:uid="{813C8E7F-A1F1-4FB3-9FDC-B446EAD87FFC}"/>
+    <hyperlink ref="J268" r:id="rId147" display="https://github.com/olaf-programmeur/images/blob/main/paul.jpg" xr:uid="{77CE3C10-4D9A-4A0A-9583-2D36B1C462FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId148"/>
@@ -19741,17 +20130,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1267</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -19763,17 +20152,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>1269</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8E5711-F255-4AEB-BFCD-91F812D921BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B8DBC1C-8BCF-4C5F-8DAF-5C71FE9ADB74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catégories" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3442" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="2274">
   <si>
     <t>id</t>
   </si>
@@ -6832,6 +6832,24 @@
   </si>
   <si>
     <t>Lavage et repassage; Où je lave le linge</t>
+  </si>
+  <si>
+    <t>Je porte des botillons l'hiver pour avoir chaud aux pieds.</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/cheveux.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/animaux.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/animaux_domestiques.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/animaux_ferme.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/animaux_sauvages.jpg</t>
   </si>
 </sst>
 </file>
@@ -7560,6 +7578,9 @@
       <c r="F12" t="s">
         <v>51</v>
       </c>
+      <c r="G12" s="15" t="s">
+        <v>2270</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -7663,8 +7684,9 @@
     <hyperlink ref="G3" r:id="rId1" xr:uid="{A625E5E7-4AEE-4A5F-B534-A9D27D0892F3}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{1B6DFCBA-89DE-497A-97AF-C64550D457E5}"/>
     <hyperlink ref="G8" r:id="rId3" xr:uid="{68C145AC-E1F7-45C2-BAB8-AF3153A5A807}"/>
-    <hyperlink ref="G11" r:id="rId4" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{DAA9E084-8DD0-4074-85A0-12C67296F768}"/>
+    <hyperlink ref="G11" r:id="rId4" xr:uid="{DAA9E084-8DD0-4074-85A0-12C67296F768}"/>
     <hyperlink ref="G2" r:id="rId5" xr:uid="{3BF83F10-F877-47AE-BE7E-042FF5158364}"/>
+    <hyperlink ref="G12" r:id="rId6" xr:uid="{C5D9604E-3A26-4D3B-BFFF-804673BB0112}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8593,6 +8615,9 @@
       <c r="F43" t="s">
         <v>225</v>
       </c>
+      <c r="G43" s="15" t="s">
+        <v>2271</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -8613,6 +8638,9 @@
       <c r="F44" t="s">
         <v>229</v>
       </c>
+      <c r="G44" s="15" t="s">
+        <v>2272</v>
+      </c>
     </row>
     <row r="45" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -8632,6 +8660,9 @@
       </c>
       <c r="F45" t="s">
         <v>233</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>2273</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9064,7 +9095,7 @@
     <hyperlink ref="G31" r:id="rId1" xr:uid="{B1D2C25F-2BFD-4013-B573-A3EBCBA523BD}"/>
     <hyperlink ref="G35" r:id="rId2" xr:uid="{9DD21B12-02D6-46B3-A45E-86C86BC69026}"/>
     <hyperlink ref="G38" r:id="rId3" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{E1A481EC-DC5E-4B98-9955-BFFF8EDEEBAE}"/>
-    <hyperlink ref="G39" r:id="rId4" display="https://github.com/olaf-programmeur/images/blob/main/dacia_duster.jpg" xr:uid="{BEF09A6A-8935-406A-95F1-B14481408005}"/>
+    <hyperlink ref="G39" r:id="rId4" xr:uid="{BEF09A6A-8935-406A-95F1-B14481408005}"/>
     <hyperlink ref="G22" r:id="rId5" display="https://github.com/olaf-programmeur/images/blob/main/cuisine.jpg" xr:uid="{F005AB03-5AE8-48E2-8F1D-7623C4DD9321}"/>
     <hyperlink ref="G5" r:id="rId6" display="https://github.com/olaf-programmeur/images/blob/main/viandes.jpg" xr:uid="{E12346B8-DE54-4AD4-9D7C-98A29AAD1809}"/>
     <hyperlink ref="G12" r:id="rId7" display="https://github.com/olaf-programmeur/images/blob/main/instruments_cuivre.jpg" xr:uid="{1D8E67CE-BD0E-4196-A54B-28E0C9767F08}"/>
@@ -9073,6 +9104,9 @@
     <hyperlink ref="G18" r:id="rId10" display="https://github.com/olaf-programmeur/images/blob/main/frere_soeurs_1.jpg" xr:uid="{5E2C43CF-DA38-4552-8C35-E1957A70CB00}"/>
     <hyperlink ref="G53" r:id="rId11" display="https://github.com/olaf-programmeur/images/blob/main/le_tronc.jpg" xr:uid="{17B5D432-5B50-4BAB-BD73-6594AA917C68}"/>
     <hyperlink ref="G2" r:id="rId12" display="https://github.com/olaf-programmeur/images/blob/main/boisson_froide.jpg" xr:uid="{1270DE65-B554-4300-AE20-1E37EFBDD378}"/>
+    <hyperlink ref="G43" r:id="rId13" xr:uid="{18F7AE91-F4D9-469B-A7F0-04336D68A02A}"/>
+    <hyperlink ref="G44" r:id="rId14" xr:uid="{AC97664E-1AAD-4E02-A538-756E642094DF}"/>
+    <hyperlink ref="G45" r:id="rId15" xr:uid="{CCCFAA0B-D510-4D68-83CB-D177FFA979C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -11351,7 +11385,7 @@
         <v>1321</v>
       </c>
       <c r="E82" t="s">
-        <v>434</v>
+        <v>2268</v>
       </c>
       <c r="G82" t="s">
         <v>137</v>
@@ -14565,7 +14599,7 @@
       </c>
       <c r="H197" s="6"/>
       <c r="J197" s="16" t="s">
-        <v>2040</v>
+        <v>2269</v>
       </c>
       <c r="K197" t="s">
         <v>1790</v>
@@ -19306,7 +19340,7 @@
     <hyperlink ref="J188" r:id="rId74" display="https://github.com/olaf-programmeur/images/blob/main/canap%C3%A9.jpg" xr:uid="{19EF0F4B-32A1-4B2B-BE17-D29B9945856D}"/>
     <hyperlink ref="J190" r:id="rId75" display="https://github.com/olaf-programmeur/images/blob/main/meuble_salon.jpg" xr:uid="{32CF85D7-C1C4-4859-938E-426775026EB3}"/>
     <hyperlink ref="J193" r:id="rId76" display="https://github.com/olaf-programmeur/images/blob/main/ventre.jpg" xr:uid="{F7C358E3-5EF3-4C2E-814C-EB548E2B0F08}"/>
-    <hyperlink ref="J197" r:id="rId77" display="https://github.com/olaf-programmeur/images/blob/main/ventre.jpg" xr:uid="{85EEC448-4DC2-467E-A22A-6564E5B84CE7}"/>
+    <hyperlink ref="J197" r:id="rId77" xr:uid="{85EEC448-4DC2-467E-A22A-6564E5B84CE7}"/>
     <hyperlink ref="J201" r:id="rId78" display="https://github.com/olaf-programmeur/images/blob/main/dents.jpg" xr:uid="{E934A777-D378-44CC-BDAD-4C610CEB108A}"/>
     <hyperlink ref="J202" r:id="rId79" display="https://github.com/olaf-programmeur/images/blob/main/oreille.jpg" xr:uid="{C1440963-B371-4D18-8673-7735F862D76C}"/>
     <hyperlink ref="J203" r:id="rId80" display="https://github.com/olaf-programmeur/images/blob/main/legumes.webp" xr:uid="{30E68B4E-796A-4F25-BF68-928BD963ECA6}"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DCD779-B298-4536-BC49-E93C7A2E6E83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49C91DB-B0CD-4F7A-AC0F-01110C946238}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catégories" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="2585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3951" uniqueCount="2592">
   <si>
     <t>id</t>
   </si>
@@ -7581,9 +7581,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/chuv.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/alterations.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/asm.png</t>
   </si>
   <si>
@@ -7644,9 +7641,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/raclette.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/les_silences.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/stores.png</t>
   </si>
   <si>
@@ -7659,9 +7653,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bateaux.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/julien.jpg</t>
-  </si>
-  <si>
     <t>r_eva</t>
   </si>
   <si>
@@ -7671,9 +7662,6 @@
     <t>Eva est la copine de Julien, elle joue du trombone à Valaisia.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/julien_eva.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/vitroceram.png</t>
   </si>
   <si>
@@ -7683,18 +7671,12 @@
     <t>Le caquelon est un récipient en céramique et le réchaud est le support sur lequel on pose le caquelon. Une flamme est placée en dessous et ils permettent de garder la fondue chaude à table. On mange la fondue avec des fourchettes.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/salle_bain.png</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/divers_musique.png</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/avs.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/orae.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/sirop.png</t>
   </si>
   <si>
@@ -7731,9 +7713,6 @@
     <t>Les avocats grossissent sur l'arbre appelé avocatier où ils peuvent rester plusieurs mois, mais ne peuvent commencer à mûrir qu'une fois cueillis. Ils sont verts ou noirs et ont un noyau au centre.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/avocat.jpg</t>
-  </si>
-  <si>
     <t>le porc</t>
   </si>
   <si>
@@ -7783,6 +7762,48 @@
   </si>
   <si>
     <t>iphone in hand</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/cafe_the.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/julien.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/julien_eva.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/cp_orae.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/toiture.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/salle_bain.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/silences.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/alterations.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/nourriture.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/fruit_avocat.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/oeuf_au_plat.jpg</t>
+  </si>
+  <si>
+    <t>destinations</t>
+  </si>
+  <si>
+    <t>Les endroits</t>
+  </si>
+  <si>
+    <t>lac de Derborence</t>
   </si>
 </sst>
 </file>
@@ -7870,7 +7891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7896,6 +7917,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8296,333 +8318,338 @@
     </row>
     <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>2556</v>
       </c>
       <c r="B3" s="11">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>1916</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B4" s="11">
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
+        <v>48</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>2586</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B5" s="11">
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>2131</v>
+        <v>2270</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>2004</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B6" s="11">
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>2271</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B7" s="11">
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>2272</v>
+        <v>2131</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2562</v>
+        <v>15</v>
       </c>
       <c r="B8" s="11">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>2268</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>2563</v>
+        <v>18</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B9" s="11">
         <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>2272</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B10" s="11">
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>1963</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11">
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>1963</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11">
         <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>2275</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>2149</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B13" s="11">
         <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B14" s="11">
         <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11">
         <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>1829</v>
       </c>
       <c r="B16">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
+        <v>1830</v>
       </c>
       <c r="E16" t="s">
         <v>52</v>
       </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1829</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
-        <v>1830</v>
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>52</v>
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A3:G16">
-    <sortCondition ref="B3:B16"/>
+  <sortState ref="A2:G17">
+    <sortCondition ref="B2:B17"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{A625E5E7-4AEE-4A5F-B534-A9D27D0892F3}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{1B6DFCBA-89DE-497A-97AF-C64550D457E5}"/>
-    <hyperlink ref="G8" r:id="rId3" xr:uid="{68C145AC-E1F7-45C2-BAB8-AF3153A5A807}"/>
-    <hyperlink ref="G11" r:id="rId4" xr:uid="{DAA9E084-8DD0-4074-85A0-12C67296F768}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{A625E5E7-4AEE-4A5F-B534-A9D27D0892F3}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{1B6DFCBA-89DE-497A-97AF-C64550D457E5}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{68C145AC-E1F7-45C2-BAB8-AF3153A5A807}"/>
+    <hyperlink ref="G10" r:id="rId4" xr:uid="{DAA9E084-8DD0-4074-85A0-12C67296F768}"/>
     <hyperlink ref="G2" r:id="rId5" xr:uid="{3BF83F10-F877-47AE-BE7E-042FF5158364}"/>
-    <hyperlink ref="G12" r:id="rId6" xr:uid="{C5D9604E-3A26-4D3B-BFFF-804673BB0112}"/>
+    <hyperlink ref="G11" r:id="rId6" xr:uid="{C5D9604E-3A26-4D3B-BFFF-804673BB0112}"/>
+    <hyperlink ref="G4" r:id="rId7" xr:uid="{6ACE99C1-3826-4719-B09E-C8DF87D24E73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8630,7 +8657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="22.796875" customWidth="1"/>
@@ -8701,6 +8728,9 @@
       <c r="F3" t="s">
         <v>72</v>
       </c>
+      <c r="G3" s="14" t="s">
+        <v>2578</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -8974,7 +9004,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9211,6 +9241,9 @@
       <c r="F27" t="s">
         <v>150</v>
       </c>
+      <c r="G27" s="14" t="s">
+        <v>2583</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -9840,227 +9873,247 @@
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>186</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="57" spans="1:7" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="27" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B57" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C57" t="s">
-        <v>2290</v>
-      </c>
-      <c r="D57" s="23" t="s">
+      <c r="C57" s="27" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="E57" t="s">
-        <v>188</v>
+      <c r="E57" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" s="27" t="s">
+        <v>2591</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="22" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D58" s="23" t="s">
         <v>187</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
-      </c>
-      <c r="F58" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B59" t="s">
         <v>39</v>
       </c>
-      <c r="C59" t="s">
-        <v>2289</v>
+      <c r="C59" s="22" t="s">
+        <v>2288</v>
       </c>
       <c r="D59" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F59" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>183</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>254</v>
+        <v>2289</v>
       </c>
       <c r="D60" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E60" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="22" t="s">
-        <v>2304</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>259</v>
+      <c r="C61" t="s">
+        <v>254</v>
+      </c>
+      <c r="D61" t="s">
+        <v>184</v>
       </c>
       <c r="E61" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F61" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B62" t="s">
         <v>65</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="F62" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>2296</v>
-      </c>
-      <c r="D63" t="s">
-        <v>210</v>
+        <v>2303</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="E63" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="D64" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>218</v>
+        <v>52</v>
       </c>
       <c r="F64" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B65" t="s">
         <v>50</v>
       </c>
       <c r="C65" s="22" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D65" t="s">
+        <v>217</v>
+      </c>
+      <c r="E65" t="s">
+        <v>218</v>
+      </c>
+      <c r="F65" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="22" t="s">
         <v>2297</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D66" t="s">
         <v>213</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E66" t="s">
         <v>214</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F66" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>2052</v>
-      </c>
-      <c r="B66" t="s">
-        <v>2269</v>
-      </c>
-      <c r="C66" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D66" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B67" s="22" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B67" t="s">
         <v>2269</v>
       </c>
       <c r="C67" t="s">
-        <v>2146</v>
+        <v>2312</v>
       </c>
       <c r="D67" t="s">
-        <v>1833</v>
+        <v>66</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>57</v>
       </c>
       <c r="F67" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F68" t="s">
         <v>1834</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A5:H66">
-    <sortCondition ref="B5:B66"/>
-    <sortCondition ref="C5:C66"/>
+  <sortState ref="A5:H67">
+    <sortCondition ref="B5:B67"/>
+    <sortCondition ref="C5:C67"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G33" r:id="rId1" xr:uid="{B1D2C25F-2BFD-4013-B573-A3EBCBA523BD}"/>
@@ -10081,6 +10134,8 @@
     <hyperlink ref="G20" r:id="rId16" xr:uid="{2690C58E-F744-4C1B-A88D-712192B71B93}"/>
     <hyperlink ref="G22" r:id="rId17" xr:uid="{CCE9BE74-9FF7-4CFC-A256-DD1AF0023E4D}"/>
     <hyperlink ref="G16" r:id="rId18" xr:uid="{FB58FC61-C097-468C-AB23-4B26D6A54FA7}"/>
+    <hyperlink ref="G3" r:id="rId19" xr:uid="{886DF703-243B-44C6-8B60-5D2B5993A203}"/>
+    <hyperlink ref="G27" r:id="rId20" xr:uid="{F950230B-1948-4689-9055-81D93185C7E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -10090,7 +10145,7 @@
           <x14:formula1>
             <xm:f>Catégories!$C$2:$C$50</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B75</xm:sqref>
+          <xm:sqref>B2:B76</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10297,7 +10352,7 @@
       <c r="H7" s="6"/>
       <c r="J7" s="24"/>
       <c r="K7" t="s">
-        <v>2584</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -11005,7 +11060,7 @@
       </c>
       <c r="H32" s="6"/>
       <c r="J32" s="14" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="M32" s="17">
         <v>7</v>
@@ -11029,7 +11084,7 @@
       </c>
       <c r="H33" s="6"/>
       <c r="J33" s="14" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="M33" s="17">
         <v>1</v>
@@ -11053,7 +11108,7 @@
       </c>
       <c r="H34" s="6"/>
       <c r="J34" s="14" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="M34" s="17">
         <v>2</v>
@@ -11077,7 +11132,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="J35" s="14" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="M35" s="17">
         <v>3</v>
@@ -11125,7 +11180,7 @@
       </c>
       <c r="H37" s="6"/>
       <c r="J37" s="14" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="M37" s="17">
         <v>5</v>
@@ -11151,7 +11206,7 @@
         <v>1830</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="M38" s="17">
         <v>6</v>
@@ -11328,7 +11383,7 @@
       </c>
       <c r="H44" s="6"/>
       <c r="J44" s="14" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
       <c r="K44" t="s">
         <v>497</v>
@@ -11358,7 +11413,7 @@
       </c>
       <c r="H45" s="6"/>
       <c r="J45" s="14" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
       <c r="K45" t="s">
         <v>501</v>
@@ -11732,14 +11787,14 @@
         <v>272</v>
       </c>
       <c r="D58" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="G58" t="s">
         <v>2051</v>
       </c>
       <c r="H58" s="6"/>
       <c r="J58" s="14" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="M58">
         <v>19</v>
@@ -11763,7 +11818,7 @@
       </c>
       <c r="H59" s="6"/>
       <c r="J59" s="14" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L59" s="8"/>
       <c r="M59">
@@ -12176,7 +12231,7 @@
       </c>
       <c r="H73" s="6"/>
       <c r="J73" s="14" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="M73">
         <v>1</v>
@@ -12200,7 +12255,7 @@
       </c>
       <c r="H74" s="6"/>
       <c r="J74" s="14" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="M74">
         <v>2</v>
@@ -12224,7 +12279,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -12248,7 +12303,7 @@
       </c>
       <c r="H76" s="6"/>
       <c r="J76" s="14" t="s">
-        <v>2517</v>
+        <v>2585</v>
       </c>
       <c r="M76">
         <v>4</v>
@@ -12272,7 +12327,7 @@
       </c>
       <c r="H77" s="6"/>
       <c r="J77" s="14" t="s">
-        <v>2538</v>
+        <v>2584</v>
       </c>
       <c r="M77">
         <v>5</v>
@@ -12296,7 +12351,7 @@
       </c>
       <c r="H78" s="6"/>
       <c r="J78" s="14" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="M78">
         <v>6</v>
@@ -12320,7 +12375,7 @@
       </c>
       <c r="H79" s="6"/>
       <c r="J79" s="14" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="M79">
         <v>7</v>
@@ -12728,7 +12783,7 @@
       </c>
       <c r="H93" s="6"/>
       <c r="J93" s="14" t="s">
-        <v>2581</v>
+        <v>2574</v>
       </c>
       <c r="K93" t="s">
         <v>767</v>
@@ -12758,7 +12813,7 @@
       </c>
       <c r="H94" s="6"/>
       <c r="J94" s="14" t="s">
-        <v>2582</v>
+        <v>2575</v>
       </c>
       <c r="K94" t="s">
         <v>758</v>
@@ -12968,7 +13023,7 @@
       </c>
       <c r="H101" s="6"/>
       <c r="J101" s="14" t="s">
-        <v>2583</v>
+        <v>2576</v>
       </c>
       <c r="K101" t="s">
         <v>781</v>
@@ -13911,7 +13966,7 @@
       </c>
       <c r="H135" s="6"/>
       <c r="J135" s="14" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="M135">
         <v>1</v>
@@ -13936,7 +13991,7 @@
       </c>
       <c r="H136" s="6"/>
       <c r="J136" s="14" t="s">
-        <v>2554</v>
+        <v>2581</v>
       </c>
       <c r="M136">
         <v>2</v>
@@ -14531,7 +14586,7 @@
       </c>
       <c r="H160" s="6"/>
       <c r="J160" s="14" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
       <c r="K160" t="s">
         <v>944</v>
@@ -14662,26 +14717,26 @@
     </row>
     <row r="165" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>2573</v>
+        <v>2566</v>
       </c>
       <c r="B165" t="s">
-        <v>2574</v>
+        <v>2567</v>
       </c>
       <c r="C165" t="s">
         <v>272</v>
       </c>
       <c r="D165" t="s">
-        <v>2575</v>
+        <v>2568</v>
       </c>
       <c r="G165" s="20" t="s">
         <v>2276</v>
       </c>
       <c r="H165" s="6"/>
       <c r="J165" s="14" t="s">
-        <v>2576</v>
+        <v>2569</v>
       </c>
       <c r="M165">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -14915,7 +14970,7 @@
       </c>
       <c r="H173" s="6"/>
       <c r="J173" s="14" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
       <c r="K173" t="s">
         <v>279</v>
@@ -15428,7 +15483,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1898</v>
       </c>
@@ -15452,7 +15507,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1114</v>
       </c>
@@ -15477,7 +15532,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1110</v>
       </c>
@@ -15502,7 +15557,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="196" spans="1:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>1122</v>
       </c>
@@ -15526,7 +15581,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="20" t="s">
         <v>1118</v>
       </c>
@@ -15551,7 +15606,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="21" t="s">
         <v>1089</v>
       </c>
@@ -15576,7 +15631,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1101</v>
       </c>
@@ -15601,7 +15656,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="23" t="s">
         <v>1105</v>
       </c>
@@ -15626,7 +15681,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1073</v>
       </c>
@@ -15651,7 +15706,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1097</v>
       </c>
@@ -15676,7 +15731,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1069</v>
       </c>
@@ -15701,7 +15756,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1077</v>
       </c>
@@ -15726,7 +15781,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1093</v>
       </c>
@@ -15751,7 +15806,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1085</v>
       </c>
@@ -15776,7 +15831,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1081</v>
       </c>
@@ -15801,401 +15856,377 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1164</v>
+        <v>2342</v>
       </c>
       <c r="B208" t="s">
-        <v>1456</v>
+        <v>2163</v>
       </c>
       <c r="C208" t="s">
         <v>272</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E208" t="s">
-        <v>1166</v>
+        <v>2164</v>
       </c>
       <c r="G208" s="22" t="s">
-        <v>2304</v>
+        <v>2590</v>
       </c>
       <c r="H208" s="6"/>
-      <c r="J208" s="23"/>
-      <c r="K208" t="s">
-        <v>1167</v>
+      <c r="J208" s="14" t="s">
+        <v>2325</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1168</v>
+        <v>2383</v>
       </c>
       <c r="B209" t="s">
-        <v>1457</v>
+        <v>2245</v>
       </c>
       <c r="C209" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E209" s="23" t="s">
-        <v>1170</v>
-      </c>
+        <v>2246</v>
+      </c>
+      <c r="E209" s="23"/>
       <c r="G209" t="s">
-        <v>2304</v>
+        <v>2590</v>
       </c>
       <c r="H209" s="6"/>
-      <c r="J209" s="23"/>
-      <c r="K209" t="s">
-        <v>1171</v>
+      <c r="J209" s="14" t="s">
+        <v>2415</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1785</v>
+        <v>2370</v>
       </c>
       <c r="B210" t="s">
-        <v>2013</v>
+        <v>2219</v>
       </c>
       <c r="C210" t="s">
         <v>272</v>
       </c>
       <c r="D210" t="s">
-        <v>922</v>
-      </c>
-      <c r="E210" s="26" t="s">
-        <v>923</v>
-      </c>
+        <v>2220</v>
+      </c>
+      <c r="E210" s="26"/>
       <c r="G210" s="6" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H210" s="6"/>
-      <c r="J210" s="26"/>
-      <c r="K210" t="s">
-        <v>1787</v>
+      <c r="J210" s="14" t="s">
+        <v>2405</v>
       </c>
       <c r="M210">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1797</v>
+        <v>2175</v>
       </c>
       <c r="B211" t="s">
-        <v>1804</v>
+        <v>2176</v>
       </c>
       <c r="C211" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D211" t="s">
-        <v>1811</v>
-      </c>
-      <c r="E211" s="5"/>
+        <v>2177</v>
+      </c>
+      <c r="E211" s="27"/>
       <c r="G211" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H211" s="6"/>
       <c r="J211" s="14" t="s">
-        <v>1925</v>
-      </c>
-      <c r="K211" t="s">
-        <v>1818</v>
+        <v>2555</v>
       </c>
       <c r="M211">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1798</v>
+        <v>2340</v>
       </c>
       <c r="B212" t="s">
-        <v>1805</v>
+        <v>2159</v>
       </c>
       <c r="C212" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D212" t="s">
-        <v>1812</v>
-      </c>
-      <c r="E212" s="5"/>
+        <v>2160</v>
+      </c>
+      <c r="E212" s="27"/>
       <c r="G212" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H212" s="6"/>
       <c r="J212" s="14" t="s">
-        <v>1926</v>
-      </c>
-      <c r="K212" t="s">
-        <v>1819</v>
+        <v>2324</v>
       </c>
       <c r="M212">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1803</v>
+        <v>2341</v>
       </c>
       <c r="B213" t="s">
-        <v>1809</v>
+        <v>2161</v>
       </c>
       <c r="C213" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D213" t="s">
-        <v>1813</v>
-      </c>
-      <c r="E213" s="5"/>
+        <v>2162</v>
+      </c>
+      <c r="E213" s="27"/>
       <c r="G213" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H213" s="6"/>
       <c r="J213" s="14" t="s">
-        <v>1927</v>
-      </c>
-      <c r="K213" t="s">
-        <v>1821</v>
+        <v>2326</v>
       </c>
       <c r="M213">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1802</v>
+        <v>2371</v>
       </c>
       <c r="B214" t="s">
-        <v>1806</v>
+        <v>2221</v>
       </c>
       <c r="C214" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D214" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E214" s="5"/>
+        <v>2222</v>
+      </c>
+      <c r="E214" s="27"/>
       <c r="G214" s="20" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H214" s="6"/>
       <c r="J214" s="14" t="s">
-        <v>1928</v>
-      </c>
-      <c r="K214" t="s">
-        <v>1820</v>
+        <v>2406</v>
       </c>
       <c r="M214">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>2059</v>
+        <v>2354</v>
       </c>
       <c r="B215" t="s">
-        <v>2062</v>
+        <v>2189</v>
       </c>
       <c r="C215" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D215" t="s">
-        <v>2065</v>
+        <v>2190</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H215" s="6"/>
       <c r="J215" s="14" t="s">
-        <v>2119</v>
+        <v>2393</v>
       </c>
       <c r="M215">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>2060</v>
+        <v>2364</v>
       </c>
       <c r="B216" t="s">
-        <v>2063</v>
+        <v>2400</v>
       </c>
       <c r="C216" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>2066</v>
+        <v>2208</v>
       </c>
       <c r="E216" s="23"/>
       <c r="G216" s="20" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H216" s="6"/>
       <c r="J216" s="14" t="s">
-        <v>2120</v>
+        <v>2399</v>
       </c>
       <c r="M216">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>2061</v>
+        <v>2365</v>
       </c>
       <c r="B217" t="s">
-        <v>2064</v>
+        <v>2209</v>
       </c>
       <c r="C217" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D217" t="s">
-        <v>2067</v>
+        <v>2210</v>
       </c>
       <c r="E217" s="26"/>
       <c r="G217" s="20" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H217" s="6"/>
       <c r="J217" s="14" t="s">
-        <v>2121</v>
+        <v>2401</v>
       </c>
       <c r="M217">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1799</v>
+        <v>2381</v>
       </c>
       <c r="B218" t="s">
-        <v>1807</v>
+        <v>2241</v>
       </c>
       <c r="C218" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D218" t="s">
-        <v>1815</v>
-      </c>
-      <c r="E218" s="5"/>
+        <v>2242</v>
+      </c>
+      <c r="E218" s="27"/>
       <c r="G218" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H218" s="6"/>
       <c r="J218" s="14" t="s">
-        <v>1929</v>
-      </c>
-      <c r="K218" t="s">
-        <v>1822</v>
+        <v>2413</v>
       </c>
       <c r="M218">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1800</v>
+        <v>2344</v>
       </c>
       <c r="B219" t="s">
-        <v>1810</v>
+        <v>2167</v>
       </c>
       <c r="C219" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D219" t="s">
-        <v>1816</v>
-      </c>
-      <c r="E219" s="5"/>
+        <v>2168</v>
+      </c>
+      <c r="E219" s="27"/>
       <c r="G219" s="20" t="s">
-        <v>2309</v>
+        <v>2590</v>
       </c>
       <c r="H219" s="6"/>
-      <c r="J219" s="26"/>
-      <c r="K219" t="s">
-        <v>1823</v>
+      <c r="J219" s="14" t="s">
+        <v>2330</v>
       </c>
       <c r="M219">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1801</v>
+        <v>1164</v>
       </c>
       <c r="B220" t="s">
-        <v>1808</v>
+        <v>1456</v>
       </c>
       <c r="C220" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D220" t="s">
-        <v>1817</v>
-      </c>
-      <c r="E220" s="5"/>
+        <v>1165</v>
+      </c>
+      <c r="E220" s="27" t="s">
+        <v>1166</v>
+      </c>
       <c r="G220" s="20" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="H220" s="6"/>
-      <c r="J220" s="14" t="s">
-        <v>1930</v>
-      </c>
+      <c r="J220" s="27"/>
       <c r="K220" t="s">
-        <v>1824</v>
-      </c>
-      <c r="M220">
-        <v>11</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>2564</v>
+        <v>1168</v>
       </c>
       <c r="B221" t="s">
-        <v>2565</v>
+        <v>1457</v>
       </c>
       <c r="C221" t="s">
         <v>484</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>2566</v>
+        <v>1169</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1170</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="H221" s="6"/>
-      <c r="J221" s="15" t="s">
-        <v>2567</v>
-      </c>
-      <c r="M221">
-        <v>12</v>
+      <c r="J221" s="27"/>
+      <c r="K221" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="222" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1617</v>
+        <v>1785</v>
       </c>
       <c r="B222" t="s">
-        <v>740</v>
+        <v>2013</v>
       </c>
       <c r="C222" t="s">
         <v>272</v>
       </c>
       <c r="D222" t="s">
-        <v>1293</v>
+        <v>922</v>
       </c>
       <c r="E222" t="s">
-        <v>741</v>
+        <v>923</v>
       </c>
       <c r="G222" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H222" s="6"/>
-      <c r="J222" s="14" t="s">
-        <v>1948</v>
-      </c>
+      <c r="J222" s="27"/>
       <c r="K222" t="s">
-        <v>740</v>
+        <v>1787</v>
       </c>
       <c r="M222">
         <v>1</v>
@@ -16203,29 +16234,27 @@
     </row>
     <row r="223" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1628</v>
+        <v>1797</v>
       </c>
       <c r="B223" t="s">
-        <v>757</v>
+        <v>1804</v>
       </c>
       <c r="C223" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D223" t="s">
-        <v>1700</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1699</v>
-      </c>
+        <v>1811</v>
+      </c>
+      <c r="E223" s="5"/>
       <c r="G223" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H223" s="6"/>
       <c r="J223" s="14" t="s">
-        <v>1949</v>
+        <v>1925</v>
       </c>
       <c r="K223" t="s">
-        <v>757</v>
+        <v>1818</v>
       </c>
       <c r="M223">
         <v>2</v>
@@ -16233,29 +16262,27 @@
     </row>
     <row r="224" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1625</v>
+        <v>1798</v>
       </c>
       <c r="B224" t="s">
-        <v>754</v>
+        <v>1805</v>
       </c>
       <c r="C224" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D224" t="s">
-        <v>1298</v>
-      </c>
-      <c r="E224" t="s">
-        <v>755</v>
-      </c>
+        <v>1812</v>
+      </c>
+      <c r="E224" s="5"/>
       <c r="G224" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H224" s="6"/>
-      <c r="J224" s="23" t="s">
-        <v>756</v>
+      <c r="J224" s="14" t="s">
+        <v>1926</v>
       </c>
       <c r="K224" t="s">
-        <v>754</v>
+        <v>1819</v>
       </c>
       <c r="M224">
         <v>3</v>
@@ -16263,29 +16290,27 @@
     </row>
     <row r="225" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1618</v>
+        <v>1803</v>
       </c>
       <c r="B225" t="s">
-        <v>742</v>
+        <v>1809</v>
       </c>
       <c r="C225" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D225" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E225" t="s">
-        <v>743</v>
-      </c>
+        <v>1813</v>
+      </c>
+      <c r="E225" s="5"/>
       <c r="G225" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H225" s="6"/>
-      <c r="J225" s="23" t="s">
-        <v>744</v>
+      <c r="J225" s="14" t="s">
+        <v>1927</v>
       </c>
       <c r="K225" t="s">
-        <v>742</v>
+        <v>1821</v>
       </c>
       <c r="M225">
         <v>4</v>
@@ -16293,29 +16318,27 @@
     </row>
     <row r="226" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1619</v>
+        <v>1802</v>
       </c>
       <c r="B226" t="s">
-        <v>745</v>
+        <v>1806</v>
       </c>
       <c r="C226" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D226" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E226" t="s">
-        <v>746</v>
-      </c>
+        <v>1814</v>
+      </c>
+      <c r="E226" s="5"/>
       <c r="G226" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H226" s="6"/>
-      <c r="J226" s="21" t="s">
-        <v>747</v>
+      <c r="J226" s="14" t="s">
+        <v>1928</v>
       </c>
       <c r="K226" t="s">
-        <v>745</v>
+        <v>1820</v>
       </c>
       <c r="M226">
         <v>5</v>
@@ -16323,29 +16346,23 @@
     </row>
     <row r="227" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1620</v>
+        <v>2059</v>
       </c>
       <c r="B227" t="s">
-        <v>748</v>
+        <v>2062</v>
       </c>
       <c r="C227" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E227" t="s">
-        <v>749</v>
+        <v>2065</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H227" s="6"/>
-      <c r="J227" s="23" t="s">
-        <v>750</v>
-      </c>
-      <c r="K227" t="s">
-        <v>748</v>
+      <c r="J227" s="14" t="s">
+        <v>2119</v>
       </c>
       <c r="M227">
         <v>6</v>
@@ -16353,29 +16370,23 @@
     </row>
     <row r="228" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1621</v>
+        <v>2060</v>
       </c>
       <c r="B228" t="s">
-        <v>751</v>
+        <v>2063</v>
       </c>
       <c r="C228" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D228" s="19" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E228" t="s">
-        <v>752</v>
+        <v>2066</v>
       </c>
       <c r="G228" s="20" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="H228" s="6"/>
-      <c r="J228" s="26" t="s">
-        <v>753</v>
-      </c>
-      <c r="K228" t="s">
-        <v>751</v>
+      <c r="J228" s="14" t="s">
+        <v>2120</v>
       </c>
       <c r="M228">
         <v>7</v>
@@ -16383,976 +16394,1028 @@
     </row>
     <row r="229" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1610</v>
+        <v>2061</v>
       </c>
       <c r="B229" t="s">
-        <v>722</v>
+        <v>2064</v>
       </c>
       <c r="C229" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D229" t="s">
-        <v>723</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1697</v>
+        <v>2067</v>
       </c>
       <c r="G229" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="H229" s="6"/>
-      <c r="J229" s="26" t="s">
-        <v>724</v>
-      </c>
-      <c r="K229" t="s">
-        <v>722</v>
+      <c r="J229" s="14" t="s">
+        <v>2121</v>
       </c>
       <c r="M229">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1611</v>
+        <v>1799</v>
       </c>
       <c r="B230" t="s">
-        <v>725</v>
+        <v>1807</v>
       </c>
       <c r="C230" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D230" t="s">
-        <v>1292</v>
-      </c>
-      <c r="E230" t="s">
-        <v>726</v>
-      </c>
+        <v>1815</v>
+      </c>
+      <c r="E230" s="5"/>
       <c r="G230" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="H230" s="6"/>
       <c r="J230" s="14" t="s">
-        <v>2577</v>
+        <v>1929</v>
       </c>
       <c r="K230" t="s">
-        <v>725</v>
+        <v>1822</v>
       </c>
       <c r="M230">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1616</v>
+        <v>1800</v>
       </c>
       <c r="B231" t="s">
-        <v>738</v>
+        <v>1810</v>
       </c>
       <c r="C231" t="s">
-        <v>1106</v>
+        <v>484</v>
       </c>
       <c r="D231" t="s">
-        <v>739</v>
-      </c>
-      <c r="E231" t="s">
-        <v>1698</v>
-      </c>
+        <v>1816</v>
+      </c>
+      <c r="E231" s="5"/>
       <c r="G231" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="H231" s="6"/>
-      <c r="J231" s="14" t="s">
-        <v>1951</v>
-      </c>
+      <c r="J231" s="27"/>
       <c r="K231" t="s">
-        <v>738</v>
+        <v>1823</v>
       </c>
       <c r="M231">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1615</v>
+        <v>1801</v>
       </c>
       <c r="B232" t="s">
-        <v>735</v>
+        <v>1808</v>
       </c>
       <c r="C232" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D232" t="s">
-        <v>736</v>
-      </c>
-      <c r="E232" t="s">
-        <v>737</v>
-      </c>
+        <v>1817</v>
+      </c>
+      <c r="E232" s="5"/>
       <c r="G232" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="H232" s="6"/>
       <c r="J232" s="14" t="s">
-        <v>2423</v>
+        <v>1930</v>
       </c>
       <c r="K232" t="s">
-        <v>735</v>
+        <v>1824</v>
       </c>
       <c r="M232">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1614</v>
+        <v>2558</v>
       </c>
       <c r="B233" t="s">
-        <v>732</v>
+        <v>2559</v>
       </c>
       <c r="C233" t="s">
         <v>484</v>
       </c>
       <c r="D233" t="s">
-        <v>733</v>
-      </c>
-      <c r="E233" t="s">
-        <v>734</v>
+        <v>2560</v>
       </c>
       <c r="G233" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="H233" s="6"/>
-      <c r="J233" s="14" t="s">
-        <v>2578</v>
-      </c>
-      <c r="K233" t="s">
-        <v>732</v>
+      <c r="J233" s="15" t="s">
+        <v>2587</v>
       </c>
       <c r="M233">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="B234" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="C234" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D234" t="s">
-        <v>728</v>
+        <v>1293</v>
       </c>
       <c r="E234" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="G234" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="H234" s="6"/>
       <c r="J234" s="14" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="K234" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="M234">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="23" t="s">
-        <v>1613</v>
+        <v>1628</v>
       </c>
       <c r="B235" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="C235" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D235" t="s">
-        <v>1291</v>
+        <v>1700</v>
       </c>
       <c r="E235" t="s">
-        <v>731</v>
+        <v>1699</v>
       </c>
       <c r="G235" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="H235" s="6"/>
       <c r="J235" s="14" t="s">
-        <v>2579</v>
+        <v>1949</v>
       </c>
       <c r="K235" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="M235">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="26" t="s">
-        <v>1784</v>
+        <v>1625</v>
       </c>
       <c r="B236" t="s">
-        <v>2012</v>
+        <v>754</v>
       </c>
       <c r="C236" t="s">
         <v>272</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>924</v>
+        <v>1298</v>
       </c>
       <c r="E236" t="s">
-        <v>925</v>
+        <v>755</v>
       </c>
       <c r="G236" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="H236" s="6"/>
-      <c r="J236" s="15" t="s">
-        <v>2426</v>
+      <c r="J236" s="27" t="s">
+        <v>756</v>
       </c>
       <c r="K236" t="s">
-        <v>926</v>
+        <v>754</v>
       </c>
       <c r="M236">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1499</v>
+        <v>1618</v>
       </c>
       <c r="B237" t="s">
-        <v>1837</v>
+        <v>742</v>
       </c>
       <c r="C237" t="s">
         <v>272</v>
       </c>
       <c r="D237" t="s">
-        <v>1217</v>
+        <v>1294</v>
       </c>
       <c r="E237" t="s">
-        <v>351</v>
+        <v>743</v>
       </c>
       <c r="G237" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="H237" s="6"/>
-      <c r="J237" s="14" t="s">
-        <v>1941</v>
+      <c r="J237" s="27" t="s">
+        <v>744</v>
       </c>
       <c r="K237" t="s">
-        <v>350</v>
+        <v>742</v>
       </c>
       <c r="M237">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="10" t="s">
-        <v>1772</v>
+      <c r="A238" s="27" t="s">
+        <v>1619</v>
       </c>
       <c r="B238" t="s">
-        <v>1773</v>
+        <v>745</v>
       </c>
       <c r="C238" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D238" t="s">
-        <v>1780</v>
+        <v>1295</v>
       </c>
       <c r="E238" t="s">
-        <v>1781</v>
+        <v>746</v>
       </c>
       <c r="G238" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="H238" s="6"/>
-      <c r="J238" s="15" t="s">
-        <v>1942</v>
+      <c r="J238" s="27" t="s">
+        <v>747</v>
+      </c>
+      <c r="K238" t="s">
+        <v>745</v>
       </c>
       <c r="M238">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1774</v>
+        <v>1620</v>
       </c>
       <c r="B239" t="s">
-        <v>1775</v>
+        <v>748</v>
       </c>
       <c r="C239" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D239" t="s">
-        <v>1782</v>
+        <v>1296</v>
       </c>
       <c r="E239" t="s">
-        <v>1783</v>
+        <v>749</v>
       </c>
       <c r="G239" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="H239" s="6"/>
-      <c r="J239" s="15" t="s">
-        <v>1943</v>
+      <c r="J239" s="27" t="s">
+        <v>750</v>
+      </c>
+      <c r="K239" t="s">
+        <v>748</v>
       </c>
       <c r="M239">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1778</v>
+        <v>1621</v>
       </c>
       <c r="B240" t="s">
-        <v>1779</v>
+        <v>751</v>
       </c>
       <c r="C240" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D240" t="s">
-        <v>1788</v>
+        <v>1297</v>
       </c>
       <c r="E240" t="s">
-        <v>1789</v>
+        <v>752</v>
       </c>
       <c r="G240" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="H240" s="6"/>
-      <c r="J240" s="15" t="s">
-        <v>1944</v>
+      <c r="J240" s="27" t="s">
+        <v>753</v>
+      </c>
+      <c r="K240" t="s">
+        <v>751</v>
       </c>
       <c r="M240">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1793</v>
+        <v>1610</v>
       </c>
       <c r="B241" t="s">
-        <v>1792</v>
+        <v>722</v>
       </c>
       <c r="C241" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D241" t="s">
-        <v>1794</v>
+        <v>723</v>
       </c>
       <c r="E241" t="s">
-        <v>1795</v>
+        <v>1697</v>
       </c>
       <c r="G241" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="H241" s="6"/>
-      <c r="J241" s="15" t="s">
-        <v>1945</v>
+      <c r="J241" s="27" t="s">
+        <v>724</v>
+      </c>
+      <c r="K241" t="s">
+        <v>722</v>
       </c>
       <c r="M241">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:13" s="26" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="26" t="s">
-        <v>2069</v>
+        <v>1611</v>
       </c>
       <c r="B242" s="26" t="s">
-        <v>2070</v>
+        <v>725</v>
       </c>
       <c r="C242" s="26" t="s">
         <v>272</v>
       </c>
       <c r="D242" s="26" t="s">
-        <v>2068</v>
+        <v>1292</v>
+      </c>
+      <c r="E242" s="26" t="s">
+        <v>726</v>
       </c>
       <c r="G242" s="26" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>2122</v>
+        <v>2570</v>
+      </c>
+      <c r="K242" s="26" t="s">
+        <v>725</v>
       </c>
       <c r="M242" s="26">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1889</v>
+        <v>1616</v>
       </c>
       <c r="B243" t="s">
-        <v>1890</v>
+        <v>738</v>
       </c>
       <c r="C243" t="s">
-        <v>484</v>
+        <v>1106</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>1891</v>
+        <v>739</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1698</v>
       </c>
       <c r="G243" s="22" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="H243" s="6"/>
-      <c r="J243" s="15" t="s">
-        <v>1946</v>
+      <c r="J243" s="14" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K243" t="s">
+        <v>738</v>
       </c>
       <c r="M243">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1776</v>
+        <v>1615</v>
       </c>
       <c r="B244" t="s">
-        <v>1777</v>
+        <v>735</v>
       </c>
       <c r="C244" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
       <c r="D244" s="19" t="s">
-        <v>1790</v>
+        <v>736</v>
       </c>
       <c r="E244" t="s">
-        <v>1791</v>
+        <v>737</v>
       </c>
       <c r="G244" s="22" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="H244" s="6"/>
-      <c r="J244" s="15" t="s">
-        <v>1947</v>
+      <c r="J244" s="14" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K244" t="s">
+        <v>735</v>
       </c>
       <c r="M244">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>2071</v>
+        <v>1614</v>
       </c>
       <c r="B245" t="s">
-        <v>2074</v>
+        <v>732</v>
       </c>
       <c r="C245" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D245" t="s">
-        <v>2073</v>
+        <v>733</v>
+      </c>
+      <c r="E245" t="s">
+        <v>734</v>
       </c>
       <c r="G245" s="22" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="H245" s="6"/>
       <c r="J245" s="14" t="s">
-        <v>2123</v>
+        <v>2571</v>
+      </c>
+      <c r="K245" t="s">
+        <v>732</v>
       </c>
       <c r="M245">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>2072</v>
+        <v>1612</v>
       </c>
       <c r="B246" t="s">
-        <v>2075</v>
+        <v>727</v>
       </c>
       <c r="C246" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D246" t="s">
-        <v>2076</v>
+        <v>728</v>
+      </c>
+      <c r="E246" t="s">
+        <v>729</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>2308</v>
+        <v>2285</v>
       </c>
       <c r="H246" s="6"/>
       <c r="J246" s="14" t="s">
-        <v>2124</v>
+        <v>1950</v>
+      </c>
+      <c r="K246" t="s">
+        <v>727</v>
       </c>
       <c r="M246">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>2386</v>
+        <v>1613</v>
       </c>
       <c r="B247" t="s">
-        <v>2251</v>
+        <v>730</v>
       </c>
       <c r="C247" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D247" t="s">
-        <v>2252</v>
+        <v>1291</v>
+      </c>
+      <c r="E247" t="s">
+        <v>731</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>2298</v>
+        <v>2285</v>
       </c>
       <c r="H247" s="6"/>
       <c r="J247" s="14" t="s">
-        <v>2417</v>
+        <v>2572</v>
+      </c>
+      <c r="K247" t="s">
+        <v>730</v>
       </c>
       <c r="M247">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>2391</v>
+        <v>1784</v>
       </c>
       <c r="B248" t="s">
-        <v>2261</v>
+        <v>2012</v>
       </c>
       <c r="C248" t="s">
         <v>272</v>
       </c>
       <c r="D248" t="s">
-        <v>2262</v>
+        <v>924</v>
+      </c>
+      <c r="E248" t="s">
+        <v>925</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H248" s="6"/>
-      <c r="J248" s="14" t="s">
-        <v>2421</v>
+      <c r="J248" s="15" t="s">
+        <v>2426</v>
+      </c>
+      <c r="K248" t="s">
+        <v>926</v>
       </c>
       <c r="M248">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>49</v>
+        <v>1499</v>
       </c>
       <c r="B249" t="s">
-        <v>1422</v>
+        <v>1837</v>
       </c>
       <c r="C249" t="s">
         <v>272</v>
       </c>
       <c r="D249" t="s">
-        <v>976</v>
+        <v>1217</v>
       </c>
       <c r="E249" t="s">
-        <v>977</v>
+        <v>351</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H249" s="6"/>
-      <c r="J249" s="23"/>
+      <c r="J249" s="14" t="s">
+        <v>1941</v>
+      </c>
       <c r="K249" t="s">
-        <v>978</v>
+        <v>350</v>
       </c>
       <c r="M249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="10" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C250" t="s">
+        <v>484</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E250" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G250" s="18" t="s">
+        <v>2308</v>
+      </c>
+      <c r="H250" s="6"/>
+      <c r="J250" s="15" t="s">
+        <v>1942</v>
+      </c>
+      <c r="M250">
         <v>3</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>972</v>
-      </c>
-      <c r="B250" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C250" t="s">
-        <v>272</v>
-      </c>
-      <c r="D250" t="s">
-        <v>973</v>
-      </c>
-      <c r="E250" t="s">
-        <v>974</v>
-      </c>
-      <c r="G250" s="18" t="s">
-        <v>2298</v>
-      </c>
-      <c r="H250" s="6"/>
-      <c r="J250" s="26"/>
-      <c r="K250" t="s">
-        <v>975</v>
-      </c>
-      <c r="M250">
-        <v>4</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>983</v>
+        <v>1774</v>
       </c>
       <c r="B251" t="s">
-        <v>1424</v>
+        <v>1775</v>
       </c>
       <c r="C251" t="s">
         <v>484</v>
       </c>
       <c r="D251" t="s">
-        <v>984</v>
+        <v>1782</v>
       </c>
       <c r="E251" t="s">
-        <v>985</v>
+        <v>1783</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H251" s="6"/>
-      <c r="J251" s="14" t="s">
-        <v>2560</v>
-      </c>
-      <c r="K251" t="s">
-        <v>986</v>
+      <c r="J251" s="15" t="s">
+        <v>1943</v>
       </c>
       <c r="M251">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>2390</v>
+        <v>1778</v>
       </c>
       <c r="B252" t="s">
-        <v>2259</v>
+        <v>1779</v>
       </c>
       <c r="C252" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D252" t="s">
-        <v>2260</v>
+        <v>1788</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1789</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H252" s="6"/>
-      <c r="J252" s="14" t="s">
-        <v>2420</v>
+      <c r="J252" s="15" t="s">
+        <v>1944</v>
       </c>
       <c r="M252">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>979</v>
+        <v>1793</v>
       </c>
       <c r="B253" t="s">
-        <v>1423</v>
+        <v>1792</v>
       </c>
       <c r="C253" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D253" t="s">
-        <v>980</v>
+        <v>1794</v>
       </c>
       <c r="E253" t="s">
-        <v>981</v>
+        <v>1795</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H253" s="6"/>
-      <c r="J253" s="26"/>
-      <c r="K253" t="s">
-        <v>982</v>
+      <c r="J253" s="15" t="s">
+        <v>1945</v>
       </c>
       <c r="M253">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>2342</v>
+        <v>2069</v>
       </c>
       <c r="B254" t="s">
-        <v>2163</v>
+        <v>2070</v>
       </c>
       <c r="C254" t="s">
         <v>272</v>
       </c>
       <c r="D254" t="s">
-        <v>2164</v>
+        <v>2068</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="H254" s="6"/>
       <c r="J254" s="14" t="s">
-        <v>2325</v>
+        <v>2122</v>
       </c>
       <c r="M254">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>2370</v>
+        <v>1889</v>
       </c>
       <c r="B255" t="s">
-        <v>2219</v>
+        <v>1890</v>
       </c>
       <c r="C255" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D255" t="s">
-        <v>2220</v>
-      </c>
-      <c r="G255" s="18" t="s">
-        <v>2298</v>
+        <v>1891</v>
+      </c>
+      <c r="G255" s="27" t="s">
+        <v>2308</v>
       </c>
       <c r="H255" s="6"/>
-      <c r="J255" s="14" t="s">
-        <v>2405</v>
+      <c r="J255" s="15" t="s">
+        <v>1946</v>
       </c>
       <c r="M255">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>2383</v>
+        <v>1776</v>
       </c>
       <c r="B256" t="s">
-        <v>2245</v>
+        <v>1777</v>
       </c>
       <c r="C256" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D256" t="s">
-        <v>2246</v>
-      </c>
-      <c r="G256" s="18" t="s">
-        <v>2298</v>
+        <v>1790</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G256" s="27" t="s">
+        <v>2308</v>
       </c>
       <c r="H256" s="6"/>
-      <c r="J256" s="14" t="s">
-        <v>2415</v>
+      <c r="J256" s="15" t="s">
+        <v>1947</v>
       </c>
       <c r="M256">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>2175</v>
+        <v>2071</v>
       </c>
       <c r="B257" t="s">
-        <v>2176</v>
+        <v>2074</v>
       </c>
       <c r="C257" t="s">
         <v>272</v>
       </c>
       <c r="D257" t="s">
-        <v>2177</v>
-      </c>
-      <c r="G257" s="20" t="s">
-        <v>2298</v>
+        <v>2073</v>
+      </c>
+      <c r="G257" s="27" t="s">
+        <v>2308</v>
       </c>
       <c r="H257" s="6"/>
       <c r="J257" s="14" t="s">
-        <v>2561</v>
+        <v>2123</v>
       </c>
       <c r="M257">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>2340</v>
+        <v>2072</v>
       </c>
       <c r="B258" t="s">
-        <v>2159</v>
+        <v>2075</v>
       </c>
       <c r="C258" t="s">
         <v>272</v>
       </c>
       <c r="D258" t="s">
-        <v>2160</v>
-      </c>
-      <c r="G258" s="20" t="s">
-        <v>2298</v>
+        <v>2076</v>
+      </c>
+      <c r="G258" s="27" t="s">
+        <v>2308</v>
       </c>
       <c r="H258" s="6"/>
       <c r="J258" s="14" t="s">
-        <v>2324</v>
+        <v>2124</v>
       </c>
       <c r="M258">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>2341</v>
+        <v>2386</v>
       </c>
       <c r="B259" t="s">
-        <v>2161</v>
+        <v>2251</v>
       </c>
       <c r="C259" t="s">
         <v>272</v>
       </c>
       <c r="D259" t="s">
-        <v>2162</v>
-      </c>
-      <c r="G259" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G259" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H259" s="6"/>
       <c r="J259" s="14" t="s">
-        <v>2326</v>
+        <v>2417</v>
       </c>
       <c r="M259">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>2371</v>
+        <v>2391</v>
       </c>
       <c r="B260" t="s">
-        <v>2221</v>
+        <v>2261</v>
       </c>
       <c r="C260" t="s">
         <v>272</v>
       </c>
       <c r="D260" t="s">
-        <v>2222</v>
-      </c>
-      <c r="G260" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="G260" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H260" s="6"/>
       <c r="J260" s="14" t="s">
-        <v>2406</v>
+        <v>2421</v>
       </c>
       <c r="M260">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>2354</v>
+        <v>49</v>
       </c>
       <c r="B261" t="s">
-        <v>2189</v>
+        <v>1422</v>
       </c>
       <c r="C261" t="s">
         <v>272</v>
       </c>
       <c r="D261" t="s">
-        <v>2190</v>
-      </c>
-      <c r="G261" s="20" t="s">
+        <v>976</v>
+      </c>
+      <c r="E261" t="s">
+        <v>977</v>
+      </c>
+      <c r="G261" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H261" s="6"/>
-      <c r="J261" s="14" t="s">
-        <v>2393</v>
+      <c r="J261" s="27"/>
+      <c r="K261" t="s">
+        <v>978</v>
       </c>
       <c r="M261">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>2381</v>
+        <v>972</v>
       </c>
       <c r="B262" t="s">
-        <v>2241</v>
+        <v>1421</v>
       </c>
       <c r="C262" t="s">
         <v>272</v>
       </c>
       <c r="D262" t="s">
-        <v>2242</v>
-      </c>
-      <c r="G262" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="E262" t="s">
+        <v>974</v>
+      </c>
+      <c r="G262" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H262" s="6"/>
-      <c r="J262" s="14" t="s">
-        <v>2413</v>
+      <c r="J262" s="27"/>
+      <c r="K262" t="s">
+        <v>975</v>
       </c>
       <c r="M262">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>2365</v>
+        <v>983</v>
       </c>
       <c r="B263" t="s">
-        <v>2209</v>
+        <v>1424</v>
       </c>
       <c r="C263" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D263" t="s">
-        <v>2210</v>
-      </c>
-      <c r="G263" s="18" t="s">
+        <v>984</v>
+      </c>
+      <c r="E263" t="s">
+        <v>985</v>
+      </c>
+      <c r="G263" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H263" s="6"/>
       <c r="J263" s="14" t="s">
-        <v>2401</v>
+        <v>2554</v>
+      </c>
+      <c r="K263" t="s">
+        <v>986</v>
       </c>
       <c r="M263">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>2364</v>
+        <v>2390</v>
       </c>
       <c r="B264" t="s">
-        <v>2400</v>
+        <v>2259</v>
       </c>
       <c r="C264" t="s">
         <v>272</v>
       </c>
       <c r="D264" t="s">
-        <v>2208</v>
-      </c>
-      <c r="G264" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="G264" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H264" s="6"/>
       <c r="J264" s="14" t="s">
-        <v>2399</v>
+        <v>2420</v>
       </c>
       <c r="M264">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>2344</v>
+        <v>979</v>
       </c>
       <c r="B265" t="s">
-        <v>2167</v>
+        <v>1423</v>
       </c>
       <c r="C265" t="s">
         <v>272</v>
       </c>
       <c r="D265" t="s">
-        <v>2168</v>
-      </c>
-      <c r="G265" s="20" t="s">
+        <v>980</v>
+      </c>
+      <c r="E265" t="s">
+        <v>981</v>
+      </c>
+      <c r="G265" s="27" t="s">
         <v>2298</v>
       </c>
       <c r="H265" s="6"/>
-      <c r="J265" s="14" t="s">
-        <v>2330</v>
+      <c r="J265" s="27"/>
+      <c r="K265" t="s">
+        <v>982</v>
       </c>
       <c r="M265">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -17376,7 +17439,7 @@
         <v>2332</v>
       </c>
       <c r="M266">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -17400,7 +17463,7 @@
         <v>2411</v>
       </c>
       <c r="M267">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -17422,6 +17485,9 @@
       <c r="H268" s="6"/>
       <c r="J268" s="14" t="s">
         <v>2516</v>
+      </c>
+      <c r="M268">
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -18229,7 +18295,9 @@
         <v>2310</v>
       </c>
       <c r="H299" s="6"/>
-      <c r="J299" s="26"/>
+      <c r="J299" s="14" t="s">
+        <v>2588</v>
+      </c>
       <c r="K299" t="s">
         <v>904</v>
       </c>
@@ -18282,7 +18350,7 @@
       </c>
       <c r="H301" s="6"/>
       <c r="J301" s="14" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="M301">
         <v>3</v>
@@ -18306,7 +18374,7 @@
       </c>
       <c r="H302" s="6"/>
       <c r="J302" s="14" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="M302">
         <v>4</v>
@@ -18330,7 +18398,7 @@
       </c>
       <c r="H303" s="6"/>
       <c r="J303" s="14" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="M303">
         <v>5</v>
@@ -18357,7 +18425,7 @@
       </c>
       <c r="H304" s="6"/>
       <c r="J304" s="14" t="s">
-        <v>2571</v>
+        <v>2564</v>
       </c>
       <c r="K304" t="s">
         <v>1706</v>
@@ -18586,7 +18654,7 @@
         <v>2139</v>
       </c>
       <c r="J313" s="14" t="s">
-        <v>2551</v>
+        <v>2583</v>
       </c>
       <c r="K313" t="s">
         <v>150</v>
@@ -18902,7 +18970,7 @@
         <v>2289</v>
       </c>
       <c r="J324" s="14" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.3">
@@ -18996,7 +19064,7 @@
         <v>2289</v>
       </c>
       <c r="J328" s="14" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="329" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -19325,7 +19393,7 @@
         <v>2299</v>
       </c>
       <c r="J340" s="14" t="s">
-        <v>2558</v>
+        <v>2552</v>
       </c>
       <c r="K340" t="s">
         <v>1065</v>
@@ -19354,7 +19422,7 @@
         <v>2299</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>2557</v>
+        <v>2551</v>
       </c>
       <c r="K341" t="s">
         <v>1067</v>
@@ -19383,7 +19451,7 @@
         <v>2299</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="K342" t="s">
         <v>1068</v>
@@ -19426,7 +19494,7 @@
         <v>1483</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>2569</v>
+        <v>2562</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>272</v>
@@ -19484,7 +19552,7 @@
         <v>1484</v>
       </c>
       <c r="B346" t="s">
-        <v>2568</v>
+        <v>2561</v>
       </c>
       <c r="C346" s="17" t="s">
         <v>272</v>
@@ -19600,7 +19668,7 @@
         <v>1482</v>
       </c>
       <c r="B350" t="s">
-        <v>2570</v>
+        <v>2563</v>
       </c>
       <c r="C350" t="s">
         <v>272</v>
@@ -19673,7 +19741,7 @@
         <v>2279</v>
       </c>
       <c r="J352" s="14" t="s">
-        <v>2580</v>
+        <v>2573</v>
       </c>
       <c r="K352" s="17" t="s">
         <v>314</v>
@@ -20133,7 +20201,7 @@
         <v>2133</v>
       </c>
       <c r="J368" s="14" t="s">
-        <v>2543</v>
+        <v>2579</v>
       </c>
       <c r="M368" s="22">
         <v>3</v>
@@ -20216,22 +20284,22 @@
     </row>
     <row r="372" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="B372" s="22" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="C372" s="22" t="s">
         <v>272</v>
       </c>
       <c r="D372" s="22" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="G372" s="22" t="s">
         <v>2133</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>2547</v>
+        <v>2580</v>
       </c>
       <c r="M372" s="22">
         <v>6</v>
@@ -21555,16 +21623,16 @@
         <v>916</v>
       </c>
       <c r="G422" s="26" t="s">
-        <v>2572</v>
+        <v>2565</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="K422" s="26" t="s">
         <v>917</v>
       </c>
       <c r="M422" s="26">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -21755,7 +21823,7 @@
         <v>2138</v>
       </c>
       <c r="J429" s="14" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="M429" s="23">
         <v>6</v>
@@ -21778,7 +21846,7 @@
         <v>2138</v>
       </c>
       <c r="J430" s="14" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="M430" s="23">
         <v>7</v>
@@ -21948,6 +22016,9 @@
       <c r="G436" s="23" t="s">
         <v>2138</v>
       </c>
+      <c r="J436" s="14" t="s">
+        <v>2582</v>
+      </c>
       <c r="K436" s="23" t="s">
         <v>479</v>
       </c>
@@ -22001,7 +22072,7 @@
         <v>2514</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -22021,7 +22092,7 @@
         <v>2514</v>
       </c>
       <c r="J439" s="14" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="440" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -22068,7 +22139,7 @@
         <v>2490</v>
       </c>
       <c r="J442" s="14" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="443" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -22216,11 +22287,11 @@
     <hyperlink ref="J435" r:id="rId17" display="https://github.com/olaf-programmeur/images/blob/main/mur.jpg" xr:uid="{587EEA60-F594-4016-803C-CEB66BA1E5BF}"/>
     <hyperlink ref="J428" r:id="rId18" display="https://github.com/olaf-programmeur/images/blob/main/fenetre.jpg" xr:uid="{53E2D24E-B720-42FE-B37D-24B6C52BACAF}"/>
     <hyperlink ref="J65" r:id="rId19" display="https://github.com/olaf-programmeur/images/blob/main/s%C3%A8che_linge.jpg" xr:uid="{029644CA-FA19-4AB5-BFB7-7BFD3C6E6F4B}"/>
-    <hyperlink ref="J222" r:id="rId20" display="https://github.com/olaf-programmeur/images/blob/main/batterie.jpg" xr:uid="{332B5C86-AAEA-4A7C-AA3B-4FB39A4D1019}"/>
-    <hyperlink ref="J223" r:id="rId21" display="https://github.com/olaf-programmeur/images/blob/main/grosse_caisse.jpg" xr:uid="{71D51027-C922-4602-8582-3F2E3E5CB2A0}"/>
-    <hyperlink ref="J234" r:id="rId22" display="https://github.com/olaf-programmeur/images/blob/main/basse.jpg" xr:uid="{F8BFD881-7F63-49CC-B835-919A654BF96B}"/>
-    <hyperlink ref="J231" r:id="rId23" display="https://github.com/olaf-programmeur/images/blob/main/alto.jpg" xr:uid="{7A0BD9D0-1209-4507-8CED-8013F4979FC8}"/>
-    <hyperlink ref="J232" r:id="rId24" xr:uid="{8C3FA86E-86C2-414F-96EB-80EC0F231C3F}"/>
+    <hyperlink ref="J234" r:id="rId20" display="https://github.com/olaf-programmeur/images/blob/main/batterie.jpg" xr:uid="{332B5C86-AAEA-4A7C-AA3B-4FB39A4D1019}"/>
+    <hyperlink ref="J235" r:id="rId21" display="https://github.com/olaf-programmeur/images/blob/main/grosse_caisse.jpg" xr:uid="{71D51027-C922-4602-8582-3F2E3E5CB2A0}"/>
+    <hyperlink ref="J246" r:id="rId22" display="https://github.com/olaf-programmeur/images/blob/main/basse.jpg" xr:uid="{F8BFD881-7F63-49CC-B835-919A654BF96B}"/>
+    <hyperlink ref="J243" r:id="rId23" display="https://github.com/olaf-programmeur/images/blob/main/alto.jpg" xr:uid="{7A0BD9D0-1209-4507-8CED-8013F4979FC8}"/>
+    <hyperlink ref="J244" r:id="rId24" xr:uid="{8C3FA86E-86C2-414F-96EB-80EC0F231C3F}"/>
     <hyperlink ref="J273" r:id="rId25" display="https://github.com/olaf-programmeur/images/blob/main/cuisse.jpg" xr:uid="{7F69A20C-4787-4AFE-A184-7F4999281637}"/>
     <hyperlink ref="J272" r:id="rId26" display="https://github.com/olaf-programmeur/images/blob/main/jambe.jpg" xr:uid="{0D5307E4-DD90-4E01-BAA8-C30063A487C4}"/>
     <hyperlink ref="J271" r:id="rId27" display="https://github.com/olaf-programmeur/images/blob/main/bras.jpg" xr:uid="{EF25790D-C418-40F0-98C2-77447ACAB26F}"/>
@@ -22269,20 +22340,20 @@
     <hyperlink ref="J189" r:id="rId70" display="https://github.com/olaf-programmeur/images/blob/main/ciel.jpg" xr:uid="{0C3AAF7A-0049-4090-98A2-062C3AB8C49B}"/>
     <hyperlink ref="J190" r:id="rId71" display="https://github.com/olaf-programmeur/images/blob/main/feu.jpg" xr:uid="{B53FC550-3981-43F7-BFD1-FBC984824DC0}"/>
     <hyperlink ref="J193" r:id="rId72" display="https://github.com/olaf-programmeur/images/blob/main/incendie.jpg" xr:uid="{D33699A2-17D5-4D1F-9E45-91538013A790}"/>
-    <hyperlink ref="J237" r:id="rId73" display="https://github.com/olaf-programmeur/images/blob/main/pomme_terre.jpg" xr:uid="{A4C36682-EB03-4230-B723-DA16513496DB}"/>
+    <hyperlink ref="J249" r:id="rId73" display="https://github.com/olaf-programmeur/images/blob/main/pomme_terre.jpg" xr:uid="{A4C36682-EB03-4230-B723-DA16513496DB}"/>
     <hyperlink ref="J68" r:id="rId74" display="https://github.com/olaf-programmeur/images/blob/main/canap%C3%A9.jpg" xr:uid="{19EF0F4B-32A1-4B2B-BE17-D29B9945856D}"/>
     <hyperlink ref="J70" r:id="rId75" display="https://github.com/olaf-programmeur/images/blob/main/meuble_salon.jpg" xr:uid="{32CF85D7-C1C4-4859-938E-426775026EB3}"/>
     <hyperlink ref="J80" r:id="rId76" display="https://github.com/olaf-programmeur/images/blob/main/ventre.jpg" xr:uid="{F7C358E3-5EF3-4C2E-814C-EB548E2B0F08}"/>
     <hyperlink ref="J84" r:id="rId77" xr:uid="{85EEC448-4DC2-467E-A22A-6564E5B84CE7}"/>
     <hyperlink ref="J88" r:id="rId78" display="https://github.com/olaf-programmeur/images/blob/main/dents.jpg" xr:uid="{E934A777-D378-44CC-BDAD-4C610CEB108A}"/>
     <hyperlink ref="J89" r:id="rId79" display="https://github.com/olaf-programmeur/images/blob/main/oreille.jpg" xr:uid="{C1440963-B371-4D18-8673-7735F862D76C}"/>
-    <hyperlink ref="J236" r:id="rId80" xr:uid="{30E68B4E-796A-4F25-BF68-928BD963ECA6}"/>
-    <hyperlink ref="J238" r:id="rId81" display="https://github.com/olaf-programmeur/images/blob/main/carottes.jpg" xr:uid="{4A842181-3070-4E8E-942D-6E149E4F7811}"/>
-    <hyperlink ref="J239" r:id="rId82" display="https://github.com/olaf-programmeur/images/blob/main/tomate.jpg" xr:uid="{0EE5EFAC-F5FF-4855-A088-BEEA25930A2C}"/>
-    <hyperlink ref="J240" r:id="rId83" display="https://github.com/olaf-programmeur/images/blob/main/chou_fleur.jpg" xr:uid="{36610DA1-73C2-415D-AA34-40E62585D87D}"/>
-    <hyperlink ref="J241" r:id="rId84" display="https://github.com/olaf-programmeur/images/blob/main/poireau.jpg" xr:uid="{9F7E2621-9468-47EE-B4B7-B3E3C0BE01DE}"/>
-    <hyperlink ref="J243" r:id="rId85" display="https://github.com/olaf-programmeur/images/blob/main/asperge.jpg" xr:uid="{9BD74A1C-7464-4645-B8EE-E10889B65BC3}"/>
-    <hyperlink ref="J244" r:id="rId86" display="https://github.com/olaf-programmeur/images/blob/main/courgette.jpg" xr:uid="{77AD92C4-A934-4AA0-A18D-33901F07A316}"/>
+    <hyperlink ref="J248" r:id="rId80" xr:uid="{30E68B4E-796A-4F25-BF68-928BD963ECA6}"/>
+    <hyperlink ref="J250" r:id="rId81" display="https://github.com/olaf-programmeur/images/blob/main/carottes.jpg" xr:uid="{4A842181-3070-4E8E-942D-6E149E4F7811}"/>
+    <hyperlink ref="J251" r:id="rId82" display="https://github.com/olaf-programmeur/images/blob/main/tomate.jpg" xr:uid="{0EE5EFAC-F5FF-4855-A088-BEEA25930A2C}"/>
+    <hyperlink ref="J252" r:id="rId83" display="https://github.com/olaf-programmeur/images/blob/main/chou_fleur.jpg" xr:uid="{36610DA1-73C2-415D-AA34-40E62585D87D}"/>
+    <hyperlink ref="J253" r:id="rId84" display="https://github.com/olaf-programmeur/images/blob/main/poireau.jpg" xr:uid="{9F7E2621-9468-47EE-B4B7-B3E3C0BE01DE}"/>
+    <hyperlink ref="J255" r:id="rId85" display="https://github.com/olaf-programmeur/images/blob/main/asperge.jpg" xr:uid="{9BD74A1C-7464-4645-B8EE-E10889B65BC3}"/>
+    <hyperlink ref="J256" r:id="rId86" display="https://github.com/olaf-programmeur/images/blob/main/courgette.jpg" xr:uid="{77AD92C4-A934-4AA0-A18D-33901F07A316}"/>
     <hyperlink ref="J277" r:id="rId87" display="https://github.com/olaf-programmeur/images/blob/main/policier.jpg" xr:uid="{D7A9F694-070A-4D20-989A-3FF659412B59}"/>
     <hyperlink ref="J395" r:id="rId88" display="https://github.com/olaf-programmeur/images/blob/main/oreillers.jpg" xr:uid="{868F1AD6-0136-444A-9BD0-81EC1AA90EEE}"/>
     <hyperlink ref="J39" r:id="rId89" display="https://github.com/olaf-programmeur/images/blob/main/cuisine.jpg" xr:uid="{CC56F71D-7498-46DD-BF9F-121CDF28A94E}"/>
@@ -22294,12 +22365,12 @@
     <hyperlink ref="J420" r:id="rId95" xr:uid="{8F3F7528-BDF0-480E-9BE8-4095253B9A60}"/>
     <hyperlink ref="J53" r:id="rId96" xr:uid="{38DBBFDC-632D-4FB4-86D1-BAAD947C780E}"/>
     <hyperlink ref="J69" r:id="rId97" display="https://github.com/olaf-programmeur/images/blob/main/fauteuil.jpg" xr:uid="{E24D4E2E-A247-4FDA-A691-958623E2993C}"/>
-    <hyperlink ref="J211" r:id="rId98" display="https://github.com/olaf-programmeur/images/blob/main/pomme.jpg" xr:uid="{3637EC4A-0003-4AFC-9F5A-D7C5A1C52A60}"/>
-    <hyperlink ref="J212" r:id="rId99" display="https://github.com/olaf-programmeur/images/blob/main/poire.jpg" xr:uid="{AC46D50A-7112-4586-860B-4F7911051ADF}"/>
-    <hyperlink ref="J213" r:id="rId100" display="https://github.com/olaf-programmeur/images/blob/main/pruneau.jpg" xr:uid="{C5DD03B9-1159-4378-AAB4-160F23987DA3}"/>
-    <hyperlink ref="J214" r:id="rId101" display="https://github.com/olaf-programmeur/images/blob/main/cerise.jpg" xr:uid="{36D4DC98-15FC-4FEA-AF43-19BC1C487F20}"/>
-    <hyperlink ref="J218" r:id="rId102" display="https://github.com/olaf-programmeur/images/blob/main/banane.jpg" xr:uid="{920D4AB1-CE21-4124-87EA-93375D37EC03}"/>
-    <hyperlink ref="J220" r:id="rId103" display="https://github.com/olaf-programmeur/images/blob/main/mandarine.jpg" xr:uid="{F22B2A92-9EF5-430C-B9B0-28004020C747}"/>
+    <hyperlink ref="J223" r:id="rId98" display="https://github.com/olaf-programmeur/images/blob/main/pomme.jpg" xr:uid="{3637EC4A-0003-4AFC-9F5A-D7C5A1C52A60}"/>
+    <hyperlink ref="J224" r:id="rId99" display="https://github.com/olaf-programmeur/images/blob/main/poire.jpg" xr:uid="{AC46D50A-7112-4586-860B-4F7911051ADF}"/>
+    <hyperlink ref="J225" r:id="rId100" display="https://github.com/olaf-programmeur/images/blob/main/pruneau.jpg" xr:uid="{C5DD03B9-1159-4378-AAB4-160F23987DA3}"/>
+    <hyperlink ref="J226" r:id="rId101" display="https://github.com/olaf-programmeur/images/blob/main/cerise.jpg" xr:uid="{36D4DC98-15FC-4FEA-AF43-19BC1C487F20}"/>
+    <hyperlink ref="J230" r:id="rId102" display="https://github.com/olaf-programmeur/images/blob/main/banane.jpg" xr:uid="{920D4AB1-CE21-4124-87EA-93375D37EC03}"/>
+    <hyperlink ref="J232" r:id="rId103" display="https://github.com/olaf-programmeur/images/blob/main/mandarine.jpg" xr:uid="{F22B2A92-9EF5-430C-B9B0-28004020C747}"/>
     <hyperlink ref="J2" r:id="rId104" display="https://github.com/olaf-programmeur/images/blob/main/sandwich.jpg" xr:uid="{4203F942-6923-415F-86A7-DF33516D7E7D}"/>
     <hyperlink ref="J90" r:id="rId105" display="https://github.com/olaf-programmeur/images/blob/main/casquette.jpg" xr:uid="{065B8976-0210-46DC-BDA0-0F64BF80D817}"/>
     <hyperlink ref="J96" r:id="rId106" display="https://github.com/olaf-programmeur/images/blob/main/coulisses.jpg" xr:uid="{96C168EC-C14C-471A-960E-A7A71729E4ED}"/>
@@ -22334,12 +22405,12 @@
     <hyperlink ref="J142" r:id="rId135" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{D398F53D-8CD1-4BCF-B123-DE35DBD79DDC}"/>
     <hyperlink ref="J138" r:id="rId136" display="https://github.com/olaf-programmeur/images/blob/main/migros.jpg" xr:uid="{F0E23162-8F08-4FE4-A006-E6DB539A7708}"/>
     <hyperlink ref="J139" r:id="rId137" display="https://github.com/olaf-programmeur/images/blob/main/raiffeisen.jpg" xr:uid="{714C2B4D-0898-41DB-8A05-E175F7FEBA1B}"/>
-    <hyperlink ref="J215" r:id="rId138" display="https://github.com/olaf-programmeur/images/blob/main/abricot.jpg" xr:uid="{C3A11FAC-028D-46A8-9D2E-0E8E473F0783}"/>
-    <hyperlink ref="J216" r:id="rId139" display="https://github.com/olaf-programmeur/images/blob/main/fraise.jpg" xr:uid="{DCD5D703-E51C-401B-8D37-48A6A98D3753}"/>
-    <hyperlink ref="J217" r:id="rId140" display="https://github.com/olaf-programmeur/images/blob/main/framboise.jpg" xr:uid="{8F33BC22-79D7-49B2-AD38-AC7B2DE00CC4}"/>
-    <hyperlink ref="J242" r:id="rId141" display="https://github.com/olaf-programmeur/images/blob/main/brocoli.jpg" xr:uid="{1DE00C68-E4E5-4E46-B2C4-D8339857392A}"/>
-    <hyperlink ref="J245" r:id="rId142" display="https://github.com/olaf-programmeur/images/blob/main/salade.jpg" xr:uid="{29F90ACB-2CDE-442C-B8D6-496883B4292C}"/>
-    <hyperlink ref="J246" r:id="rId143" display="https://github.com/olaf-programmeur/images/blob/main/betterave.jpg" xr:uid="{0BDF27A7-4A52-40CA-87C1-C6B42A43DFAE}"/>
+    <hyperlink ref="J227" r:id="rId138" display="https://github.com/olaf-programmeur/images/blob/main/abricot.jpg" xr:uid="{C3A11FAC-028D-46A8-9D2E-0E8E473F0783}"/>
+    <hyperlink ref="J228" r:id="rId139" display="https://github.com/olaf-programmeur/images/blob/main/fraise.jpg" xr:uid="{DCD5D703-E51C-401B-8D37-48A6A98D3753}"/>
+    <hyperlink ref="J229" r:id="rId140" display="https://github.com/olaf-programmeur/images/blob/main/framboise.jpg" xr:uid="{8F33BC22-79D7-49B2-AD38-AC7B2DE00CC4}"/>
+    <hyperlink ref="J254" r:id="rId141" display="https://github.com/olaf-programmeur/images/blob/main/brocoli.jpg" xr:uid="{1DE00C68-E4E5-4E46-B2C4-D8339857392A}"/>
+    <hyperlink ref="J257" r:id="rId142" display="https://github.com/olaf-programmeur/images/blob/main/salade.jpg" xr:uid="{29F90ACB-2CDE-442C-B8D6-496883B4292C}"/>
+    <hyperlink ref="J258" r:id="rId143" display="https://github.com/olaf-programmeur/images/blob/main/betterave.jpg" xr:uid="{0BDF27A7-4A52-40CA-87C1-C6B42A43DFAE}"/>
     <hyperlink ref="J298" r:id="rId144" display="https://github.com/olaf-programmeur/images/blob/main/pennes.jpg" xr:uid="{02C2C23C-A0CD-4BB3-BFA5-6CDC3A550DBF}"/>
     <hyperlink ref="J296" r:id="rId145" display="https://github.com/olaf-programmeur/images/blob/main/cornettes.jpg" xr:uid="{C29F3D59-2ED2-421C-A66E-AD8EA0124A11}"/>
     <hyperlink ref="J371" r:id="rId146" display="https://github.com/olaf-programmeur/images/blob/main/Emile.jpg" xr:uid="{813C8E7F-A1F1-4FB3-9FDC-B446EAD87FFC}"/>
@@ -22349,21 +22420,21 @@
     <hyperlink ref="J4" r:id="rId150" xr:uid="{094B1DC6-B715-44A8-A022-8CA7671EA44A}"/>
     <hyperlink ref="J145" r:id="rId151" xr:uid="{2F9569E2-A190-458B-A95C-5B625A41F329}"/>
     <hyperlink ref="J143" r:id="rId152" xr:uid="{5E78873D-C1C5-4DFD-8940-0CDCEC28552D}"/>
-    <hyperlink ref="J258" r:id="rId153" xr:uid="{204015A8-BD35-4418-B96B-809A201B1368}"/>
-    <hyperlink ref="J259" r:id="rId154" xr:uid="{6D26B26C-76E3-4B00-B8B5-75CB4FD99845}"/>
-    <hyperlink ref="J254" r:id="rId155" xr:uid="{FA3070F6-7981-4CB2-989B-7FA71FCFF2F8}"/>
+    <hyperlink ref="J212" r:id="rId153" xr:uid="{204015A8-BD35-4418-B96B-809A201B1368}"/>
+    <hyperlink ref="J213" r:id="rId154" xr:uid="{6D26B26C-76E3-4B00-B8B5-75CB4FD99845}"/>
+    <hyperlink ref="J208" r:id="rId155" xr:uid="{FA3070F6-7981-4CB2-989B-7FA71FCFF2F8}"/>
     <hyperlink ref="J105" r:id="rId156" xr:uid="{F6920F36-564D-4DA8-A9A1-4F51CDAEA04D}"/>
-    <hyperlink ref="J265" r:id="rId157" xr:uid="{16FA4419-B570-49DF-BB4E-5DC27528AB69}"/>
+    <hyperlink ref="J219" r:id="rId157" xr:uid="{16FA4419-B570-49DF-BB4E-5DC27528AB69}"/>
     <hyperlink ref="J286" r:id="rId158" xr:uid="{2BABD663-3A9C-474F-A4D7-79DD98FEA1FE}"/>
     <hyperlink ref="J48" r:id="rId159" xr:uid="{921343C8-8EBE-4E41-B3E5-3DFC502C800C}"/>
     <hyperlink ref="J266" r:id="rId160" xr:uid="{BB3BFAEA-F1B0-4515-A6EC-476DE5ADA0AB}"/>
-    <hyperlink ref="J257" r:id="rId161" xr:uid="{CC5998FF-91DB-47E7-8BB1-63810F642791}"/>
+    <hyperlink ref="J211" r:id="rId161" xr:uid="{CC5998FF-91DB-47E7-8BB1-63810F642791}"/>
     <hyperlink ref="J152" r:id="rId162" xr:uid="{4A87911C-8A18-433E-AD92-C148B729EC57}"/>
     <hyperlink ref="J151" r:id="rId163" xr:uid="{E59A3CEA-5E66-41EC-BD81-25463CB291D5}"/>
     <hyperlink ref="J121" r:id="rId164" xr:uid="{1038A930-9F8E-46CF-A677-D667E634B628}"/>
     <hyperlink ref="J278" r:id="rId165" xr:uid="{F21D0B24-37A5-4476-AD16-A4B32A6EAFE7}"/>
     <hyperlink ref="J287" r:id="rId166" xr:uid="{2FE14798-69C8-41B6-ADB7-BDD91366D775}"/>
-    <hyperlink ref="J261" r:id="rId167" xr:uid="{30F298FB-C474-49E4-9F73-CAA80E68AFAA}"/>
+    <hyperlink ref="J215" r:id="rId167" xr:uid="{30F298FB-C474-49E4-9F73-CAA80E68AFAA}"/>
     <hyperlink ref="J285" r:id="rId168" xr:uid="{9AA0AA4E-D773-439F-95D5-340A89470A8F}"/>
     <hyperlink ref="J288" r:id="rId169" xr:uid="{F6833586-915F-44A5-8A8C-F0EF1273DC53}"/>
     <hyperlink ref="J144" r:id="rId170" xr:uid="{C41D5318-97C5-4596-BD8E-8807366147FC}"/>
@@ -22371,32 +22442,32 @@
     <hyperlink ref="J149" r:id="rId172" xr:uid="{0803094F-E0E5-4FDE-8FDA-9D1878960E42}"/>
     <hyperlink ref="J157" r:id="rId173" xr:uid="{BDF39CF6-4E45-47E4-B29E-A08B77550EE6}"/>
     <hyperlink ref="J156" r:id="rId174" xr:uid="{A50F65BA-8847-436C-A1F0-9E51E4F08C2B}"/>
-    <hyperlink ref="J264" r:id="rId175" xr:uid="{59F1EBB2-14B3-4245-AF68-0C0D681A7901}"/>
-    <hyperlink ref="J263" r:id="rId176" xr:uid="{DE321ABC-C6AE-49F2-98AD-0FD38646B061}"/>
+    <hyperlink ref="J216" r:id="rId175" xr:uid="{59F1EBB2-14B3-4245-AF68-0C0D681A7901}"/>
+    <hyperlink ref="J217" r:id="rId176" xr:uid="{DE321ABC-C6AE-49F2-98AD-0FD38646B061}"/>
     <hyperlink ref="J150" r:id="rId177" xr:uid="{823630DE-DC00-4C1F-904A-4689DF26C11E}"/>
     <hyperlink ref="J155" r:id="rId178" xr:uid="{578B293C-8A3E-4D31-BA67-1507315D4DCF}"/>
     <hyperlink ref="J154" r:id="rId179" xr:uid="{87990F93-D659-402D-B705-3656025E4B77}"/>
     <hyperlink ref="J280" r:id="rId180" xr:uid="{6742B27A-AFC0-445B-AC5B-0D1DA350EA7C}"/>
-    <hyperlink ref="J255" r:id="rId181" xr:uid="{395074CC-322C-4343-BD63-7C14704961F5}"/>
-    <hyperlink ref="J260" r:id="rId182" xr:uid="{FE320407-202E-4D7D-8CBA-9B3D5DB1B8C0}"/>
+    <hyperlink ref="J210" r:id="rId181" xr:uid="{395074CC-322C-4343-BD63-7C14704961F5}"/>
+    <hyperlink ref="J214" r:id="rId182" xr:uid="{FE320407-202E-4D7D-8CBA-9B3D5DB1B8C0}"/>
     <hyperlink ref="J279" r:id="rId183" xr:uid="{B280B51C-4C98-4487-91FA-DE1A5BE9927A}"/>
     <hyperlink ref="J284" r:id="rId184" xr:uid="{39AA4674-8F59-472E-B2DE-D8F15E1A0255}"/>
     <hyperlink ref="J282" r:id="rId185" xr:uid="{795F5AA9-FA85-4F41-B325-AB1FD2B922F8}"/>
     <hyperlink ref="J106" r:id="rId186" xr:uid="{F0C4A975-4CC0-49C2-AB07-42B5B1937D60}"/>
     <hyperlink ref="J267" r:id="rId187" xr:uid="{B228FE52-A77B-4F49-8AF4-660F379E5B6B}"/>
     <hyperlink ref="J283" r:id="rId188" xr:uid="{F77312E5-CE3A-4151-B1FD-FB21132A635B}"/>
-    <hyperlink ref="J262" r:id="rId189" xr:uid="{06F25856-F5D9-4ADA-8932-9103C485CDBB}"/>
+    <hyperlink ref="J218" r:id="rId189" xr:uid="{06F25856-F5D9-4ADA-8932-9103C485CDBB}"/>
     <hyperlink ref="J6" r:id="rId190" xr:uid="{791599E1-3C50-47AD-812F-622C5E957457}"/>
-    <hyperlink ref="J256" r:id="rId191" xr:uid="{30202DAA-0C08-484E-9910-2A67A654DA2D}"/>
+    <hyperlink ref="J209" r:id="rId191" xr:uid="{30202DAA-0C08-484E-9910-2A67A654DA2D}"/>
     <hyperlink ref="J153" r:id="rId192" xr:uid="{2BC8974F-B4DA-420D-9F73-81B49B42AF10}"/>
-    <hyperlink ref="J247" r:id="rId193" xr:uid="{C4B9CE1E-23C5-4085-A5C9-430F4093C9D9}"/>
+    <hyperlink ref="J259" r:id="rId193" xr:uid="{C4B9CE1E-23C5-4085-A5C9-430F4093C9D9}"/>
     <hyperlink ref="J148" r:id="rId194" xr:uid="{DC88B1D2-D663-467C-A5B9-C86B5FCF83E4}"/>
     <hyperlink ref="J446" r:id="rId195" xr:uid="{BC2F70D3-5660-46E9-B657-9C94A97A90F4}"/>
-    <hyperlink ref="J252" r:id="rId196" xr:uid="{A4346AD4-5FAA-461A-8F23-682E97FACB86}"/>
-    <hyperlink ref="J248" r:id="rId197" xr:uid="{5F0B67EF-AC79-45F4-A5DA-40BA3EC54F83}"/>
+    <hyperlink ref="J264" r:id="rId196" xr:uid="{A4346AD4-5FAA-461A-8F23-682E97FACB86}"/>
+    <hyperlink ref="J260" r:id="rId197" xr:uid="{5F0B67EF-AC79-45F4-A5DA-40BA3EC54F83}"/>
     <hyperlink ref="J379" r:id="rId198" xr:uid="{E90F5920-D952-4CE1-BB80-E5B4100CA1D2}"/>
     <hyperlink ref="J45" r:id="rId199" xr:uid="{305E9B76-3780-474C-AD49-48CBA4B786C3}"/>
-    <hyperlink ref="J251" r:id="rId200" xr:uid="{84AE39AD-DEEA-430C-91E7-8B8FF13A7EF6}"/>
+    <hyperlink ref="J263" r:id="rId200" xr:uid="{84AE39AD-DEEA-430C-91E7-8B8FF13A7EF6}"/>
     <hyperlink ref="J44" r:id="rId201" xr:uid="{FFBCE73E-D7F6-4EE8-9446-ACF05D8F5B06}"/>
     <hyperlink ref="J268" r:id="rId202" xr:uid="{26AB34FC-79AB-4808-BD87-16F3865FC2A2}"/>
     <hyperlink ref="J36" r:id="rId203" xr:uid="{F47BB4EC-83B4-48B8-96A0-9BD49166F329}"/>
@@ -22436,33 +22507,35 @@
     <hyperlink ref="J135" r:id="rId237" xr:uid="{B1468646-4832-418D-BC68-307DAD32C650}"/>
     <hyperlink ref="J136" r:id="rId238" xr:uid="{BE6A64A3-5784-46D2-BA66-F76C45A61909}"/>
     <hyperlink ref="J160" r:id="rId239" xr:uid="{183169B9-99D9-41CF-8AE9-1486789308ED}"/>
-    <hyperlink ref="J221" r:id="rId240" xr:uid="{5E17BB7B-FB90-4DDA-BC78-731848D421AC}"/>
+    <hyperlink ref="J233" r:id="rId240" xr:uid="{5E17BB7B-FB90-4DDA-BC78-731848D421AC}"/>
     <hyperlink ref="J422" r:id="rId241" xr:uid="{555A24CD-8548-4D48-84A9-C7592640CCC6}"/>
     <hyperlink ref="J165" r:id="rId242" xr:uid="{68FF3892-36AB-43C6-979B-9083E0DE205F}"/>
-    <hyperlink ref="J230" r:id="rId243" xr:uid="{65916066-F252-46DC-8F9B-B657073C1133}"/>
-    <hyperlink ref="J233" r:id="rId244" xr:uid="{E3CDC362-15C0-4AF3-ABF2-C66AA6D1603E}"/>
-    <hyperlink ref="J235" r:id="rId245" xr:uid="{7254F38F-4A17-48DA-84D0-A1910CBC3C02}"/>
+    <hyperlink ref="J242" r:id="rId243" xr:uid="{65916066-F252-46DC-8F9B-B657073C1133}"/>
+    <hyperlink ref="J245" r:id="rId244" xr:uid="{E3CDC362-15C0-4AF3-ABF2-C66AA6D1603E}"/>
+    <hyperlink ref="J247" r:id="rId245" xr:uid="{7254F38F-4A17-48DA-84D0-A1910CBC3C02}"/>
     <hyperlink ref="J352" r:id="rId246" xr:uid="{56FEB524-26D5-42E3-A955-A10F1F2516F3}"/>
     <hyperlink ref="J93" r:id="rId247" xr:uid="{5825BC31-1D38-4F9D-B20A-28E48278D826}"/>
     <hyperlink ref="J94" r:id="rId248" xr:uid="{7690B3FB-763E-424C-ABD3-EC3916268FDF}"/>
     <hyperlink ref="J101" r:id="rId249" xr:uid="{8BEE59FF-BC87-43AF-A538-92C851B85539}"/>
+    <hyperlink ref="J436" r:id="rId250" xr:uid="{D67167E9-E4FE-4251-A54D-D534FE10F54D}"/>
+    <hyperlink ref="J299" r:id="rId251" xr:uid="{94F4848D-4ADE-41B8-B8D1-F25A10C1792B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId250"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId252"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E61355C6-45BD-4E35-BC61-8EFDC3DC3AC1}">
           <x14:formula1>
-            <xm:f>'Sous-catégories'!$C$2:$C$105</xm:f>
+            <xm:f>'Sous-catégories'!$C$2:$C$106</xm:f>
           </x14:formula1>
           <xm:sqref>G1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A6D0438-8991-480B-92C8-50D535BE9ACA}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D65B05D7-5572-4881-AE8F-8F0F58CED2EF}">
           <x14:formula1>
-            <xm:f>'Sous-catégories'!$C$2:$C$101</xm:f>
+            <xm:f>'Sous-catégories'!$C$2:$C$100</xm:f>
           </x14:formula1>
-          <xm:sqref>G440:G500 G422:G437 G2:G420</xm:sqref>
+          <xm:sqref>G2:G500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -23241,17 +23314,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1181</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -23263,17 +23336,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>1183</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C44BD9B-11C9-43BC-BF86-335584009BF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778DA638-95AC-46A8-A0DA-857C6B5B99D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="2592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="2592">
   <si>
     <t>id</t>
   </si>
@@ -9437,6 +9437,9 @@
       <c r="F36" t="s">
         <v>207</v>
       </c>
+      <c r="G36" s="14" t="s">
+        <v>2591</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -10145,6 +10148,7 @@
     <hyperlink ref="G33" r:id="rId20" xr:uid="{0B0F2D97-5943-4654-A57D-CD9883C2248D}"/>
     <hyperlink ref="G39" r:id="rId21" xr:uid="{DAA3242A-FBF3-417A-9C88-1FB43926DE87}"/>
     <hyperlink ref="G38" r:id="rId22" xr:uid="{E0B462DC-5C4B-4337-9135-0DB6475233C6}"/>
+    <hyperlink ref="G36" r:id="rId23" xr:uid="{C01DD900-B8C6-430D-ACC7-1CCD5AE87A66}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7A6CD6-33A6-46E9-B2D1-8B6137A2C11F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D35C00-3ED2-4765-B03E-35782C5F3F2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="2764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4254" uniqueCount="2802">
   <si>
     <t>id</t>
   </si>
@@ -8313,13 +8313,127 @@
     <t>cles</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/figures_notes.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/germaine.jpg</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/jason.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/figure_notes.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/beau_villain.jpg</t>
+  </si>
+  <si>
+    <t>good versus bad</t>
+  </si>
+  <si>
+    <t>warm versus cold</t>
+  </si>
+  <si>
+    <t>expensive versus cheap</t>
+  </si>
+  <si>
+    <t>quiet versus noisy</t>
+  </si>
+  <si>
+    <t>light versus dark</t>
+  </si>
+  <si>
+    <t>happy versus unhappy</t>
+  </si>
+  <si>
+    <t>courageous versus coward</t>
+  </si>
+  <si>
+    <t>wooly versus rogue</t>
+  </si>
+  <si>
+    <t>funny versus serious</t>
+  </si>
+  <si>
+    <t>hard versus loose</t>
+  </si>
+  <si>
+    <t>fatty versus thin</t>
+  </si>
+  <si>
+    <t>easy versus difficult</t>
+  </si>
+  <si>
+    <t>strong versus fragile</t>
+  </si>
+  <si>
+    <t>nice versus bad</t>
+  </si>
+  <si>
+    <t>tall versus small</t>
+  </si>
+  <si>
+    <t>high versus low</t>
+  </si>
+  <si>
+    <t>happy versu unhappy</t>
+  </si>
+  <si>
+    <t>clever versus stupid</t>
+  </si>
+  <si>
+    <t>young versus old</t>
+  </si>
+  <si>
+    <t>large versus narrow</t>
+  </si>
+  <si>
+    <t>long versus short</t>
+  </si>
+  <si>
+    <t>heavy versus light</t>
+  </si>
+  <si>
+    <t>new versus old</t>
+  </si>
+  <si>
+    <t>new versus ancient</t>
+  </si>
+  <si>
+    <t>open versus closed</t>
+  </si>
+  <si>
+    <t>full versus empty</t>
+  </si>
+  <si>
+    <t>polite versus unpolite</t>
+  </si>
+  <si>
+    <t>first versus last</t>
+  </si>
+  <si>
+    <t>near versus far away</t>
+  </si>
+  <si>
+    <t>clean versus dirty</t>
+  </si>
+  <si>
+    <t>quick versus slow</t>
+  </si>
+  <si>
+    <t>healthy versus ill</t>
+  </si>
+  <si>
+    <t>rich versus poor</t>
+  </si>
+  <si>
+    <t>dry versus wet</t>
+  </si>
+  <si>
+    <t>silent versus noisy</t>
+  </si>
+  <si>
+    <t>easy versus complicate</t>
+  </si>
+  <si>
+    <t>true versus false</t>
   </si>
 </sst>
 </file>
@@ -12866,7 +12980,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -21133,7 +21247,7 @@
         <v>2133</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21202,7 +21316,7 @@
         <v>2131</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -22829,7 +22943,7 @@
       </c>
       <c r="J448" s="14"/>
     </row>
-    <row r="449" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="23" t="s">
         <v>2384</v>
       </c>
@@ -22844,7 +22958,7 @@
       </c>
       <c r="J449" s="14"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>2591</v>
       </c>
@@ -22864,7 +22978,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="451" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
         <v>2760</v>
       </c>
@@ -22884,7 +22998,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>2600</v>
       </c>
@@ -22903,8 +23017,11 @@
       <c r="G452" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J452" s="14" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>2602</v>
       </c>
@@ -22923,8 +23040,12 @@
       <c r="G453" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J453" s="14"/>
+      <c r="K453" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>2604</v>
       </c>
@@ -22943,8 +23064,11 @@
       <c r="G454" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K454" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>2606</v>
       </c>
@@ -22963,8 +23087,11 @@
       <c r="G455" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K455" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>2608</v>
       </c>
@@ -22980,8 +23107,11 @@
       <c r="G456" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K456" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>2610</v>
       </c>
@@ -23000,8 +23130,11 @@
       <c r="G457" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K457" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>2612</v>
       </c>
@@ -23020,8 +23153,11 @@
       <c r="G458" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K458" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>2614</v>
       </c>
@@ -23040,8 +23176,11 @@
       <c r="G459" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K459" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>2616</v>
       </c>
@@ -23060,8 +23199,11 @@
       <c r="G460" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K460" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>2618</v>
       </c>
@@ -23080,8 +23222,11 @@
       <c r="G461" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K461" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>2620</v>
       </c>
@@ -23100,8 +23245,11 @@
       <c r="G462" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K462" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>2622</v>
       </c>
@@ -23120,8 +23268,11 @@
       <c r="G463" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K463" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>2624</v>
       </c>
@@ -23140,8 +23291,11 @@
       <c r="G464" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K464" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>2626</v>
       </c>
@@ -23160,8 +23314,11 @@
       <c r="G465" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K465" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>2628</v>
       </c>
@@ -23180,8 +23337,11 @@
       <c r="G466" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K466" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>2630</v>
       </c>
@@ -23200,8 +23360,11 @@
       <c r="G467" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K467" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>2632</v>
       </c>
@@ -23220,8 +23383,11 @@
       <c r="G468" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K468" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>2634</v>
       </c>
@@ -23240,8 +23406,11 @@
       <c r="G469" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K469" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>2636</v>
       </c>
@@ -23260,8 +23429,11 @@
       <c r="G470" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K470" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>2638</v>
       </c>
@@ -23280,8 +23452,11 @@
       <c r="G471" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K471" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>2640</v>
       </c>
@@ -23300,8 +23475,11 @@
       <c r="G472" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K472" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>2642</v>
       </c>
@@ -23320,8 +23498,11 @@
       <c r="G473" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K473" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>2644</v>
       </c>
@@ -23340,8 +23521,11 @@
       <c r="G474" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K474" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>2646</v>
       </c>
@@ -23360,8 +23544,11 @@
       <c r="G475" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K475" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>2648</v>
       </c>
@@ -23380,8 +23567,11 @@
       <c r="G476" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K476" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>2650</v>
       </c>
@@ -23400,8 +23590,11 @@
       <c r="G477" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K477" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>2652</v>
       </c>
@@ -23420,8 +23613,11 @@
       <c r="G478" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K478" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>2654</v>
       </c>
@@ -23440,8 +23636,11 @@
       <c r="G479" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K479" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>2656</v>
       </c>
@@ -23460,8 +23659,11 @@
       <c r="G480" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K480" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>2658</v>
       </c>
@@ -23480,8 +23682,11 @@
       <c r="G481" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K481" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>2660</v>
       </c>
@@ -23500,8 +23705,11 @@
       <c r="G482" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K482" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>2662</v>
       </c>
@@ -23520,8 +23728,11 @@
       <c r="G483" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K483" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>2664</v>
       </c>
@@ -23540,8 +23751,11 @@
       <c r="G484" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K484" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>2666</v>
       </c>
@@ -23560,8 +23774,11 @@
       <c r="G485" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K485" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>2668</v>
       </c>
@@ -23580,8 +23797,11 @@
       <c r="G486" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K486" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>2670</v>
       </c>
@@ -23600,8 +23820,11 @@
       <c r="G487" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K487" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>2672</v>
       </c>
@@ -23620,8 +23843,11 @@
       <c r="G488" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K488" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>2674</v>
       </c>
@@ -23640,8 +23866,11 @@
       <c r="G489" s="29" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K489" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>2676</v>
       </c>
@@ -23659,6 +23888,9 @@
       </c>
       <c r="G490" s="29" t="s">
         <v>2598</v>
+      </c>
+      <c r="K490" t="s">
+        <v>2801</v>
       </c>
     </row>
   </sheetData>
@@ -23928,9 +24160,10 @@
     <hyperlink ref="J450" r:id="rId252" xr:uid="{D567BB6B-200C-4DF1-96A3-89D574FAD9A2}"/>
     <hyperlink ref="J451" r:id="rId253" xr:uid="{C7230777-0726-4B03-8D76-346F4625573C}"/>
     <hyperlink ref="J383" r:id="rId254" xr:uid="{4A54E760-26AA-4DC3-8FDD-553BE7D8DB56}"/>
+    <hyperlink ref="J452" r:id="rId255" xr:uid="{AA438D1E-A7F6-4E55-8283-4089FEA815A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId255"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId256"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE1649A-CF3E-4EAD-9184-26049AE606AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A13B0E4-910C-4FD5-811B-B0A787F032F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catégories" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4254" uniqueCount="2801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="2813">
   <si>
     <t>id</t>
   </si>
@@ -7842,9 +7842,6 @@
     <t>a_calme</t>
   </si>
   <si>
-    <t>calme  ↔  agité</t>
-  </si>
-  <si>
     <t>a_chaud</t>
   </si>
   <si>
@@ -7875,12 +7872,6 @@
     <t>courageux  ↔  peureux</t>
   </si>
   <si>
-    <t>a_doux</t>
-  </si>
-  <si>
-    <t>doux  ↔  rugueux</t>
-  </si>
-  <si>
     <t>a_drôle</t>
   </si>
   <si>
@@ -8085,9 +8076,6 @@
     <t>Un pompier qui entre dans le feu est courageux, quelqu'un qui tremble devant une souris est peureux.</t>
   </si>
   <si>
-    <t>Le pelage d'un chat est doux, l'écorce d'un arbre est rugueuse.</t>
-  </si>
-  <si>
     <t>Un clown qui fait rire est drôle, un juge au tribunal est sérieux.</t>
   </si>
   <si>
@@ -8199,9 +8187,6 @@
     <t>🦸 ↔ 🙈</t>
   </si>
   <si>
-    <t>🐱 ↔ 🌳</t>
-  </si>
-  <si>
     <t>🤡 ↔ ⚖️</t>
   </si>
   <si>
@@ -8343,9 +8328,6 @@
     <t>courageous versus coward</t>
   </si>
   <si>
-    <t>wooly versus rogue</t>
-  </si>
-  <si>
     <t>funny versus serious</t>
   </si>
   <si>
@@ -8431,6 +8413,62 @@
   </si>
   <si>
     <t>true versus false</t>
+  </si>
+  <si>
+    <t>fil_debroussailleuse</t>
+  </si>
+  <si>
+    <t>le fil pour la débroussailleuse</t>
+  </si>
+  <si>
+    <t>Il s'agit d'un fil en plastique utilisé par la débroussailleuse pour couper les herbes.</t>
+  </si>
+  <si>
+    <t>tablette_ipad</t>
+  </si>
+  <si>
+    <t>l'Ipad ou la tablette</t>
+  </si>
+  <si>
+    <t>J’aime
+Je n’aime pas
+Appareil électronique, tablette tactile (on utilise les doigts) conçue par l'entreprise Apple, combinant portabilité, écran tactile et fonctionnalités multimédias (musique/films/jeux).</t>
+  </si>
+  <si>
+    <t>calme  ↔  agité (énervé)</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bon_mauvais.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/calme_agite.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/chaud_froid.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/cher_bon_marche.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/clair_sombre.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/content_triste.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/courageux_peureux.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/drole_serieux.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/fil_debroussailleuse.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/ipad.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/iphone.png</t>
   </si>
 </sst>
 </file>
@@ -8518,7 +8556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8544,6 +8582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -10854,7 +10893,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M490"/>
+  <dimension ref="A1:M491"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.796875" customWidth="1"/>
@@ -11046,10 +11085,12 @@
         <v>1149</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>252</v>
+        <v>2595</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="J7" s="24"/>
+      <c r="J7" s="14" t="s">
+        <v>2812</v>
+      </c>
       <c r="K7" t="s">
         <v>2569</v>
       </c>
@@ -12978,7 +13019,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2762</v>
+        <v>2757</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -18515,7 +18556,7 @@
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="14" t="s">
-        <v>2754</v>
+        <v>2749</v>
       </c>
       <c r="M280">
         <v>6</v>
@@ -21245,7 +21286,7 @@
         <v>2132</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21314,7 +21355,7 @@
         <v>2130</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2760</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -22773,7 +22814,7 @@
         <v>2508</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -22978,22 +23019,22 @@
     </row>
     <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
-        <v>2759</v>
+        <v>2754</v>
       </c>
       <c r="B451" s="29" t="s">
-        <v>2755</v>
+        <v>2750</v>
       </c>
       <c r="C451" s="29" t="s">
         <v>270</v>
       </c>
       <c r="D451" s="29" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
       <c r="G451" s="29" t="s">
         <v>2595</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>2757</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
@@ -23007,16 +23048,16 @@
         <v>1104</v>
       </c>
       <c r="D452" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="F452" t="s">
-        <v>2716</v>
+        <v>2712</v>
       </c>
       <c r="G452" t="s">
         <v>2597</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>2763</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
@@ -23030,17 +23071,19 @@
         <v>1104</v>
       </c>
       <c r="D453" t="s">
-        <v>2678</v>
+        <v>2675</v>
       </c>
       <c r="F453" t="s">
-        <v>2717</v>
+        <v>2713</v>
       </c>
       <c r="G453" s="29" t="s">
         <v>2597</v>
       </c>
-      <c r="J453" s="14"/>
+      <c r="J453" s="14" t="s">
+        <v>2802</v>
+      </c>
       <c r="K453" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
@@ -23048,847 +23091,885 @@
         <v>2603</v>
       </c>
       <c r="B454" t="s">
-        <v>2604</v>
+        <v>2801</v>
       </c>
       <c r="C454" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D454" t="s">
-        <v>2679</v>
+        <v>2676</v>
       </c>
       <c r="F454" t="s">
-        <v>2718</v>
+        <v>2714</v>
       </c>
       <c r="G454" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J454" s="14" t="s">
+        <v>2803</v>
+      </c>
       <c r="K454" t="s">
-        <v>2767</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B455" t="s">
         <v>2605</v>
-      </c>
-      <c r="B455" t="s">
-        <v>2606</v>
       </c>
       <c r="C455" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D455" t="s">
-        <v>2680</v>
+        <v>2677</v>
       </c>
       <c r="F455" t="s">
-        <v>2719</v>
+        <v>2715</v>
       </c>
       <c r="G455" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J455" s="14" t="s">
+        <v>2804</v>
+      </c>
       <c r="K455" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B456" t="s">
         <v>2607</v>
-      </c>
-      <c r="B456" t="s">
-        <v>2608</v>
       </c>
       <c r="C456" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D456" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="G456" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J456" s="14" t="s">
+        <v>2805</v>
+      </c>
       <c r="K456" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B457" t="s">
         <v>2609</v>
-      </c>
-      <c r="B457" t="s">
-        <v>2610</v>
       </c>
       <c r="C457" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D457" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="F457" t="s">
-        <v>2720</v>
+        <v>2716</v>
       </c>
       <c r="G457" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J457" s="14" t="s">
+        <v>2806</v>
+      </c>
       <c r="K457" t="s">
-        <v>2768</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B458" t="s">
         <v>2611</v>
-      </c>
-      <c r="B458" t="s">
-        <v>2612</v>
       </c>
       <c r="C458" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D458" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="F458" t="s">
-        <v>2721</v>
+        <v>2717</v>
       </c>
       <c r="G458" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J458" s="14" t="s">
+        <v>2807</v>
+      </c>
       <c r="K458" t="s">
-        <v>2769</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B459" t="s">
         <v>2613</v>
-      </c>
-      <c r="B459" t="s">
-        <v>2614</v>
       </c>
       <c r="C459" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D459" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="F459" t="s">
-        <v>2722</v>
+        <v>2718</v>
       </c>
       <c r="G459" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J459" s="14" t="s">
+        <v>2808</v>
+      </c>
       <c r="K459" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B460" t="s">
         <v>2615</v>
-      </c>
-      <c r="B460" t="s">
-        <v>2616</v>
       </c>
       <c r="C460" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D460" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="F460" t="s">
-        <v>2723</v>
+        <v>2719</v>
       </c>
       <c r="G460" s="29" t="s">
         <v>2597</v>
       </c>
+      <c r="J460" s="14" t="s">
+        <v>2809</v>
+      </c>
       <c r="K460" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B461" t="s">
         <v>2617</v>
-      </c>
-      <c r="B461" t="s">
-        <v>2618</v>
       </c>
       <c r="C461" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D461" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="F461" t="s">
-        <v>2724</v>
+        <v>2720</v>
       </c>
       <c r="G461" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K461" t="s">
-        <v>2772</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B462" t="s">
         <v>2619</v>
-      </c>
-      <c r="B462" t="s">
-        <v>2620</v>
       </c>
       <c r="C462" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D462" t="s">
-        <v>2687</v>
+        <v>2684</v>
       </c>
       <c r="F462" t="s">
-        <v>2725</v>
+        <v>2721</v>
       </c>
       <c r="G462" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K462" t="s">
-        <v>2773</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B463" t="s">
         <v>2621</v>
-      </c>
-      <c r="B463" t="s">
-        <v>2622</v>
       </c>
       <c r="C463" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D463" t="s">
-        <v>2688</v>
+        <v>2685</v>
       </c>
       <c r="F463" t="s">
-        <v>2726</v>
+        <v>2722</v>
       </c>
       <c r="G463" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K463" t="s">
-        <v>2774</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B464" t="s">
         <v>2623</v>
-      </c>
-      <c r="B464" t="s">
-        <v>2624</v>
       </c>
       <c r="C464" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D464" t="s">
-        <v>2689</v>
+        <v>2686</v>
       </c>
       <c r="F464" t="s">
-        <v>2727</v>
+        <v>2723</v>
       </c>
       <c r="G464" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K464" t="s">
-        <v>2775</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B465" t="s">
         <v>2625</v>
-      </c>
-      <c r="B465" t="s">
-        <v>2626</v>
       </c>
       <c r="C465" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D465" t="s">
-        <v>2690</v>
+        <v>2687</v>
       </c>
       <c r="F465" t="s">
-        <v>2728</v>
+        <v>2724</v>
       </c>
       <c r="G465" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K465" t="s">
-        <v>2776</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B466" t="s">
         <v>2627</v>
-      </c>
-      <c r="B466" t="s">
-        <v>2628</v>
       </c>
       <c r="C466" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D466" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="F466" t="s">
-        <v>2729</v>
+        <v>2725</v>
       </c>
       <c r="G466" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K466" t="s">
-        <v>2777</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B467" t="s">
         <v>2629</v>
-      </c>
-      <c r="B467" t="s">
-        <v>2630</v>
       </c>
       <c r="C467" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D467" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="F467" t="s">
-        <v>2730</v>
+        <v>2726</v>
       </c>
       <c r="G467" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K467" t="s">
-        <v>2778</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B468" t="s">
         <v>2631</v>
-      </c>
-      <c r="B468" t="s">
-        <v>2632</v>
       </c>
       <c r="C468" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D468" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="F468" t="s">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="G468" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K468" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B469" t="s">
         <v>2633</v>
-      </c>
-      <c r="B469" t="s">
-        <v>2634</v>
       </c>
       <c r="C469" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D469" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="F469" t="s">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="G469" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K469" t="s">
-        <v>2779</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B470" t="s">
         <v>2635</v>
-      </c>
-      <c r="B470" t="s">
-        <v>2636</v>
       </c>
       <c r="C470" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D470" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="F470" t="s">
-        <v>2733</v>
+        <v>2729</v>
       </c>
       <c r="G470" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K470" t="s">
-        <v>2780</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B471" t="s">
         <v>2637</v>
-      </c>
-      <c r="B471" t="s">
-        <v>2638</v>
       </c>
       <c r="C471" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D471" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
       <c r="F471" t="s">
-        <v>2734</v>
+        <v>2730</v>
       </c>
       <c r="G471" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K471" t="s">
-        <v>2781</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B472" t="s">
         <v>2639</v>
-      </c>
-      <c r="B472" t="s">
-        <v>2640</v>
       </c>
       <c r="C472" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D472" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="F472" t="s">
-        <v>2735</v>
+        <v>2731</v>
       </c>
       <c r="G472" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K472" t="s">
-        <v>2782</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B473" t="s">
         <v>2641</v>
-      </c>
-      <c r="B473" t="s">
-        <v>2642</v>
       </c>
       <c r="C473" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D473" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="F473" t="s">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="G473" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K473" t="s">
-        <v>2783</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B474" t="s">
         <v>2643</v>
-      </c>
-      <c r="B474" t="s">
-        <v>2644</v>
       </c>
       <c r="C474" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D474" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="F474" t="s">
-        <v>2737</v>
+        <v>2733</v>
       </c>
       <c r="G474" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K474" t="s">
-        <v>2784</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B475" t="s">
         <v>2645</v>
-      </c>
-      <c r="B475" t="s">
-        <v>2646</v>
       </c>
       <c r="C475" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D475" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="F475" t="s">
-        <v>2738</v>
+        <v>2734</v>
       </c>
       <c r="G475" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K475" t="s">
-        <v>2785</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B476" t="s">
         <v>2647</v>
-      </c>
-      <c r="B476" t="s">
-        <v>2648</v>
       </c>
       <c r="C476" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D476" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="F476" t="s">
-        <v>2739</v>
+        <v>2735</v>
       </c>
       <c r="G476" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K476" t="s">
-        <v>2786</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B477" t="s">
         <v>2649</v>
-      </c>
-      <c r="B477" t="s">
-        <v>2650</v>
       </c>
       <c r="C477" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D477" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="F477" t="s">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="G477" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K477" t="s">
-        <v>2787</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B478" t="s">
         <v>2651</v>
-      </c>
-      <c r="B478" t="s">
-        <v>2652</v>
       </c>
       <c r="C478" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D478" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="F478" t="s">
-        <v>2741</v>
+        <v>2737</v>
       </c>
       <c r="G478" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K478" t="s">
-        <v>2788</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B479" t="s">
         <v>2653</v>
-      </c>
-      <c r="B479" t="s">
-        <v>2654</v>
       </c>
       <c r="C479" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D479" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="F479" t="s">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="G479" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K479" t="s">
-        <v>2789</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B480" t="s">
         <v>2655</v>
-      </c>
-      <c r="B480" t="s">
-        <v>2656</v>
       </c>
       <c r="C480" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D480" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="F480" t="s">
-        <v>2743</v>
+        <v>2739</v>
       </c>
       <c r="G480" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K480" t="s">
-        <v>2790</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B481" t="s">
         <v>2657</v>
-      </c>
-      <c r="B481" t="s">
-        <v>2658</v>
       </c>
       <c r="C481" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D481" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="F481" t="s">
-        <v>2744</v>
+        <v>2740</v>
       </c>
       <c r="G481" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K481" t="s">
-        <v>2791</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B482" t="s">
         <v>2659</v>
-      </c>
-      <c r="B482" t="s">
-        <v>2660</v>
       </c>
       <c r="C482" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D482" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="F482" t="s">
-        <v>2745</v>
+        <v>2741</v>
       </c>
       <c r="G482" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K482" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B483" t="s">
         <v>2661</v>
-      </c>
-      <c r="B483" t="s">
-        <v>2662</v>
       </c>
       <c r="C483" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D483" t="s">
-        <v>2708</v>
+        <v>2705</v>
       </c>
       <c r="F483" t="s">
-        <v>2746</v>
+        <v>2742</v>
       </c>
       <c r="G483" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K483" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B484" t="s">
         <v>2663</v>
-      </c>
-      <c r="B484" t="s">
-        <v>2664</v>
       </c>
       <c r="C484" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D484" t="s">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="F484" t="s">
-        <v>2747</v>
+        <v>2743</v>
       </c>
       <c r="G484" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K484" t="s">
-        <v>2794</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B485" t="s">
         <v>2665</v>
-      </c>
-      <c r="B485" t="s">
-        <v>2666</v>
       </c>
       <c r="C485" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D485" t="s">
-        <v>2710</v>
+        <v>2707</v>
       </c>
       <c r="F485" t="s">
-        <v>2748</v>
+        <v>2744</v>
       </c>
       <c r="G485" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K485" t="s">
-        <v>2796</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B486" t="s">
         <v>2667</v>
-      </c>
-      <c r="B486" t="s">
-        <v>2668</v>
       </c>
       <c r="C486" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D486" t="s">
-        <v>2711</v>
+        <v>2708</v>
       </c>
       <c r="F486" t="s">
-        <v>2749</v>
+        <v>2745</v>
       </c>
       <c r="G486" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K486" t="s">
-        <v>2795</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B487" t="s">
         <v>2669</v>
-      </c>
-      <c r="B487" t="s">
-        <v>2670</v>
       </c>
       <c r="C487" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D487" t="s">
-        <v>2712</v>
+        <v>2709</v>
       </c>
       <c r="F487" t="s">
-        <v>2750</v>
+        <v>2746</v>
       </c>
       <c r="G487" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K487" t="s">
-        <v>2797</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B488" t="s">
         <v>2671</v>
-      </c>
-      <c r="B488" t="s">
-        <v>2672</v>
       </c>
       <c r="C488" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D488" t="s">
-        <v>2713</v>
+        <v>2710</v>
       </c>
       <c r="F488" t="s">
-        <v>2751</v>
+        <v>2747</v>
       </c>
       <c r="G488" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K488" t="s">
-        <v>2798</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B489" t="s">
         <v>2673</v>
-      </c>
-      <c r="B489" t="s">
-        <v>2674</v>
       </c>
       <c r="C489" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D489" t="s">
-        <v>2714</v>
+        <v>2711</v>
       </c>
       <c r="F489" t="s">
-        <v>2752</v>
+        <v>2748</v>
       </c>
       <c r="G489" s="29" t="s">
         <v>2597</v>
       </c>
       <c r="K489" t="s">
-        <v>2799</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>2675</v>
+        <v>2795</v>
       </c>
       <c r="B490" t="s">
-        <v>2676</v>
-      </c>
-      <c r="C490" s="29" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C490" t="s">
         <v>1104</v>
       </c>
       <c r="D490" t="s">
-        <v>2715</v>
-      </c>
-      <c r="F490" t="s">
-        <v>2753</v>
-      </c>
-      <c r="G490" s="29" t="s">
-        <v>2597</v>
-      </c>
-      <c r="K490" t="s">
+        <v>2797</v>
+      </c>
+      <c r="G490" t="s">
+        <v>2136</v>
+      </c>
+      <c r="J490" s="14" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A491" s="30" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B491" s="30" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C491" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D491" s="30" t="s">
         <v>2800</v>
+      </c>
+      <c r="G491" s="30" t="s">
+        <v>2595</v>
+      </c>
+      <c r="J491" s="14" t="s">
+        <v>2811</v>
       </c>
     </row>
   </sheetData>
@@ -23899,7 +23980,7 @@
     <sortCondition ref="B2:B449"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G502:G509" xr:uid="{1E404653-0967-4485-8802-BC02506443F4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G501:G508" xr:uid="{1E404653-0967-4485-8802-BC02506443F4}">
       <formula1>$C$2:$C$102</formula1>
     </dataValidation>
   </dataValidations>
@@ -24159,9 +24240,20 @@
     <hyperlink ref="J451" r:id="rId253" xr:uid="{C7230777-0726-4B03-8D76-346F4625573C}"/>
     <hyperlink ref="J383" r:id="rId254" xr:uid="{4A54E760-26AA-4DC3-8FDD-553BE7D8DB56}"/>
     <hyperlink ref="J452" r:id="rId255" xr:uid="{AA438D1E-A7F6-4E55-8283-4089FEA815A9}"/>
+    <hyperlink ref="J490" r:id="rId256" xr:uid="{CC823740-B01C-42E3-9FE2-E6B1B76A2CA4}"/>
+    <hyperlink ref="J491" r:id="rId257" xr:uid="{E16AE97D-4D84-4557-A9E9-BABF7F3A006D}"/>
+    <hyperlink ref="J7" r:id="rId258" xr:uid="{BE71E1AF-D392-467D-8303-4A4FD350AE33}"/>
+    <hyperlink ref="J453" r:id="rId259" xr:uid="{EBC008FF-B4A0-46F9-9796-05B4166A9C2C}"/>
+    <hyperlink ref="J454" r:id="rId260" xr:uid="{3D659344-8535-4C0C-96FE-90C1F61D5EEB}"/>
+    <hyperlink ref="J455" r:id="rId261" xr:uid="{5534783A-7983-49F7-9FDC-CD2FC052E0D8}"/>
+    <hyperlink ref="J456" r:id="rId262" xr:uid="{827AE4CF-BE21-42A9-B46B-764D84BD25D5}"/>
+    <hyperlink ref="J457" r:id="rId263" xr:uid="{7383B90A-149A-43EF-BB3B-7097E3D50D32}"/>
+    <hyperlink ref="J458" r:id="rId264" xr:uid="{8B43E59E-EC63-49AD-8A59-66C05EE475AA}"/>
+    <hyperlink ref="J459" r:id="rId265" xr:uid="{F09EA9A6-8AF9-4BF2-A211-21B8CDAD6B40}"/>
+    <hyperlink ref="J460" r:id="rId266" xr:uid="{693C6F31-41B5-4F0F-8E7A-65674D99197C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId256"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId267"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -24175,7 +24267,7 @@
           <x14:formula1>
             <xm:f>'Sous-catégories'!$C$2:$C$100</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G501</xm:sqref>
+          <xm:sqref>G2:G500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -24954,17 +25046,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>1179</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -24976,17 +25068,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="33" t="s">
         <v>1181</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A13B0E4-910C-4FD5-811B-B0A787F032F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F337290-4D72-4338-A5D0-1BFCCE814391}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="2813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="2815">
   <si>
     <t>id</t>
   </si>
@@ -6366,9 +6366,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/mobiliere_ass.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/helvetia_ass.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/migros.jpg</t>
   </si>
   <si>
@@ -6483,9 +6480,6 @@
     <t>le téléphone ou l'Iphone</t>
   </si>
   <si>
-    <t>Professeur Joseph-André Ghyka, neurologue</t>
-  </si>
-  <si>
     <t>admin_conthey</t>
   </si>
   <si>
@@ -6808,9 +6802,6 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bagheera.jpg</t>
-  </si>
-  <si>
-    <t>Le professeur Joseph-André Ghyka est mon neurologue. Il exerce à Sierre.</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/pr_ghyka.jpg</t>
@@ -8469,6 +8460,21 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/iphone.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/dessert.jpg</t>
+  </si>
+  <si>
+    <t>Professeur Joseph-André Ghika, neurologue</t>
+  </si>
+  <si>
+    <t>Le professeur Joseph-André Ghika est mon neurologue. Il exerce à Sierre.</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/helvetia_ass.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bouquetin.png</t>
   </si>
 </sst>
 </file>
@@ -8966,13 +8972,13 @@
     </row>
     <row r="2" spans="1:7" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="B2" s="29">
         <v>10</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="D2" s="29" t="s">
         <v>66</v>
@@ -8981,7 +8987,7 @@
         <v>67</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="11" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -8992,7 +8998,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>1826</v>
@@ -9006,13 +9012,13 @@
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="B4" s="29">
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -9024,7 +9030,7 @@
         <v>9</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9035,7 +9041,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="D5" t="s">
         <v>46</v>
@@ -9047,7 +9053,7 @@
         <v>48</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9058,7 +9064,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -9081,7 +9087,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -9104,7 +9110,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -9150,7 +9156,7 @@
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -9173,7 +9179,7 @@
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -9196,7 +9202,7 @@
         <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -9208,7 +9214,7 @@
         <v>44</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9380,10 +9386,10 @@
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="D2" t="s">
         <v>74</v>
@@ -9403,10 +9409,10 @@
         <v>70</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -9418,7 +9424,7 @@
         <v>72</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9426,10 +9432,10 @@
         <v>77</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="D4" t="s">
         <v>78</v>
@@ -9446,10 +9452,10 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="D5" t="s">
         <v>82</v>
@@ -9469,10 +9475,10 @@
         <v>84</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -9492,10 +9498,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D7" t="s">
         <v>89</v>
@@ -9512,10 +9518,10 @@
         <v>93</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
@@ -9535,7 +9541,7 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
@@ -9555,7 +9561,7 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="D10" t="s">
         <v>98</v>
@@ -9575,7 +9581,7 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="D11" t="s">
         <v>246</v>
@@ -9592,10 +9598,10 @@
         <v>169</v>
       </c>
       <c r="B12" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -9615,10 +9621,10 @@
         <v>171</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="D13" t="s">
         <v>172</v>
@@ -9635,10 +9641,10 @@
         <v>174</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="D14" t="s">
         <v>175</v>
@@ -9658,10 +9664,10 @@
         <v>1823</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>175</v>
@@ -9678,13 +9684,13 @@
     </row>
     <row r="16" spans="1:7" s="23" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>35</v>
@@ -9693,18 +9699,18 @@
         <v>52</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B17" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C17" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D17" t="s">
         <v>164</v>
@@ -9721,13 +9727,13 @@
     </row>
     <row r="18" spans="1:7" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>164</v>
@@ -9741,13 +9747,13 @@
     </row>
     <row r="19" spans="1:7" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>164</v>
@@ -9761,13 +9767,13 @@
     </row>
     <row r="20" spans="1:7" s="17" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>164</v>
@@ -9779,7 +9785,7 @@
         <v>2080</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9787,10 +9793,10 @@
         <v>166</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C21" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D21" t="s">
         <v>167</v>
@@ -9804,13 +9810,13 @@
     </row>
     <row r="22" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>188</v>
@@ -9819,7 +9825,7 @@
         <v>57</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9827,10 +9833,10 @@
         <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -9847,7 +9853,7 @@
         <v>134</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C24" t="s">
         <v>2047</v>
@@ -9870,7 +9876,7 @@
         <v>138</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C25" t="s">
         <v>139</v>
@@ -9893,7 +9899,7 @@
         <v>142</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C26" t="s">
         <v>143</v>
@@ -9916,10 +9922,10 @@
         <v>147</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C27" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -9931,7 +9937,7 @@
         <v>149</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9939,7 +9945,7 @@
         <v>150</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C28" t="s">
         <v>151</v>
@@ -9962,7 +9968,7 @@
         <v>154</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C29" t="s">
         <v>155</v>
@@ -9982,10 +9988,10 @@
         <v>157</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C30" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="D30" t="s">
         <v>158</v>
@@ -10005,10 +10011,10 @@
         <v>161</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C31" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D31" t="s">
         <v>158</v>
@@ -10028,10 +10034,10 @@
         <v>1733</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>201</v>
@@ -10048,10 +10054,10 @@
         <v>1782</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C33" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D33" t="s">
         <v>203</v>
@@ -10063,7 +10069,7 @@
         <v>1784</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>2420</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10071,10 +10077,10 @@
         <v>1783</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>203</v>
@@ -10091,7 +10097,7 @@
         <v>1735</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>91</v>
@@ -10111,10 +10117,10 @@
         <v>204</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C36" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D36" t="s">
         <v>205</v>
@@ -10126,7 +10132,7 @@
         <v>206</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10134,10 +10140,10 @@
         <v>1686</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C37" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D37" t="s">
         <v>201</v>
@@ -10157,10 +10163,10 @@
         <v>1684</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C38" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D38" t="s">
         <v>205</v>
@@ -10172,7 +10178,7 @@
         <v>1685</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>2586</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10180,10 +10186,10 @@
         <v>200</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C39" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D39" t="s">
         <v>201</v>
@@ -10195,7 +10201,7 @@
         <v>202</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10203,7 +10209,7 @@
         <v>222</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C40" t="s">
         <v>223</v>
@@ -10223,7 +10229,7 @@
         <v>218</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C41" t="s">
         <v>219</v>
@@ -10246,10 +10252,10 @@
         <v>226</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C42" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="D42" t="s">
         <v>227</v>
@@ -10266,7 +10272,7 @@
         <v>230</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C43" t="s">
         <v>231</v>
@@ -10286,10 +10292,10 @@
         <v>235</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="D44" t="s">
         <v>236</v>
@@ -10306,10 +10312,10 @@
         <v>187</v>
       </c>
       <c r="B45" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="D45" t="s">
         <v>188</v>
@@ -10321,7 +10327,7 @@
         <v>189</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10329,10 +10335,10 @@
         <v>190</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="D46" t="s">
         <v>191</v>
@@ -10344,7 +10350,7 @@
         <v>192</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10352,10 +10358,10 @@
         <v>193</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="D47" t="s">
         <v>194</v>
@@ -10367,7 +10373,7 @@
         <v>195</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10375,10 +10381,10 @@
         <v>196</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>197</v>
@@ -10398,10 +10404,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -10421,10 +10427,10 @@
         <v>114</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="D50" t="s">
         <v>115</v>
@@ -10444,10 +10450,10 @@
         <v>119</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -10464,10 +10470,10 @@
         <v>123</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="D52" t="s">
         <v>124</v>
@@ -10487,10 +10493,10 @@
         <v>128</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>129</v>
@@ -10573,13 +10579,13 @@
     </row>
     <row r="57" spans="1:7" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="27" t="s">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>39</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>185</v>
@@ -10588,7 +10594,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10599,7 +10605,7 @@
         <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>185</v>
@@ -10616,7 +10622,7 @@
         <v>39</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="D59" t="s">
         <v>185</v>
@@ -10636,7 +10642,7 @@
         <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="D60" t="s">
         <v>179</v>
@@ -10676,7 +10682,7 @@
         <v>65</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>257</v>
@@ -10696,7 +10702,7 @@
         <v>65</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>249</v>
@@ -10716,7 +10722,7 @@
         <v>50</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="D64" t="s">
         <v>208</v>
@@ -10736,7 +10742,7 @@
         <v>50</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="D65" t="s">
         <v>215</v>
@@ -10756,7 +10762,7 @@
         <v>50</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="D66" t="s">
         <v>211</v>
@@ -10773,10 +10779,10 @@
         <v>2048</v>
       </c>
       <c r="B67" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C67" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="D67" t="s">
         <v>66</v>
@@ -10793,10 +10799,10 @@
         <v>1830</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C68" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D68" t="s">
         <v>1831</v>
@@ -10810,13 +10816,13 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="B69" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="C69" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="D69" s="29" t="s">
         <v>98</v>
@@ -10825,21 +10831,21 @@
         <v>13</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="B70" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="C70" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
     </row>
   </sheetData>
@@ -11016,7 +11022,7 @@
         <v>252</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="K4" t="s">
         <v>1146</v>
@@ -11049,31 +11055,31 @@
     </row>
     <row r="6" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2377</v>
+        <v>2374</v>
       </c>
       <c r="B6" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="C6" t="s">
         <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>252</v>
       </c>
       <c r="H6" s="6"/>
       <c r="J6" s="14" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B7" t="s">
         <v>2149</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2150</v>
       </c>
       <c r="C7" t="s">
         <v>270</v>
@@ -11085,14 +11091,14 @@
         <v>1149</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="14" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="K7" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -11162,7 +11168,7 @@
         <v>704</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H10" s="6"/>
       <c r="J10" s="14" t="s">
@@ -11192,7 +11198,7 @@
         <v>695</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H11" s="6"/>
       <c r="K11" t="s">
@@ -11219,7 +11225,7 @@
         <v>674</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H12" s="6"/>
       <c r="J12" s="20" t="s">
@@ -11249,7 +11255,7 @@
         <v>678</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H13" s="6"/>
       <c r="J13" s="23" t="s">
@@ -11279,7 +11285,7 @@
         <v>682</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H14" s="6"/>
       <c r="J14" s="20"/>
@@ -11307,7 +11313,7 @@
         <v>691</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H15" s="6"/>
       <c r="J15" s="23"/>
@@ -11335,7 +11341,7 @@
         <v>701</v>
       </c>
       <c r="G16" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H16" s="6"/>
       <c r="J16" s="19"/>
@@ -11363,7 +11369,7 @@
         <v>698</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H17" s="6"/>
       <c r="K17" t="s">
@@ -11390,7 +11396,7 @@
         <v>711</v>
       </c>
       <c r="G18" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H18" s="6"/>
       <c r="J18" t="s">
@@ -11420,7 +11426,7 @@
         <v>714</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H19" s="6"/>
       <c r="J19" t="s">
@@ -11450,7 +11456,7 @@
         <v>688</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H20" s="6"/>
       <c r="K20" t="s">
@@ -11477,7 +11483,7 @@
         <v>685</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H21" s="6"/>
       <c r="J21" s="23"/>
@@ -11505,7 +11511,7 @@
         <v>719</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H22" s="6"/>
       <c r="J22" s="14" t="s">
@@ -11535,7 +11541,7 @@
         <v>716</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H23" s="6"/>
       <c r="K23" t="s">
@@ -11562,7 +11568,7 @@
         <v>709</v>
       </c>
       <c r="G24" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H24" s="6"/>
       <c r="J24" s="23"/>
@@ -11591,7 +11597,7 @@
         <v>1720</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H25" s="6"/>
       <c r="J25" s="23"/>
@@ -11620,7 +11626,7 @@
         <v>641</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H26" s="6"/>
       <c r="J26" s="14" t="s">
@@ -11651,7 +11657,7 @@
         <v>643</v>
       </c>
       <c r="G27" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H27" s="6"/>
       <c r="J27" s="14" t="s">
@@ -11681,7 +11687,7 @@
         <v>654</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H28" s="6"/>
       <c r="J28" s="14" t="s">
@@ -11711,7 +11717,7 @@
         <v>652</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="J29" s="14" t="s">
         <v>1919</v>
@@ -11740,7 +11746,7 @@
         <v>645</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="J30" s="23" t="s">
         <v>646</v>
@@ -11769,7 +11775,7 @@
         <v>649</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H31" s="6"/>
       <c r="J31" s="23" t="s">
@@ -11784,23 +11790,23 @@
     </row>
     <row r="32" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2458</v>
+        <v>2455</v>
       </c>
       <c r="B32" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
       <c r="C32" t="s">
         <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H32" s="6"/>
       <c r="J32" s="14" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="M32" s="17">
         <v>7</v>
@@ -11808,23 +11814,23 @@
     </row>
     <row r="33" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>2432</v>
+        <v>2429</v>
       </c>
       <c r="B33" t="s">
-        <v>2461</v>
+        <v>2458</v>
       </c>
       <c r="C33" t="s">
         <v>270</v>
       </c>
       <c r="D33" t="s">
-        <v>2496</v>
+        <v>2493</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H33" s="6"/>
       <c r="J33" s="14" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="M33" s="17">
         <v>1</v>
@@ -11832,23 +11838,23 @@
     </row>
     <row r="34" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2439</v>
+        <v>2436</v>
       </c>
       <c r="B34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
       <c r="C34" t="s">
         <v>270</v>
       </c>
       <c r="D34" t="s">
-        <v>2492</v>
+        <v>2489</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H34" s="6"/>
       <c r="J34" s="14" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="M34" s="17">
         <v>2</v>
@@ -11856,23 +11862,23 @@
     </row>
     <row r="35" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="B35" t="s">
-        <v>2478</v>
+        <v>2475</v>
       </c>
       <c r="C35" t="s">
         <v>270</v>
       </c>
       <c r="D35" t="s">
-        <v>2479</v>
+        <v>2476</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H35" s="6"/>
       <c r="J35" s="14" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="M35" s="17">
         <v>3</v>
@@ -11880,23 +11886,23 @@
     </row>
     <row r="36" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>2423</v>
+        <v>2420</v>
       </c>
       <c r="B36" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C36" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" t="s">
         <v>2477</v>
       </c>
-      <c r="C36" t="s">
-        <v>270</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2480</v>
-      </c>
       <c r="G36" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H36" s="6"/>
       <c r="J36" s="14" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="M36" s="17">
         <v>4</v>
@@ -11904,23 +11910,23 @@
     </row>
     <row r="37" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>2441</v>
+        <v>2438</v>
       </c>
       <c r="B37" t="s">
-        <v>2500</v>
+        <v>2497</v>
       </c>
       <c r="C37" t="s">
         <v>270</v>
       </c>
       <c r="D37" t="s">
-        <v>2501</v>
+        <v>2498</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H37" s="6"/>
       <c r="J37" s="14" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="M37" s="17">
         <v>5</v>
@@ -11928,25 +11934,25 @@
     </row>
     <row r="38" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="B38" t="s">
-        <v>2475</v>
+        <v>2472</v>
       </c>
       <c r="C38" t="s">
         <v>270</v>
       </c>
       <c r="D38" t="s">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>1828</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="M38" s="17">
         <v>6</v>
@@ -12123,7 +12129,7 @@
       </c>
       <c r="H44" s="6"/>
       <c r="J44" s="14" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="K44" t="s">
         <v>495</v>
@@ -12153,7 +12159,7 @@
       </c>
       <c r="H45" s="6"/>
       <c r="J45" s="14" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="K45" t="s">
         <v>499</v>
@@ -12224,23 +12230,23 @@
     </row>
     <row r="48" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="B48" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C48" t="s">
         <v>270</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="G48" s="22" t="s">
         <v>2047</v>
       </c>
       <c r="H48" s="6"/>
       <c r="J48" s="14" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="M48">
         <v>10</v>
@@ -12387,7 +12393,7 @@
       </c>
       <c r="H53" s="6"/>
       <c r="J53" s="15" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
       <c r="K53" t="s">
         <v>537</v>
@@ -12518,23 +12524,23 @@
     </row>
     <row r="58" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="B58" t="s">
-        <v>2453</v>
+        <v>2450</v>
       </c>
       <c r="C58" t="s">
         <v>270</v>
       </c>
       <c r="D58" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="G58" t="s">
         <v>2047</v>
       </c>
       <c r="H58" s="6"/>
       <c r="J58" s="14" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="M58">
         <v>19</v>
@@ -12542,23 +12548,23 @@
     </row>
     <row r="59" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>2436</v>
+        <v>2433</v>
       </c>
       <c r="B59" t="s">
-        <v>2464</v>
+        <v>2461</v>
       </c>
       <c r="C59" t="s">
         <v>270</v>
       </c>
       <c r="D59" t="s">
-        <v>2497</v>
+        <v>2494</v>
       </c>
       <c r="G59" t="s">
         <v>2047</v>
       </c>
       <c r="H59" s="6"/>
       <c r="J59" s="14" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="L59" s="8"/>
       <c r="M59">
@@ -12700,7 +12706,7 @@
         <v>451</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="H64" s="6"/>
       <c r="J64" s="14" t="s">
@@ -12730,7 +12736,7 @@
         <v>453</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="H65" s="6"/>
       <c r="J65" s="14" t="s">
@@ -12760,7 +12766,7 @@
         <v>455</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="H66" s="6"/>
       <c r="J66" s="14" t="s">
@@ -12904,7 +12910,7 @@
         <v>270</v>
       </c>
       <c r="D71" t="s">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="E71" t="s">
         <v>563</v>
@@ -12955,23 +12961,23 @@
     </row>
     <row r="73" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2443</v>
+        <v>2440</v>
       </c>
       <c r="B73" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="C73" t="s">
         <v>270</v>
       </c>
       <c r="D73" t="s">
-        <v>2493</v>
+        <v>2490</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H73" s="6"/>
       <c r="J73" s="14" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="M73">
         <v>1</v>
@@ -12979,23 +12985,23 @@
     </row>
     <row r="74" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>2428</v>
+        <v>2425</v>
       </c>
       <c r="B74" t="s">
-        <v>2454</v>
+        <v>2451</v>
       </c>
       <c r="C74" t="s">
         <v>270</v>
       </c>
       <c r="D74" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H74" s="6"/>
       <c r="J74" s="14" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="M74">
         <v>2</v>
@@ -13003,23 +13009,23 @@
     </row>
     <row r="75" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>2434</v>
+        <v>2431</v>
       </c>
       <c r="B75" t="s">
-        <v>2463</v>
+        <v>2460</v>
       </c>
       <c r="C75" t="s">
         <v>270</v>
       </c>
       <c r="D75" t="s">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -13027,23 +13033,23 @@
     </row>
     <row r="76" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>2424</v>
+        <v>2421</v>
       </c>
       <c r="B76" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="C76" t="s">
         <v>270</v>
       </c>
       <c r="D76" t="s">
-        <v>2485</v>
+        <v>2482</v>
       </c>
       <c r="G76" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H76" s="6"/>
       <c r="J76" s="14" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
       <c r="M76">
         <v>4</v>
@@ -13051,23 +13057,23 @@
     </row>
     <row r="77" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
       <c r="B77" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="C77" t="s">
         <v>270</v>
       </c>
       <c r="D77" t="s">
-        <v>2494</v>
+        <v>2491</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H77" s="6"/>
       <c r="J77" s="14" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="M77">
         <v>5</v>
@@ -13075,23 +13081,23 @@
     </row>
     <row r="78" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
       <c r="B78" t="s">
-        <v>2468</v>
+        <v>2465</v>
       </c>
       <c r="C78" t="s">
         <v>270</v>
       </c>
       <c r="D78" t="s">
-        <v>2499</v>
+        <v>2496</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H78" s="6"/>
       <c r="J78" s="14" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="M78">
         <v>6</v>
@@ -13099,23 +13105,23 @@
     </row>
     <row r="79" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="B79" t="s">
-        <v>2455</v>
+        <v>2452</v>
       </c>
       <c r="C79" t="s">
         <v>270</v>
       </c>
       <c r="D79" t="s">
-        <v>2483</v>
+        <v>2480</v>
       </c>
       <c r="G79" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="H79" s="6"/>
       <c r="J79" s="14" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="M79">
         <v>7</v>
@@ -13259,7 +13265,7 @@
       </c>
       <c r="H84" s="6"/>
       <c r="J84" s="15" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="K84" t="s">
         <v>1693</v>
@@ -13429,7 +13435,7 @@
         <v>449</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="H90" s="6"/>
       <c r="J90" s="14" t="s">
@@ -13459,7 +13465,7 @@
         <v>446</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="H91" s="6"/>
       <c r="J91" s="23" t="s">
@@ -13489,7 +13495,7 @@
         <v>763</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H92" s="6"/>
       <c r="J92" s="19" t="s">
@@ -13519,11 +13525,11 @@
         <v>766</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H93" s="6"/>
       <c r="J93" s="14" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="K93" t="s">
         <v>765</v>
@@ -13549,11 +13555,11 @@
         <v>757</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H94" s="6"/>
       <c r="J94" s="14" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="K94" t="s">
         <v>756</v>
@@ -13579,7 +13585,7 @@
         <v>759</v>
       </c>
       <c r="G95" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H95" s="6"/>
       <c r="J95" s="23" t="s">
@@ -13609,7 +13615,7 @@
         <v>1699</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H96" s="6"/>
       <c r="J96" s="14" t="s">
@@ -13639,7 +13645,7 @@
         <v>777</v>
       </c>
       <c r="G97" s="22" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H97" s="6"/>
       <c r="J97" s="21" t="s">
@@ -13669,7 +13675,7 @@
         <v>769</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H98" s="6"/>
       <c r="J98" s="23" t="s">
@@ -13699,7 +13705,7 @@
         <v>772</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H99" s="6"/>
       <c r="J99" s="23" t="s">
@@ -13729,7 +13735,7 @@
         <v>775</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H100" s="6"/>
       <c r="J100" s="14" t="s">
@@ -13759,11 +13765,11 @@
         <v>780</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H101" s="6"/>
       <c r="J101" s="14" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="K101" t="s">
         <v>779</v>
@@ -13789,7 +13795,7 @@
         <v>782</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="H102" s="6"/>
       <c r="J102" s="14" t="s">
@@ -13816,7 +13822,7 @@
         <v>346</v>
       </c>
       <c r="G103" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="H103" s="6"/>
       <c r="J103" s="19"/>
@@ -13841,7 +13847,7 @@
         <v>350</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="H104" s="6"/>
       <c r="J104" s="23"/>
@@ -13851,30 +13857,30 @@
     </row>
     <row r="105" spans="1:13" s="11" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>270</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="B106" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="C106" t="s">
         <v>270</v>
@@ -13883,11 +13889,11 @@
         <v>1692</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="H106" s="6"/>
       <c r="J106" s="14" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -13907,7 +13913,7 @@
         <v>847</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H107" s="6"/>
       <c r="K107" t="s">
@@ -13934,7 +13940,7 @@
         <v>853</v>
       </c>
       <c r="G108" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H108" s="6"/>
       <c r="K108" t="s">
@@ -13961,7 +13967,7 @@
         <v>850</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H109" s="6"/>
       <c r="J109" s="20"/>
@@ -13989,7 +13995,7 @@
         <v>1741</v>
       </c>
       <c r="G110" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H110" s="6"/>
       <c r="J110" s="21"/>
@@ -14017,7 +14023,7 @@
         <v>1746</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H111" s="6"/>
       <c r="J111" s="21"/>
@@ -14045,7 +14051,7 @@
         <v>841</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="H112" s="6"/>
       <c r="J112" s="23"/>
@@ -14073,11 +14079,11 @@
         <v>1723</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="H113" s="6"/>
       <c r="J113" s="15" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="K113" t="s">
         <v>840</v>
@@ -14103,11 +14109,11 @@
         <v>1692</v>
       </c>
       <c r="G114" s="22" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="H114" s="6"/>
       <c r="J114" s="15" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="K114" t="s">
         <v>838</v>
@@ -14134,7 +14140,7 @@
         <v>844</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="H115" s="6"/>
       <c r="K115" t="s">
@@ -14161,7 +14167,7 @@
         <v>856</v>
       </c>
       <c r="G116" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H116" s="6"/>
       <c r="J116" s="23"/>
@@ -14186,7 +14192,7 @@
         <v>2021</v>
       </c>
       <c r="G117" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H117" s="6"/>
       <c r="J117" s="14" t="s">
@@ -14213,7 +14219,7 @@
         <v>2022</v>
       </c>
       <c r="G118" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H118" s="6"/>
       <c r="J118" s="14" t="s">
@@ -14243,7 +14249,7 @@
         <v>1755</v>
       </c>
       <c r="G119" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H119" s="6"/>
       <c r="J119" s="14" t="s">
@@ -14273,7 +14279,7 @@
         <v>1691</v>
       </c>
       <c r="G120" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H120" s="6"/>
       <c r="J120" s="14" t="s">
@@ -14288,23 +14294,23 @@
     </row>
     <row r="121" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="B121" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C121" t="s">
         <v>270</v>
       </c>
       <c r="D121" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="G121" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H121" s="6"/>
       <c r="J121" s="14" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="M121">
         <v>6</v>
@@ -14327,7 +14333,7 @@
         <v>1751</v>
       </c>
       <c r="G122" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H122" s="6"/>
       <c r="J122" s="14" t="s">
@@ -14354,7 +14360,7 @@
         <v>1724</v>
       </c>
       <c r="G123" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H123" s="6"/>
       <c r="J123" s="23" t="s">
@@ -14384,10 +14390,12 @@
         <v>1725</v>
       </c>
       <c r="G124" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H124" s="8"/>
-      <c r="J124" s="25"/>
+      <c r="J124" s="14" t="s">
+        <v>2814</v>
+      </c>
       <c r="K124" s="12" t="s">
         <v>860</v>
       </c>
@@ -14412,7 +14420,7 @@
         <v>866</v>
       </c>
       <c r="G125" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H125" s="6"/>
       <c r="J125" s="14" t="s">
@@ -14442,7 +14450,7 @@
         <v>862</v>
       </c>
       <c r="G126" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H126" s="6"/>
       <c r="J126" s="19"/>
@@ -14470,7 +14478,7 @@
         <v>873</v>
       </c>
       <c r="G127" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H127" s="6"/>
       <c r="J127" s="19"/>
@@ -14498,7 +14506,7 @@
         <v>868</v>
       </c>
       <c r="G128" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H128" s="6"/>
       <c r="J128" s="23"/>
@@ -14526,7 +14534,7 @@
         <v>871</v>
       </c>
       <c r="G129" s="22" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="H129" s="6"/>
       <c r="J129" s="25"/>
@@ -14554,7 +14562,7 @@
         <v>905</v>
       </c>
       <c r="G130" s="22" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="H130" s="6"/>
       <c r="J130" s="14" t="s">
@@ -14584,7 +14592,7 @@
         <v>907</v>
       </c>
       <c r="G131" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="H131" s="6"/>
       <c r="J131" s="14" t="s">
@@ -14614,7 +14622,7 @@
         <v>1762</v>
       </c>
       <c r="G132" s="22" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="H132" s="6"/>
       <c r="J132" s="14" t="s">
@@ -14644,11 +14652,11 @@
         <v>1760</v>
       </c>
       <c r="G133" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="H133" s="6"/>
       <c r="J133" s="14" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="K133" t="s">
         <v>1764</v>
@@ -14674,7 +14682,7 @@
         <v>1768</v>
       </c>
       <c r="G134" s="22" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="H134" s="6"/>
       <c r="J134" s="14" t="s">
@@ -14702,11 +14710,11 @@
       </c>
       <c r="E135" s="23"/>
       <c r="G135" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H135" s="6"/>
       <c r="J135" s="14" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
       <c r="M135">
         <v>1</v>
@@ -14727,11 +14735,11 @@
       </c>
       <c r="E136" s="23"/>
       <c r="G136" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H136" s="6"/>
       <c r="J136" s="14" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="M136">
         <v>2</v>
@@ -14752,7 +14760,7 @@
       </c>
       <c r="E137" s="23"/>
       <c r="G137" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H137" s="6"/>
       <c r="J137" s="14" t="s">
@@ -14777,11 +14785,11 @@
       </c>
       <c r="E138" s="20"/>
       <c r="G138" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H138" s="6"/>
       <c r="J138" s="14" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="M138">
         <v>4</v>
@@ -14802,11 +14810,11 @@
       </c>
       <c r="E139" s="21"/>
       <c r="G139" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H139" s="6"/>
       <c r="J139" s="14" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="M139">
         <v>5</v>
@@ -14827,7 +14835,7 @@
       </c>
       <c r="E140" s="21"/>
       <c r="G140" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H140" s="6"/>
       <c r="J140" s="14" t="s">
@@ -14852,11 +14860,11 @@
       </c>
       <c r="E141" s="23"/>
       <c r="G141" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H141" s="6"/>
       <c r="J141" s="14" t="s">
-        <v>2112</v>
+        <v>2813</v>
       </c>
       <c r="M141">
         <v>7</v>
@@ -14877,11 +14885,11 @@
       </c>
       <c r="E142" s="23"/>
       <c r="G142" s="22" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="H142" s="6"/>
       <c r="J142" s="14" t="s">
-        <v>2112</v>
+        <v>2813</v>
       </c>
       <c r="M142">
         <v>8</v>
@@ -14889,24 +14897,24 @@
     </row>
     <row r="143" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B143" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C143" t="s">
+        <v>270</v>
+      </c>
+      <c r="D143" t="s">
         <v>2152</v>
-      </c>
-      <c r="B143" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C143" t="s">
-        <v>270</v>
-      </c>
-      <c r="D143" t="s">
-        <v>2154</v>
       </c>
       <c r="E143" s="23"/>
       <c r="G143" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H143" s="6"/>
       <c r="J143" s="14" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="M143">
         <v>1</v>
@@ -14914,23 +14922,23 @@
     </row>
     <row r="144" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="B144" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C144" t="s">
         <v>270</v>
       </c>
       <c r="D144" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="G144" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H144" s="6"/>
       <c r="J144" s="14" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="M144">
         <v>2</v>
@@ -14953,11 +14961,11 @@
         <v>937</v>
       </c>
       <c r="G145" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H145" s="6"/>
       <c r="J145" s="14" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="K145" t="s">
         <v>938</v>
@@ -14977,10 +14985,10 @@
         <v>270</v>
       </c>
       <c r="D146" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="G146" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H146" s="6"/>
       <c r="J146" s="14"/>
@@ -14990,19 +14998,19 @@
     </row>
     <row r="147" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="B147" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C147" t="s">
         <v>270</v>
       </c>
       <c r="D147" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="G147" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H147" s="6"/>
       <c r="J147" s="24"/>
@@ -15012,23 +15020,23 @@
     </row>
     <row r="148" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="B148" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="C148" t="s">
         <v>270</v>
       </c>
       <c r="D148" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="G148" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H148" s="6"/>
       <c r="J148" s="14" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="M148">
         <v>6</v>
@@ -15036,23 +15044,23 @@
     </row>
     <row r="149" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="B149" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="C149" t="s">
         <v>270</v>
       </c>
       <c r="D149" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="G149" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H149" s="6"/>
       <c r="J149" s="14" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="M149">
         <v>7</v>
@@ -15060,23 +15068,23 @@
     </row>
     <row r="150" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="B150" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C150" t="s">
         <v>270</v>
       </c>
       <c r="D150" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="G150" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H150" s="6"/>
       <c r="J150" s="14" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="M150">
         <v>8</v>
@@ -15084,23 +15092,23 @@
     </row>
     <row r="151" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="B151" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="C151" t="s">
         <v>270</v>
       </c>
       <c r="D151" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="G151" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H151" s="6"/>
       <c r="J151" s="14" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="M151">
         <v>9</v>
@@ -15108,23 +15116,23 @@
     </row>
     <row r="152" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="B152" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C152" t="s">
         <v>270</v>
       </c>
       <c r="D152" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="G152" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H152" s="6"/>
       <c r="J152" s="14" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="M152">
         <v>10</v>
@@ -15132,23 +15140,23 @@
     </row>
     <row r="153" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="19" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="B153" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="C153" t="s">
         <v>270</v>
       </c>
       <c r="D153" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="G153" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H153" s="6"/>
       <c r="J153" s="14" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
       <c r="M153">
         <v>11</v>
@@ -15156,23 +15164,23 @@
     </row>
     <row r="154" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="B154" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="C154" t="s">
         <v>270</v>
       </c>
       <c r="D154" s="20" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="G154" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H154" s="6"/>
       <c r="J154" s="14" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="M154">
         <v>13</v>
@@ -15180,23 +15188,23 @@
     </row>
     <row r="155" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="B155" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C155" t="s">
         <v>270</v>
       </c>
       <c r="D155" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="G155" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H155" s="6"/>
       <c r="J155" s="14" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="M155">
         <v>14</v>
@@ -15204,23 +15212,23 @@
     </row>
     <row r="156" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="B156" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C156" t="s">
         <v>270</v>
       </c>
       <c r="D156" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="G156" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H156" s="6"/>
       <c r="J156" s="14" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="M156">
         <v>15</v>
@@ -15228,22 +15236,22 @@
     </row>
     <row r="157" spans="1:13" s="11" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>270</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="G157" s="22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="J157" s="14" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="M157" s="11">
         <v>16</v>
@@ -15266,7 +15274,7 @@
         <v>945</v>
       </c>
       <c r="G158" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H158" s="6"/>
       <c r="J158" s="23"/>
@@ -15294,7 +15302,7 @@
         <v>949</v>
       </c>
       <c r="G159" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H159" s="6"/>
       <c r="J159" s="23"/>
@@ -15322,11 +15330,11 @@
         <v>941</v>
       </c>
       <c r="G160" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="H160" s="6"/>
       <c r="J160" s="14" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="K160" t="s">
         <v>942</v>
@@ -15352,7 +15360,7 @@
         <v>294</v>
       </c>
       <c r="G161" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="H161" s="6"/>
       <c r="J161" s="23" t="s">
@@ -15382,7 +15390,7 @@
         <v>300</v>
       </c>
       <c r="G162" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="H162" s="6"/>
       <c r="J162" s="14" t="s">
@@ -15412,7 +15420,7 @@
         <v>298</v>
       </c>
       <c r="G163" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="H163" s="6"/>
       <c r="J163" s="14" t="s">
@@ -15442,7 +15450,7 @@
         <v>302</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="H164" s="8"/>
       <c r="J164" s="14" t="s">
@@ -15457,23 +15465,23 @@
     </row>
     <row r="165" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="B165" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="C165" t="s">
         <v>270</v>
       </c>
       <c r="D165" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="H165" s="6"/>
       <c r="J165" s="14" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="M165">
         <v>6</v>
@@ -15496,7 +15504,7 @@
         <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H166" s="6"/>
       <c r="J166" s="23" t="s">
@@ -15526,7 +15534,7 @@
         <v>1701</v>
       </c>
       <c r="G167" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H167" s="6"/>
       <c r="J167" s="26" t="s">
@@ -15556,7 +15564,7 @@
         <v>280</v>
       </c>
       <c r="G168" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H168" s="6"/>
       <c r="J168" s="14" t="s">
@@ -15586,7 +15594,7 @@
         <v>283</v>
       </c>
       <c r="G169" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H169" s="6"/>
       <c r="J169" s="26" t="s">
@@ -15616,7 +15624,7 @@
         <v>292</v>
       </c>
       <c r="G170" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H170" s="6"/>
       <c r="J170" s="14" t="s">
@@ -15646,7 +15654,7 @@
         <v>289</v>
       </c>
       <c r="G171" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H171" s="6"/>
       <c r="J171" s="23" t="s">
@@ -15676,7 +15684,7 @@
         <v>286</v>
       </c>
       <c r="G172" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H172" s="6"/>
       <c r="J172" s="26" t="s">
@@ -15706,11 +15714,11 @@
         <v>278</v>
       </c>
       <c r="G173" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="H173" s="6"/>
       <c r="J173" s="14" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="K173" t="s">
         <v>277</v>
@@ -15736,7 +15744,7 @@
         <v>443</v>
       </c>
       <c r="G174" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="H174" s="6"/>
       <c r="J174" s="14" t="s">
@@ -15766,7 +15774,7 @@
         <v>440</v>
       </c>
       <c r="G175" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="H175" s="6"/>
       <c r="J175" s="26"/>
@@ -15791,10 +15799,10 @@
         <v>1232</v>
       </c>
       <c r="E176" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="G176" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="H176" s="6"/>
       <c r="J176" s="14" t="s">
@@ -15824,7 +15832,7 @@
         <v>918</v>
       </c>
       <c r="G177" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="H177" s="6"/>
       <c r="J177" s="15" t="s">
@@ -15851,7 +15859,7 @@
         <v>899</v>
       </c>
       <c r="G178" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="H178" s="6"/>
       <c r="J178" s="23"/>
@@ -15876,7 +15884,7 @@
         <v>910</v>
       </c>
       <c r="G179" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="H179" s="6"/>
       <c r="J179" s="26"/>
@@ -15901,7 +15909,7 @@
         <v>1680</v>
       </c>
       <c r="G180" s="22" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="H180" s="6"/>
       <c r="J180" s="14" t="s">
@@ -15928,7 +15936,7 @@
         <v>933</v>
       </c>
       <c r="G181" s="22" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="H181" s="6"/>
       <c r="J181" s="14" t="s">
@@ -15955,7 +15963,7 @@
         <v>825</v>
       </c>
       <c r="G182" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="H182" s="6"/>
       <c r="J182" s="23"/>
@@ -15980,7 +15988,7 @@
         <v>831</v>
       </c>
       <c r="G183" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="H183" s="6"/>
       <c r="J183" s="23"/>
@@ -16005,7 +16013,7 @@
         <v>821</v>
       </c>
       <c r="G184" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="H184" s="6"/>
       <c r="J184" s="23"/>
@@ -16030,7 +16038,7 @@
         <v>835</v>
       </c>
       <c r="G185" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="H185" s="6"/>
       <c r="J185" s="23" t="s">
@@ -16057,7 +16065,7 @@
         <v>1722</v>
       </c>
       <c r="G186" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="H186" s="6"/>
       <c r="J186" s="20"/>
@@ -16082,7 +16090,7 @@
         <v>804</v>
       </c>
       <c r="G187" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H187" s="6"/>
       <c r="J187" s="23"/>
@@ -16107,7 +16115,7 @@
         <v>788</v>
       </c>
       <c r="G188" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H188" s="6"/>
       <c r="J188" s="26" t="s">
@@ -16134,7 +16142,7 @@
         <v>797</v>
       </c>
       <c r="G189" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H189" s="6"/>
       <c r="J189" s="14" t="s">
@@ -16161,7 +16169,7 @@
         <v>785</v>
       </c>
       <c r="G190" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H190" s="6"/>
       <c r="J190" s="14" t="s">
@@ -16188,7 +16196,7 @@
         <v>800</v>
       </c>
       <c r="G191" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H191" s="6"/>
       <c r="J191" s="23"/>
@@ -16213,7 +16221,7 @@
         <v>793</v>
       </c>
       <c r="G192" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H192" s="6"/>
       <c r="J192" s="26" t="s">
@@ -16240,7 +16248,7 @@
         <v>1899</v>
       </c>
       <c r="G193" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="H193" s="6"/>
       <c r="J193" s="14" t="s">
@@ -16264,7 +16272,7 @@
         <v>1114</v>
       </c>
       <c r="G194" s="20" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="H194" s="6"/>
       <c r="J194" s="20"/>
@@ -16289,7 +16297,7 @@
         <v>1110</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="H195" s="6"/>
       <c r="J195" s="21"/>
@@ -16314,7 +16322,7 @@
         <v>1122</v>
       </c>
       <c r="G196" s="20" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="J196" s="23"/>
       <c r="K196" s="6" t="s">
@@ -16338,7 +16346,7 @@
         <v>1118</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="H197" s="6"/>
       <c r="J197" s="23"/>
@@ -16363,7 +16371,7 @@
         <v>1089</v>
       </c>
       <c r="G198" s="20" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H198" s="6"/>
       <c r="J198" s="23"/>
@@ -16388,7 +16396,7 @@
         <v>1101</v>
       </c>
       <c r="G199" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H199" s="6"/>
       <c r="J199" s="23"/>
@@ -16413,7 +16421,7 @@
         <v>1106</v>
       </c>
       <c r="G200" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H200" s="6"/>
       <c r="J200" s="23"/>
@@ -16438,7 +16446,7 @@
         <v>1073</v>
       </c>
       <c r="G201" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H201" s="6"/>
       <c r="J201" s="23"/>
@@ -16463,7 +16471,7 @@
         <v>1097</v>
       </c>
       <c r="G202" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H202" s="6"/>
       <c r="J202" s="23"/>
@@ -16488,7 +16496,7 @@
         <v>1069</v>
       </c>
       <c r="G203" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H203" s="6"/>
       <c r="J203" s="23"/>
@@ -16513,7 +16521,7 @@
         <v>1077</v>
       </c>
       <c r="G204" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H204" s="6"/>
       <c r="J204" s="23"/>
@@ -16538,7 +16546,7 @@
         <v>1093</v>
       </c>
       <c r="G205" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H205" s="6"/>
       <c r="J205" s="23"/>
@@ -16563,7 +16571,7 @@
         <v>1085</v>
       </c>
       <c r="G206" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H206" s="6"/>
       <c r="J206" s="23"/>
@@ -16588,7 +16596,7 @@
         <v>1081</v>
       </c>
       <c r="G207" s="22" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="H207" s="6"/>
       <c r="J207" s="23"/>
@@ -16598,23 +16606,23 @@
     </row>
     <row r="208" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="B208" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C208" t="s">
         <v>270</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="G208" s="22" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H208" s="6"/>
       <c r="J208" s="14" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="M208">
         <v>1</v>
@@ -16622,24 +16630,24 @@
     </row>
     <row r="209" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
       <c r="B209" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="C209" t="s">
         <v>270</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="E209" s="23"/>
       <c r="G209" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H209" s="6"/>
       <c r="J209" s="14" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="M209">
         <v>2</v>
@@ -16647,24 +16655,24 @@
     </row>
     <row r="210" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="B210" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C210" t="s">
         <v>270</v>
       </c>
       <c r="D210" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="E210" s="26"/>
       <c r="G210" s="6" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H210" s="6"/>
       <c r="J210" s="14" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="M210">
         <v>3</v>
@@ -16672,24 +16680,24 @@
     </row>
     <row r="211" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B211" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C211" t="s">
+        <v>270</v>
+      </c>
+      <c r="D211" t="s">
         <v>2171</v>
-      </c>
-      <c r="B211" t="s">
-        <v>2172</v>
-      </c>
-      <c r="C211" t="s">
-        <v>270</v>
-      </c>
-      <c r="D211" t="s">
-        <v>2173</v>
       </c>
       <c r="E211" s="27"/>
       <c r="G211" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H211" s="6"/>
       <c r="J211" s="14" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="M211">
         <v>4</v>
@@ -16697,24 +16705,24 @@
     </row>
     <row r="212" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="B212" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C212" t="s">
         <v>270</v>
       </c>
       <c r="D212" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="E212" s="27"/>
       <c r="G212" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H212" s="6"/>
       <c r="J212" s="14" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="M212">
         <v>5</v>
@@ -16722,24 +16730,24 @@
     </row>
     <row r="213" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="B213" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C213" t="s">
         <v>270</v>
       </c>
       <c r="D213" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="E213" s="27"/>
       <c r="G213" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H213" s="6"/>
       <c r="J213" s="14" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="M213">
         <v>6</v>
@@ -16747,24 +16755,24 @@
     </row>
     <row r="214" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
       <c r="B214" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C214" t="s">
         <v>270</v>
       </c>
       <c r="D214" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="E214" s="27"/>
       <c r="G214" s="20" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H214" s="6"/>
       <c r="J214" s="14" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="M214">
         <v>7</v>
@@ -16772,23 +16780,23 @@
     </row>
     <row r="215" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="B215" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="C215" t="s">
         <v>270</v>
       </c>
       <c r="D215" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H215" s="6"/>
       <c r="J215" s="14" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="M215">
         <v>8</v>
@@ -16796,24 +16804,24 @@
     </row>
     <row r="216" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="B216" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="C216" t="s">
         <v>270</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="E216" s="23"/>
       <c r="G216" s="20" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H216" s="6"/>
       <c r="J216" s="14" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="M216">
         <v>9</v>
@@ -16821,24 +16829,24 @@
     </row>
     <row r="217" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="B217" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C217" t="s">
         <v>270</v>
       </c>
       <c r="D217" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="E217" s="26"/>
       <c r="G217" s="20" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H217" s="6"/>
       <c r="J217" s="14" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="M217">
         <v>10</v>
@@ -16846,24 +16854,24 @@
     </row>
     <row r="218" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="B218" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="C218" t="s">
         <v>270</v>
       </c>
       <c r="D218" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E218" s="27"/>
       <c r="G218" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H218" s="6"/>
       <c r="J218" s="14" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="M218">
         <v>11</v>
@@ -16871,24 +16879,24 @@
     </row>
     <row r="219" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="B219" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C219" t="s">
         <v>270</v>
       </c>
       <c r="D219" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="E219" s="27"/>
       <c r="G219" s="20" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="H219" s="6"/>
       <c r="J219" s="14" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="M219">
         <v>12</v>
@@ -16911,7 +16919,7 @@
         <v>1164</v>
       </c>
       <c r="G220" s="20" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="H220" s="6"/>
       <c r="J220" s="27"/>
@@ -16936,7 +16944,7 @@
         <v>1168</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="H221" s="6"/>
       <c r="J221" s="27"/>
@@ -16961,7 +16969,7 @@
         <v>921</v>
       </c>
       <c r="G222" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H222" s="6"/>
       <c r="J222" s="27"/>
@@ -16987,7 +16995,7 @@
       </c>
       <c r="E223" s="5"/>
       <c r="G223" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H223" s="6"/>
       <c r="J223" s="14" t="s">
@@ -17015,7 +17023,7 @@
       </c>
       <c r="E224" s="5"/>
       <c r="G224" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H224" s="6"/>
       <c r="J224" s="14" t="s">
@@ -17043,7 +17051,7 @@
       </c>
       <c r="E225" s="5"/>
       <c r="G225" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H225" s="6"/>
       <c r="J225" s="14" t="s">
@@ -17071,7 +17079,7 @@
       </c>
       <c r="E226" s="5"/>
       <c r="G226" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H226" s="6"/>
       <c r="J226" s="14" t="s">
@@ -17098,11 +17106,11 @@
         <v>2061</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H227" s="6"/>
       <c r="J227" s="14" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="M227">
         <v>6</v>
@@ -17122,11 +17130,11 @@
         <v>2062</v>
       </c>
       <c r="G228" s="20" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H228" s="6"/>
       <c r="J228" s="14" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="M228">
         <v>7</v>
@@ -17146,11 +17154,11 @@
         <v>2063</v>
       </c>
       <c r="G229" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H229" s="6"/>
       <c r="J229" s="14" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="M229">
         <v>8</v>
@@ -17171,7 +17179,7 @@
       </c>
       <c r="E230" s="5"/>
       <c r="G230" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H230" s="6"/>
       <c r="J230" s="14" t="s">
@@ -17199,7 +17207,7 @@
       </c>
       <c r="E231" s="5"/>
       <c r="G231" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H231" s="6"/>
       <c r="J231" s="27"/>
@@ -17225,7 +17233,7 @@
       </c>
       <c r="E232" s="5"/>
       <c r="G232" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H232" s="6"/>
       <c r="J232" s="14" t="s">
@@ -17240,23 +17248,23 @@
     </row>
     <row r="233" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="B233" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="C233" t="s">
         <v>482</v>
       </c>
       <c r="D233" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="G233" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="H233" s="6"/>
       <c r="J233" s="15" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="M233">
         <v>12</v>
@@ -17279,7 +17287,7 @@
         <v>739</v>
       </c>
       <c r="G234" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H234" s="6"/>
       <c r="J234" s="14" t="s">
@@ -17309,7 +17317,7 @@
         <v>1697</v>
       </c>
       <c r="G235" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H235" s="6"/>
       <c r="J235" s="14" t="s">
@@ -17339,7 +17347,7 @@
         <v>753</v>
       </c>
       <c r="G236" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H236" s="6"/>
       <c r="J236" s="27" t="s">
@@ -17369,7 +17377,7 @@
         <v>741</v>
       </c>
       <c r="G237" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H237" s="6"/>
       <c r="J237" s="27" t="s">
@@ -17399,7 +17407,7 @@
         <v>744</v>
       </c>
       <c r="G238" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H238" s="6"/>
       <c r="J238" s="27" t="s">
@@ -17429,7 +17437,7 @@
         <v>747</v>
       </c>
       <c r="G239" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H239" s="6"/>
       <c r="J239" s="27" t="s">
@@ -17459,7 +17467,7 @@
         <v>750</v>
       </c>
       <c r="G240" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="H240" s="6"/>
       <c r="J240" s="27" t="s">
@@ -17489,7 +17497,7 @@
         <v>1695</v>
       </c>
       <c r="G241" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H241" s="6"/>
       <c r="J241" s="27" t="s">
@@ -17519,10 +17527,10 @@
         <v>724</v>
       </c>
       <c r="G242" s="26" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="K242" s="26" t="s">
         <v>723</v>
@@ -17548,7 +17556,7 @@
         <v>1696</v>
       </c>
       <c r="G243" s="22" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H243" s="6"/>
       <c r="J243" s="14" t="s">
@@ -17578,11 +17586,11 @@
         <v>735</v>
       </c>
       <c r="G244" s="22" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H244" s="6"/>
       <c r="J244" s="14" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="K244" t="s">
         <v>733</v>
@@ -17608,11 +17616,11 @@
         <v>732</v>
       </c>
       <c r="G245" s="22" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H245" s="6"/>
       <c r="J245" s="14" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="K245" t="s">
         <v>730</v>
@@ -17638,7 +17646,7 @@
         <v>727</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H246" s="6"/>
       <c r="J246" s="14" t="s">
@@ -17668,11 +17676,11 @@
         <v>729</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="H247" s="6"/>
       <c r="J247" s="14" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="K247" t="s">
         <v>728</v>
@@ -17698,11 +17706,11 @@
         <v>923</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H248" s="6"/>
       <c r="J248" s="15" t="s">
-        <v>2420</v>
+        <v>2417</v>
       </c>
       <c r="K248" t="s">
         <v>924</v>
@@ -17728,7 +17736,7 @@
         <v>349</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H249" s="6"/>
       <c r="J249" s="14" t="s">
@@ -17758,7 +17766,7 @@
         <v>1779</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H250" s="6"/>
       <c r="J250" s="15" t="s">
@@ -17785,7 +17793,7 @@
         <v>1781</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H251" s="6"/>
       <c r="J251" s="15" t="s">
@@ -17812,7 +17820,7 @@
         <v>1787</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H252" s="6"/>
       <c r="J252" s="15" t="s">
@@ -17839,7 +17847,7 @@
         <v>1793</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H253" s="6"/>
       <c r="J253" s="15" t="s">
@@ -17863,11 +17871,11 @@
         <v>2064</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H254" s="6"/>
       <c r="J254" s="14" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="M254">
         <v>7</v>
@@ -17887,7 +17895,7 @@
         <v>1889</v>
       </c>
       <c r="G255" s="27" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H255" s="6"/>
       <c r="J255" s="15" t="s">
@@ -17914,7 +17922,7 @@
         <v>1789</v>
       </c>
       <c r="G256" s="27" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H256" s="6"/>
       <c r="J256" s="15" t="s">
@@ -17938,11 +17946,11 @@
         <v>2069</v>
       </c>
       <c r="G257" s="27" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H257" s="6"/>
       <c r="J257" s="14" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="M257">
         <v>10</v>
@@ -17962,11 +17970,11 @@
         <v>2072</v>
       </c>
       <c r="G258" s="27" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="H258" s="6"/>
       <c r="J258" s="14" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="M258">
         <v>11</v>
@@ -17974,23 +17982,23 @@
     </row>
     <row r="259" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="B259" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C259" t="s">
         <v>270</v>
       </c>
       <c r="D259" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="G259" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H259" s="6"/>
       <c r="J259" s="14" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="M259">
         <v>1</v>
@@ -17998,23 +18006,23 @@
     </row>
     <row r="260" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="B260" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C260" t="s">
         <v>270</v>
       </c>
       <c r="D260" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="G260" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H260" s="6"/>
       <c r="J260" s="14" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="M260">
         <v>2</v>
@@ -18037,7 +18045,7 @@
         <v>975</v>
       </c>
       <c r="G261" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H261" s="6"/>
       <c r="J261" s="27"/>
@@ -18065,7 +18073,7 @@
         <v>972</v>
       </c>
       <c r="G262" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H262" s="6"/>
       <c r="J262" s="27"/>
@@ -18093,11 +18101,11 @@
         <v>983</v>
       </c>
       <c r="G263" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H263" s="6"/>
       <c r="J263" s="14" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="K263" t="s">
         <v>984</v>
@@ -18108,23 +18116,23 @@
     </row>
     <row r="264" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
       <c r="B264" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C264" t="s">
         <v>270</v>
       </c>
       <c r="D264" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="G264" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H264" s="6"/>
       <c r="J264" s="14" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
       <c r="M264">
         <v>6</v>
@@ -18147,7 +18155,7 @@
         <v>979</v>
       </c>
       <c r="G265" s="27" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H265" s="6"/>
       <c r="J265" s="27"/>
@@ -18160,23 +18168,23 @@
     </row>
     <row r="266" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="B266" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="C266" t="s">
         <v>270</v>
       </c>
       <c r="D266" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G266" s="20" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H266" s="6"/>
       <c r="J266" s="14" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="M266">
         <v>8</v>
@@ -18184,23 +18192,23 @@
     </row>
     <row r="267" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="B267" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="C267" t="s">
         <v>270</v>
       </c>
       <c r="D267" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H267" s="6"/>
       <c r="J267" s="14" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="M267">
         <v>9</v>
@@ -18208,23 +18216,23 @@
     </row>
     <row r="268" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>2449</v>
+        <v>2446</v>
       </c>
       <c r="B268" t="s">
-        <v>2450</v>
+        <v>2447</v>
       </c>
       <c r="C268" t="s">
         <v>270</v>
       </c>
       <c r="D268" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="G268" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="H268" s="6"/>
       <c r="J268" s="14" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="M268">
         <v>10</v>
@@ -18425,7 +18433,7 @@
         <v>1130</v>
       </c>
       <c r="G275" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H275" s="6"/>
       <c r="J275" s="26"/>
@@ -18438,23 +18446,23 @@
     </row>
     <row r="276" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>2431</v>
+        <v>2428</v>
       </c>
       <c r="B276" t="s">
-        <v>2459</v>
+        <v>2456</v>
       </c>
       <c r="C276" t="s">
         <v>270</v>
       </c>
       <c r="D276" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
       <c r="G276" s="20" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H276" s="6"/>
       <c r="J276" s="14" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
       <c r="M276">
         <v>2</v>
@@ -18477,7 +18485,7 @@
         <v>1138</v>
       </c>
       <c r="G277" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H277" s="6"/>
       <c r="J277" s="15" t="s">
@@ -18492,23 +18500,23 @@
     </row>
     <row r="278" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="B278" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="C278" t="s">
         <v>270</v>
       </c>
       <c r="D278" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="G278" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H278" s="6"/>
       <c r="J278" s="14" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="M278">
         <v>4</v>
@@ -18516,23 +18524,23 @@
     </row>
     <row r="279" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="B279" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="C279" t="s">
         <v>270</v>
       </c>
       <c r="D279" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="G279" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H279" s="6"/>
       <c r="J279" s="14" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="M279">
         <v>5</v>
@@ -18540,23 +18548,23 @@
     </row>
     <row r="280" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="B280" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C280" t="s">
         <v>270</v>
       </c>
       <c r="D280" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="G280" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="14" t="s">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="M280">
         <v>6</v>
@@ -18564,23 +18572,23 @@
     </row>
     <row r="281" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="B281" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C281" t="s">
         <v>270</v>
       </c>
       <c r="D281" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="G281" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H281" s="6"/>
       <c r="J281" s="14" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="M281">
         <v>7</v>
@@ -18588,23 +18596,23 @@
     </row>
     <row r="282" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="B282" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C282" t="s">
         <v>270</v>
       </c>
       <c r="D282" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="G282" s="20" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H282" s="6"/>
       <c r="J282" s="14" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
       <c r="M282">
         <v>8</v>
@@ -18612,23 +18620,23 @@
     </row>
     <row r="283" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="B283" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="C283" t="s">
         <v>270</v>
       </c>
       <c r="D283" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H283" s="6"/>
       <c r="J283" s="14" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
       <c r="M283">
         <v>9</v>
@@ -18636,23 +18644,23 @@
     </row>
     <row r="284" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="B284" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C284" t="s">
         <v>270</v>
       </c>
       <c r="D284" s="20" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H284" s="6"/>
       <c r="J284" s="14" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="M284">
         <v>10</v>
@@ -18660,22 +18668,22 @@
     </row>
     <row r="285" spans="1:13" s="11" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="11" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>270</v>
       </c>
       <c r="D285" s="21" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="G285" s="16" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="J285" s="14" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="M285" s="11">
         <v>11</v>
@@ -18683,23 +18691,23 @@
     </row>
     <row r="286" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="B286" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C286" t="s">
         <v>270</v>
       </c>
       <c r="D286" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="G286" s="16" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H286" s="6"/>
       <c r="J286" s="14" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="M286">
         <v>12</v>
@@ -18707,23 +18715,23 @@
     </row>
     <row r="287" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="B287" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C287" t="s">
         <v>270</v>
       </c>
       <c r="D287" s="23" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="G287" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H287" s="6"/>
       <c r="J287" s="14" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="M287">
         <v>13</v>
@@ -18731,23 +18739,23 @@
     </row>
     <row r="288" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="B288" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C288" t="s">
         <v>270</v>
       </c>
       <c r="D288" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="G288" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H288" s="6"/>
       <c r="J288" s="14" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="M288">
         <v>14</v>
@@ -18770,7 +18778,7 @@
         <v>1134</v>
       </c>
       <c r="G289" s="22" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="H289" s="6"/>
       <c r="K289" t="s">
@@ -18797,7 +18805,7 @@
         <v>882</v>
       </c>
       <c r="G290" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="H290" s="6"/>
       <c r="J290" s="23"/>
@@ -18822,7 +18830,7 @@
         <v>1730</v>
       </c>
       <c r="G291" s="16" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="J291" s="20"/>
       <c r="K291" s="16" t="s">
@@ -18846,7 +18854,7 @@
         <v>877</v>
       </c>
       <c r="G292" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="H292" s="6"/>
       <c r="J292" s="23"/>
@@ -18871,7 +18879,7 @@
         <v>1727</v>
       </c>
       <c r="G293" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="H293" s="6"/>
       <c r="J293" s="23"/>
@@ -18896,7 +18904,7 @@
         <v>337</v>
       </c>
       <c r="G294" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H294" s="6"/>
       <c r="J294" s="26"/>
@@ -18924,7 +18932,7 @@
         <v>342</v>
       </c>
       <c r="G295" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H295" s="6"/>
       <c r="J295" s="14" t="s">
@@ -18951,11 +18959,11 @@
         <v>2077</v>
       </c>
       <c r="G296" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H296" s="6"/>
       <c r="J296" s="14" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="M296">
         <v>3</v>
@@ -18978,7 +18986,7 @@
         <v>340</v>
       </c>
       <c r="G297" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H297" s="6"/>
       <c r="J297" s="14" t="s">
@@ -19005,11 +19013,11 @@
         <v>2078</v>
       </c>
       <c r="G298" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H298" s="6"/>
       <c r="J298" s="14" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="M298">
         <v>5</v>
@@ -19032,11 +19040,11 @@
         <v>1682</v>
       </c>
       <c r="G299" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H299" s="6"/>
       <c r="J299" s="14" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
       <c r="K299" t="s">
         <v>902</v>
@@ -19062,7 +19070,7 @@
         <v>2014</v>
       </c>
       <c r="G300" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H300" s="6"/>
       <c r="J300" s="14" t="s">
@@ -19074,23 +19082,23 @@
     </row>
     <row r="301" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>2442</v>
+        <v>2439</v>
       </c>
       <c r="B301" t="s">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="C301" t="s">
         <v>270</v>
       </c>
       <c r="D301" t="s">
-        <v>2502</v>
+        <v>2499</v>
       </c>
       <c r="G301" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H301" s="6"/>
       <c r="J301" s="14" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="M301">
         <v>3</v>
@@ -19098,23 +19106,23 @@
     </row>
     <row r="302" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>2435</v>
+        <v>2432</v>
       </c>
       <c r="B302" t="s">
-        <v>2460</v>
+        <v>2457</v>
       </c>
       <c r="C302" t="s">
         <v>270</v>
       </c>
       <c r="D302" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="G302" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H302" s="6"/>
       <c r="J302" s="14" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="M302">
         <v>4</v>
@@ -19122,23 +19130,23 @@
     </row>
     <row r="303" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>2444</v>
+        <v>2441</v>
       </c>
       <c r="B303" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="C303" t="s">
         <v>270</v>
       </c>
       <c r="D303" t="s">
-        <v>2503</v>
+        <v>2500</v>
       </c>
       <c r="G303" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H303" s="6"/>
       <c r="J303" s="14" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="M303">
         <v>5</v>
@@ -19161,11 +19169,11 @@
         <v>930</v>
       </c>
       <c r="G304" s="22" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="H304" s="6"/>
       <c r="J304" s="14" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
       <c r="K304" t="s">
         <v>1704</v>
@@ -19191,7 +19199,7 @@
         <v>334</v>
       </c>
       <c r="G305" s="22" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="H305" s="6"/>
       <c r="J305" t="s">
@@ -19218,7 +19226,7 @@
         <v>331</v>
       </c>
       <c r="G306" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="H306" s="6"/>
       <c r="J306" s="19" t="s">
@@ -19245,7 +19253,7 @@
         <v>1126</v>
       </c>
       <c r="G307" s="22" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="H307" s="6"/>
       <c r="J307" s="23"/>
@@ -19270,7 +19278,7 @@
         <v>968</v>
       </c>
       <c r="G308" s="20" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="H308" s="6"/>
       <c r="J308" s="26"/>
@@ -19295,7 +19303,7 @@
         <v>953</v>
       </c>
       <c r="G309" s="20" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="H309" s="6"/>
       <c r="J309" s="24"/>
@@ -19320,7 +19328,7 @@
         <v>964</v>
       </c>
       <c r="G310" s="8" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="K310" t="s">
         <v>965</v>
@@ -19343,7 +19351,7 @@
         <v>956</v>
       </c>
       <c r="G311" s="20" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="J311" s="20"/>
       <c r="K311" t="s">
@@ -19367,7 +19375,7 @@
         <v>960</v>
       </c>
       <c r="G312" s="20" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="J312" s="26"/>
       <c r="K312" t="s">
@@ -19391,10 +19399,10 @@
         <v>597</v>
       </c>
       <c r="G313" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J313" s="14" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="K313" t="s">
         <v>149</v>
@@ -19420,7 +19428,7 @@
         <v>608</v>
       </c>
       <c r="G314" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J314" s="26" t="s">
         <v>609</v>
@@ -19449,7 +19457,7 @@
         <v>612</v>
       </c>
       <c r="G315" s="8" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J315" s="14" t="s">
         <v>1958</v>
@@ -19478,7 +19486,7 @@
         <v>615</v>
       </c>
       <c r="G316" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J316" s="26" t="s">
         <v>616</v>
@@ -19507,7 +19515,7 @@
         <v>599</v>
       </c>
       <c r="G317" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J317" s="14" t="s">
         <v>1959</v>
@@ -19536,7 +19544,7 @@
         <v>606</v>
       </c>
       <c r="G318" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J318" s="14" t="s">
         <v>1955</v>
@@ -19565,7 +19573,7 @@
         <v>602</v>
       </c>
       <c r="G319" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J319" s="26" t="s">
         <v>603</v>
@@ -19594,7 +19602,7 @@
         <v>1709</v>
       </c>
       <c r="G320" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J320" s="14" t="s">
         <v>1957</v>
@@ -19623,7 +19631,7 @@
         <v>624</v>
       </c>
       <c r="G321" s="8" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J321" s="26" t="s">
         <v>625</v>
@@ -19652,7 +19660,7 @@
         <v>621</v>
       </c>
       <c r="G322" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J322" s="14" t="s">
         <v>1956</v>
@@ -19681,7 +19689,7 @@
         <v>618</v>
       </c>
       <c r="G323" s="20" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="J323" s="26" t="s">
         <v>619</v>
@@ -19695,22 +19703,22 @@
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="8" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
       <c r="B324" t="s">
-        <v>2452</v>
+        <v>2449</v>
       </c>
       <c r="C324" s="8" t="s">
         <v>270</v>
       </c>
       <c r="D324" t="s">
-        <v>2481</v>
+        <v>2478</v>
       </c>
       <c r="G324" s="20" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J324" s="14" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.3">
@@ -19730,7 +19738,7 @@
         <v>810</v>
       </c>
       <c r="G325" s="20" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J325" s="23"/>
       <c r="K325" t="s">
@@ -19754,7 +19762,7 @@
         <v>813</v>
       </c>
       <c r="G326" s="20" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J326" s="26"/>
       <c r="K326" t="s">
@@ -19778,7 +19786,7 @@
         <v>808</v>
       </c>
       <c r="G327" s="8" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J327" s="14" t="s">
         <v>1989</v>
@@ -19789,22 +19797,22 @@
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="8" t="s">
-        <v>2433</v>
+        <v>2430</v>
       </c>
       <c r="B328" t="s">
-        <v>2462</v>
+        <v>2459</v>
       </c>
       <c r="C328" s="8" t="s">
         <v>270</v>
       </c>
       <c r="D328" t="s">
-        <v>2488</v>
+        <v>2485</v>
       </c>
       <c r="G328" s="8" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J328" s="14" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="329" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -19824,7 +19832,7 @@
         <v>817</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="J329" s="19"/>
       <c r="K329" s="11" t="s">
@@ -20130,10 +20138,10 @@
         <v>1062</v>
       </c>
       <c r="G340" s="20" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="J340" s="14" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="K340" t="s">
         <v>1063</v>
@@ -20159,10 +20167,10 @@
         <v>1717</v>
       </c>
       <c r="G341" s="20" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="K341" t="s">
         <v>1065</v>
@@ -20188,10 +20196,10 @@
         <v>1039</v>
       </c>
       <c r="G342" s="20" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="K342" t="s">
         <v>1066</v>
@@ -20217,7 +20225,7 @@
         <v>321</v>
       </c>
       <c r="G343" s="20" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J343" s="14" t="s">
         <v>1992</v>
@@ -20234,7 +20242,7 @@
         <v>1481</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>270</v>
@@ -20246,7 +20254,7 @@
         <v>306</v>
       </c>
       <c r="G344" s="20" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J344" s="14" t="s">
         <v>1990</v>
@@ -20275,7 +20283,7 @@
         <v>318</v>
       </c>
       <c r="G345" s="20" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J345" s="19" t="s">
         <v>319</v>
@@ -20292,7 +20300,7 @@
         <v>1482</v>
       </c>
       <c r="B346" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C346" s="17" t="s">
         <v>270</v>
@@ -20304,7 +20312,7 @@
         <v>308</v>
       </c>
       <c r="G346" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J346" s="19" t="s">
         <v>309</v>
@@ -20333,7 +20341,7 @@
         <v>328</v>
       </c>
       <c r="G347" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J347" s="23" t="s">
         <v>329</v>
@@ -20362,7 +20370,7 @@
         <v>325</v>
       </c>
       <c r="G348" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J348" s="26" t="s">
         <v>326</v>
@@ -20391,7 +20399,7 @@
         <v>323</v>
       </c>
       <c r="G349" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J349" s="14" t="s">
         <v>1994</v>
@@ -20408,7 +20416,7 @@
         <v>1480</v>
       </c>
       <c r="B350" t="s">
-        <v>2555</v>
+        <v>2552</v>
       </c>
       <c r="C350" t="s">
         <v>270</v>
@@ -20420,7 +20428,7 @@
         <v>303</v>
       </c>
       <c r="G350" s="17" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J350" s="14" t="s">
         <v>1991</v>
@@ -20449,7 +20457,7 @@
         <v>311</v>
       </c>
       <c r="G351" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J351" s="14" t="s">
         <v>1993</v>
@@ -20478,10 +20486,10 @@
         <v>313</v>
       </c>
       <c r="G352" s="22" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J352" s="14" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
       <c r="K352" s="17" t="s">
         <v>312</v>
@@ -20507,7 +20515,7 @@
         <v>315</v>
       </c>
       <c r="G353" s="17" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="J353" s="26" t="s">
         <v>316</v>
@@ -20882,7 +20890,7 @@
         <v>1719</v>
       </c>
       <c r="G366" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J366" s="14" t="s">
         <v>1962</v>
@@ -20911,7 +20919,7 @@
         <v>1872</v>
       </c>
       <c r="G367" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J367" s="14" t="s">
         <v>2101</v>
@@ -20938,10 +20946,10 @@
         <v>1875</v>
       </c>
       <c r="G368" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J368" s="14" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="M368" s="22">
         <v>3</v>
@@ -20964,7 +20972,7 @@
         <v>1873</v>
       </c>
       <c r="G369" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J369" s="14" t="s">
         <v>2103</v>
@@ -20990,7 +20998,7 @@
         <v>1874</v>
       </c>
       <c r="G370" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J370" s="14" t="s">
         <v>2105</v>
@@ -21013,7 +21021,7 @@
         <v>2088</v>
       </c>
       <c r="G371" s="26" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J371" s="14" t="s">
         <v>2102</v>
@@ -21024,22 +21032,22 @@
     </row>
     <row r="372" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="B372" s="22" t="s">
-        <v>2534</v>
+        <v>2531</v>
       </c>
       <c r="C372" s="22" t="s">
         <v>270</v>
       </c>
       <c r="D372" s="22" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="G372" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
       <c r="M372" s="22">
         <v>6</v>
@@ -21059,7 +21067,7 @@
         <v>2087</v>
       </c>
       <c r="G373" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J373" s="14" t="s">
         <v>2104</v>
@@ -21082,7 +21090,7 @@
         <v>1878</v>
       </c>
       <c r="G374" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="J374" s="14" t="s">
         <v>1996</v>
@@ -21105,7 +21113,7 @@
         <v>1879</v>
       </c>
       <c r="G375" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="J375" s="14" t="s">
         <v>1997</v>
@@ -21128,7 +21136,7 @@
         <v>1886</v>
       </c>
       <c r="G376" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="J376" s="14" t="s">
         <v>2109</v>
@@ -21151,7 +21159,7 @@
         <v>1882</v>
       </c>
       <c r="G377" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="J377" s="14" t="s">
         <v>2106</v>
@@ -21174,7 +21182,7 @@
         <v>1885</v>
       </c>
       <c r="G378" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="J378" s="14" t="s">
         <v>2108</v>
@@ -21197,10 +21205,10 @@
         <v>2046</v>
       </c>
       <c r="G379" s="22" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="J379" s="14" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="380" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -21208,19 +21216,19 @@
         <v>2044</v>
       </c>
       <c r="B380" s="22" t="s">
-        <v>2151</v>
+        <v>2811</v>
       </c>
       <c r="C380" s="22" t="s">
         <v>270</v>
       </c>
       <c r="D380" s="22" t="s">
-        <v>2260</v>
+        <v>2812</v>
       </c>
       <c r="G380" s="22" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="J380" s="14" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="381" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -21234,10 +21242,10 @@
         <v>270</v>
       </c>
       <c r="D381" s="22" t="s">
-        <v>2421</v>
+        <v>2418</v>
       </c>
       <c r="G381" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="J381" s="14" t="s">
         <v>2016</v>
@@ -21260,7 +21268,7 @@
         <v>1880</v>
       </c>
       <c r="G382" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="J382" s="14" t="s">
         <v>1998</v>
@@ -21283,10 +21291,10 @@
         <v>1883</v>
       </c>
       <c r="G383" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21306,7 +21314,7 @@
         <v>1881</v>
       </c>
       <c r="G384" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="J384" s="14" t="s">
         <v>1999</v>
@@ -21329,7 +21337,7 @@
         <v>1884</v>
       </c>
       <c r="G385" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="J385" s="14" t="s">
         <v>2107</v>
@@ -21352,10 +21360,10 @@
         <v>1877</v>
       </c>
       <c r="G386" s="22" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2755</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -21372,7 +21380,7 @@
         <v>1876</v>
       </c>
       <c r="G387" s="22" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="J387" s="14" t="s">
         <v>1995</v>
@@ -21395,7 +21403,7 @@
         <v>668</v>
       </c>
       <c r="G388" s="22" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="J388" s="23" t="s">
         <v>669</v>
@@ -21421,7 +21429,7 @@
         <v>656</v>
       </c>
       <c r="G389" s="22" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="J389" s="23" t="s">
         <v>657</v>
@@ -21447,7 +21455,7 @@
         <v>664</v>
       </c>
       <c r="G390" s="22" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="J390" s="23" t="s">
         <v>665</v>
@@ -21473,7 +21481,7 @@
         <v>660</v>
       </c>
       <c r="G391" s="22" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="J391" s="26" t="s">
         <v>661</v>
@@ -21845,7 +21853,7 @@
         <v>1017</v>
       </c>
       <c r="G404" s="22" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="J404" s="14" t="s">
         <v>1979</v>
@@ -21874,7 +21882,7 @@
         <v>1022</v>
       </c>
       <c r="G405" s="22" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="J405" s="23" t="s">
         <v>1023</v>
@@ -21903,7 +21911,7 @@
         <v>1019</v>
       </c>
       <c r="G406" s="22" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="J406" s="23" t="s">
         <v>1020</v>
@@ -21932,7 +21940,7 @@
         <v>1025</v>
       </c>
       <c r="G407" s="22" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="J407" s="23" t="s">
         <v>1026</v>
@@ -21961,7 +21969,7 @@
         <v>437</v>
       </c>
       <c r="G408" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="J408" s="26" t="s">
         <v>438</v>
@@ -21990,7 +21998,7 @@
         <v>435</v>
       </c>
       <c r="G409" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="J409" s="15" t="s">
         <v>1981</v>
@@ -22019,7 +22027,7 @@
         <v>1703</v>
       </c>
       <c r="G410" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="J410" s="14" t="s">
         <v>1980</v>
@@ -22048,7 +22056,7 @@
         <v>430</v>
       </c>
       <c r="G411" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="J411" s="26" t="s">
         <v>431</v>
@@ -22077,7 +22085,7 @@
         <v>433</v>
       </c>
       <c r="G412" s="22" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="J412" s="15" t="s">
         <v>1982</v>
@@ -22106,7 +22114,7 @@
         <v>423</v>
       </c>
       <c r="G413" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J413" s="23" t="s">
         <v>424</v>
@@ -22135,7 +22143,7 @@
         <v>413</v>
       </c>
       <c r="G414" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J414" s="23" t="s">
         <v>414</v>
@@ -22164,7 +22172,7 @@
         <v>418</v>
       </c>
       <c r="G415" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J415" s="23"/>
       <c r="K415" s="22" t="s">
@@ -22191,7 +22199,7 @@
         <v>416</v>
       </c>
       <c r="G416" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J416" s="26" t="s">
         <v>417</v>
@@ -22220,7 +22228,7 @@
         <v>421</v>
       </c>
       <c r="G417" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J417" s="15" t="s">
         <v>1983</v>
@@ -22249,7 +22257,7 @@
         <v>426</v>
       </c>
       <c r="G418" s="22" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="J418" s="23" t="s">
         <v>427</v>
@@ -22278,7 +22286,7 @@
         <v>888</v>
       </c>
       <c r="G419" s="22" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="J419" s="26" t="s">
         <v>889</v>
@@ -22307,7 +22315,7 @@
         <v>1893</v>
       </c>
       <c r="G420" s="22" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="J420" s="15" t="s">
         <v>1985</v>
@@ -22336,7 +22344,7 @@
         <v>897</v>
       </c>
       <c r="G421" s="23" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="J421" s="14" t="s">
         <v>1984</v>
@@ -22365,10 +22373,10 @@
         <v>914</v>
       </c>
       <c r="G422" s="26" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="K422" s="26" t="s">
         <v>915</v>
@@ -22394,7 +22402,7 @@
         <v>893</v>
       </c>
       <c r="G423" s="23" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="J423" s="23" t="s">
         <v>894</v>
@@ -22423,7 +22431,7 @@
         <v>458</v>
       </c>
       <c r="G424" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="K424" s="23" t="s">
         <v>459</v>
@@ -22449,7 +22457,7 @@
         <v>461</v>
       </c>
       <c r="G425" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J425" s="23" t="s">
         <v>462</v>
@@ -22478,7 +22486,7 @@
         <v>465</v>
       </c>
       <c r="G426" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J426" s="23" t="s">
         <v>466</v>
@@ -22507,7 +22515,7 @@
         <v>468</v>
       </c>
       <c r="G427" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J427" s="23" t="s">
         <v>469</v>
@@ -22536,7 +22544,7 @@
         <v>472</v>
       </c>
       <c r="G428" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J428" s="14" t="s">
         <v>1986</v>
@@ -22550,22 +22558,22 @@
     </row>
     <row r="429" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="23" t="s">
-        <v>2446</v>
+        <v>2443</v>
       </c>
       <c r="B429" s="23" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
       <c r="C429" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D429" s="23" t="s">
-        <v>2504</v>
+        <v>2501</v>
       </c>
       <c r="G429" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J429" s="14" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="M429" s="23">
         <v>6</v>
@@ -22573,22 +22581,22 @@
     </row>
     <row r="430" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="23" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="B430" s="23" t="s">
-        <v>2474</v>
+        <v>2471</v>
       </c>
       <c r="C430" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D430" s="23" t="s">
-        <v>2495</v>
+        <v>2492</v>
       </c>
       <c r="G430" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J430" s="14" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="M430" s="23">
         <v>7</v>
@@ -22611,7 +22619,7 @@
         <v>484</v>
       </c>
       <c r="G431" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J431" s="14" t="s">
         <v>1988</v>
@@ -22640,7 +22648,7 @@
         <v>489</v>
       </c>
       <c r="G432" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J432" s="23" t="s">
         <v>490</v>
@@ -22669,7 +22677,7 @@
         <v>1705</v>
       </c>
       <c r="G433" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J433" s="23" t="s">
         <v>487</v>
@@ -22698,7 +22706,7 @@
         <v>492</v>
       </c>
       <c r="G434" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J434" s="14" t="s">
         <v>1894</v>
@@ -22727,7 +22735,7 @@
         <v>474</v>
       </c>
       <c r="G435" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J435" s="14" t="s">
         <v>1987</v>
@@ -22756,10 +22764,10 @@
         <v>476</v>
       </c>
       <c r="G436" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J436" s="14" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
       <c r="K436" s="23" t="s">
         <v>477</v>
@@ -22785,7 +22793,7 @@
         <v>479</v>
       </c>
       <c r="G437" s="23" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="J437" s="23" t="s">
         <v>480</v>
@@ -22799,133 +22807,133 @@
     </row>
     <row r="438" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="23" t="s">
-        <v>2437</v>
+        <v>2434</v>
       </c>
       <c r="B438" s="23" t="s">
-        <v>2465</v>
+        <v>2462</v>
       </c>
       <c r="C438" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D438" s="23" t="s">
-        <v>2498</v>
+        <v>2495</v>
       </c>
       <c r="G438" s="23" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="23" t="s">
-        <v>2438</v>
+        <v>2435</v>
       </c>
       <c r="B439" s="23" t="s">
-        <v>2466</v>
+        <v>2463</v>
       </c>
       <c r="C439" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D439" s="23" t="s">
-        <v>2491</v>
+        <v>2488</v>
       </c>
       <c r="G439" s="23" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="J439" s="14" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="440" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="23" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="B440" s="23" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C440" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D440" s="23" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="J440" s="14"/>
     </row>
     <row r="441" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="23" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="B441" s="23" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C441" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D441" s="23" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="J441" s="14"/>
     </row>
     <row r="442" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="23" t="s">
-        <v>2430</v>
+        <v>2427</v>
       </c>
       <c r="B442" s="23" t="s">
-        <v>2456</v>
+        <v>2453</v>
       </c>
       <c r="C442" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D442" s="23" t="s">
-        <v>2484</v>
+        <v>2481</v>
       </c>
       <c r="J442" s="14" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="443" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="23" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="B443" s="23" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C443" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D443" s="23" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="J443" s="14"/>
     </row>
     <row r="444" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="23" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="B444" s="23" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C444" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D444" s="23" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="J444" s="14"/>
     </row>
     <row r="445" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="23" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="B445" s="23" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="C445" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D445" s="23" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="H445" s="23" t="s">
         <v>1828</v>
@@ -22934,1042 +22942,1042 @@
     </row>
     <row r="446" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="23" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="B446" s="23" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C446" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D446" s="23" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="H446" s="23" t="s">
         <v>1828</v>
       </c>
       <c r="J446" s="14" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="447" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="23" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="B447" s="23" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C447" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D447" s="23" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="J447" s="14"/>
     </row>
     <row r="448" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="23" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="B448" s="23" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="C448" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D448" s="23" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="J448" s="14"/>
     </row>
     <row r="449" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="23" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
       <c r="B449" s="23" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="C449" s="23" t="s">
         <v>270</v>
       </c>
       <c r="D449" s="23" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="J449" s="14"/>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B450" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C450" t="s">
+        <v>270</v>
+      </c>
+      <c r="D450" t="s">
+        <v>2589</v>
+      </c>
+      <c r="G450" t="s">
+        <v>2592</v>
+      </c>
+      <c r="J450" s="14" t="s">
         <v>2590</v>
-      </c>
-      <c r="B450" t="s">
-        <v>2591</v>
-      </c>
-      <c r="C450" t="s">
-        <v>270</v>
-      </c>
-      <c r="D450" t="s">
-        <v>2592</v>
-      </c>
-      <c r="G450" t="s">
-        <v>2595</v>
-      </c>
-      <c r="J450" s="14" t="s">
-        <v>2593</v>
       </c>
     </row>
     <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="B451" s="29" t="s">
-        <v>2750</v>
+        <v>2747</v>
       </c>
       <c r="C451" s="29" t="s">
         <v>270</v>
       </c>
       <c r="D451" s="29" t="s">
-        <v>2751</v>
+        <v>2748</v>
       </c>
       <c r="G451" s="29" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>2752</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="B452" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="C452" t="s">
         <v>1104</v>
       </c>
       <c r="D452" t="s">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F452" t="s">
-        <v>2712</v>
+        <v>2709</v>
       </c>
       <c r="G452" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>2758</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="B453" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="C453" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D453" t="s">
-        <v>2675</v>
+        <v>2672</v>
       </c>
       <c r="F453" t="s">
-        <v>2713</v>
+        <v>2710</v>
       </c>
       <c r="G453" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>2802</v>
+        <v>2799</v>
       </c>
       <c r="K453" t="s">
-        <v>2759</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="B454" t="s">
-        <v>2801</v>
+        <v>2798</v>
       </c>
       <c r="C454" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D454" t="s">
-        <v>2676</v>
+        <v>2673</v>
       </c>
       <c r="F454" t="s">
-        <v>2714</v>
+        <v>2711</v>
       </c>
       <c r="G454" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>2803</v>
+        <v>2800</v>
       </c>
       <c r="K454" t="s">
-        <v>2762</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="B455" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="C455" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D455" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="F455" t="s">
-        <v>2715</v>
+        <v>2712</v>
       </c>
       <c r="G455" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>2804</v>
+        <v>2801</v>
       </c>
       <c r="K455" t="s">
-        <v>2760</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="B456" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="C456" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D456" t="s">
-        <v>2678</v>
+        <v>2675</v>
       </c>
       <c r="G456" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="K456" t="s">
-        <v>2761</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="B457" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="C457" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D457" t="s">
-        <v>2679</v>
+        <v>2676</v>
       </c>
       <c r="F457" t="s">
-        <v>2716</v>
+        <v>2713</v>
       </c>
       <c r="G457" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>2806</v>
+        <v>2803</v>
       </c>
       <c r="K457" t="s">
-        <v>2763</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="B458" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="C458" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D458" t="s">
-        <v>2680</v>
+        <v>2677</v>
       </c>
       <c r="F458" t="s">
-        <v>2717</v>
+        <v>2714</v>
       </c>
       <c r="G458" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>2807</v>
+        <v>2804</v>
       </c>
       <c r="K458" t="s">
-        <v>2764</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="B459" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="C459" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D459" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="F459" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="G459" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>2808</v>
+        <v>2805</v>
       </c>
       <c r="K459" t="s">
-        <v>2765</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="B460" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="C460" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D460" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="F460" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
       <c r="G460" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>2809</v>
+        <v>2806</v>
       </c>
       <c r="K460" t="s">
-        <v>2766</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="B461" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="C461" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D461" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="F461" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="G461" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K461" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="B462" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="C462" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D462" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="F462" t="s">
-        <v>2721</v>
+        <v>2718</v>
       </c>
       <c r="G462" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K462" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>2620</v>
+        <v>2617</v>
       </c>
       <c r="B463" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="C463" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D463" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="F463" t="s">
-        <v>2722</v>
+        <v>2719</v>
       </c>
       <c r="G463" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K463" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="B464" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="C464" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D464" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="F464" t="s">
-        <v>2723</v>
+        <v>2720</v>
       </c>
       <c r="G464" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K464" t="s">
-        <v>2770</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="B465" t="s">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="C465" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D465" t="s">
-        <v>2687</v>
+        <v>2684</v>
       </c>
       <c r="F465" t="s">
-        <v>2724</v>
+        <v>2721</v>
       </c>
       <c r="G465" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K465" t="s">
-        <v>2771</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>2626</v>
+        <v>2623</v>
       </c>
       <c r="B466" t="s">
-        <v>2627</v>
+        <v>2624</v>
       </c>
       <c r="C466" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D466" t="s">
-        <v>2688</v>
+        <v>2685</v>
       </c>
       <c r="F466" t="s">
-        <v>2725</v>
+        <v>2722</v>
       </c>
       <c r="G466" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K466" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>2628</v>
+        <v>2625</v>
       </c>
       <c r="B467" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="C467" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D467" t="s">
-        <v>2689</v>
+        <v>2686</v>
       </c>
       <c r="F467" t="s">
-        <v>2726</v>
+        <v>2723</v>
       </c>
       <c r="G467" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K467" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>2630</v>
+        <v>2627</v>
       </c>
       <c r="B468" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="C468" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D468" t="s">
-        <v>2690</v>
+        <v>2687</v>
       </c>
       <c r="F468" t="s">
-        <v>2727</v>
+        <v>2724</v>
       </c>
       <c r="G468" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K468" t="s">
-        <v>2773</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="B469" t="s">
-        <v>2633</v>
+        <v>2630</v>
       </c>
       <c r="C469" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D469" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="F469" t="s">
-        <v>2728</v>
+        <v>2725</v>
       </c>
       <c r="G469" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K469" t="s">
-        <v>2774</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="B470" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="C470" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D470" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="F470" t="s">
-        <v>2729</v>
+        <v>2726</v>
       </c>
       <c r="G470" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K470" t="s">
-        <v>2775</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="B471" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="C471" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D471" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="F471" t="s">
-        <v>2730</v>
+        <v>2727</v>
       </c>
       <c r="G471" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K471" t="s">
-        <v>2776</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="B472" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="C472" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D472" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="F472" t="s">
-        <v>2731</v>
+        <v>2728</v>
       </c>
       <c r="G472" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K472" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>2640</v>
+        <v>2637</v>
       </c>
       <c r="B473" t="s">
-        <v>2641</v>
+        <v>2638</v>
       </c>
       <c r="C473" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D473" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="F473" t="s">
-        <v>2732</v>
+        <v>2729</v>
       </c>
       <c r="G473" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K473" t="s">
-        <v>2778</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>2642</v>
+        <v>2639</v>
       </c>
       <c r="B474" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C474" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D474" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
       <c r="F474" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
       <c r="G474" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K474" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="B475" t="s">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="C475" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D475" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="F475" t="s">
-        <v>2734</v>
+        <v>2731</v>
       </c>
       <c r="G475" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K475" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="B476" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="C476" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D476" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="F476" t="s">
-        <v>2735</v>
+        <v>2732</v>
       </c>
       <c r="G476" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K476" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="B477" t="s">
-        <v>2649</v>
+        <v>2646</v>
       </c>
       <c r="C477" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D477" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="F477" t="s">
-        <v>2736</v>
+        <v>2733</v>
       </c>
       <c r="G477" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K477" t="s">
-        <v>2782</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>2650</v>
+        <v>2647</v>
       </c>
       <c r="B478" t="s">
-        <v>2651</v>
+        <v>2648</v>
       </c>
       <c r="C478" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D478" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="F478" t="s">
-        <v>2737</v>
+        <v>2734</v>
       </c>
       <c r="G478" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K478" t="s">
-        <v>2783</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>2652</v>
+        <v>2649</v>
       </c>
       <c r="B479" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="C479" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D479" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="F479" t="s">
-        <v>2738</v>
+        <v>2735</v>
       </c>
       <c r="G479" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K479" t="s">
-        <v>2784</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>2654</v>
+        <v>2651</v>
       </c>
       <c r="B480" t="s">
-        <v>2655</v>
+        <v>2652</v>
       </c>
       <c r="C480" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D480" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="F480" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="G480" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K480" t="s">
-        <v>2785</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>2656</v>
+        <v>2653</v>
       </c>
       <c r="B481" t="s">
-        <v>2657</v>
+        <v>2654</v>
       </c>
       <c r="C481" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D481" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="F481" t="s">
-        <v>2740</v>
+        <v>2737</v>
       </c>
       <c r="G481" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K481" t="s">
-        <v>2786</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>2658</v>
+        <v>2655</v>
       </c>
       <c r="B482" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="C482" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D482" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="F482" t="s">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="G482" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K482" t="s">
-        <v>2787</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="B483" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
       <c r="C483" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D483" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="F483" t="s">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="G483" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K483" t="s">
-        <v>2788</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>2662</v>
+        <v>2659</v>
       </c>
       <c r="B484" t="s">
-        <v>2663</v>
+        <v>2660</v>
       </c>
       <c r="C484" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D484" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="F484" t="s">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="G484" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K484" t="s">
-        <v>2790</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>2664</v>
+        <v>2661</v>
       </c>
       <c r="B485" t="s">
-        <v>2665</v>
+        <v>2662</v>
       </c>
       <c r="C485" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D485" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="F485" t="s">
-        <v>2744</v>
+        <v>2741</v>
       </c>
       <c r="G485" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K485" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="B486" t="s">
-        <v>2667</v>
+        <v>2664</v>
       </c>
       <c r="C486" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D486" t="s">
-        <v>2708</v>
+        <v>2705</v>
       </c>
       <c r="F486" t="s">
-        <v>2745</v>
+        <v>2742</v>
       </c>
       <c r="G486" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K486" t="s">
-        <v>2791</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="B487" t="s">
-        <v>2669</v>
+        <v>2666</v>
       </c>
       <c r="C487" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D487" t="s">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="F487" t="s">
-        <v>2746</v>
+        <v>2743</v>
       </c>
       <c r="G487" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K487" t="s">
-        <v>2792</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>2670</v>
+        <v>2667</v>
       </c>
       <c r="B488" t="s">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="C488" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D488" t="s">
-        <v>2710</v>
+        <v>2707</v>
       </c>
       <c r="F488" t="s">
-        <v>2747</v>
+        <v>2744</v>
       </c>
       <c r="G488" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K488" t="s">
-        <v>2793</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>2672</v>
+        <v>2669</v>
       </c>
       <c r="B489" t="s">
-        <v>2673</v>
+        <v>2670</v>
       </c>
       <c r="C489" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D489" t="s">
-        <v>2711</v>
+        <v>2708</v>
       </c>
       <c r="F489" t="s">
-        <v>2748</v>
+        <v>2745</v>
       </c>
       <c r="G489" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K489" t="s">
-        <v>2794</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>2795</v>
+        <v>2792</v>
       </c>
       <c r="B490" t="s">
-        <v>2796</v>
+        <v>2793</v>
       </c>
       <c r="C490" t="s">
         <v>1104</v>
       </c>
       <c r="D490" t="s">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="G490" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="J490" s="14" t="s">
-        <v>2810</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="491" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="30" t="s">
-        <v>2798</v>
+        <v>2795</v>
       </c>
       <c r="B491" s="30" t="s">
-        <v>2799</v>
+        <v>2796</v>
       </c>
       <c r="C491" s="30" t="s">
         <v>270</v>
       </c>
       <c r="D491" s="30" t="s">
-        <v>2800</v>
+        <v>2797</v>
       </c>
       <c r="G491" s="30" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="J491" s="14" t="s">
-        <v>2811</v>
+        <v>2808</v>
       </c>
     </row>
   </sheetData>
@@ -24118,8 +24126,8 @@
     <hyperlink ref="J376" r:id="rId131" display="https://github.com/olaf-programmeur/images/blob/main/olivier.jpg" xr:uid="{7A079B6C-CAEF-487A-9835-CDD17CE4E3FF}"/>
     <hyperlink ref="J137" r:id="rId132" display="https://github.com/olaf-programmeur/images/blob/main/kpt_ass.png" xr:uid="{739DD512-7187-4ABE-80D2-AB3A75A97B9A}"/>
     <hyperlink ref="J140" r:id="rId133" display="https://github.com/olaf-programmeur/images/blob/main/mobiliere_ass.png" xr:uid="{FA90ED60-5F49-40C3-8120-9748EC5C0DF6}"/>
-    <hyperlink ref="J141" r:id="rId134" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{51402ACF-C4AF-4E8E-83F6-C10D822E38CB}"/>
-    <hyperlink ref="J142" r:id="rId135" display="https://github.com/olaf-programmeur/images/blob/main/helvetia_ass.jpg" xr:uid="{D398F53D-8CD1-4BCF-B123-DE35DBD79DDC}"/>
+    <hyperlink ref="J141" r:id="rId134" xr:uid="{51402ACF-C4AF-4E8E-83F6-C10D822E38CB}"/>
+    <hyperlink ref="J142" r:id="rId135" xr:uid="{D398F53D-8CD1-4BCF-B123-DE35DBD79DDC}"/>
     <hyperlink ref="J138" r:id="rId136" display="https://github.com/olaf-programmeur/images/blob/main/migros.jpg" xr:uid="{F0E23162-8F08-4FE4-A006-E6DB539A7708}"/>
     <hyperlink ref="J139" r:id="rId137" display="https://github.com/olaf-programmeur/images/blob/main/raiffeisen.jpg" xr:uid="{714C2B4D-0898-41DB-8A05-E175F7FEBA1B}"/>
     <hyperlink ref="J227" r:id="rId138" display="https://github.com/olaf-programmeur/images/blob/main/abricot.jpg" xr:uid="{C3A11FAC-028D-46A8-9D2E-0E8E473F0783}"/>
@@ -24251,9 +24259,10 @@
     <hyperlink ref="J458" r:id="rId264" xr:uid="{8B43E59E-EC63-49AD-8A59-66C05EE475AA}"/>
     <hyperlink ref="J459" r:id="rId265" xr:uid="{F09EA9A6-8AF9-4BF2-A211-21B8CDAD6B40}"/>
     <hyperlink ref="J460" r:id="rId266" xr:uid="{693C6F31-41B5-4F0F-8E7A-65674D99197C}"/>
+    <hyperlink ref="J124" r:id="rId267" xr:uid="{D3E5E08B-D8D9-44B7-8BBC-F655D845F3A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId267"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId268"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -24565,55 +24574,55 @@
     </row>
     <row r="2" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B2" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B3" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B4" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B5" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B6" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B7" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -24621,10 +24630,10 @@
     </row>
     <row r="9" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B9" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24653,55 +24662,55 @@
     </row>
     <row r="13" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B13" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B14" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B15" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B16" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B17" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B18" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B19" t="s">
         <v>135</v>
@@ -24709,7 +24718,7 @@
     </row>
     <row r="20" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B20" t="s">
         <v>139</v>
@@ -24717,7 +24726,7 @@
     </row>
     <row r="21" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B21" t="s">
         <v>143</v>
@@ -24725,15 +24734,15 @@
     </row>
     <row r="22" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B22" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B23" t="s">
         <v>151</v>
@@ -24741,7 +24750,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B24" t="s">
         <v>155</v>
@@ -24749,82 +24758,82 @@
     </row>
     <row r="25" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B25" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B26" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B32" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B33" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B34" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24832,7 +24841,7 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24840,7 +24849,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24848,63 +24857,63 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B38" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B39" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B40" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B41" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B42" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B43" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24912,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24920,7 +24929,7 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24928,12 +24937,12 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B48" t="s">
         <v>219</v>
@@ -24941,7 +24950,7 @@
     </row>
     <row r="49" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B49" t="s">
         <v>223</v>
@@ -24949,15 +24958,15 @@
     </row>
     <row r="50" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B50" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B51" t="s">
         <v>231</v>
@@ -24965,10 +24974,10 @@
     </row>
     <row r="52" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B52" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24976,7 +24985,7 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24984,7 +24993,7 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -24992,7 +25001,7 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -25000,7 +25009,7 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -25016,7 +25025,7 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\vocab-app-main_version_actuelle\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F337290-4D72-4338-A5D0-1BFCCE814391}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801A38E-C2BA-4F8D-872D-EB38CC23792F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="2815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="2822">
   <si>
     <t>id</t>
   </si>
@@ -7917,12 +7917,6 @@
     <t>haut  ↔  bas</t>
   </si>
   <si>
-    <t>a_heureux</t>
-  </si>
-  <si>
-    <t>heureux  ↔  malheureux</t>
-  </si>
-  <si>
     <t>a_intelligent</t>
   </si>
   <si>
@@ -7977,12 +7971,6 @@
     <t>plein  ↔  vide</t>
   </si>
   <si>
-    <t>a_poli</t>
-  </si>
-  <si>
-    <t>poli  ↔  impoli</t>
-  </si>
-  <si>
     <t>a_premier</t>
   </si>
   <si>
@@ -8094,9 +8082,6 @@
     <t>Le sommet du Haut-de-Cry est haut et le fond de la Lizerne est bas.</t>
   </si>
   <si>
-    <t>On est heureux quand tout va bien et qu'on a de la joie, on est malheureux quand on a beaucoup de peine.</t>
-  </si>
-  <si>
     <t>Quelqu'un d'intelligent comprend vite et trouve des solutions, quelqu'un qui ne réfléchit pas dit des choses bêtes.</t>
   </si>
   <si>
@@ -8124,9 +8109,6 @@
     <t>Un verre rempli d'eau est plein, un verre sans rien dedans est vide.</t>
   </si>
   <si>
-    <t>Dire « bonjour » et « merci », c'est être poli ; couper la parole, c'est être impoli.</t>
-  </si>
-  <si>
     <t>Celui qui finit en tête d'un concours de musique est le premier, celui qui finit tout à la fin est le dernier.</t>
   </si>
   <si>
@@ -8205,9 +8187,6 @@
     <t>🏔️ ↔ 🕳️</t>
   </si>
   <si>
-    <t>😊 ↔ 😭</t>
-  </si>
-  <si>
     <t>🧠 ↔ 🤪</t>
   </si>
   <si>
@@ -8235,9 +8214,6 @@
     <t>🥛 ↔ 🥤</t>
   </si>
   <si>
-    <t>🙇 ↔ 🙄</t>
-  </si>
-  <si>
     <t>🥇 ↔ 🏁</t>
   </si>
   <si>
@@ -8343,9 +8319,6 @@
     <t>high versus low</t>
   </si>
   <si>
-    <t>happy versu unhappy</t>
-  </si>
-  <si>
     <t>clever versus stupid</t>
   </si>
   <si>
@@ -8371,9 +8344,6 @@
   </si>
   <si>
     <t>full versus empty</t>
-  </si>
-  <si>
-    <t>polite versus unpolite</t>
   </si>
   <si>
     <t>first versus last</t>
@@ -8475,6 +8445,57 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bouquetin.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/mur_mou.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/epais_fin.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/facile_difficile.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/fort_faible.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/grand_petit.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/gros_mince.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/haut_bas.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/intelligent_bete.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/jeune_vieux.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/large_etroit.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/long_court.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/lourd_leger.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/neuf_use.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/nouveau_ancien.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/ouvert_ferme.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/plein_vide.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/premier_dernier.jpg</t>
   </si>
 </sst>
 </file>
@@ -10178,7 +10199,7 @@
         <v>1685</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>2810</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10899,7 +10920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M491"/>
+  <dimension ref="A1:M489"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.796875" customWidth="1"/>
@@ -11095,7 +11116,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="14" t="s">
-        <v>2809</v>
+        <v>2799</v>
       </c>
       <c r="K7" t="s">
         <v>2566</v>
@@ -13025,7 +13046,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2754</v>
+        <v>2746</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -14394,7 +14415,7 @@
       </c>
       <c r="H124" s="8"/>
       <c r="J124" s="14" t="s">
-        <v>2814</v>
+        <v>2804</v>
       </c>
       <c r="K124" s="12" t="s">
         <v>860</v>
@@ -14864,7 +14885,7 @@
       </c>
       <c r="H141" s="6"/>
       <c r="J141" s="14" t="s">
-        <v>2813</v>
+        <v>2803</v>
       </c>
       <c r="M141">
         <v>7</v>
@@ -14889,7 +14910,7 @@
       </c>
       <c r="H142" s="6"/>
       <c r="J142" s="14" t="s">
-        <v>2813</v>
+        <v>2803</v>
       </c>
       <c r="M142">
         <v>8</v>
@@ -18564,7 +18585,7 @@
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="14" t="s">
-        <v>2746</v>
+        <v>2738</v>
       </c>
       <c r="M280">
         <v>6</v>
@@ -21216,13 +21237,13 @@
         <v>2044</v>
       </c>
       <c r="B380" s="22" t="s">
-        <v>2811</v>
+        <v>2801</v>
       </c>
       <c r="C380" s="22" t="s">
         <v>270</v>
       </c>
       <c r="D380" s="22" t="s">
-        <v>2812</v>
+        <v>2802</v>
       </c>
       <c r="G380" s="22" t="s">
         <v>2141</v>
@@ -21294,7 +21315,7 @@
         <v>2131</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2753</v>
+        <v>2745</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21363,7 +21384,7 @@
         <v>2129</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2752</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -22822,7 +22843,7 @@
         <v>2505</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2750</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -23027,22 +23048,22 @@
     </row>
     <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
-        <v>2751</v>
+        <v>2743</v>
       </c>
       <c r="B451" s="29" t="s">
-        <v>2747</v>
+        <v>2739</v>
       </c>
       <c r="C451" s="29" t="s">
         <v>270</v>
       </c>
       <c r="D451" s="29" t="s">
-        <v>2748</v>
+        <v>2740</v>
       </c>
       <c r="G451" s="29" t="s">
         <v>2592</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>2749</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
@@ -23056,16 +23077,16 @@
         <v>1104</v>
       </c>
       <c r="D452" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F452" t="s">
-        <v>2709</v>
+        <v>2703</v>
       </c>
       <c r="G452" t="s">
         <v>2594</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>2755</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
@@ -23079,19 +23100,19 @@
         <v>1104</v>
       </c>
       <c r="D453" t="s">
-        <v>2672</v>
+        <v>2668</v>
       </c>
       <c r="F453" t="s">
-        <v>2710</v>
+        <v>2704</v>
       </c>
       <c r="G453" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>2799</v>
+        <v>2789</v>
       </c>
       <c r="K453" t="s">
-        <v>2756</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
@@ -23099,25 +23120,25 @@
         <v>2600</v>
       </c>
       <c r="B454" t="s">
-        <v>2798</v>
+        <v>2788</v>
       </c>
       <c r="C454" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D454" t="s">
-        <v>2673</v>
+        <v>2669</v>
       </c>
       <c r="F454" t="s">
-        <v>2711</v>
+        <v>2705</v>
       </c>
       <c r="G454" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>2800</v>
+        <v>2790</v>
       </c>
       <c r="K454" t="s">
-        <v>2759</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
@@ -23131,19 +23152,19 @@
         <v>1104</v>
       </c>
       <c r="D455" t="s">
-        <v>2674</v>
+        <v>2670</v>
       </c>
       <c r="F455" t="s">
-        <v>2712</v>
+        <v>2706</v>
       </c>
       <c r="G455" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>2801</v>
+        <v>2791</v>
       </c>
       <c r="K455" t="s">
-        <v>2757</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
@@ -23157,16 +23178,16 @@
         <v>1104</v>
       </c>
       <c r="D456" t="s">
-        <v>2675</v>
+        <v>2671</v>
       </c>
       <c r="G456" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="K456" t="s">
-        <v>2758</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
@@ -23180,19 +23201,19 @@
         <v>1104</v>
       </c>
       <c r="D457" t="s">
-        <v>2676</v>
+        <v>2672</v>
       </c>
       <c r="F457" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
       <c r="G457" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>2803</v>
+        <v>2793</v>
       </c>
       <c r="K457" t="s">
-        <v>2760</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
@@ -23206,19 +23227,19 @@
         <v>1104</v>
       </c>
       <c r="D458" t="s">
-        <v>2677</v>
+        <v>2673</v>
       </c>
       <c r="F458" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="G458" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>2804</v>
+        <v>2794</v>
       </c>
       <c r="K458" t="s">
-        <v>2761</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
@@ -23232,19 +23253,19 @@
         <v>1104</v>
       </c>
       <c r="D459" t="s">
-        <v>2678</v>
+        <v>2674</v>
       </c>
       <c r="F459" t="s">
-        <v>2715</v>
+        <v>2709</v>
       </c>
       <c r="G459" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>2805</v>
+        <v>2795</v>
       </c>
       <c r="K459" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
@@ -23258,19 +23279,19 @@
         <v>1104</v>
       </c>
       <c r="D460" t="s">
-        <v>2679</v>
+        <v>2675</v>
       </c>
       <c r="F460" t="s">
-        <v>2716</v>
+        <v>2710</v>
       </c>
       <c r="G460" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>2806</v>
+        <v>2796</v>
       </c>
       <c r="K460" t="s">
-        <v>2763</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
@@ -23284,16 +23305,19 @@
         <v>1104</v>
       </c>
       <c r="D461" t="s">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="F461" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="G461" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J461" s="14" t="s">
+        <v>2805</v>
+      </c>
       <c r="K461" t="s">
-        <v>2764</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
@@ -23307,16 +23331,19 @@
         <v>1104</v>
       </c>
       <c r="D462" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="F462" t="s">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="G462" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J462" s="14" t="s">
+        <v>2806</v>
+      </c>
       <c r="K462" t="s">
-        <v>2765</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
@@ -23330,16 +23357,19 @@
         <v>1104</v>
       </c>
       <c r="D463" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="F463" t="s">
-        <v>2719</v>
+        <v>2713</v>
       </c>
       <c r="G463" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J463" s="14" t="s">
+        <v>2807</v>
+      </c>
       <c r="K463" t="s">
-        <v>2766</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
@@ -23353,16 +23383,19 @@
         <v>1104</v>
       </c>
       <c r="D464" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F464" t="s">
-        <v>2720</v>
+        <v>2714</v>
       </c>
       <c r="G464" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J464" s="14" t="s">
+        <v>2808</v>
+      </c>
       <c r="K464" t="s">
-        <v>2767</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
@@ -23376,16 +23409,17 @@
         <v>1104</v>
       </c>
       <c r="D465" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="F465" t="s">
-        <v>2721</v>
+        <v>2715</v>
       </c>
       <c r="G465" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J465" s="14"/>
       <c r="K465" t="s">
-        <v>2768</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
@@ -23399,16 +23433,19 @@
         <v>1104</v>
       </c>
       <c r="D466" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="F466" t="s">
-        <v>2722</v>
+        <v>2716</v>
       </c>
       <c r="G466" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J466" s="14" t="s">
+        <v>2809</v>
+      </c>
       <c r="K466" t="s">
-        <v>2769</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
@@ -23422,16 +23459,19 @@
         <v>1104</v>
       </c>
       <c r="D467" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="F467" t="s">
-        <v>2723</v>
+        <v>2717</v>
       </c>
       <c r="G467" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J467" s="14" t="s">
+        <v>2810</v>
+      </c>
       <c r="K467" t="s">
-        <v>2765</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
@@ -23445,16 +23485,19 @@
         <v>1104</v>
       </c>
       <c r="D468" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="F468" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="G468" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J468" s="14" t="s">
+        <v>2811</v>
+      </c>
       <c r="K468" t="s">
-        <v>2770</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
@@ -23468,16 +23511,19 @@
         <v>1104</v>
       </c>
       <c r="D469" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="F469" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="G469" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J469" s="14" t="s">
+        <v>2812</v>
+      </c>
       <c r="K469" t="s">
-        <v>2771</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
@@ -23491,16 +23537,19 @@
         <v>1104</v>
       </c>
       <c r="D470" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="F470" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="G470" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J470" s="14" t="s">
+        <v>2813</v>
+      </c>
       <c r="K470" t="s">
-        <v>2772</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
@@ -23514,16 +23563,19 @@
         <v>1104</v>
       </c>
       <c r="D471" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="F471" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="G471" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J471" s="14" t="s">
+        <v>2814</v>
+      </c>
       <c r="K471" t="s">
-        <v>2773</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
@@ -23537,16 +23589,19 @@
         <v>1104</v>
       </c>
       <c r="D472" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="F472" t="s">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="G472" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J472" s="14" t="s">
+        <v>2815</v>
+      </c>
       <c r="K472" t="s">
-        <v>2774</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
@@ -23560,16 +23615,19 @@
         <v>1104</v>
       </c>
       <c r="D473" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="F473" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="G473" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J473" s="14" t="s">
+        <v>2816</v>
+      </c>
       <c r="K473" t="s">
-        <v>2775</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
@@ -23583,16 +23641,19 @@
         <v>1104</v>
       </c>
       <c r="D474" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="F474" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="G474" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J474" s="14" t="s">
+        <v>2817</v>
+      </c>
       <c r="K474" t="s">
-        <v>2776</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
@@ -23606,16 +23667,19 @@
         <v>1104</v>
       </c>
       <c r="D475" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="F475" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="G475" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J475" s="14" t="s">
+        <v>2818</v>
+      </c>
       <c r="K475" t="s">
-        <v>2777</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
@@ -23629,16 +23693,19 @@
         <v>1104</v>
       </c>
       <c r="D476" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="F476" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
       <c r="G476" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J476" s="14" t="s">
+        <v>2819</v>
+      </c>
       <c r="K476" t="s">
-        <v>2778</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
@@ -23652,16 +23719,19 @@
         <v>1104</v>
       </c>
       <c r="D477" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="F477" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
       <c r="G477" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J477" s="14" t="s">
+        <v>2820</v>
+      </c>
       <c r="K477" t="s">
-        <v>2779</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
@@ -23675,16 +23745,19 @@
         <v>1104</v>
       </c>
       <c r="D478" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="F478" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
       <c r="G478" s="29" t="s">
         <v>2594</v>
       </c>
+      <c r="J478" s="14" t="s">
+        <v>2821</v>
+      </c>
       <c r="K478" t="s">
-        <v>2780</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
@@ -23698,16 +23771,16 @@
         <v>1104</v>
       </c>
       <c r="D479" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="F479" t="s">
-        <v>2735</v>
+        <v>2729</v>
       </c>
       <c r="G479" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K479" t="s">
-        <v>2781</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
@@ -23721,16 +23794,16 @@
         <v>1104</v>
       </c>
       <c r="D480" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="F480" t="s">
-        <v>2736</v>
+        <v>2730</v>
       </c>
       <c r="G480" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K480" t="s">
-        <v>2782</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
@@ -23744,16 +23817,16 @@
         <v>1104</v>
       </c>
       <c r="D481" t="s">
-        <v>2700</v>
+        <v>2696</v>
       </c>
       <c r="F481" t="s">
-        <v>2737</v>
+        <v>2731</v>
       </c>
       <c r="G481" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K481" t="s">
-        <v>2783</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
@@ -23767,16 +23840,16 @@
         <v>1104</v>
       </c>
       <c r="D482" t="s">
-        <v>2701</v>
+        <v>2697</v>
       </c>
       <c r="F482" t="s">
-        <v>2738</v>
+        <v>2732</v>
       </c>
       <c r="G482" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K482" t="s">
-        <v>2784</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
@@ -23790,16 +23863,16 @@
         <v>1104</v>
       </c>
       <c r="D483" t="s">
-        <v>2702</v>
+        <v>2698</v>
       </c>
       <c r="F483" t="s">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="G483" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K483" t="s">
-        <v>2785</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
@@ -23813,16 +23886,16 @@
         <v>1104</v>
       </c>
       <c r="D484" t="s">
-        <v>2703</v>
+        <v>2699</v>
       </c>
       <c r="F484" t="s">
-        <v>2740</v>
+        <v>2734</v>
       </c>
       <c r="G484" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K484" t="s">
-        <v>2787</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
@@ -23836,16 +23909,16 @@
         <v>1104</v>
       </c>
       <c r="D485" t="s">
-        <v>2704</v>
+        <v>2700</v>
       </c>
       <c r="F485" t="s">
-        <v>2741</v>
+        <v>2735</v>
       </c>
       <c r="G485" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K485" t="s">
-        <v>2786</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
@@ -23859,16 +23932,16 @@
         <v>1104</v>
       </c>
       <c r="D486" t="s">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="F486" t="s">
-        <v>2742</v>
+        <v>2736</v>
       </c>
       <c r="G486" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K486" t="s">
-        <v>2788</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
@@ -23882,102 +23955,56 @@
         <v>1104</v>
       </c>
       <c r="D487" t="s">
-        <v>2706</v>
+        <v>2702</v>
       </c>
       <c r="F487" t="s">
-        <v>2743</v>
+        <v>2737</v>
       </c>
       <c r="G487" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K487" t="s">
-        <v>2789</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>2667</v>
+        <v>2782</v>
       </c>
       <c r="B488" t="s">
-        <v>2668</v>
-      </c>
-      <c r="C488" s="29" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C488" t="s">
         <v>1104</v>
       </c>
       <c r="D488" t="s">
-        <v>2707</v>
-      </c>
-      <c r="F488" t="s">
-        <v>2744</v>
-      </c>
-      <c r="G488" s="29" t="s">
-        <v>2594</v>
-      </c>
-      <c r="K488" t="s">
-        <v>2790</v>
-      </c>
-    </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A489" t="s">
-        <v>2669</v>
-      </c>
-      <c r="B489" t="s">
-        <v>2670</v>
-      </c>
-      <c r="C489" s="29" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D489" t="s">
-        <v>2708</v>
-      </c>
-      <c r="F489" t="s">
-        <v>2745</v>
-      </c>
-      <c r="G489" s="29" t="s">
-        <v>2594</v>
-      </c>
-      <c r="K489" t="s">
-        <v>2791</v>
-      </c>
-    </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A490" t="s">
-        <v>2792</v>
-      </c>
-      <c r="B490" t="s">
-        <v>2793</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D490" t="s">
-        <v>2794</v>
-      </c>
-      <c r="G490" t="s">
+        <v>2784</v>
+      </c>
+      <c r="G488" t="s">
         <v>2135</v>
       </c>
-      <c r="J490" s="14" t="s">
-        <v>2807</v>
-      </c>
-    </row>
-    <row r="491" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="30" t="s">
-        <v>2795</v>
-      </c>
-      <c r="B491" s="30" t="s">
-        <v>2796</v>
-      </c>
-      <c r="C491" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="D491" s="30" t="s">
+      <c r="J488" s="14" t="s">
         <v>2797</v>
       </c>
-      <c r="G491" s="30" t="s">
+    </row>
+    <row r="489" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="30" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B489" s="30" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C489" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D489" s="30" t="s">
+        <v>2787</v>
+      </c>
+      <c r="G489" s="30" t="s">
         <v>2592</v>
       </c>
-      <c r="J491" s="14" t="s">
-        <v>2808</v>
+      <c r="J489" s="14" t="s">
+        <v>2798</v>
       </c>
     </row>
   </sheetData>
@@ -23988,7 +24015,7 @@
     <sortCondition ref="B2:B449"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G501:G508" xr:uid="{1E404653-0967-4485-8802-BC02506443F4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G499:G506" xr:uid="{1E404653-0967-4485-8802-BC02506443F4}">
       <formula1>$C$2:$C$102</formula1>
     </dataValidation>
   </dataValidations>
@@ -24248,8 +24275,8 @@
     <hyperlink ref="J451" r:id="rId253" xr:uid="{C7230777-0726-4B03-8D76-346F4625573C}"/>
     <hyperlink ref="J383" r:id="rId254" xr:uid="{4A54E760-26AA-4DC3-8FDD-553BE7D8DB56}"/>
     <hyperlink ref="J452" r:id="rId255" xr:uid="{AA438D1E-A7F6-4E55-8283-4089FEA815A9}"/>
-    <hyperlink ref="J490" r:id="rId256" xr:uid="{CC823740-B01C-42E3-9FE2-E6B1B76A2CA4}"/>
-    <hyperlink ref="J491" r:id="rId257" xr:uid="{E16AE97D-4D84-4557-A9E9-BABF7F3A006D}"/>
+    <hyperlink ref="J488" r:id="rId256" xr:uid="{CC823740-B01C-42E3-9FE2-E6B1B76A2CA4}"/>
+    <hyperlink ref="J489" r:id="rId257" xr:uid="{E16AE97D-4D84-4557-A9E9-BABF7F3A006D}"/>
     <hyperlink ref="J7" r:id="rId258" xr:uid="{BE71E1AF-D392-467D-8303-4A4FD350AE33}"/>
     <hyperlink ref="J453" r:id="rId259" xr:uid="{EBC008FF-B4A0-46F9-9796-05B4166A9C2C}"/>
     <hyperlink ref="J454" r:id="rId260" xr:uid="{3D659344-8535-4C0C-96FE-90C1F61D5EEB}"/>
@@ -24260,9 +24287,26 @@
     <hyperlink ref="J459" r:id="rId265" xr:uid="{F09EA9A6-8AF9-4BF2-A211-21B8CDAD6B40}"/>
     <hyperlink ref="J460" r:id="rId266" xr:uid="{693C6F31-41B5-4F0F-8E7A-65674D99197C}"/>
     <hyperlink ref="J124" r:id="rId267" xr:uid="{D3E5E08B-D8D9-44B7-8BBC-F655D845F3A2}"/>
+    <hyperlink ref="J461" r:id="rId268" xr:uid="{5E0D26F0-F406-4867-BE00-F26145A3D9CC}"/>
+    <hyperlink ref="J462" r:id="rId269" xr:uid="{EB4315DA-901E-4CF1-A5AD-2C68D42093B1}"/>
+    <hyperlink ref="J463" r:id="rId270" xr:uid="{AF4B84AF-3B52-4827-8FA2-3F823A423448}"/>
+    <hyperlink ref="J464" r:id="rId271" xr:uid="{FAB39517-7A38-4962-BBAC-3041B9CC127C}"/>
+    <hyperlink ref="J466" r:id="rId272" xr:uid="{9D65662C-BD3E-45D0-A571-6B899E8203B9}"/>
+    <hyperlink ref="J467" r:id="rId273" xr:uid="{405B25A5-64FD-4359-B584-00B9A50BC200}"/>
+    <hyperlink ref="J468" r:id="rId274" xr:uid="{1F6C3C24-FAA8-4063-A009-D7A711F969BE}"/>
+    <hyperlink ref="J469" r:id="rId275" xr:uid="{FDFEAB92-32CD-4943-A479-1C5C541E0CFE}"/>
+    <hyperlink ref="J470" r:id="rId276" xr:uid="{32084E2E-041C-475B-9265-5261D6F7059C}"/>
+    <hyperlink ref="J471" r:id="rId277" xr:uid="{6111DA5C-EBF3-43D6-A26B-19B2DEF29239}"/>
+    <hyperlink ref="J472" r:id="rId278" xr:uid="{91F832E9-176C-42FC-9F47-C0C3687463C6}"/>
+    <hyperlink ref="J473" r:id="rId279" xr:uid="{5D40F858-C000-4F9F-9EE3-77644E956A80}"/>
+    <hyperlink ref="J474" r:id="rId280" xr:uid="{17EE1BD1-E309-4A9B-BFB3-2BBAC1ED4075}"/>
+    <hyperlink ref="J475" r:id="rId281" xr:uid="{A635509C-1EA8-4C33-80E5-22E7559CCF31}"/>
+    <hyperlink ref="J476" r:id="rId282" xr:uid="{93EA1A82-F107-47FD-A5BB-84A46184CA9C}"/>
+    <hyperlink ref="J477" r:id="rId283" xr:uid="{BF9C7DAE-D98D-470E-8501-E0B192F35B31}"/>
+    <hyperlink ref="J478" r:id="rId284" display="https://raw.githubusercontent.com/olaf-programmeur/images/main/plein_vide.jpg" xr:uid="{512C5DBA-6FAF-4332-B584-B4302CA5C0BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId268"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -24276,7 +24320,7 @@
           <x14:formula1>
             <xm:f>'Sous-catégories'!$C$2:$C$100</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G500</xm:sqref>
+          <xm:sqref>G2:G498</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\vocab-app-main_version_actuelle\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801A38E-C2BA-4F8D-872D-EB38CC23792F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDB44B-7369-4206-B6B7-4330AF8A49AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7959,12 +7959,6 @@
     <t>nouveau  ↔  ancien</t>
   </si>
   <si>
-    <t>a_ouvert</t>
-  </si>
-  <si>
-    <t>ouvert  ↔  fermé</t>
-  </si>
-  <si>
     <t>a_plein</t>
   </si>
   <si>
@@ -8447,15 +8441,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/bouquetin.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/mur_mou.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/epais_fin.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/facile_difficile.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/fort_faible.jpg</t>
   </si>
   <si>
@@ -8465,9 +8450,6 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/gros_mince.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/haut_bas.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/intelligent_bete.jpg</t>
   </si>
   <si>
@@ -8477,25 +8459,43 @@
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/large_etroit.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/long_court.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/lourd_leger.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/neuf_use.jpg</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/nouveau_ancien.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/ouvert_ferme.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/plein_vide.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/premier_dernier.jpg</t>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/dur_mou.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/epais_fin.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/facile_difficile.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/haut_bas.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/long_court.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/lourd_leger.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/ouvert_ferme.png</t>
+  </si>
+  <si>
+    <t>fermé  ↔  ouvert</t>
+  </si>
+  <si>
+    <t>a_ferme</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/premier_dernier.png</t>
   </si>
 </sst>
 </file>
@@ -10199,7 +10199,7 @@
         <v>1685</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="14" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="K7" t="s">
         <v>2566</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="H124" s="8"/>
       <c r="J124" s="14" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="K124" s="12" t="s">
         <v>860</v>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="H141" s="6"/>
       <c r="J141" s="14" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
       <c r="M141">
         <v>7</v>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="H142" s="6"/>
       <c r="J142" s="14" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
       <c r="M142">
         <v>8</v>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="14" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="M280">
         <v>6</v>
@@ -21237,13 +21237,13 @@
         <v>2044</v>
       </c>
       <c r="B380" s="22" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="C380" s="22" t="s">
         <v>270</v>
       </c>
       <c r="D380" s="22" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="G380" s="22" t="s">
         <v>2141</v>
@@ -21315,7 +21315,7 @@
         <v>2131</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21384,7 +21384,7 @@
         <v>2129</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -22843,7 +22843,7 @@
         <v>2505</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -23048,22 +23048,22 @@
     </row>
     <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="B451" s="29" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="C451" s="29" t="s">
         <v>270</v>
       </c>
       <c r="D451" s="29" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="G451" s="29" t="s">
         <v>2592</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
@@ -23077,16 +23077,16 @@
         <v>1104</v>
       </c>
       <c r="D452" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F452" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="G452" t="s">
         <v>2594</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
@@ -23100,19 +23100,19 @@
         <v>1104</v>
       </c>
       <c r="D453" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F453" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="G453" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="K453" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
@@ -23120,25 +23120,25 @@
         <v>2600</v>
       </c>
       <c r="B454" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="C454" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D454" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="F454" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="G454" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="K454" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
@@ -23152,19 +23152,19 @@
         <v>1104</v>
       </c>
       <c r="D455" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="F455" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="G455" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="K455" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
@@ -23178,16 +23178,16 @@
         <v>1104</v>
       </c>
       <c r="D456" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="G456" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="K456" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
@@ -23201,19 +23201,19 @@
         <v>1104</v>
       </c>
       <c r="D457" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="F457" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="G457" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="K457" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
@@ -23227,19 +23227,19 @@
         <v>1104</v>
       </c>
       <c r="D458" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="F458" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="G458" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="K458" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
@@ -23253,19 +23253,19 @@
         <v>1104</v>
       </c>
       <c r="D459" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="F459" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="G459" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
       <c r="K459" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
@@ -23279,19 +23279,19 @@
         <v>1104</v>
       </c>
       <c r="D460" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="F460" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="G460" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="K460" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
@@ -23305,19 +23305,19 @@
         <v>1104</v>
       </c>
       <c r="D461" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="F461" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="G461" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J461" s="14" t="s">
-        <v>2805</v>
+        <v>2812</v>
       </c>
       <c r="K461" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
@@ -23331,19 +23331,19 @@
         <v>1104</v>
       </c>
       <c r="D462" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="F462" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="G462" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>2806</v>
+        <v>2813</v>
       </c>
       <c r="K462" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
@@ -23357,19 +23357,19 @@
         <v>1104</v>
       </c>
       <c r="D463" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="F463" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="G463" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>2807</v>
+        <v>2814</v>
       </c>
       <c r="K463" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
@@ -23383,19 +23383,19 @@
         <v>1104</v>
       </c>
       <c r="D464" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="F464" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="G464" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J464" s="14" t="s">
-        <v>2808</v>
+        <v>2803</v>
       </c>
       <c r="K464" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
@@ -23409,17 +23409,17 @@
         <v>1104</v>
       </c>
       <c r="D465" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="F465" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="G465" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J465" s="14"/>
       <c r="K465" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
@@ -23433,19 +23433,19 @@
         <v>1104</v>
       </c>
       <c r="D466" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="F466" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="G466" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>2809</v>
+        <v>2804</v>
       </c>
       <c r="K466" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
@@ -23459,19 +23459,19 @@
         <v>1104</v>
       </c>
       <c r="D467" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="F467" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="G467" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="K467" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
@@ -23485,19 +23485,19 @@
         <v>1104</v>
       </c>
       <c r="D468" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="F468" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="G468" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>2811</v>
+        <v>2815</v>
       </c>
       <c r="K468" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
@@ -23511,19 +23511,19 @@
         <v>1104</v>
       </c>
       <c r="D469" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="F469" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="G469" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>2812</v>
+        <v>2806</v>
       </c>
       <c r="K469" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
@@ -23537,19 +23537,19 @@
         <v>1104</v>
       </c>
       <c r="D470" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="F470" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="G470" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J470" s="14" t="s">
-        <v>2813</v>
+        <v>2807</v>
       </c>
       <c r="K470" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
@@ -23563,19 +23563,19 @@
         <v>1104</v>
       </c>
       <c r="D471" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="F471" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="G471" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>2814</v>
+        <v>2808</v>
       </c>
       <c r="K471" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
@@ -23589,19 +23589,19 @@
         <v>1104</v>
       </c>
       <c r="D472" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="F472" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="G472" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J472" s="14" t="s">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="K472" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
@@ -23615,19 +23615,19 @@
         <v>1104</v>
       </c>
       <c r="D473" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="F473" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="G473" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J473" s="14" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="K473" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
@@ -23641,19 +23641,19 @@
         <v>1104</v>
       </c>
       <c r="D474" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="F474" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="G474" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J474" s="14" t="s">
-        <v>2817</v>
+        <v>2809</v>
       </c>
       <c r="K474" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
@@ -23667,88 +23667,88 @@
         <v>1104</v>
       </c>
       <c r="D475" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="F475" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="G475" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>2818</v>
+        <v>2810</v>
       </c>
       <c r="K475" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>2643</v>
+        <v>2820</v>
       </c>
       <c r="B476" t="s">
-        <v>2644</v>
+        <v>2819</v>
       </c>
       <c r="C476" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D476" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="F476" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="G476" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="K476" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="B477" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="C477" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D477" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="F477" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="G477" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J477" s="14" t="s">
-        <v>2820</v>
+        <v>2811</v>
       </c>
       <c r="K477" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="B478" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="C478" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D478" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="F478" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="G478" s="29" t="s">
         <v>2594</v>
@@ -23757,254 +23757,254 @@
         <v>2821</v>
       </c>
       <c r="K478" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B479" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C479" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D479" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="F479" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="G479" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K479" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="B480" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C480" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D480" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="F480" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="G480" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K480" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="B481" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="C481" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D481" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="F481" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="G481" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K481" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="B482" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="C482" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D482" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="F482" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="G482" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K482" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="B483" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="C483" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D483" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="F483" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="G483" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K483" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="B484" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C484" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D484" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="F484" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="G484" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K484" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="B485" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C485" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D485" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="F485" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="G485" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K485" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="B486" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C486" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D486" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="F486" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="G486" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K486" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="B487" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="C487" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D487" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="F487" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="G487" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K487" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="B488" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="C488" t="s">
         <v>1104</v>
       </c>
       <c r="D488" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="G488" t="s">
         <v>2135</v>
       </c>
       <c r="J488" s="14" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="489" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="30" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B489" s="30" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C489" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D489" s="30" t="s">
         <v>2785</v>
-      </c>
-      <c r="B489" s="30" t="s">
-        <v>2786</v>
-      </c>
-      <c r="C489" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="D489" s="30" t="s">
-        <v>2787</v>
       </c>
       <c r="G489" s="30" t="s">
         <v>2592</v>
       </c>
       <c r="J489" s="14" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
     </row>
   </sheetData>
@@ -24303,7 +24303,7 @@
     <hyperlink ref="J475" r:id="rId281" xr:uid="{A635509C-1EA8-4C33-80E5-22E7559CCF31}"/>
     <hyperlink ref="J476" r:id="rId282" xr:uid="{93EA1A82-F107-47FD-A5BB-84A46184CA9C}"/>
     <hyperlink ref="J477" r:id="rId283" xr:uid="{BF9C7DAE-D98D-470E-8501-E0B192F35B31}"/>
-    <hyperlink ref="J478" r:id="rId284" display="https://raw.githubusercontent.com/olaf-programmeur/images/main/plein_vide.jpg" xr:uid="{512C5DBA-6FAF-4332-B584-B4302CA5C0BC}"/>
+    <hyperlink ref="J478" r:id="rId284" xr:uid="{512C5DBA-6FAF-4332-B584-B4302CA5C0BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oroh\Documents\Personnel\Programmes\application_herve\app_mots\vocab-app-main_version_actuelle\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDB44B-7369-4206-B6B7-4330AF8A49AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33332220-60F2-4D08-97E4-772F3EF1F3C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8472" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7959,12 +7959,6 @@
     <t>nouveau  ↔  ancien</t>
   </si>
   <si>
-    <t>a_plein</t>
-  </si>
-  <si>
-    <t>plein  ↔  vide</t>
-  </si>
-  <si>
     <t>a_premier</t>
   </si>
   <si>
@@ -8496,6 +8490,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/olaf-programmeur/images/main/premier_dernier.png</t>
+  </si>
+  <si>
+    <t>a_vide</t>
+  </si>
+  <si>
+    <t>vide  ↔  plein</t>
   </si>
 </sst>
 </file>
@@ -10199,7 +10199,7 @@
         <v>1685</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="J7" s="14" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
       <c r="K7" t="s">
         <v>2566</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="H75" s="6"/>
       <c r="J75" s="14" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="M75">
         <v>3</v>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="H124" s="8"/>
       <c r="J124" s="14" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="K124" s="12" t="s">
         <v>860</v>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="H141" s="6"/>
       <c r="J141" s="14" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="M141">
         <v>7</v>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="H142" s="6"/>
       <c r="J142" s="14" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="M142">
         <v>8</v>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="14" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="M280">
         <v>6</v>
@@ -21237,13 +21237,13 @@
         <v>2044</v>
       </c>
       <c r="B380" s="22" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="C380" s="22" t="s">
         <v>270</v>
       </c>
       <c r="D380" s="22" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
       <c r="G380" s="22" t="s">
         <v>2141</v>
@@ -21315,7 +21315,7 @@
         <v>2131</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="M383" s="22">
         <v>3</v>
@@ -21384,7 +21384,7 @@
         <v>2129</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="387" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -22843,7 +22843,7 @@
         <v>2505</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="439" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -23048,22 +23048,22 @@
     </row>
     <row r="451" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B451" s="29" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="C451" s="29" t="s">
         <v>270</v>
       </c>
       <c r="D451" s="29" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="G451" s="29" t="s">
         <v>2592</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
@@ -23077,16 +23077,16 @@
         <v>1104</v>
       </c>
       <c r="D452" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="F452" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="G452" t="s">
         <v>2594</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
@@ -23100,19 +23100,19 @@
         <v>1104</v>
       </c>
       <c r="D453" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="F453" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="G453" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="K453" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
@@ -23120,25 +23120,25 @@
         <v>2600</v>
       </c>
       <c r="B454" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="C454" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D454" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F454" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="G454" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="K454" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
@@ -23152,19 +23152,19 @@
         <v>1104</v>
       </c>
       <c r="D455" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F455" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="G455" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="K455" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
@@ -23178,16 +23178,16 @@
         <v>1104</v>
       </c>
       <c r="D456" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="G456" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="K456" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
@@ -23201,19 +23201,19 @@
         <v>1104</v>
       </c>
       <c r="D457" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="F457" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="G457" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="K457" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
@@ -23227,19 +23227,19 @@
         <v>1104</v>
       </c>
       <c r="D458" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="F458" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="G458" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="K458" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
@@ -23253,19 +23253,19 @@
         <v>1104</v>
       </c>
       <c r="D459" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="F459" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="G459" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="K459" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
@@ -23279,19 +23279,19 @@
         <v>1104</v>
       </c>
       <c r="D460" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="F460" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="G460" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="K460" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
@@ -23305,19 +23305,19 @@
         <v>1104</v>
       </c>
       <c r="D461" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="F461" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="G461" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J461" s="14" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
       <c r="K461" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
@@ -23331,19 +23331,19 @@
         <v>1104</v>
       </c>
       <c r="D462" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="F462" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="G462" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
       <c r="K462" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
@@ -23357,19 +23357,19 @@
         <v>1104</v>
       </c>
       <c r="D463" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="F463" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="G463" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
       <c r="K463" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
@@ -23383,19 +23383,19 @@
         <v>1104</v>
       </c>
       <c r="D464" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="F464" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="G464" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J464" s="14" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
       <c r="K464" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
@@ -23409,17 +23409,17 @@
         <v>1104</v>
       </c>
       <c r="D465" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="F465" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="G465" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J465" s="14"/>
       <c r="K465" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
@@ -23433,19 +23433,19 @@
         <v>1104</v>
       </c>
       <c r="D466" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="F466" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="G466" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="K466" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
@@ -23459,19 +23459,19 @@
         <v>1104</v>
       </c>
       <c r="D467" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="F467" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="G467" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
       <c r="K467" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
@@ -23485,19 +23485,19 @@
         <v>1104</v>
       </c>
       <c r="D468" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="F468" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="G468" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
       <c r="K468" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
@@ -23511,19 +23511,19 @@
         <v>1104</v>
       </c>
       <c r="D469" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="F469" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="G469" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
       <c r="K469" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
@@ -23537,19 +23537,19 @@
         <v>1104</v>
       </c>
       <c r="D470" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="F470" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="G470" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J470" s="14" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
       <c r="K470" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
@@ -23563,19 +23563,19 @@
         <v>1104</v>
       </c>
       <c r="D471" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="F471" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="G471" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
       <c r="K471" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
@@ -23589,19 +23589,19 @@
         <v>1104</v>
       </c>
       <c r="D472" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="F472" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="G472" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J472" s="14" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="K472" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
@@ -23615,19 +23615,19 @@
         <v>1104</v>
       </c>
       <c r="D473" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="F473" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="G473" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J473" s="14" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
       <c r="K473" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
@@ -23641,19 +23641,19 @@
         <v>1104</v>
       </c>
       <c r="D474" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="F474" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="G474" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J474" s="14" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
       <c r="K474" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
@@ -23667,344 +23667,344 @@
         <v>1104</v>
       </c>
       <c r="D475" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="F475" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="G475" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>2810</v>
+        <v>2808</v>
       </c>
       <c r="K475" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
       <c r="B476" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
       <c r="C476" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D476" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="F476" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="G476" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="K476" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>2643</v>
+        <v>2820</v>
       </c>
       <c r="B477" t="s">
-        <v>2644</v>
+        <v>2821</v>
       </c>
       <c r="C477" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D477" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="F477" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="G477" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J477" s="14" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="K477" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="B478" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="C478" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D478" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="F478" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="G478" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="J478" s="14" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
       <c r="K478" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="B479" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="C479" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D479" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="F479" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="G479" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K479" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="B480" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C480" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D480" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="F480" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="G480" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K480" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="B481" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C481" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D481" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="F481" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="G481" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K481" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="B482" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="C482" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D482" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="F482" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="G482" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K482" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="B483" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="C483" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D483" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="F483" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="G483" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K483" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="B484" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="C484" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D484" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="F484" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="G484" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K484" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="B485" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C485" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D485" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="F485" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="G485" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K485" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="B486" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C486" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D486" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="F486" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="G486" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K486" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="B487" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C487" s="29" t="s">
         <v>1104</v>
       </c>
       <c r="D487" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="F487" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="G487" s="29" t="s">
         <v>2594</v>
       </c>
       <c r="K487" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="B488" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="C488" t="s">
         <v>1104</v>
       </c>
       <c r="D488" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="G488" t="s">
         <v>2135</v>
       </c>
       <c r="J488" s="14" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="489" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="30" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B489" s="30" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C489" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D489" s="30" t="s">
         <v>2783</v>
-      </c>
-      <c r="B489" s="30" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C489" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="D489" s="30" t="s">
-        <v>2785</v>
       </c>
       <c r="G489" s="30" t="s">
         <v>2592</v>
       </c>
       <c r="J489" s="14" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
     </row>
   </sheetData>
